--- a/price_list.xlsx
+++ b/price_list.xlsx
@@ -8985,7 +8985,7 @@
         <v>871</v>
       </c>
       <c r="C406" s="0" t="s">
-        <v>376</v>
+        <v>140</v>
       </c>
       <c r="D406" s="0">
         <v>857.67</v>
@@ -9268,7 +9268,7 @@
         <v>45</v>
       </c>
       <c r="D426" s="0">
-        <v>4399.56</v>
+        <v>4708</v>
       </c>
     </row>
     <row r="427">

--- a/price_list.xlsx
+++ b/price_list.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1087" uniqueCount="1087">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1089" uniqueCount="1089">
   <si>
     <t>Solo Activos</t>
   </si>
@@ -2859,6 +2859,12 @@
   </si>
   <si>
     <t>SUPER-O 100 MG X 100 COMP - 000024653</t>
+  </si>
+  <si>
+    <t>000024713</t>
+  </si>
+  <si>
+    <t>SUPER-O 100mg Comp. Rec. x 20 - 000024713</t>
   </si>
   <si>
     <t>000009961</t>
@@ -3338,7 +3344,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A2:D508"/>
+  <dimension ref="A2:D509"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
@@ -9517,10 +9523,10 @@
         <v>950</v>
       </c>
       <c r="C444" s="0" t="s">
-        <v>92</v>
+        <v>140</v>
       </c>
       <c r="D444" s="0">
-        <v>266200</v>
+        <v>3340</v>
       </c>
     </row>
     <row r="445">
@@ -9534,7 +9540,7 @@
         <v>92</v>
       </c>
       <c r="D445" s="0">
-        <v>194991.5</v>
+        <v>266200</v>
       </c>
     </row>
     <row r="446">
@@ -9548,7 +9554,7 @@
         <v>92</v>
       </c>
       <c r="D446" s="0">
-        <v>289492.5</v>
+        <v>194991.5</v>
       </c>
     </row>
     <row r="447">
@@ -9559,24 +9565,24 @@
         <v>956</v>
       </c>
       <c r="C447" s="0" t="s">
-        <v>957</v>
+        <v>92</v>
       </c>
       <c r="D447" s="0">
-        <v>13722.52</v>
+        <v>289492.5</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" s="0" t="s">
+        <v>957</v>
+      </c>
+      <c r="B448" s="0" t="s">
         <v>958</v>
       </c>
-      <c r="B448" s="0" t="s">
+      <c r="C448" s="0" t="s">
         <v>959</v>
       </c>
-      <c r="C448" s="0" t="s">
-        <v>957</v>
-      </c>
       <c r="D448" s="0">
-        <v>15072</v>
+        <v>13722.52</v>
       </c>
     </row>
     <row r="449">
@@ -9587,10 +9593,10 @@
         <v>961</v>
       </c>
       <c r="C449" s="0" t="s">
-        <v>957</v>
+        <v>959</v>
       </c>
       <c r="D449" s="0">
-        <v>6555.64</v>
+        <v>15072</v>
       </c>
     </row>
     <row r="450">
@@ -9601,10 +9607,10 @@
         <v>963</v>
       </c>
       <c r="C450" s="0" t="s">
-        <v>957</v>
+        <v>959</v>
       </c>
       <c r="D450" s="0">
-        <v>8964.61</v>
+        <v>6555.64</v>
       </c>
     </row>
     <row r="451">
@@ -9615,10 +9621,10 @@
         <v>965</v>
       </c>
       <c r="C451" s="0" t="s">
-        <v>957</v>
+        <v>959</v>
       </c>
       <c r="D451" s="0">
-        <v>11735</v>
+        <v>8964.61</v>
       </c>
     </row>
     <row r="452">
@@ -9629,10 +9635,10 @@
         <v>967</v>
       </c>
       <c r="C452" s="0" t="s">
-        <v>70</v>
+        <v>959</v>
       </c>
       <c r="D452" s="0">
-        <v>4276</v>
+        <v>11735</v>
       </c>
     </row>
     <row r="453">
@@ -9643,10 +9649,10 @@
         <v>969</v>
       </c>
       <c r="C453" s="0" t="s">
-        <v>140</v>
+        <v>70</v>
       </c>
       <c r="D453" s="0">
-        <v>3930</v>
+        <v>4276</v>
       </c>
     </row>
     <row r="454">
@@ -9657,10 +9663,10 @@
         <v>971</v>
       </c>
       <c r="C454" s="0" t="s">
-        <v>92</v>
+        <v>140</v>
       </c>
       <c r="D454" s="0">
-        <v>4392.3</v>
+        <v>3930</v>
       </c>
     </row>
     <row r="455">
@@ -9671,24 +9677,24 @@
         <v>973</v>
       </c>
       <c r="C455" s="0" t="s">
-        <v>974</v>
+        <v>92</v>
       </c>
       <c r="D455" s="0">
-        <v>5254.41</v>
+        <v>4392.3</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" s="0" t="s">
+        <v>974</v>
+      </c>
+      <c r="B456" s="0" t="s">
         <v>975</v>
       </c>
-      <c r="B456" s="0" t="s">
+      <c r="C456" s="0" t="s">
         <v>976</v>
       </c>
-      <c r="C456" s="0" t="s">
-        <v>52</v>
-      </c>
       <c r="D456" s="0">
-        <v>1200</v>
+        <v>5254.41</v>
       </c>
     </row>
     <row r="457">
@@ -9702,7 +9708,7 @@
         <v>52</v>
       </c>
       <c r="D457" s="0">
-        <v>278</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="458">
@@ -9716,7 +9722,7 @@
         <v>52</v>
       </c>
       <c r="D458" s="0">
-        <v>562</v>
+        <v>278</v>
       </c>
     </row>
     <row r="459">
@@ -9727,10 +9733,10 @@
         <v>982</v>
       </c>
       <c r="C459" s="0" t="s">
-        <v>376</v>
+        <v>52</v>
       </c>
       <c r="D459" s="0">
-        <v>65142.6</v>
+        <v>562</v>
       </c>
     </row>
     <row r="460">
@@ -9744,7 +9750,7 @@
         <v>376</v>
       </c>
       <c r="D460" s="0">
-        <v>23482.7</v>
+        <v>65142.6</v>
       </c>
     </row>
     <row r="461">
@@ -9755,10 +9761,10 @@
         <v>986</v>
       </c>
       <c r="C461" s="0" t="s">
-        <v>28</v>
+        <v>376</v>
       </c>
       <c r="D461" s="0">
-        <v>6029.59</v>
+        <v>23482.7</v>
       </c>
     </row>
     <row r="462">
@@ -9769,10 +9775,10 @@
         <v>988</v>
       </c>
       <c r="C462" s="0" t="s">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="D462" s="0">
-        <v>12000</v>
+        <v>6029.59</v>
       </c>
     </row>
     <row r="463">
@@ -9786,7 +9792,7 @@
         <v>52</v>
       </c>
       <c r="D463" s="0">
-        <v>17425</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="464">
@@ -9797,66 +9803,66 @@
         <v>992</v>
       </c>
       <c r="C464" s="0" t="s">
-        <v>993</v>
+        <v>52</v>
       </c>
       <c r="D464" s="0">
-        <v>1958</v>
+        <v>17425</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" s="0" t="s">
+        <v>993</v>
+      </c>
+      <c r="B465" s="0" t="s">
         <v>994</v>
       </c>
-      <c r="B465" s="0" t="s">
+      <c r="C465" s="0" t="s">
         <v>995</v>
       </c>
-      <c r="C465" s="0" t="s">
-        <v>996</v>
-      </c>
       <c r="D465" s="0">
-        <v>2282.3</v>
+        <v>1958</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" s="0" t="s">
+        <v>996</v>
+      </c>
+      <c r="B466" s="0" t="s">
         <v>997</v>
       </c>
-      <c r="B466" s="0" t="s">
+      <c r="C466" s="0" t="s">
         <v>998</v>
       </c>
-      <c r="C466" s="0" t="s">
-        <v>999</v>
-      </c>
       <c r="D466" s="0">
-        <v>386</v>
+        <v>2282.3</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" s="0" t="s">
+        <v>999</v>
+      </c>
+      <c r="B467" s="0" t="s">
         <v>1000</v>
       </c>
-      <c r="B467" s="0" t="s">
+      <c r="C467" s="0" t="s">
         <v>1001</v>
       </c>
-      <c r="C467" s="0" t="s">
-        <v>1002</v>
-      </c>
       <c r="D467" s="0">
-        <v>385.4</v>
+        <v>386</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" s="0" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B468" s="0" t="s">
         <v>1003</v>
       </c>
-      <c r="B468" s="0" t="s">
+      <c r="C468" s="0" t="s">
         <v>1004</v>
       </c>
-      <c r="C468" s="0" t="s">
-        <v>92</v>
-      </c>
       <c r="D468" s="0">
-        <v>296147.5</v>
+        <v>385.4</v>
       </c>
     </row>
     <row r="469">
@@ -9867,10 +9873,10 @@
         <v>1006</v>
       </c>
       <c r="C469" s="0" t="s">
-        <v>123</v>
+        <v>92</v>
       </c>
       <c r="D469" s="0">
-        <v>1890</v>
+        <v>296147.5</v>
       </c>
     </row>
     <row r="470">
@@ -9881,10 +9887,10 @@
         <v>1008</v>
       </c>
       <c r="C470" s="0" t="s">
-        <v>580</v>
+        <v>123</v>
       </c>
       <c r="D470" s="0">
-        <v>71176.4</v>
+        <v>1890</v>
       </c>
     </row>
     <row r="471">
@@ -9895,10 +9901,10 @@
         <v>1010</v>
       </c>
       <c r="C471" s="0" t="s">
-        <v>140</v>
+        <v>580</v>
       </c>
       <c r="D471" s="0">
-        <v>87</v>
+        <v>71176.4</v>
       </c>
     </row>
     <row r="472">
@@ -9909,10 +9915,10 @@
         <v>1012</v>
       </c>
       <c r="C472" s="0" t="s">
-        <v>70</v>
+        <v>140</v>
       </c>
       <c r="D472" s="0">
-        <v>950</v>
+        <v>87</v>
       </c>
     </row>
     <row r="473">
@@ -9923,10 +9929,10 @@
         <v>1014</v>
       </c>
       <c r="C473" s="0" t="s">
-        <v>469</v>
+        <v>70</v>
       </c>
       <c r="D473" s="0">
-        <v>342641</v>
+        <v>950</v>
       </c>
     </row>
     <row r="474">
@@ -9937,10 +9943,10 @@
         <v>1016</v>
       </c>
       <c r="C474" s="0" t="s">
-        <v>160</v>
+        <v>469</v>
       </c>
       <c r="D474" s="0">
-        <v>2200</v>
+        <v>342641</v>
       </c>
     </row>
     <row r="475">
@@ -9951,10 +9957,10 @@
         <v>1018</v>
       </c>
       <c r="C475" s="0" t="s">
-        <v>478</v>
+        <v>160</v>
       </c>
       <c r="D475" s="0">
-        <v>41000</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="476">
@@ -9965,10 +9971,10 @@
         <v>1020</v>
       </c>
       <c r="C476" s="0" t="s">
-        <v>70</v>
+        <v>478</v>
       </c>
       <c r="D476" s="0">
-        <v>5790</v>
+        <v>41000</v>
       </c>
     </row>
     <row r="477">
@@ -9979,10 +9985,10 @@
         <v>1022</v>
       </c>
       <c r="C477" s="0" t="s">
-        <v>919</v>
+        <v>70</v>
       </c>
       <c r="D477" s="0">
-        <v>880</v>
+        <v>5790</v>
       </c>
     </row>
     <row r="478">
@@ -10021,10 +10027,10 @@
         <v>1028</v>
       </c>
       <c r="C480" s="0" t="s">
-        <v>21</v>
+        <v>919</v>
       </c>
       <c r="D480" s="0">
-        <v>563.36</v>
+        <v>880</v>
       </c>
     </row>
     <row r="481">
@@ -10035,10 +10041,10 @@
         <v>1030</v>
       </c>
       <c r="C481" s="0" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D481" s="0">
-        <v>3520</v>
+        <v>563.36</v>
       </c>
     </row>
     <row r="482">
@@ -10052,7 +10058,7 @@
         <v>15</v>
       </c>
       <c r="D482" s="0">
-        <v>2600</v>
+        <v>3520</v>
       </c>
     </row>
     <row r="483">
@@ -10063,10 +10069,10 @@
         <v>1034</v>
       </c>
       <c r="C483" s="0" t="s">
-        <v>281</v>
+        <v>15</v>
       </c>
       <c r="D483" s="0">
-        <v>3700</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="484">
@@ -10080,7 +10086,7 @@
         <v>281</v>
       </c>
       <c r="D484" s="0">
-        <v>2600</v>
+        <v>3700</v>
       </c>
     </row>
     <row r="485">
@@ -10091,10 +10097,10 @@
         <v>1038</v>
       </c>
       <c r="C485" s="0" t="s">
-        <v>15</v>
+        <v>281</v>
       </c>
       <c r="D485" s="0">
-        <v>2235</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="486">
@@ -10108,7 +10114,7 @@
         <v>15</v>
       </c>
       <c r="D486" s="0">
-        <v>3850</v>
+        <v>2235</v>
       </c>
     </row>
     <row r="487">
@@ -10119,24 +10125,24 @@
         <v>1042</v>
       </c>
       <c r="C487" s="0" t="s">
-        <v>1043</v>
+        <v>15</v>
       </c>
       <c r="D487" s="0">
-        <v>1</v>
+        <v>3850</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" s="0" t="s">
+        <v>1043</v>
+      </c>
+      <c r="B488" s="0" t="s">
         <v>1044</v>
       </c>
-      <c r="B488" s="0" t="s">
+      <c r="C488" s="0" t="s">
         <v>1045</v>
       </c>
-      <c r="C488" s="0" t="s">
-        <v>28</v>
-      </c>
       <c r="D488" s="0">
-        <v>14819</v>
+        <v>1</v>
       </c>
     </row>
     <row r="489">
@@ -10147,10 +10153,10 @@
         <v>1047</v>
       </c>
       <c r="C489" s="0" t="s">
-        <v>376</v>
+        <v>28</v>
       </c>
       <c r="D489" s="0">
-        <v>3859.93</v>
+        <v>14819</v>
       </c>
     </row>
     <row r="490">
@@ -10164,7 +10170,7 @@
         <v>376</v>
       </c>
       <c r="D490" s="0">
-        <v>11751.49</v>
+        <v>3859.93</v>
       </c>
     </row>
     <row r="491">
@@ -10175,10 +10181,10 @@
         <v>1051</v>
       </c>
       <c r="C491" s="0" t="s">
-        <v>338</v>
+        <v>376</v>
       </c>
       <c r="D491" s="0">
-        <v>6000</v>
+        <v>11751.49</v>
       </c>
     </row>
     <row r="492">
@@ -10192,7 +10198,7 @@
         <v>338</v>
       </c>
       <c r="D492" s="0">
-        <v>3000</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="493">
@@ -10203,10 +10209,10 @@
         <v>1055</v>
       </c>
       <c r="C493" s="0" t="s">
-        <v>37</v>
+        <v>338</v>
       </c>
       <c r="D493" s="0">
-        <v>618</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="494">
@@ -10217,24 +10223,24 @@
         <v>1057</v>
       </c>
       <c r="C494" s="0" t="s">
-        <v>1058</v>
+        <v>37</v>
       </c>
       <c r="D494" s="0">
-        <v>24600</v>
+        <v>618</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" s="0" t="s">
+        <v>1058</v>
+      </c>
+      <c r="B495" s="0" t="s">
         <v>1059</v>
       </c>
-      <c r="B495" s="0" t="s">
+      <c r="C495" s="0" t="s">
         <v>1060</v>
       </c>
-      <c r="C495" s="0" t="s">
-        <v>105</v>
-      </c>
       <c r="D495" s="0">
-        <v>0</v>
+        <v>24600</v>
       </c>
     </row>
     <row r="496">
@@ -10245,10 +10251,10 @@
         <v>1062</v>
       </c>
       <c r="C496" s="0" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="D496" s="0">
-        <v>43590.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="497">
@@ -10259,10 +10265,10 @@
         <v>1064</v>
       </c>
       <c r="C497" s="0" t="s">
-        <v>469</v>
+        <v>92</v>
       </c>
       <c r="D497" s="0">
-        <v>207558.07</v>
+        <v>43590.25</v>
       </c>
     </row>
     <row r="498">
@@ -10273,10 +10279,10 @@
         <v>1066</v>
       </c>
       <c r="C498" s="0" t="s">
-        <v>376</v>
+        <v>469</v>
       </c>
       <c r="D498" s="0">
-        <v>77429.29</v>
+        <v>207558.07</v>
       </c>
     </row>
     <row r="499">
@@ -10290,7 +10296,7 @@
         <v>376</v>
       </c>
       <c r="D499" s="0">
-        <v>42913.42</v>
+        <v>77429.29</v>
       </c>
     </row>
     <row r="500">
@@ -10304,7 +10310,7 @@
         <v>376</v>
       </c>
       <c r="D500" s="0">
-        <v>88806.25</v>
+        <v>42913.42</v>
       </c>
     </row>
     <row r="501">
@@ -10318,7 +10324,7 @@
         <v>376</v>
       </c>
       <c r="D501" s="0">
-        <v>50781.52</v>
+        <v>88806.25</v>
       </c>
     </row>
     <row r="502">
@@ -10329,10 +10335,10 @@
         <v>1074</v>
       </c>
       <c r="C502" s="0" t="s">
-        <v>21</v>
+        <v>376</v>
       </c>
       <c r="D502" s="0">
-        <v>1600</v>
+        <v>50781.52</v>
       </c>
     </row>
     <row r="503">
@@ -10343,10 +10349,10 @@
         <v>1076</v>
       </c>
       <c r="C503" s="0" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D503" s="0">
-        <v>3455.8</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="504">
@@ -10360,7 +10366,7 @@
         <v>28</v>
       </c>
       <c r="D504" s="0">
-        <v>3987</v>
+        <v>3455.8</v>
       </c>
     </row>
     <row r="505">
@@ -10374,7 +10380,7 @@
         <v>28</v>
       </c>
       <c r="D505" s="0">
-        <v>4010.17</v>
+        <v>3987</v>
       </c>
     </row>
     <row r="506">
@@ -10388,7 +10394,7 @@
         <v>28</v>
       </c>
       <c r="D506" s="0">
-        <v>3382.65</v>
+        <v>4010.17</v>
       </c>
     </row>
     <row r="507">
@@ -10399,10 +10405,10 @@
         <v>1084</v>
       </c>
       <c r="C507" s="0" t="s">
-        <v>160</v>
+        <v>28</v>
       </c>
       <c r="D507" s="0">
-        <v>430</v>
+        <v>3382.65</v>
       </c>
     </row>
     <row r="508">
@@ -10413,9 +10419,23 @@
         <v>1086</v>
       </c>
       <c r="C508" s="0" t="s">
+        <v>160</v>
+      </c>
+      <c r="D508" s="0">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="0" t="s">
+        <v>1087</v>
+      </c>
+      <c r="B509" s="0" t="s">
+        <v>1088</v>
+      </c>
+      <c r="C509" s="0" t="s">
         <v>140</v>
       </c>
-      <c r="D508" s="0">
+      <c r="D509" s="0">
         <v>465</v>
       </c>
     </row>

--- a/price_list.xlsx
+++ b/price_list.xlsx
@@ -3492,7 +3492,7 @@
         <v>28</v>
       </c>
       <c r="D13" s="0">
-        <v>134.59</v>
+        <v>139.48</v>
       </c>
     </row>
     <row r="14">
@@ -3674,7 +3674,7 @@
         <v>28</v>
       </c>
       <c r="D26" s="0">
-        <v>160.14</v>
+        <v>162.86</v>
       </c>
     </row>
     <row r="27">
@@ -4304,7 +4304,7 @@
         <v>52</v>
       </c>
       <c r="D71" s="0">
-        <v>1075</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="72">
@@ -4472,7 +4472,7 @@
         <v>52</v>
       </c>
       <c r="D83" s="0">
-        <v>330</v>
+        <v>362</v>
       </c>
     </row>
     <row r="84">
@@ -5102,7 +5102,7 @@
         <v>28</v>
       </c>
       <c r="D128" s="0">
-        <v>7118.9</v>
+        <v>7377.5</v>
       </c>
     </row>
     <row r="129">
@@ -5312,7 +5312,7 @@
         <v>52</v>
       </c>
       <c r="D143" s="0">
-        <v>1800</v>
+        <v>1785</v>
       </c>
     </row>
     <row r="144">
@@ -5326,7 +5326,7 @@
         <v>52</v>
       </c>
       <c r="D144" s="0">
-        <v>2060</v>
+        <v>2058</v>
       </c>
     </row>
     <row r="145">
@@ -5508,7 +5508,7 @@
         <v>28</v>
       </c>
       <c r="D157" s="0">
-        <v>103000</v>
+        <v>106950.8</v>
       </c>
     </row>
     <row r="158">
@@ -5522,7 +5522,7 @@
         <v>28</v>
       </c>
       <c r="D158" s="0">
-        <v>114000</v>
+        <v>118372.7</v>
       </c>
     </row>
     <row r="159">
@@ -5536,7 +5536,7 @@
         <v>28</v>
       </c>
       <c r="D159" s="0">
-        <v>135000</v>
+        <v>140178.2</v>
       </c>
     </row>
     <row r="160">
@@ -5718,7 +5718,7 @@
         <v>28</v>
       </c>
       <c r="D172" s="0">
-        <v>954.8</v>
+        <v>972.9</v>
       </c>
     </row>
     <row r="173">
@@ -5746,7 +5746,7 @@
         <v>28</v>
       </c>
       <c r="D174" s="0">
-        <v>2743.71</v>
+        <v>2908.78</v>
       </c>
     </row>
     <row r="175">
@@ -5760,7 +5760,7 @@
         <v>392</v>
       </c>
       <c r="D175" s="0">
-        <v>81</v>
+        <v>61</v>
       </c>
     </row>
     <row r="176">
@@ -5970,7 +5970,7 @@
         <v>28</v>
       </c>
       <c r="D190" s="0">
-        <v>9041.55</v>
+        <v>9748.5</v>
       </c>
     </row>
     <row r="191">
@@ -6558,7 +6558,7 @@
         <v>52</v>
       </c>
       <c r="D232" s="0">
-        <v>500</v>
+        <v>597</v>
       </c>
     </row>
     <row r="233">
@@ -6572,7 +6572,7 @@
         <v>52</v>
       </c>
       <c r="D233" s="0">
-        <v>210</v>
+        <v>223</v>
       </c>
     </row>
     <row r="234">
@@ -6712,7 +6712,7 @@
         <v>28</v>
       </c>
       <c r="D243" s="0">
-        <v>13636.84</v>
+        <v>14608.16</v>
       </c>
     </row>
     <row r="244">
@@ -7496,7 +7496,7 @@
         <v>28</v>
       </c>
       <c r="D299" s="0">
-        <v>7372.42</v>
+        <v>7655.2</v>
       </c>
     </row>
     <row r="300">
@@ -8392,7 +8392,7 @@
         <v>140</v>
       </c>
       <c r="D363" s="0">
-        <v>1229</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="364">
@@ -8406,7 +8406,7 @@
         <v>140</v>
       </c>
       <c r="D364" s="0">
-        <v>4500</v>
+        <v>4712</v>
       </c>
     </row>
     <row r="365">
@@ -8434,7 +8434,7 @@
         <v>28</v>
       </c>
       <c r="D366" s="0">
-        <v>1945.1</v>
+        <v>1986</v>
       </c>
     </row>
     <row r="367">
@@ -8938,7 +8938,7 @@
         <v>52</v>
       </c>
       <c r="D402" s="0">
-        <v>158</v>
+        <v>153</v>
       </c>
     </row>
     <row r="403">
@@ -8952,7 +8952,7 @@
         <v>28</v>
       </c>
       <c r="D403" s="0">
-        <v>714.74</v>
+        <v>740.7</v>
       </c>
     </row>
     <row r="404">
@@ -9316,7 +9316,7 @@
         <v>919</v>
       </c>
       <c r="D429" s="0">
-        <v>580</v>
+        <v>626</v>
       </c>
     </row>
     <row r="430">
@@ -9330,7 +9330,7 @@
         <v>919</v>
       </c>
       <c r="D430" s="0">
-        <v>580</v>
+        <v>626</v>
       </c>
     </row>
     <row r="431">
@@ -9344,7 +9344,7 @@
         <v>919</v>
       </c>
       <c r="D431" s="0">
-        <v>580</v>
+        <v>626</v>
       </c>
     </row>
     <row r="432">
@@ -9708,7 +9708,7 @@
         <v>52</v>
       </c>
       <c r="D457" s="0">
-        <v>1200</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="458">
@@ -9722,7 +9722,7 @@
         <v>52</v>
       </c>
       <c r="D458" s="0">
-        <v>278</v>
+        <v>298</v>
       </c>
     </row>
     <row r="459">
@@ -9736,7 +9736,7 @@
         <v>52</v>
       </c>
       <c r="D459" s="0">
-        <v>562</v>
+        <v>596</v>
       </c>
     </row>
     <row r="460">
@@ -10156,7 +10156,7 @@
         <v>28</v>
       </c>
       <c r="D489" s="0">
-        <v>14819</v>
+        <v>15189</v>
       </c>
     </row>
     <row r="490">
@@ -10366,7 +10366,7 @@
         <v>28</v>
       </c>
       <c r="D504" s="0">
-        <v>3455.8</v>
+        <v>3521.4</v>
       </c>
     </row>
     <row r="505">
@@ -10394,7 +10394,7 @@
         <v>28</v>
       </c>
       <c r="D506" s="0">
-        <v>4010.17</v>
+        <v>4086.37</v>
       </c>
     </row>
     <row r="507">

--- a/price_list.xlsx
+++ b/price_list.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1089" uniqueCount="1089">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1092" uniqueCount="1092">
   <si>
     <t>Solo Activos</t>
   </si>
@@ -1806,6 +1806,15 @@
   </si>
   <si>
     <t>JERINGA 1 ML EUROMIX - 000024331</t>
+  </si>
+  <si>
+    <t>DJE00515</t>
+  </si>
+  <si>
+    <t>JERINGA 1 ML X 1 - SM - DJE00515</t>
+  </si>
+  <si>
+    <t>SM</t>
   </si>
   <si>
     <t>000024702</t>
@@ -3344,7 +3353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A2:D509"/>
+  <dimension ref="A2:D510"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
@@ -7146,7 +7155,7 @@
         <v>600</v>
       </c>
       <c r="D274" s="0">
-        <v>65</v>
+        <v>34.98</v>
       </c>
     </row>
     <row r="275">
@@ -7157,7 +7166,7 @@
         <v>602</v>
       </c>
       <c r="C275" s="0" t="s">
-        <v>52</v>
+        <v>603</v>
       </c>
       <c r="D275" s="0">
         <v>65</v>
@@ -7165,97 +7174,97 @@
     </row>
     <row r="276">
       <c r="A276" s="0" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B276" s="0" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C276" s="0" t="s">
         <v>52</v>
       </c>
       <c r="D276" s="0">
-        <v>92</v>
+        <v>65</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="0" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B277" s="0" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C277" s="0" t="s">
         <v>52</v>
       </c>
       <c r="D277" s="0">
-        <v>33</v>
+        <v>92</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="0" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B278" s="0" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C278" s="0" t="s">
         <v>52</v>
       </c>
       <c r="D278" s="0">
-        <v>54.8</v>
+        <v>33</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="0" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B279" s="0" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C279" s="0" t="s">
-        <v>338</v>
+        <v>52</v>
       </c>
       <c r="D279" s="0">
-        <v>300</v>
+        <v>54.8</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="0" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B280" s="0" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C280" s="0" t="s">
         <v>338</v>
       </c>
       <c r="D280" s="0">
-        <v>370</v>
+        <v>300</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="0" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B281" s="0" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="C281" s="0" t="s">
-        <v>359</v>
+        <v>338</v>
       </c>
       <c r="D281" s="0">
-        <v>450</v>
+        <v>370</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="0" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B282" s="0" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C282" s="0" t="s">
-        <v>37</v>
+        <v>359</v>
       </c>
       <c r="D282" s="0">
         <v>450</v>
@@ -7263,13 +7272,13 @@
     </row>
     <row r="283">
       <c r="A283" s="0" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B283" s="0" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C283" s="0" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="D283" s="0">
         <v>450</v>
@@ -7277,296 +7286,296 @@
     </row>
     <row r="284">
       <c r="A284" s="0" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B284" s="0" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C284" s="0" t="s">
         <v>15</v>
       </c>
       <c r="D284" s="0">
-        <v>1650</v>
+        <v>450</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="0" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B285" s="0" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="C285" s="0" t="s">
         <v>15</v>
       </c>
       <c r="D285" s="0">
-        <v>2100</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="0" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B286" s="0" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C286" s="0" t="s">
         <v>15</v>
       </c>
       <c r="D286" s="0">
-        <v>1980</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="0" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B287" s="0" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C287" s="0" t="s">
         <v>15</v>
       </c>
       <c r="D287" s="0">
-        <v>2160</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="0" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B288" s="0" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="C288" s="0" t="s">
         <v>15</v>
       </c>
       <c r="D288" s="0">
-        <v>1500</v>
+        <v>2160</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="0" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B289" s="0" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C289" s="0" t="s">
         <v>15</v>
       </c>
       <c r="D289" s="0">
-        <v>2600</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="0" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B290" s="0" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="C290" s="0" t="s">
         <v>15</v>
       </c>
       <c r="D290" s="0">
-        <v>2000</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="0" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B291" s="0" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C291" s="0" t="s">
         <v>15</v>
       </c>
       <c r="D291" s="0">
-        <v>6700</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="0" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B292" s="0" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="C292" s="0" t="s">
         <v>15</v>
       </c>
       <c r="D292" s="0">
-        <v>1650</v>
+        <v>6700</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="0" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="B293" s="0" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="C293" s="0" t="s">
         <v>15</v>
       </c>
       <c r="D293" s="0">
-        <v>1035</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="0" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B294" s="0" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C294" s="0" t="s">
         <v>15</v>
       </c>
       <c r="D294" s="0">
-        <v>2600</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="0" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B295" s="0" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C295" s="0" t="s">
         <v>15</v>
       </c>
       <c r="D295" s="0">
-        <v>2400</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="0" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B296" s="0" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="C296" s="0" t="s">
-        <v>140</v>
+        <v>15</v>
       </c>
       <c r="D296" s="0">
-        <v>4590</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="0" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B297" s="0" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="C297" s="0" t="s">
         <v>140</v>
       </c>
       <c r="D297" s="0">
-        <v>2300</v>
+        <v>4590</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="0" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="B298" s="0" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="C298" s="0" t="s">
         <v>140</v>
       </c>
       <c r="D298" s="0">
-        <v>1150</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="0" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B299" s="0" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C299" s="0" t="s">
-        <v>28</v>
+        <v>140</v>
       </c>
       <c r="D299" s="0">
-        <v>7655.2</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="0" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B300" s="0" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C300" s="0" t="s">
-        <v>123</v>
+        <v>28</v>
       </c>
       <c r="D300" s="0">
-        <v>1790</v>
+        <v>7655.2</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="0" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B301" s="0" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C301" s="0" t="s">
         <v>123</v>
       </c>
       <c r="D301" s="0">
-        <v>3016.53</v>
+        <v>1790</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="0" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B302" s="0" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="C302" s="0" t="s">
         <v>123</v>
       </c>
       <c r="D302" s="0">
-        <v>4800</v>
+        <v>3016.53</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="0" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="B303" s="0" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="C303" s="0" t="s">
         <v>123</v>
       </c>
       <c r="D303" s="0">
-        <v>4450</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="0" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="B304" s="0" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="C304" s="0" t="s">
-        <v>661</v>
+        <v>123</v>
       </c>
       <c r="D304" s="0">
-        <v>0</v>
+        <v>4450</v>
       </c>
     </row>
     <row r="305">
@@ -7577,130 +7586,130 @@
         <v>663</v>
       </c>
       <c r="C305" s="0" t="s">
-        <v>28</v>
+        <v>664</v>
       </c>
       <c r="D305" s="0">
-        <v>494</v>
+        <v>0</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="0" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="B306" s="0" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="C306" s="0" t="s">
         <v>28</v>
       </c>
       <c r="D306" s="0">
-        <v>665.3</v>
+        <v>494</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="0" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="B307" s="0" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="C307" s="0" t="s">
-        <v>92</v>
+        <v>28</v>
       </c>
       <c r="D307" s="0">
-        <v>33940.5</v>
+        <v>665.3</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="0" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="B308" s="0" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C308" s="0" t="s">
         <v>92</v>
       </c>
       <c r="D308" s="0">
-        <v>4525.4</v>
+        <v>33940.5</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="0" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="B309" s="0" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="C309" s="0" t="s">
-        <v>151</v>
+        <v>92</v>
       </c>
       <c r="D309" s="0">
-        <v>896</v>
+        <v>4525.4</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="0" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="B310" s="0" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C310" s="0" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="D310" s="0">
-        <v>1250</v>
+        <v>896</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="0" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B311" s="0" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="C311" s="0" t="s">
-        <v>92</v>
+        <v>140</v>
       </c>
       <c r="D311" s="0">
-        <v>332750</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="0" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B312" s="0" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="C312" s="0" t="s">
-        <v>202</v>
+        <v>92</v>
       </c>
       <c r="D312" s="0">
-        <v>17440</v>
+        <v>332750</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="0" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B313" s="0" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="C313" s="0" t="s">
         <v>202</v>
       </c>
       <c r="D313" s="0">
-        <v>4390</v>
+        <v>17440</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="0" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B314" s="0" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="C314" s="0" t="s">
         <v>202</v>
@@ -7711,128 +7720,128 @@
     </row>
     <row r="315">
       <c r="A315" s="0" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="B315" s="0" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="C315" s="0" t="s">
-        <v>281</v>
+        <v>202</v>
       </c>
       <c r="D315" s="0">
-        <v>2250</v>
+        <v>4390</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="0" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="B316" s="0" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="C316" s="0" t="s">
-        <v>202</v>
+        <v>281</v>
       </c>
       <c r="D316" s="0">
-        <v>3355</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="0" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="B317" s="0" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="C317" s="0" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="D317" s="0">
-        <v>7500</v>
+        <v>3355</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="0" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B318" s="0" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="C318" s="0" t="s">
-        <v>92</v>
+        <v>207</v>
       </c>
       <c r="D318" s="0">
-        <v>25289</v>
+        <v>7500</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="0" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="B319" s="0" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C319" s="0" t="s">
         <v>92</v>
       </c>
       <c r="D319" s="0">
-        <v>252890</v>
+        <v>25289</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="0" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="B320" s="0" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="C320" s="0" t="s">
-        <v>52</v>
+        <v>92</v>
       </c>
       <c r="D320" s="0">
-        <v>160</v>
+        <v>252890</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="0" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="B321" s="0" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="C321" s="0" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="D321" s="0">
-        <v>285.6</v>
+        <v>160</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="0" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="B322" s="0" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="C322" s="0" t="s">
         <v>21</v>
       </c>
       <c r="D322" s="0">
-        <v>338</v>
+        <v>285.6</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="0" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="B323" s="0" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="C323" s="0" t="s">
-        <v>700</v>
+        <v>21</v>
       </c>
       <c r="D323" s="0">
-        <v>770</v>
+        <v>338</v>
       </c>
     </row>
     <row r="324">
@@ -7857,245 +7866,245 @@
         <v>705</v>
       </c>
       <c r="C325" s="0" t="s">
-        <v>15</v>
+        <v>706</v>
       </c>
       <c r="D325" s="0">
-        <v>973.5</v>
+        <v>770</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="0" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B326" s="0" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="C326" s="0" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="D326" s="0">
-        <v>507.08</v>
+        <v>973.5</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="0" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="B327" s="0" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="C327" s="0" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D327" s="0">
-        <v>450</v>
+        <v>507.08</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="0" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="B328" s="0" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="C328" s="0" t="s">
-        <v>151</v>
+        <v>15</v>
       </c>
       <c r="D328" s="0">
-        <v>760</v>
+        <v>450</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="0" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="B329" s="0" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="C329" s="0" t="s">
-        <v>281</v>
+        <v>151</v>
       </c>
       <c r="D329" s="0">
-        <v>5900</v>
+        <v>760</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="0" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="B330" s="0" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="C330" s="0" t="s">
         <v>281</v>
       </c>
       <c r="D330" s="0">
-        <v>2900</v>
+        <v>5900</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="0" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="B331" s="0" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="C331" s="0" t="s">
-        <v>140</v>
+        <v>281</v>
       </c>
       <c r="D331" s="0">
-        <v>890</v>
+        <v>2900</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="0" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B332" s="0" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="C332" s="0" t="s">
         <v>140</v>
       </c>
       <c r="D332" s="0">
-        <v>594</v>
+        <v>890</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="0" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="B333" s="0" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="C333" s="0" t="s">
         <v>140</v>
       </c>
       <c r="D333" s="0">
-        <v>65</v>
+        <v>594</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="0" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="B334" s="0" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="C334" s="0" t="s">
-        <v>92</v>
+        <v>140</v>
       </c>
       <c r="D334" s="0">
-        <v>11313.5</v>
+        <v>65</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="0" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="B335" s="0" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="C335" s="0" t="s">
-        <v>34</v>
+        <v>92</v>
       </c>
       <c r="D335" s="0">
-        <v>420</v>
+        <v>11313.5</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" s="0" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B336" s="0" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="C336" s="0" t="s">
-        <v>359</v>
+        <v>34</v>
       </c>
       <c r="D336" s="0">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" s="0" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B337" s="0" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C337" s="0" t="s">
-        <v>21</v>
+        <v>359</v>
       </c>
       <c r="D337" s="0">
-        <v>377</v>
+        <v>418</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" s="0" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="B338" s="0" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="C338" s="0" t="s">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="D338" s="0">
-        <v>5780.66</v>
+        <v>377</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" s="0" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="B339" s="0" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C339" s="0" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="D339" s="0">
-        <v>898</v>
+        <v>5780.66</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" s="0" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="B340" s="0" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="C340" s="0" t="s">
-        <v>123</v>
+        <v>70</v>
       </c>
       <c r="D340" s="0">
-        <v>4767</v>
+        <v>898</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" s="0" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="B341" s="0" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="C341" s="0" t="s">
-        <v>34</v>
+        <v>123</v>
       </c>
       <c r="D341" s="0">
-        <v>650</v>
+        <v>4767</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" s="0" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="B342" s="0" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="C342" s="0" t="s">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="D342" s="0">
         <v>650</v>
@@ -8103,44 +8112,44 @@
     </row>
     <row r="343">
       <c r="A343" s="0" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="B343" s="0" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="C343" s="0" t="s">
-        <v>15</v>
+        <v>70</v>
       </c>
       <c r="D343" s="0">
-        <v>2178</v>
+        <v>650</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" s="0" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="B344" s="0" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C344" s="0" t="s">
-        <v>92</v>
+        <v>15</v>
       </c>
       <c r="D344" s="0">
-        <v>7986</v>
+        <v>2178</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" s="0" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="B345" s="0" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="C345" s="0" t="s">
-        <v>746</v>
+        <v>92</v>
       </c>
       <c r="D345" s="0">
-        <v>1910</v>
+        <v>7986</v>
       </c>
     </row>
     <row r="346">
@@ -8151,326 +8160,326 @@
         <v>748</v>
       </c>
       <c r="C346" s="0" t="s">
-        <v>151</v>
+        <v>749</v>
       </c>
       <c r="D346" s="0">
-        <v>900</v>
+        <v>1910</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" s="0" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="B347" s="0" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="C347" s="0" t="s">
-        <v>21</v>
+        <v>151</v>
       </c>
       <c r="D347" s="0">
-        <v>1722</v>
+        <v>900</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" s="0" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="B348" s="0" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="C348" s="0" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="D348" s="0">
-        <v>59000</v>
+        <v>1722</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" s="0" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="B349" s="0" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="C349" s="0" t="s">
-        <v>151</v>
+        <v>34</v>
       </c>
       <c r="D349" s="0">
-        <v>750</v>
+        <v>59000</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" s="0" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="B350" s="0" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="C350" s="0" t="s">
         <v>151</v>
       </c>
       <c r="D350" s="0">
-        <v>1212</v>
+        <v>750</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" s="0" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="B351" s="0" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="C351" s="0" t="s">
         <v>151</v>
       </c>
       <c r="D351" s="0">
-        <v>1300</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" s="0" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="B352" s="0" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="C352" s="0" t="s">
         <v>151</v>
       </c>
       <c r="D352" s="0">
-        <v>1500</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" s="0" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="B353" s="0" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="C353" s="0" t="s">
         <v>151</v>
       </c>
       <c r="D353" s="0">
-        <v>1400</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" s="0" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="B354" s="0" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="C354" s="0" t="s">
-        <v>261</v>
+        <v>151</v>
       </c>
       <c r="D354" s="0">
-        <v>11959</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" s="0" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="B355" s="0" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C355" s="0" t="s">
-        <v>140</v>
+        <v>261</v>
       </c>
       <c r="D355" s="0">
-        <v>350</v>
+        <v>11959</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" s="0" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="B356" s="0" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="C356" s="0" t="s">
-        <v>281</v>
+        <v>140</v>
       </c>
       <c r="D356" s="0">
-        <v>1450</v>
+        <v>350</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" s="0" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="B357" s="0" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="C357" s="0" t="s">
-        <v>92</v>
+        <v>281</v>
       </c>
       <c r="D357" s="0">
-        <v>7320.5</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" s="0" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="B358" s="0" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="C358" s="0" t="s">
-        <v>15</v>
+        <v>92</v>
       </c>
       <c r="D358" s="0">
-        <v>900</v>
+        <v>7320.5</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" s="0" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="B359" s="0" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="C359" s="0" t="s">
-        <v>281</v>
+        <v>15</v>
       </c>
       <c r="D359" s="0">
-        <v>566</v>
+        <v>900</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" s="0" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="B360" s="0" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="C360" s="0" t="s">
-        <v>469</v>
+        <v>281</v>
       </c>
       <c r="D360" s="0">
-        <v>64925</v>
+        <v>566</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" s="0" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="B361" s="0" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="C361" s="0" t="s">
-        <v>15</v>
+        <v>469</v>
       </c>
       <c r="D361" s="0">
-        <v>1100</v>
+        <v>64925</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" s="0" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="B362" s="0" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="C362" s="0" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="D362" s="0">
-        <v>1623</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" s="0" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="B363" s="0" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="C363" s="0" t="s">
-        <v>140</v>
+        <v>21</v>
       </c>
       <c r="D363" s="0">
-        <v>1269</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" s="0" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="B364" s="0" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="C364" s="0" t="s">
         <v>140</v>
       </c>
       <c r="D364" s="0">
-        <v>4712</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" s="0" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="B365" s="0" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="C365" s="0" t="s">
-        <v>28</v>
+        <v>140</v>
       </c>
       <c r="D365" s="0">
-        <v>1250</v>
+        <v>4712</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" s="0" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="B366" s="0" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="C366" s="0" t="s">
         <v>28</v>
       </c>
       <c r="D366" s="0">
-        <v>1986</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" s="0" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="B367" s="0" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="C367" s="0" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="D367" s="0">
-        <v>450</v>
+        <v>1986</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" s="0" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="B368" s="0" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="C368" s="0" t="s">
         <v>15</v>
       </c>
       <c r="D368" s="0">
-        <v>825</v>
+        <v>450</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" s="0" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="B369" s="0" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="C369" s="0" t="s">
         <v>15</v>
@@ -8481,83 +8490,83 @@
     </row>
     <row r="370">
       <c r="A370" s="0" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="B370" s="0" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="C370" s="0" t="s">
-        <v>379</v>
+        <v>15</v>
       </c>
       <c r="D370" s="0">
-        <v>134775.6</v>
+        <v>825</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" s="0" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="B371" s="0" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="C371" s="0" t="s">
         <v>379</v>
       </c>
       <c r="D371" s="0">
-        <v>175991.55</v>
+        <v>134775.6</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" s="0" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="B372" s="0" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="C372" s="0" t="s">
-        <v>70</v>
+        <v>379</v>
       </c>
       <c r="D372" s="0">
-        <v>3427</v>
+        <v>175991.55</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" s="0" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="B373" s="0" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="C373" s="0" t="s">
         <v>70</v>
       </c>
       <c r="D373" s="0">
-        <v>10618</v>
+        <v>3427</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" s="0" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="B374" s="0" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="C374" s="0" t="s">
-        <v>281</v>
+        <v>70</v>
       </c>
       <c r="D374" s="0">
-        <v>515</v>
+        <v>10618</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" s="0" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="B375" s="0" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="C375" s="0" t="s">
-        <v>37</v>
+        <v>281</v>
       </c>
       <c r="D375" s="0">
         <v>515</v>
@@ -8565,86 +8574,86 @@
     </row>
     <row r="376">
       <c r="A376" s="0" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="B376" s="0" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="C376" s="0" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="D376" s="0">
-        <v>10000</v>
+        <v>515</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" s="0" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="B377" s="0" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="C377" s="0" t="s">
-        <v>469</v>
+        <v>52</v>
       </c>
       <c r="D377" s="0">
-        <v>207558.08</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" s="0" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="B378" s="0" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="C378" s="0" t="s">
         <v>469</v>
       </c>
       <c r="D378" s="0">
-        <v>249069.69</v>
+        <v>207558.08</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" s="0" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="B379" s="0" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="C379" s="0" t="s">
-        <v>70</v>
+        <v>469</v>
       </c>
       <c r="D379" s="0">
-        <v>10522</v>
+        <v>249069.69</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" s="0" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="B380" s="0" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="C380" s="0" t="s">
         <v>70</v>
       </c>
       <c r="D380" s="0">
-        <v>19481</v>
+        <v>10522</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" s="0" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="B381" s="0" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="C381" s="0" t="s">
-        <v>819</v>
+        <v>70</v>
       </c>
       <c r="D381" s="0">
-        <v>1080</v>
+        <v>19481</v>
       </c>
     </row>
     <row r="382">
@@ -8655,24 +8664,24 @@
         <v>821</v>
       </c>
       <c r="C382" s="0" t="s">
-        <v>18</v>
+        <v>822</v>
       </c>
       <c r="D382" s="0">
-        <v>586.49</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" s="0" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="B383" s="0" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="C383" s="0" t="s">
-        <v>824</v>
+        <v>18</v>
       </c>
       <c r="D383" s="0">
-        <v>520</v>
+        <v>586.49</v>
       </c>
     </row>
     <row r="384">
@@ -8683,108 +8692,108 @@
         <v>826</v>
       </c>
       <c r="C384" s="0" t="s">
-        <v>824</v>
+        <v>827</v>
       </c>
       <c r="D384" s="0">
-        <v>300</v>
+        <v>520</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" s="0" t="s">
+        <v>828</v>
+      </c>
+      <c r="B385" s="0" t="s">
+        <v>829</v>
+      </c>
+      <c r="C385" s="0" t="s">
         <v>827</v>
       </c>
-      <c r="B385" s="0" t="s">
-        <v>828</v>
-      </c>
-      <c r="C385" s="0" t="s">
-        <v>15</v>
-      </c>
       <c r="D385" s="0">
-        <v>2200</v>
+        <v>300</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" s="0" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="B386" s="0" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="C386" s="0" t="s">
         <v>15</v>
       </c>
       <c r="D386" s="0">
-        <v>2800</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" s="0" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="B387" s="0" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="C387" s="0" t="s">
-        <v>92</v>
+        <v>15</v>
       </c>
       <c r="D387" s="0">
-        <v>5190.9</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" s="0" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="B388" s="0" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="C388" s="0" t="s">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="D388" s="0">
-        <v>2969</v>
+        <v>5190.9</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" s="0" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="B389" s="0" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="C389" s="0" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="D389" s="0">
-        <v>3800</v>
+        <v>2969</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" s="0" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="B390" s="0" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="C390" s="0" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="D390" s="0">
-        <v>4000</v>
+        <v>3800</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" s="0" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="B391" s="0" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="C391" s="0" t="s">
-        <v>841</v>
+        <v>15</v>
       </c>
       <c r="D391" s="0">
-        <v>3800</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="392">
@@ -8795,318 +8804,318 @@
         <v>843</v>
       </c>
       <c r="C392" s="0" t="s">
-        <v>21</v>
+        <v>844</v>
       </c>
       <c r="D392" s="0">
-        <v>353</v>
+        <v>3800</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" s="0" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="B393" s="0" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="C393" s="0" t="s">
-        <v>110</v>
+        <v>21</v>
       </c>
       <c r="D393" s="0">
-        <v>1800</v>
+        <v>353</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" s="0" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="B394" s="0" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="C394" s="0" t="s">
-        <v>15</v>
+        <v>110</v>
       </c>
       <c r="D394" s="0">
-        <v>2948</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" s="0" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="B395" s="0" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="C395" s="0" t="s">
-        <v>92</v>
+        <v>15</v>
       </c>
       <c r="D395" s="0">
-        <v>146.41</v>
+        <v>2948</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" s="0" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="B396" s="0" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="C396" s="0" t="s">
-        <v>207</v>
+        <v>92</v>
       </c>
       <c r="D396" s="0">
-        <v>65537</v>
+        <v>146.41</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" s="0" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="B397" s="0" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="C397" s="0" t="s">
-        <v>140</v>
+        <v>207</v>
       </c>
       <c r="D397" s="0">
-        <v>4130.4</v>
+        <v>65537</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" s="0" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="B398" s="0" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="C398" s="0" t="s">
         <v>140</v>
       </c>
       <c r="D398" s="0">
-        <v>4283</v>
+        <v>4130.4</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" s="0" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="B399" s="0" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="C399" s="0" t="s">
         <v>140</v>
       </c>
       <c r="D399" s="0">
-        <v>6524.8</v>
+        <v>4283</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" s="0" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="B400" s="0" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="C400" s="0" t="s">
-        <v>308</v>
+        <v>140</v>
       </c>
       <c r="D400" s="0">
-        <v>570</v>
+        <v>6524.8</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" s="0" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="B401" s="0" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="C401" s="0" t="s">
-        <v>70</v>
+        <v>308</v>
       </c>
       <c r="D401" s="0">
-        <v>550</v>
+        <v>570</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" s="0" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="B402" s="0" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="C402" s="0" t="s">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="D402" s="0">
-        <v>153</v>
+        <v>550</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" s="0" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="B403" s="0" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="C403" s="0" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="D403" s="0">
-        <v>740.7</v>
+        <v>153</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" s="0" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="B404" s="0" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="C404" s="0" t="s">
-        <v>59</v>
+        <v>28</v>
       </c>
       <c r="D404" s="0">
-        <v>101000</v>
+        <v>740.7</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" s="0" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="B405" s="0" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="C405" s="0" t="s">
-        <v>123</v>
+        <v>59</v>
       </c>
       <c r="D405" s="0">
-        <v>6251</v>
+        <v>101000</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" s="0" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="B406" s="0" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="C406" s="0" t="s">
-        <v>140</v>
+        <v>123</v>
       </c>
       <c r="D406" s="0">
-        <v>857.67</v>
+        <v>6251</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" s="0" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B407" s="0" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="C407" s="0" t="s">
-        <v>92</v>
+        <v>140</v>
       </c>
       <c r="D407" s="0">
-        <v>1164.66</v>
+        <v>857.67</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" s="0" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="B408" s="0" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="C408" s="0" t="s">
-        <v>151</v>
+        <v>92</v>
       </c>
       <c r="D408" s="0">
-        <v>360</v>
+        <v>1164.66</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" s="0" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="B409" s="0" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="C409" s="0" t="s">
         <v>151</v>
       </c>
       <c r="D409" s="0">
-        <v>450</v>
+        <v>360</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" s="0" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="B410" s="0" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="C410" s="0" t="s">
         <v>151</v>
       </c>
       <c r="D410" s="0">
-        <v>2150</v>
+        <v>450</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" s="0" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="B411" s="0" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="C411" s="0" t="s">
-        <v>580</v>
+        <v>151</v>
       </c>
       <c r="D411" s="0">
-        <v>25192.82</v>
+        <v>2150</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" s="0" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="B412" s="0" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="C412" s="0" t="s">
-        <v>70</v>
+        <v>580</v>
       </c>
       <c r="D412" s="0">
-        <v>3500</v>
+        <v>25192.82</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" s="0" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="B413" s="0" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="C413" s="0" t="s">
-        <v>175</v>
+        <v>70</v>
       </c>
       <c r="D413" s="0">
-        <v>600</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" s="0" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="B414" s="0" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="C414" s="0" t="s">
-        <v>888</v>
+        <v>175</v>
       </c>
       <c r="D414" s="0">
-        <v>1080</v>
+        <v>600</v>
       </c>
     </row>
     <row r="415">
@@ -9117,189 +9126,189 @@
         <v>890</v>
       </c>
       <c r="C415" s="0" t="s">
-        <v>338</v>
+        <v>891</v>
       </c>
       <c r="D415" s="0">
-        <v>8628</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" s="0" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="B416" s="0" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="C416" s="0" t="s">
-        <v>40</v>
+        <v>338</v>
       </c>
       <c r="D416" s="0">
-        <v>27991.54</v>
+        <v>8628</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" s="0" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="B417" s="0" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="C417" s="0" t="s">
-        <v>140</v>
+        <v>40</v>
       </c>
       <c r="D417" s="0">
-        <v>1020</v>
+        <v>27991.54</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" s="0" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="B418" s="0" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="C418" s="0" t="s">
         <v>140</v>
       </c>
       <c r="D418" s="0">
-        <v>4106</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" s="0" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="B419" s="0" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="C419" s="0" t="s">
-        <v>281</v>
+        <v>140</v>
       </c>
       <c r="D419" s="0">
-        <v>450</v>
+        <v>4106</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" s="0" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="B420" s="0" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="C420" s="0" t="s">
-        <v>45</v>
+        <v>281</v>
       </c>
       <c r="D420" s="0">
-        <v>6344.43</v>
+        <v>450</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" s="0" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="B421" s="0" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="C421" s="0" t="s">
         <v>45</v>
       </c>
       <c r="D421" s="0">
-        <v>2862.28</v>
+        <v>6344.43</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" s="0" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="B422" s="0" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="C422" s="0" t="s">
         <v>45</v>
       </c>
       <c r="D422" s="0">
-        <v>2131.18</v>
+        <v>2862.28</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" s="0" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="B423" s="0" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="C423" s="0" t="s">
         <v>45</v>
       </c>
       <c r="D423" s="0">
-        <v>29795.68</v>
+        <v>2131.18</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" s="0" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="B424" s="0" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="C424" s="0" t="s">
         <v>45</v>
       </c>
       <c r="D424" s="0">
-        <v>2307.09</v>
+        <v>29795.68</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" s="0" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="B425" s="0" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="C425" s="0" t="s">
         <v>45</v>
       </c>
       <c r="D425" s="0">
-        <v>5249.48</v>
+        <v>2307.09</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" s="0" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="B426" s="0" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="C426" s="0" t="s">
         <v>45</v>
       </c>
       <c r="D426" s="0">
-        <v>4708</v>
+        <v>5249.48</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" s="0" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="B427" s="0" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="C427" s="0" t="s">
-        <v>478</v>
+        <v>45</v>
       </c>
       <c r="D427" s="0">
-        <v>510</v>
+        <v>4708</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" s="0" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="B428" s="0" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="C428" s="0" t="s">
-        <v>37</v>
+        <v>478</v>
       </c>
       <c r="D428" s="0">
         <v>510</v>
@@ -9307,16 +9316,16 @@
     </row>
     <row r="429">
       <c r="A429" s="0" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="B429" s="0" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="C429" s="0" t="s">
-        <v>919</v>
+        <v>37</v>
       </c>
       <c r="D429" s="0">
-        <v>626</v>
+        <v>510</v>
       </c>
     </row>
     <row r="430">
@@ -9327,7 +9336,7 @@
         <v>921</v>
       </c>
       <c r="C430" s="0" t="s">
-        <v>919</v>
+        <v>922</v>
       </c>
       <c r="D430" s="0">
         <v>626</v>
@@ -9335,13 +9344,13 @@
     </row>
     <row r="431">
       <c r="A431" s="0" t="s">
+        <v>923</v>
+      </c>
+      <c r="B431" s="0" t="s">
+        <v>924</v>
+      </c>
+      <c r="C431" s="0" t="s">
         <v>922</v>
-      </c>
-      <c r="B431" s="0" t="s">
-        <v>923</v>
-      </c>
-      <c r="C431" s="0" t="s">
-        <v>919</v>
       </c>
       <c r="D431" s="0">
         <v>626</v>
@@ -9349,27 +9358,27 @@
     </row>
     <row r="432">
       <c r="A432" s="0" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="B432" s="0" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="C432" s="0" t="s">
-        <v>919</v>
+        <v>922</v>
       </c>
       <c r="D432" s="0">
-        <v>342</v>
+        <v>626</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" s="0" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="B433" s="0" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="C433" s="0" t="s">
-        <v>919</v>
+        <v>922</v>
       </c>
       <c r="D433" s="0">
         <v>342</v>
@@ -9377,13 +9386,13 @@
     </row>
     <row r="434">
       <c r="A434" s="0" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="B434" s="0" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="C434" s="0" t="s">
-        <v>919</v>
+        <v>922</v>
       </c>
       <c r="D434" s="0">
         <v>342</v>
@@ -9391,27 +9400,27 @@
     </row>
     <row r="435">
       <c r="A435" s="0" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="B435" s="0" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="C435" s="0" t="s">
-        <v>919</v>
+        <v>922</v>
       </c>
       <c r="D435" s="0">
-        <v>0</v>
+        <v>342</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" s="0" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="B436" s="0" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="C436" s="0" t="s">
-        <v>919</v>
+        <v>922</v>
       </c>
       <c r="D436" s="0">
         <v>0</v>
@@ -9419,16 +9428,16 @@
     </row>
     <row r="437">
       <c r="A437" s="0" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="B437" s="0" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="C437" s="0" t="s">
-        <v>936</v>
+        <v>922</v>
       </c>
       <c r="D437" s="0">
-        <v>453</v>
+        <v>0</v>
       </c>
     </row>
     <row r="438">
@@ -9439,7 +9448,7 @@
         <v>938</v>
       </c>
       <c r="C438" s="0" t="s">
-        <v>919</v>
+        <v>939</v>
       </c>
       <c r="D438" s="0">
         <v>453</v>
@@ -9447,41 +9456,41 @@
     </row>
     <row r="439">
       <c r="A439" s="0" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="B439" s="0" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="C439" s="0" t="s">
-        <v>70</v>
+        <v>922</v>
       </c>
       <c r="D439" s="0">
-        <v>19322</v>
+        <v>453</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" s="0" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B440" s="0" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="C440" s="0" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="D440" s="0">
-        <v>430</v>
+        <v>19322</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" s="0" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="B441" s="0" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="C441" s="0" t="s">
-        <v>281</v>
+        <v>34</v>
       </c>
       <c r="D441" s="0">
         <v>430</v>
@@ -9489,100 +9498,100 @@
     </row>
     <row r="442">
       <c r="A442" s="0" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B442" s="0" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="C442" s="0" t="s">
-        <v>115</v>
+        <v>281</v>
       </c>
       <c r="D442" s="0">
-        <v>14000</v>
+        <v>430</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" s="0" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="B443" s="0" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="C443" s="0" t="s">
-        <v>140</v>
+        <v>115</v>
       </c>
       <c r="D443" s="0">
-        <v>15400</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" s="0" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="B444" s="0" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="C444" s="0" t="s">
         <v>140</v>
       </c>
       <c r="D444" s="0">
-        <v>3340</v>
+        <v>15400</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" s="0" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="B445" s="0" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="C445" s="0" t="s">
-        <v>92</v>
+        <v>140</v>
       </c>
       <c r="D445" s="0">
-        <v>266200</v>
+        <v>3340</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" s="0" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="B446" s="0" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="C446" s="0" t="s">
         <v>92</v>
       </c>
       <c r="D446" s="0">
-        <v>194991.5</v>
+        <v>266200</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" s="0" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="B447" s="0" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="C447" s="0" t="s">
         <v>92</v>
       </c>
       <c r="D447" s="0">
-        <v>289492.5</v>
+        <v>194991.5</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" s="0" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="B448" s="0" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="C448" s="0" t="s">
-        <v>959</v>
+        <v>92</v>
       </c>
       <c r="D448" s="0">
-        <v>13722.52</v>
+        <v>289492.5</v>
       </c>
     </row>
     <row r="449">
@@ -9593,108 +9602,108 @@
         <v>961</v>
       </c>
       <c r="C449" s="0" t="s">
-        <v>959</v>
+        <v>962</v>
       </c>
       <c r="D449" s="0">
-        <v>15072</v>
+        <v>13722.52</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" s="0" t="s">
+        <v>963</v>
+      </c>
+      <c r="B450" s="0" t="s">
+        <v>964</v>
+      </c>
+      <c r="C450" s="0" t="s">
         <v>962</v>
       </c>
-      <c r="B450" s="0" t="s">
-        <v>963</v>
-      </c>
-      <c r="C450" s="0" t="s">
-        <v>959</v>
-      </c>
       <c r="D450" s="0">
-        <v>6555.64</v>
+        <v>15072</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" s="0" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="B451" s="0" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="C451" s="0" t="s">
-        <v>959</v>
+        <v>962</v>
       </c>
       <c r="D451" s="0">
-        <v>8964.61</v>
+        <v>6555.64</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" s="0" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="B452" s="0" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="C452" s="0" t="s">
-        <v>959</v>
+        <v>962</v>
       </c>
       <c r="D452" s="0">
-        <v>11735</v>
+        <v>8964.61</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" s="0" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="B453" s="0" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="C453" s="0" t="s">
-        <v>70</v>
+        <v>962</v>
       </c>
       <c r="D453" s="0">
-        <v>4276</v>
+        <v>11735</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" s="0" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="B454" s="0" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="C454" s="0" t="s">
-        <v>140</v>
+        <v>70</v>
       </c>
       <c r="D454" s="0">
-        <v>3930</v>
+        <v>4276</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" s="0" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="B455" s="0" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="C455" s="0" t="s">
-        <v>92</v>
+        <v>140</v>
       </c>
       <c r="D455" s="0">
-        <v>4392.3</v>
+        <v>3930</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" s="0" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="B456" s="0" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="C456" s="0" t="s">
-        <v>976</v>
+        <v>92</v>
       </c>
       <c r="D456" s="0">
-        <v>5254.41</v>
+        <v>4392.3</v>
       </c>
     </row>
     <row r="457">
@@ -9705,122 +9714,122 @@
         <v>978</v>
       </c>
       <c r="C457" s="0" t="s">
-        <v>52</v>
+        <v>979</v>
       </c>
       <c r="D457" s="0">
-        <v>1297</v>
+        <v>5254.41</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" s="0" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="B458" s="0" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="C458" s="0" t="s">
         <v>52</v>
       </c>
       <c r="D458" s="0">
-        <v>298</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" s="0" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="B459" s="0" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="C459" s="0" t="s">
         <v>52</v>
       </c>
       <c r="D459" s="0">
-        <v>596</v>
+        <v>298</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" s="0" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="B460" s="0" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="C460" s="0" t="s">
-        <v>376</v>
+        <v>52</v>
       </c>
       <c r="D460" s="0">
-        <v>65142.6</v>
+        <v>596</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" s="0" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="B461" s="0" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="C461" s="0" t="s">
         <v>376</v>
       </c>
       <c r="D461" s="0">
-        <v>23482.7</v>
+        <v>65142.6</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" s="0" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="B462" s="0" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="C462" s="0" t="s">
-        <v>28</v>
+        <v>376</v>
       </c>
       <c r="D462" s="0">
-        <v>6029.59</v>
+        <v>23482.7</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" s="0" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="B463" s="0" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="C463" s="0" t="s">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="D463" s="0">
-        <v>12000</v>
+        <v>6029.59</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" s="0" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="B464" s="0" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="C464" s="0" t="s">
         <v>52</v>
       </c>
       <c r="D464" s="0">
-        <v>17425</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" s="0" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="B465" s="0" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="C465" s="0" t="s">
-        <v>995</v>
+        <v>52</v>
       </c>
       <c r="D465" s="0">
-        <v>1958</v>
+        <v>17425</v>
       </c>
     </row>
     <row r="466">
@@ -9834,7 +9843,7 @@
         <v>998</v>
       </c>
       <c r="D466" s="0">
-        <v>2282.3</v>
+        <v>1958</v>
       </c>
     </row>
     <row r="467">
@@ -9848,7 +9857,7 @@
         <v>1001</v>
       </c>
       <c r="D467" s="0">
-        <v>386</v>
+        <v>2282.3</v>
       </c>
     </row>
     <row r="468">
@@ -9862,7 +9871,7 @@
         <v>1004</v>
       </c>
       <c r="D468" s="0">
-        <v>385.4</v>
+        <v>386</v>
       </c>
     </row>
     <row r="469">
@@ -9873,147 +9882,147 @@
         <v>1006</v>
       </c>
       <c r="C469" s="0" t="s">
-        <v>92</v>
+        <v>1007</v>
       </c>
       <c r="D469" s="0">
-        <v>296147.5</v>
+        <v>385.4</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" s="0" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="B470" s="0" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="C470" s="0" t="s">
-        <v>123</v>
+        <v>92</v>
       </c>
       <c r="D470" s="0">
-        <v>1890</v>
+        <v>296147.5</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" s="0" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="B471" s="0" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="C471" s="0" t="s">
-        <v>580</v>
+        <v>123</v>
       </c>
       <c r="D471" s="0">
-        <v>71176.4</v>
+        <v>1890</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" s="0" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="B472" s="0" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="C472" s="0" t="s">
-        <v>140</v>
+        <v>580</v>
       </c>
       <c r="D472" s="0">
-        <v>87</v>
+        <v>71176.4</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" s="0" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="B473" s="0" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="C473" s="0" t="s">
-        <v>70</v>
+        <v>140</v>
       </c>
       <c r="D473" s="0">
-        <v>950</v>
+        <v>87</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" s="0" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="B474" s="0" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="C474" s="0" t="s">
-        <v>469</v>
+        <v>70</v>
       </c>
       <c r="D474" s="0">
-        <v>342641</v>
+        <v>950</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" s="0" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="B475" s="0" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="C475" s="0" t="s">
-        <v>160</v>
+        <v>469</v>
       </c>
       <c r="D475" s="0">
-        <v>2200</v>
+        <v>342641</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" s="0" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="B476" s="0" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="C476" s="0" t="s">
-        <v>478</v>
+        <v>160</v>
       </c>
       <c r="D476" s="0">
-        <v>41000</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" s="0" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="B477" s="0" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="C477" s="0" t="s">
-        <v>70</v>
+        <v>478</v>
       </c>
       <c r="D477" s="0">
-        <v>5790</v>
+        <v>41000</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" s="0" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="B478" s="0" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="C478" s="0" t="s">
-        <v>919</v>
+        <v>70</v>
       </c>
       <c r="D478" s="0">
-        <v>880</v>
+        <v>5790</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" s="0" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="B479" s="0" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="C479" s="0" t="s">
-        <v>919</v>
+        <v>922</v>
       </c>
       <c r="D479" s="0">
         <v>880</v>
@@ -10021,13 +10030,13 @@
     </row>
     <row r="480">
       <c r="A480" s="0" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="B480" s="0" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="C480" s="0" t="s">
-        <v>919</v>
+        <v>922</v>
       </c>
       <c r="D480" s="0">
         <v>880</v>
@@ -10035,114 +10044,114 @@
     </row>
     <row r="481">
       <c r="A481" s="0" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="B481" s="0" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="C481" s="0" t="s">
-        <v>21</v>
+        <v>922</v>
       </c>
       <c r="D481" s="0">
-        <v>563.36</v>
+        <v>880</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" s="0" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="B482" s="0" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="C482" s="0" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D482" s="0">
-        <v>3520</v>
+        <v>563.36</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" s="0" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="B483" s="0" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="C483" s="0" t="s">
         <v>15</v>
       </c>
       <c r="D483" s="0">
-        <v>2600</v>
+        <v>3520</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" s="0" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="B484" s="0" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="C484" s="0" t="s">
-        <v>281</v>
+        <v>15</v>
       </c>
       <c r="D484" s="0">
-        <v>3700</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" s="0" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="B485" s="0" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="C485" s="0" t="s">
         <v>281</v>
       </c>
       <c r="D485" s="0">
-        <v>2600</v>
+        <v>3700</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" s="0" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="B486" s="0" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="C486" s="0" t="s">
-        <v>15</v>
+        <v>281</v>
       </c>
       <c r="D486" s="0">
-        <v>2235</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" s="0" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="B487" s="0" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="C487" s="0" t="s">
         <v>15</v>
       </c>
       <c r="D487" s="0">
-        <v>3850</v>
+        <v>2235</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" s="0" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="B488" s="0" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="C488" s="0" t="s">
-        <v>1045</v>
+        <v>15</v>
       </c>
       <c r="D488" s="0">
-        <v>1</v>
+        <v>3850</v>
       </c>
     </row>
     <row r="489">
@@ -10153,94 +10162,94 @@
         <v>1047</v>
       </c>
       <c r="C489" s="0" t="s">
-        <v>28</v>
+        <v>1048</v>
       </c>
       <c r="D489" s="0">
-        <v>15189</v>
+        <v>1</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" s="0" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="B490" s="0" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="C490" s="0" t="s">
-        <v>376</v>
+        <v>28</v>
       </c>
       <c r="D490" s="0">
-        <v>3859.93</v>
+        <v>15189</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" s="0" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="B491" s="0" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="C491" s="0" t="s">
         <v>376</v>
       </c>
       <c r="D491" s="0">
-        <v>11751.49</v>
+        <v>3859.93</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" s="0" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="B492" s="0" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="C492" s="0" t="s">
-        <v>338</v>
+        <v>376</v>
       </c>
       <c r="D492" s="0">
-        <v>6000</v>
+        <v>11751.49</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" s="0" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="B493" s="0" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="C493" s="0" t="s">
         <v>338</v>
       </c>
       <c r="D493" s="0">
-        <v>3000</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" s="0" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="B494" s="0" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="C494" s="0" t="s">
-        <v>37</v>
+        <v>338</v>
       </c>
       <c r="D494" s="0">
-        <v>618</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" s="0" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="B495" s="0" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="C495" s="0" t="s">
-        <v>1060</v>
+        <v>37</v>
       </c>
       <c r="D495" s="0">
-        <v>24600</v>
+        <v>618</v>
       </c>
     </row>
     <row r="496">
@@ -10251,191 +10260,205 @@
         <v>1062</v>
       </c>
       <c r="C496" s="0" t="s">
-        <v>105</v>
+        <v>1063</v>
       </c>
       <c r="D496" s="0">
-        <v>0</v>
+        <v>24600</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" s="0" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="B497" s="0" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="C497" s="0" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="D497" s="0">
-        <v>43590.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" s="0" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="B498" s="0" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="C498" s="0" t="s">
-        <v>469</v>
+        <v>92</v>
       </c>
       <c r="D498" s="0">
-        <v>207558.07</v>
+        <v>43590.25</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" s="0" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="B499" s="0" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="C499" s="0" t="s">
-        <v>376</v>
+        <v>469</v>
       </c>
       <c r="D499" s="0">
-        <v>77429.29</v>
+        <v>207558.07</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" s="0" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="B500" s="0" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="C500" s="0" t="s">
         <v>376</v>
       </c>
       <c r="D500" s="0">
-        <v>42913.42</v>
+        <v>77429.29</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" s="0" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="B501" s="0" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="C501" s="0" t="s">
         <v>376</v>
       </c>
       <c r="D501" s="0">
-        <v>88806.25</v>
+        <v>42913.42</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" s="0" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="B502" s="0" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="C502" s="0" t="s">
         <v>376</v>
       </c>
       <c r="D502" s="0">
-        <v>50781.52</v>
+        <v>88806.25</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" s="0" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="B503" s="0" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="C503" s="0" t="s">
-        <v>21</v>
+        <v>376</v>
       </c>
       <c r="D503" s="0">
-        <v>1600</v>
+        <v>50781.52</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" s="0" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="B504" s="0" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="C504" s="0" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D504" s="0">
-        <v>3521.4</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" s="0" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="B505" s="0" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="C505" s="0" t="s">
         <v>28</v>
       </c>
       <c r="D505" s="0">
-        <v>3987</v>
+        <v>3521.4</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" s="0" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="B506" s="0" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="C506" s="0" t="s">
         <v>28</v>
       </c>
       <c r="D506" s="0">
-        <v>4086.37</v>
+        <v>3987</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" s="0" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="B507" s="0" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="C507" s="0" t="s">
         <v>28</v>
       </c>
       <c r="D507" s="0">
-        <v>3382.65</v>
+        <v>4086.37</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" s="0" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="B508" s="0" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="C508" s="0" t="s">
-        <v>160</v>
+        <v>28</v>
       </c>
       <c r="D508" s="0">
-        <v>430</v>
+        <v>3382.65</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" s="0" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="B509" s="0" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="C509" s="0" t="s">
+        <v>160</v>
+      </c>
+      <c r="D509" s="0">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" s="0" t="s">
+        <v>1090</v>
+      </c>
+      <c r="B510" s="0" t="s">
+        <v>1091</v>
+      </c>
+      <c r="C510" s="0" t="s">
         <v>140</v>
       </c>
-      <c r="D509" s="0">
+      <c r="D510" s="0">
         <v>465</v>
       </c>
     </row>

--- a/price_list.xlsx
+++ b/price_list.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1092" uniqueCount="1092">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1094" uniqueCount="1094">
   <si>
     <t>Solo Activos</t>
   </si>
@@ -629,6 +629,15 @@
     <t>BUPICAINA HIPERBARICA 0.5% Amp. x 1 x 4ml - 000008614</t>
   </si>
   <si>
+    <t>990100346</t>
+  </si>
+  <si>
+    <t>BUPIVACAINA 0.50% GOBBI S/E FA - 990100346</t>
+  </si>
+  <si>
+    <t>GOBBI-NOVAG</t>
+  </si>
+  <si>
     <t>000010052</t>
   </si>
   <si>
@@ -1446,9 +1455,6 @@
   </si>
   <si>
     <t xml:space="preserve">GOBBICAINA SIN EPINEFRINA 1% AMP. DE VIDRIO X  5ML - 000022255</t>
-  </si>
-  <si>
-    <t>GOBBI-NOVAG</t>
   </si>
   <si>
     <t>000016343</t>
@@ -3353,7 +3359,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A2:D510"/>
+  <dimension ref="A2:D511"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
@@ -4173,7 +4179,7 @@
         <v>18</v>
       </c>
       <c r="D61" s="0">
-        <v>436.1</v>
+        <v>330</v>
       </c>
     </row>
     <row r="62">
@@ -4369,7 +4375,7 @@
         <v>175</v>
       </c>
       <c r="D75" s="0">
-        <v>600</v>
+        <v>675</v>
       </c>
     </row>
     <row r="76">
@@ -4565,7 +4571,7 @@
         <v>207</v>
       </c>
       <c r="D89" s="0">
-        <v>3000</v>
+        <v>2595</v>
       </c>
     </row>
     <row r="90">
@@ -4576,7 +4582,7 @@
         <v>209</v>
       </c>
       <c r="C90" s="0" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D90" s="0">
         <v>3000</v>
@@ -4584,94 +4590,94 @@
     </row>
     <row r="91">
       <c r="A91" s="0" t="s">
+        <v>211</v>
+      </c>
+      <c r="B91" s="0" t="s">
+        <v>212</v>
+      </c>
+      <c r="C91" s="0" t="s">
         <v>210</v>
       </c>
-      <c r="B91" s="0" t="s">
-        <v>211</v>
-      </c>
-      <c r="C91" s="0" t="s">
-        <v>110</v>
-      </c>
       <c r="D91" s="0">
-        <v>1770</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="0" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B92" s="0" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C92" s="0" t="s">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="D92" s="0">
-        <v>900</v>
+        <v>1770</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="0" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B93" s="0" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C93" s="0" t="s">
-        <v>140</v>
+        <v>70</v>
       </c>
       <c r="D93" s="0">
-        <v>720.72</v>
+        <v>900</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="0" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B94" s="0" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C94" s="0" t="s">
         <v>140</v>
       </c>
       <c r="D94" s="0">
-        <v>613.76</v>
+        <v>720.72</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="0" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B95" s="0" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C95" s="0" t="s">
-        <v>52</v>
+        <v>140</v>
       </c>
       <c r="D95" s="0">
-        <v>190</v>
+        <v>613.76</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="0" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B96" s="0" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C96" s="0" t="s">
         <v>52</v>
       </c>
       <c r="D96" s="0">
-        <v>180</v>
+        <v>190</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="0" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B97" s="0" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C97" s="0" t="s">
         <v>52</v>
@@ -4682,10 +4688,10 @@
     </row>
     <row r="98">
       <c r="A98" s="0" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B98" s="0" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C98" s="0" t="s">
         <v>52</v>
@@ -4696,114 +4702,114 @@
     </row>
     <row r="99">
       <c r="A99" s="0" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B99" s="0" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C99" s="0" t="s">
         <v>52</v>
       </c>
       <c r="D99" s="0">
-        <v>190</v>
+        <v>180</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="0" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B100" s="0" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C100" s="0" t="s">
-        <v>15</v>
+        <v>52</v>
       </c>
       <c r="D100" s="0">
-        <v>1760</v>
+        <v>190</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="0" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B101" s="0" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C101" s="0" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D101" s="0">
-        <v>1117.4</v>
+        <v>1760</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="0" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B102" s="0" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C102" s="0" t="s">
-        <v>92</v>
+        <v>18</v>
       </c>
       <c r="D102" s="0">
-        <v>3274.24</v>
+        <v>1117.4</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="0" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B103" s="0" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C103" s="0" t="s">
         <v>92</v>
       </c>
       <c r="D103" s="0">
-        <v>2475.72</v>
+        <v>3274.24</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="0" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B104" s="0" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C104" s="0" t="s">
         <v>92</v>
       </c>
       <c r="D104" s="0">
-        <v>3713.58</v>
+        <v>2475.72</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="0" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B105" s="0" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C105" s="0" t="s">
-        <v>118</v>
+        <v>92</v>
       </c>
       <c r="D105" s="0">
-        <v>1810</v>
+        <v>3713.58</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="0" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B106" s="0" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C106" s="0" t="s">
-        <v>242</v>
+        <v>118</v>
       </c>
       <c r="D106" s="0">
-        <v>1800</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="107">
@@ -4814,122 +4820,122 @@
         <v>244</v>
       </c>
       <c r="C107" s="0" t="s">
-        <v>15</v>
+        <v>245</v>
       </c>
       <c r="D107" s="0">
-        <v>1600</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="0" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B108" s="0" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C108" s="0" t="s">
         <v>15</v>
       </c>
       <c r="D108" s="0">
-        <v>1800</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="0" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B109" s="0" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C109" s="0" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="D109" s="0">
-        <v>1600</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="0" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B110" s="0" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C110" s="0" t="s">
-        <v>118</v>
+        <v>34</v>
       </c>
       <c r="D110" s="0">
-        <v>1900</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="0" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B111" s="0" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C111" s="0" t="s">
-        <v>15</v>
+        <v>118</v>
       </c>
       <c r="D111" s="0">
-        <v>1600</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="0" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B112" s="0" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C112" s="0" t="s">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="D112" s="0">
-        <v>5771.79</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="0" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B113" s="0" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C113" s="0" t="s">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="D113" s="0">
-        <v>975</v>
+        <v>5771.79</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="0" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B114" s="0" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C114" s="0" t="s">
-        <v>140</v>
+        <v>18</v>
       </c>
       <c r="D114" s="0">
-        <v>993</v>
+        <v>975</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="0" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B115" s="0" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C115" s="0" t="s">
-        <v>261</v>
+        <v>140</v>
       </c>
       <c r="D115" s="0">
-        <v>2800</v>
+        <v>993</v>
       </c>
     </row>
     <row r="116">
@@ -4940,94 +4946,94 @@
         <v>263</v>
       </c>
       <c r="C116" s="0" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D116" s="0">
-        <v>4525.4</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="0" t="s">
+        <v>265</v>
+      </c>
+      <c r="B117" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C117" s="0" t="s">
         <v>264</v>
       </c>
-      <c r="B117" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="C117" s="0" t="s">
-        <v>21</v>
-      </c>
       <c r="D117" s="0">
-        <v>2954</v>
+        <v>4525.4</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="0" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B118" s="0" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C118" s="0" t="s">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="D118" s="0">
-        <v>11313.5</v>
+        <v>2954</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="0" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B119" s="0" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C119" s="0" t="s">
-        <v>34</v>
+        <v>92</v>
       </c>
       <c r="D119" s="0">
-        <v>2200</v>
+        <v>11313.5</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="0" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B120" s="0" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C120" s="0" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D120" s="0">
-        <v>2400</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="0" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B121" s="0" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C121" s="0" t="s">
-        <v>92</v>
+        <v>37</v>
       </c>
       <c r="D121" s="0">
-        <v>212.96</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="0" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B122" s="0" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C122" s="0" t="s">
-        <v>276</v>
+        <v>92</v>
       </c>
       <c r="D122" s="0">
-        <v>0</v>
+        <v>212.96</v>
       </c>
     </row>
     <row r="123">
@@ -5038,7 +5044,7 @@
         <v>278</v>
       </c>
       <c r="C123" s="0" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="D123" s="0">
         <v>0</v>
@@ -5046,16 +5052,16 @@
     </row>
     <row r="124">
       <c r="A124" s="0" t="s">
+        <v>280</v>
+      </c>
+      <c r="B124" s="0" t="s">
+        <v>281</v>
+      </c>
+      <c r="C124" s="0" t="s">
         <v>279</v>
       </c>
-      <c r="B124" s="0" t="s">
-        <v>280</v>
-      </c>
-      <c r="C124" s="0" t="s">
-        <v>281</v>
-      </c>
       <c r="D124" s="0">
-        <v>520</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -5066,7 +5072,7 @@
         <v>283</v>
       </c>
       <c r="C125" s="0" t="s">
-        <v>34</v>
+        <v>284</v>
       </c>
       <c r="D125" s="0">
         <v>520</v>
@@ -5074,58 +5080,58 @@
     </row>
     <row r="126">
       <c r="A126" s="0" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B126" s="0" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C126" s="0" t="s">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="D126" s="0">
-        <v>22</v>
+        <v>520</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="0" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B127" s="0" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C127" s="0" t="s">
-        <v>15</v>
+        <v>52</v>
       </c>
       <c r="D127" s="0">
-        <v>3200</v>
+        <v>22</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="0" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B128" s="0" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C128" s="0" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="D128" s="0">
-        <v>7377.5</v>
+        <v>3200</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="0" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B129" s="0" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C129" s="0" t="s">
-        <v>292</v>
+        <v>28</v>
       </c>
       <c r="D129" s="0">
-        <v>16095</v>
+        <v>7377.5</v>
       </c>
     </row>
     <row r="130">
@@ -5136,66 +5142,66 @@
         <v>294</v>
       </c>
       <c r="C130" s="0" t="s">
-        <v>140</v>
+        <v>295</v>
       </c>
       <c r="D130" s="0">
-        <v>2800</v>
+        <v>16095</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="0" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B131" s="0" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C131" s="0" t="s">
         <v>140</v>
       </c>
       <c r="D131" s="0">
-        <v>6536</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="0" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B132" s="0" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C132" s="0" t="s">
-        <v>15</v>
+        <v>140</v>
       </c>
       <c r="D132" s="0">
-        <v>4200</v>
+        <v>6536</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="0" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B133" s="0" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C133" s="0" t="s">
         <v>15</v>
       </c>
       <c r="D133" s="0">
-        <v>1050</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="0" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B134" s="0" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C134" s="0" t="s">
-        <v>303</v>
+        <v>15</v>
       </c>
       <c r="D134" s="0">
-        <v>3350</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="135">
@@ -5206,7 +5212,7 @@
         <v>305</v>
       </c>
       <c r="C135" s="0" t="s">
-        <v>123</v>
+        <v>306</v>
       </c>
       <c r="D135" s="0">
         <v>3350</v>
@@ -5214,16 +5220,16 @@
     </row>
     <row r="136">
       <c r="A136" s="0" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B136" s="0" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C136" s="0" t="s">
-        <v>308</v>
+        <v>123</v>
       </c>
       <c r="D136" s="0">
-        <v>0</v>
+        <v>3350</v>
       </c>
     </row>
     <row r="137">
@@ -5234,52 +5240,52 @@
         <v>310</v>
       </c>
       <c r="C137" s="0" t="s">
-        <v>18</v>
+        <v>311</v>
       </c>
       <c r="D137" s="0">
-        <v>589.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="0" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B138" s="0" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C138" s="0" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D138" s="0">
-        <v>1600</v>
+        <v>589.9</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="0" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B139" s="0" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C139" s="0" t="s">
         <v>15</v>
       </c>
       <c r="D139" s="0">
-        <v>2000</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="0" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B140" s="0" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C140" s="0" t="s">
-        <v>317</v>
+        <v>15</v>
       </c>
       <c r="D140" s="0">
-        <v>2728</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="141">
@@ -5290,91 +5296,91 @@
         <v>319</v>
       </c>
       <c r="C141" s="0" t="s">
-        <v>70</v>
+        <v>320</v>
       </c>
       <c r="D141" s="0">
-        <v>0</v>
+        <v>2728</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="0" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B142" s="0" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C142" s="0" t="s">
         <v>70</v>
       </c>
       <c r="D142" s="0">
-        <v>88248.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="0" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B143" s="0" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C143" s="0" t="s">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="D143" s="0">
-        <v>1785</v>
+        <v>88248.3</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="0" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B144" s="0" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C144" s="0" t="s">
         <v>52</v>
       </c>
       <c r="D144" s="0">
-        <v>2058</v>
+        <v>1785</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="0" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B145" s="0" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C145" s="0" t="s">
-        <v>15</v>
+        <v>52</v>
       </c>
       <c r="D145" s="0">
-        <v>1270</v>
+        <v>2058</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="0" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B146" s="0" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C146" s="0" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="D146" s="0">
-        <v>700</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="0" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B147" s="0" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C147" s="0" t="s">
-        <v>70</v>
+        <v>31</v>
       </c>
       <c r="D147" s="0">
         <v>700</v>
@@ -5382,13 +5388,13 @@
     </row>
     <row r="148">
       <c r="A148" s="0" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B148" s="0" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C148" s="0" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="D148" s="0">
         <v>700</v>
@@ -5396,30 +5402,30 @@
     </row>
     <row r="149">
       <c r="A149" s="0" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B149" s="0" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C149" s="0" t="s">
-        <v>92</v>
+        <v>34</v>
       </c>
       <c r="D149" s="0">
-        <v>1663.75</v>
+        <v>700</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="0" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B150" s="0" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C150" s="0" t="s">
-        <v>338</v>
+        <v>92</v>
       </c>
       <c r="D150" s="0">
-        <v>4500</v>
+        <v>1663.75</v>
       </c>
     </row>
     <row r="151">
@@ -5430,136 +5436,136 @@
         <v>340</v>
       </c>
       <c r="C151" s="0" t="s">
-        <v>34</v>
+        <v>341</v>
       </c>
       <c r="D151" s="0">
-        <v>390</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="0" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B152" s="0" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C152" s="0" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="D152" s="0">
-        <v>500</v>
+        <v>390</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="0" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B153" s="0" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C153" s="0" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="D153" s="0">
-        <v>400</v>
+        <v>500</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="0" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B154" s="0" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C154" s="0" t="s">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="D154" s="0">
-        <v>410</v>
+        <v>400</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="0" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B155" s="0" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C155" s="0" t="s">
         <v>70</v>
       </c>
       <c r="D155" s="0">
-        <v>580</v>
+        <v>410</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="0" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B156" s="0" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C156" s="0" t="s">
-        <v>15</v>
+        <v>70</v>
       </c>
       <c r="D156" s="0">
-        <v>572</v>
+        <v>580</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="0" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B157" s="0" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C157" s="0" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="D157" s="0">
-        <v>106950.8</v>
+        <v>572</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="0" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B158" s="0" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C158" s="0" t="s">
         <v>28</v>
       </c>
       <c r="D158" s="0">
-        <v>118372.7</v>
+        <v>106950.8</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="0" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B159" s="0" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C159" s="0" t="s">
         <v>28</v>
       </c>
       <c r="D159" s="0">
-        <v>140178.2</v>
+        <v>118372.7</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="0" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B160" s="0" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C160" s="0" t="s">
-        <v>359</v>
+        <v>28</v>
       </c>
       <c r="D160" s="0">
-        <v>650</v>
+        <v>140178.2</v>
       </c>
     </row>
     <row r="161">
@@ -5570,35 +5576,35 @@
         <v>361</v>
       </c>
       <c r="C161" s="0" t="s">
-        <v>110</v>
+        <v>362</v>
       </c>
       <c r="D161" s="0">
-        <v>1590</v>
+        <v>650</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="0" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B162" s="0" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C162" s="0" t="s">
-        <v>34</v>
+        <v>110</v>
       </c>
       <c r="D162" s="0">
-        <v>650</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="0" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B163" s="0" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C163" s="0" t="s">
-        <v>151</v>
+        <v>34</v>
       </c>
       <c r="D163" s="0">
         <v>650</v>
@@ -5606,13 +5612,13 @@
     </row>
     <row r="164">
       <c r="A164" s="0" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B164" s="0" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C164" s="0" t="s">
-        <v>15</v>
+        <v>151</v>
       </c>
       <c r="D164" s="0">
         <v>650</v>
@@ -5620,58 +5626,58 @@
     </row>
     <row r="165">
       <c r="A165" s="0" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B165" s="0" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C165" s="0" t="s">
         <v>15</v>
       </c>
       <c r="D165" s="0">
-        <v>1700</v>
+        <v>650</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="0" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B166" s="0" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C166" s="0" t="s">
         <v>15</v>
       </c>
       <c r="D166" s="0">
-        <v>0</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="0" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B167" s="0" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C167" s="0" t="s">
-        <v>115</v>
+        <v>15</v>
       </c>
       <c r="D167" s="0">
-        <v>1290</v>
+        <v>0</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="0" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B168" s="0" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C168" s="0" t="s">
-        <v>376</v>
+        <v>115</v>
       </c>
       <c r="D168" s="0">
-        <v>55058.9</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="169">
@@ -5685,7 +5691,7 @@
         <v>379</v>
       </c>
       <c r="D169" s="0">
-        <v>104695.98</v>
+        <v>55058.9</v>
       </c>
     </row>
     <row r="170">
@@ -5696,80 +5702,80 @@
         <v>381</v>
       </c>
       <c r="C170" s="0" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="D170" s="0">
-        <v>80478.92</v>
+        <v>104695.98</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="0" t="s">
+        <v>383</v>
+      </c>
+      <c r="B171" s="0" t="s">
+        <v>384</v>
+      </c>
+      <c r="C171" s="0" t="s">
         <v>382</v>
       </c>
-      <c r="B171" s="0" t="s">
-        <v>383</v>
-      </c>
-      <c r="C171" s="0" t="s">
-        <v>379</v>
-      </c>
       <c r="D171" s="0">
-        <v>92546.68</v>
+        <v>80478.92</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="0" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B172" s="0" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C172" s="0" t="s">
-        <v>28</v>
+        <v>382</v>
       </c>
       <c r="D172" s="0">
-        <v>972.9</v>
+        <v>92546.68</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="0" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B173" s="0" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C173" s="0" t="s">
         <v>28</v>
       </c>
       <c r="D173" s="0">
-        <v>265.3</v>
+        <v>972.9</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="0" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B174" s="0" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C174" s="0" t="s">
         <v>28</v>
       </c>
       <c r="D174" s="0">
-        <v>2908.78</v>
+        <v>265.3</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="0" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B175" s="0" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C175" s="0" t="s">
-        <v>392</v>
+        <v>28</v>
       </c>
       <c r="D175" s="0">
-        <v>61</v>
+        <v>2908.78</v>
       </c>
     </row>
     <row r="176">
@@ -5780,318 +5786,318 @@
         <v>394</v>
       </c>
       <c r="C176" s="0" t="s">
-        <v>18</v>
+        <v>395</v>
       </c>
       <c r="D176" s="0">
-        <v>270</v>
+        <v>61</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="0" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B177" s="0" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C177" s="0" t="s">
-        <v>151</v>
+        <v>18</v>
       </c>
       <c r="D177" s="0">
-        <v>257</v>
+        <v>270</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="0" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B178" s="0" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C178" s="0" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="D178" s="0">
-        <v>2859</v>
+        <v>257</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="0" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B179" s="0" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C179" s="0" t="s">
         <v>140</v>
       </c>
       <c r="D179" s="0">
-        <v>3573.45</v>
+        <v>2859</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="0" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B180" s="0" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C180" s="0" t="s">
-        <v>123</v>
+        <v>140</v>
       </c>
       <c r="D180" s="0">
-        <v>5218</v>
+        <v>3573.45</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="0" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B181" s="0" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C181" s="0" t="s">
-        <v>376</v>
+        <v>123</v>
       </c>
       <c r="D181" s="0">
-        <v>37527.35</v>
+        <v>5218</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="0" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B182" s="0" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C182" s="0" t="s">
-        <v>18</v>
+        <v>379</v>
       </c>
       <c r="D182" s="0">
-        <v>825.18</v>
+        <v>37527.35</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="0" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B183" s="0" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C183" s="0" t="s">
         <v>18</v>
       </c>
       <c r="D183" s="0">
-        <v>2687.98</v>
+        <v>825.18</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="0" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B184" s="0" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C184" s="0" t="s">
         <v>18</v>
       </c>
       <c r="D184" s="0">
-        <v>6764.67</v>
+        <v>2687.98</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="0" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B185" s="0" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C185" s="0" t="s">
         <v>18</v>
       </c>
       <c r="D185" s="0">
-        <v>353.46</v>
+        <v>6764.67</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="0" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B186" s="0" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C186" s="0" t="s">
         <v>18</v>
       </c>
       <c r="D186" s="0">
-        <v>10799.76</v>
+        <v>353.46</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="0" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B187" s="0" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C187" s="0" t="s">
         <v>18</v>
       </c>
       <c r="D187" s="0">
-        <v>3939.57</v>
+        <v>10799.76</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="0" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B188" s="0" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C188" s="0" t="s">
         <v>18</v>
       </c>
       <c r="D188" s="0">
-        <v>412.8</v>
+        <v>3939.57</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="0" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B189" s="0" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C189" s="0" t="s">
         <v>18</v>
       </c>
       <c r="D189" s="0">
-        <v>2184.81</v>
+        <v>412.8</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="0" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B190" s="0" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C190" s="0" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D190" s="0">
-        <v>9748.5</v>
+        <v>2184.81</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="0" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B191" s="0" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C191" s="0" t="s">
-        <v>70</v>
+        <v>28</v>
       </c>
       <c r="D191" s="0">
-        <v>430</v>
+        <v>9748.5</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="0" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B192" s="0" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C192" s="0" t="s">
         <v>70</v>
       </c>
       <c r="D192" s="0">
-        <v>800</v>
+        <v>430</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="0" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B193" s="0" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C193" s="0" t="s">
-        <v>242</v>
+        <v>70</v>
       </c>
       <c r="D193" s="0">
-        <v>2280</v>
+        <v>800</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="0" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B194" s="0" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C194" s="0" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="D194" s="0">
-        <v>1620</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="0" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B195" s="0" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C195" s="0" t="s">
-        <v>376</v>
+        <v>245</v>
       </c>
       <c r="D195" s="0">
-        <v>236458.17</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="0" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B196" s="0" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C196" s="0" t="s">
-        <v>28</v>
+        <v>379</v>
       </c>
       <c r="D196" s="0">
-        <v>317.2</v>
+        <v>236458.17</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="0" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B197" s="0" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C197" s="0" t="s">
-        <v>376</v>
+        <v>28</v>
       </c>
       <c r="D197" s="0">
-        <v>25100</v>
+        <v>317.2</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="0" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B198" s="0" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C198" s="0" t="s">
-        <v>439</v>
+        <v>379</v>
       </c>
       <c r="D198" s="0">
-        <v>20900</v>
+        <v>25100</v>
       </c>
     </row>
     <row r="199">
@@ -6102,136 +6108,136 @@
         <v>441</v>
       </c>
       <c r="C199" s="0" t="s">
-        <v>45</v>
+        <v>442</v>
       </c>
       <c r="D199" s="0">
-        <v>4729.48</v>
+        <v>20900</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="0" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B200" s="0" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C200" s="0" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="D200" s="0">
-        <v>1104.46</v>
+        <v>4729.48</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="0" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B201" s="0" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C201" s="0" t="s">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="D201" s="0">
-        <v>11646.25</v>
+        <v>1104.46</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="0" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B202" s="0" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C202" s="0" t="s">
-        <v>123</v>
+        <v>92</v>
       </c>
       <c r="D202" s="0">
-        <v>6072</v>
+        <v>11646.25</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="0" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B203" s="0" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C203" s="0" t="s">
-        <v>70</v>
+        <v>123</v>
       </c>
       <c r="D203" s="0">
-        <v>400</v>
+        <v>6072</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="0" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B204" s="0" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C204" s="0" t="s">
-        <v>21</v>
+        <v>70</v>
       </c>
       <c r="D204" s="0">
-        <v>409</v>
+        <v>400</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="0" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B205" s="0" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C205" s="0" t="s">
-        <v>64</v>
+        <v>21</v>
       </c>
       <c r="D205" s="0">
-        <v>10748</v>
+        <v>409</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="0" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B206" s="0" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C206" s="0" t="s">
         <v>64</v>
       </c>
       <c r="D206" s="0">
-        <v>12898</v>
+        <v>10748</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="0" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B207" s="0" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C207" s="0" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="D207" s="0">
-        <v>2000</v>
+        <v>12898</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="0" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B208" s="0" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C208" s="0" t="s">
-        <v>460</v>
+        <v>52</v>
       </c>
       <c r="D208" s="0">
-        <v>0</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="209">
@@ -6242,52 +6248,52 @@
         <v>462</v>
       </c>
       <c r="C209" s="0" t="s">
-        <v>15</v>
+        <v>463</v>
       </c>
       <c r="D209" s="0">
-        <v>490</v>
+        <v>0</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="0" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B210" s="0" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C210" s="0" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="D210" s="0">
-        <v>0</v>
+        <v>490</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="0" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B211" s="0" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C211" s="0" t="s">
-        <v>160</v>
+        <v>34</v>
       </c>
       <c r="D211" s="0">
-        <v>25171.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="0" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B212" s="0" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C212" s="0" t="s">
-        <v>469</v>
+        <v>160</v>
       </c>
       <c r="D212" s="0">
-        <v>60630</v>
+        <v>25171.1</v>
       </c>
     </row>
     <row r="213">
@@ -6298,52 +6304,52 @@
         <v>471</v>
       </c>
       <c r="C213" s="0" t="s">
-        <v>151</v>
+        <v>472</v>
       </c>
       <c r="D213" s="0">
-        <v>1800</v>
+        <v>60630</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="0" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B214" s="0" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C214" s="0" t="s">
-        <v>34</v>
+        <v>151</v>
       </c>
       <c r="D214" s="0">
-        <v>0</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="0" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B215" s="0" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C215" s="0" t="s">
-        <v>140</v>
+        <v>34</v>
       </c>
       <c r="D215" s="0">
-        <v>492.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="0" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B216" s="0" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C216" s="0" t="s">
-        <v>478</v>
+        <v>140</v>
       </c>
       <c r="D216" s="0">
-        <v>495</v>
+        <v>492.2</v>
       </c>
     </row>
     <row r="217">
@@ -6354,10 +6360,10 @@
         <v>480</v>
       </c>
       <c r="C217" s="0" t="s">
-        <v>18</v>
+        <v>207</v>
       </c>
       <c r="D217" s="0">
-        <v>1819.72</v>
+        <v>495</v>
       </c>
     </row>
     <row r="218">
@@ -6371,7 +6377,7 @@
         <v>18</v>
       </c>
       <c r="D218" s="0">
-        <v>4391.81</v>
+        <v>1819.72</v>
       </c>
     </row>
     <row r="219">
@@ -6382,10 +6388,10 @@
         <v>484</v>
       </c>
       <c r="C219" s="0" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="D219" s="0">
-        <v>4700</v>
+        <v>4391.81</v>
       </c>
     </row>
     <row r="220">
@@ -6399,7 +6405,7 @@
         <v>52</v>
       </c>
       <c r="D220" s="0">
-        <v>4670</v>
+        <v>4700</v>
       </c>
     </row>
     <row r="221">
@@ -6438,21 +6444,21 @@
         <v>492</v>
       </c>
       <c r="C223" s="0" t="s">
-        <v>493</v>
+        <v>52</v>
       </c>
       <c r="D223" s="0">
-        <v>265</v>
+        <v>4670</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="0" t="s">
+        <v>493</v>
+      </c>
+      <c r="B224" s="0" t="s">
         <v>494</v>
       </c>
-      <c r="B224" s="0" t="s">
+      <c r="C224" s="0" t="s">
         <v>495</v>
-      </c>
-      <c r="C224" s="0" t="s">
-        <v>493</v>
       </c>
       <c r="D224" s="0">
         <v>265</v>
@@ -6466,7 +6472,7 @@
         <v>497</v>
       </c>
       <c r="C225" s="0" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="D225" s="0">
         <v>265</v>
@@ -6480,7 +6486,7 @@
         <v>499</v>
       </c>
       <c r="C226" s="0" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="D226" s="0">
         <v>265</v>
@@ -6494,7 +6500,7 @@
         <v>501</v>
       </c>
       <c r="C227" s="0" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="D227" s="0">
         <v>265</v>
@@ -6508,7 +6514,7 @@
         <v>503</v>
       </c>
       <c r="C228" s="0" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="D228" s="0">
         <v>265</v>
@@ -6522,21 +6528,21 @@
         <v>505</v>
       </c>
       <c r="C229" s="0" t="s">
-        <v>506</v>
+        <v>495</v>
       </c>
       <c r="D229" s="0">
-        <v>4700</v>
+        <v>265</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="0" t="s">
+        <v>506</v>
+      </c>
+      <c r="B230" s="0" t="s">
         <v>507</v>
       </c>
-      <c r="B230" s="0" t="s">
+      <c r="C230" s="0" t="s">
         <v>508</v>
-      </c>
-      <c r="C230" s="0" t="s">
-        <v>509</v>
       </c>
       <c r="D230" s="0">
         <v>4700</v>
@@ -6544,13 +6550,13 @@
     </row>
     <row r="231">
       <c r="A231" s="0" t="s">
+        <v>509</v>
+      </c>
+      <c r="B231" s="0" t="s">
         <v>510</v>
       </c>
-      <c r="B231" s="0" t="s">
+      <c r="C231" s="0" t="s">
         <v>511</v>
-      </c>
-      <c r="C231" s="0" t="s">
-        <v>52</v>
       </c>
       <c r="D231" s="0">
         <v>4700</v>
@@ -6567,7 +6573,7 @@
         <v>52</v>
       </c>
       <c r="D232" s="0">
-        <v>597</v>
+        <v>4700</v>
       </c>
     </row>
     <row r="233">
@@ -6581,7 +6587,7 @@
         <v>52</v>
       </c>
       <c r="D233" s="0">
-        <v>223</v>
+        <v>597</v>
       </c>
     </row>
     <row r="234">
@@ -6595,7 +6601,7 @@
         <v>52</v>
       </c>
       <c r="D234" s="0">
-        <v>247</v>
+        <v>223</v>
       </c>
     </row>
     <row r="235">
@@ -6606,10 +6612,10 @@
         <v>519</v>
       </c>
       <c r="C235" s="0" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="D235" s="0">
-        <v>5600</v>
+        <v>247</v>
       </c>
     </row>
     <row r="236">
@@ -6620,10 +6626,10 @@
         <v>521</v>
       </c>
       <c r="C236" s="0" t="s">
-        <v>151</v>
+        <v>37</v>
       </c>
       <c r="D236" s="0">
-        <v>6000</v>
+        <v>5600</v>
       </c>
     </row>
     <row r="237">
@@ -6634,10 +6640,10 @@
         <v>523</v>
       </c>
       <c r="C237" s="0" t="s">
-        <v>70</v>
+        <v>151</v>
       </c>
       <c r="D237" s="0">
-        <v>80000</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="238">
@@ -6651,7 +6657,7 @@
         <v>70</v>
       </c>
       <c r="D238" s="0">
-        <v>90000</v>
+        <v>80000</v>
       </c>
     </row>
     <row r="239">
@@ -6665,7 +6671,7 @@
         <v>70</v>
       </c>
       <c r="D239" s="0">
-        <v>110000</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="240">
@@ -6676,10 +6682,10 @@
         <v>529</v>
       </c>
       <c r="C240" s="0" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="D240" s="0">
-        <v>900</v>
+        <v>110000</v>
       </c>
     </row>
     <row r="241">
@@ -6690,10 +6696,10 @@
         <v>531</v>
       </c>
       <c r="C241" s="0" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="D241" s="0">
-        <v>1100</v>
+        <v>900</v>
       </c>
     </row>
     <row r="242">
@@ -6707,7 +6713,7 @@
         <v>15</v>
       </c>
       <c r="D242" s="0">
-        <v>2500</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="243">
@@ -6718,10 +6724,10 @@
         <v>535</v>
       </c>
       <c r="C243" s="0" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="D243" s="0">
-        <v>14608.16</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="244">
@@ -6732,10 +6738,10 @@
         <v>537</v>
       </c>
       <c r="C244" s="0" t="s">
-        <v>151</v>
+        <v>28</v>
       </c>
       <c r="D244" s="0">
-        <v>700</v>
+        <v>14608.16</v>
       </c>
     </row>
     <row r="245">
@@ -6746,7 +6752,7 @@
         <v>539</v>
       </c>
       <c r="C245" s="0" t="s">
-        <v>37</v>
+        <v>151</v>
       </c>
       <c r="D245" s="0">
         <v>700</v>
@@ -6760,10 +6766,10 @@
         <v>541</v>
       </c>
       <c r="C246" s="0" t="s">
-        <v>281</v>
+        <v>37</v>
       </c>
       <c r="D246" s="0">
-        <v>450</v>
+        <v>700</v>
       </c>
     </row>
     <row r="247">
@@ -6774,10 +6780,10 @@
         <v>543</v>
       </c>
       <c r="C247" s="0" t="s">
-        <v>15</v>
+        <v>284</v>
       </c>
       <c r="D247" s="0">
-        <v>555</v>
+        <v>450</v>
       </c>
     </row>
     <row r="248">
@@ -6791,7 +6797,7 @@
         <v>15</v>
       </c>
       <c r="D248" s="0">
-        <v>825</v>
+        <v>555</v>
       </c>
     </row>
     <row r="249">
@@ -6805,7 +6811,7 @@
         <v>15</v>
       </c>
       <c r="D249" s="0">
-        <v>36.3</v>
+        <v>825</v>
       </c>
     </row>
     <row r="250">
@@ -6819,7 +6825,7 @@
         <v>15</v>
       </c>
       <c r="D250" s="0">
-        <v>544.5</v>
+        <v>36.3</v>
       </c>
     </row>
     <row r="251">
@@ -6833,7 +6839,7 @@
         <v>15</v>
       </c>
       <c r="D251" s="0">
-        <v>750</v>
+        <v>544.5</v>
       </c>
     </row>
     <row r="252">
@@ -6844,10 +6850,10 @@
         <v>553</v>
       </c>
       <c r="C252" s="0" t="s">
-        <v>151</v>
+        <v>15</v>
       </c>
       <c r="D252" s="0">
-        <v>1130</v>
+        <v>750</v>
       </c>
     </row>
     <row r="253">
@@ -6858,10 +6864,10 @@
         <v>555</v>
       </c>
       <c r="C253" s="0" t="s">
-        <v>52</v>
+        <v>151</v>
       </c>
       <c r="D253" s="0">
-        <v>4510</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="254">
@@ -6914,10 +6920,10 @@
         <v>563</v>
       </c>
       <c r="C257" s="0" t="s">
-        <v>15</v>
+        <v>52</v>
       </c>
       <c r="D257" s="0">
-        <v>902</v>
+        <v>4510</v>
       </c>
     </row>
     <row r="258">
@@ -6931,7 +6937,7 @@
         <v>15</v>
       </c>
       <c r="D258" s="0">
-        <v>880</v>
+        <v>902</v>
       </c>
     </row>
     <row r="259">
@@ -6942,10 +6948,10 @@
         <v>567</v>
       </c>
       <c r="C259" s="0" t="s">
-        <v>140</v>
+        <v>15</v>
       </c>
       <c r="D259" s="0">
-        <v>430</v>
+        <v>880</v>
       </c>
     </row>
     <row r="260">
@@ -6959,7 +6965,7 @@
         <v>140</v>
       </c>
       <c r="D260" s="0">
-        <v>373</v>
+        <v>430</v>
       </c>
     </row>
     <row r="261">
@@ -6970,10 +6976,10 @@
         <v>571</v>
       </c>
       <c r="C261" s="0" t="s">
-        <v>18</v>
+        <v>140</v>
       </c>
       <c r="D261" s="0">
-        <v>318.63</v>
+        <v>373</v>
       </c>
     </row>
     <row r="262">
@@ -6987,7 +6993,7 @@
         <v>18</v>
       </c>
       <c r="D262" s="0">
-        <v>415.15</v>
+        <v>300</v>
       </c>
     </row>
     <row r="263">
@@ -7001,7 +7007,7 @@
         <v>18</v>
       </c>
       <c r="D263" s="0">
-        <v>760</v>
+        <v>420</v>
       </c>
     </row>
     <row r="264">
@@ -7015,7 +7021,7 @@
         <v>18</v>
       </c>
       <c r="D264" s="0">
-        <v>820</v>
+        <v>760</v>
       </c>
     </row>
     <row r="265">
@@ -7026,24 +7032,24 @@
         <v>579</v>
       </c>
       <c r="C265" s="0" t="s">
-        <v>580</v>
+        <v>18</v>
       </c>
       <c r="D265" s="0">
-        <v>177940.1</v>
+        <v>820</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="0" t="s">
+        <v>580</v>
+      </c>
+      <c r="B266" s="0" t="s">
         <v>581</v>
       </c>
-      <c r="B266" s="0" t="s">
+      <c r="C266" s="0" t="s">
         <v>582</v>
       </c>
-      <c r="C266" s="0" t="s">
-        <v>70</v>
-      </c>
       <c r="D266" s="0">
-        <v>28000</v>
+        <v>177940.1</v>
       </c>
     </row>
     <row r="267">
@@ -7057,7 +7063,7 @@
         <v>70</v>
       </c>
       <c r="D267" s="0">
-        <v>34000</v>
+        <v>28000</v>
       </c>
     </row>
     <row r="268">
@@ -7068,10 +7074,10 @@
         <v>586</v>
       </c>
       <c r="C268" s="0" t="s">
-        <v>469</v>
+        <v>70</v>
       </c>
       <c r="D268" s="0">
-        <v>227939.52</v>
+        <v>34000</v>
       </c>
     </row>
     <row r="269">
@@ -7082,10 +7088,10 @@
         <v>588</v>
       </c>
       <c r="C269" s="0" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="D269" s="0">
-        <v>184488.7</v>
+        <v>227939.52</v>
       </c>
     </row>
     <row r="270">
@@ -7096,10 +7102,10 @@
         <v>590</v>
       </c>
       <c r="C270" s="0" t="s">
-        <v>15</v>
+        <v>472</v>
       </c>
       <c r="D270" s="0">
-        <v>1760</v>
+        <v>184488.7</v>
       </c>
     </row>
     <row r="271">
@@ -7110,24 +7116,24 @@
         <v>592</v>
       </c>
       <c r="C271" s="0" t="s">
-        <v>593</v>
+        <v>15</v>
       </c>
       <c r="D271" s="0">
-        <v>26350</v>
+        <v>1760</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="0" t="s">
+        <v>593</v>
+      </c>
+      <c r="B272" s="0" t="s">
         <v>594</v>
       </c>
-      <c r="B272" s="0" t="s">
+      <c r="C272" s="0" t="s">
         <v>595</v>
       </c>
-      <c r="C272" s="0" t="s">
-        <v>478</v>
-      </c>
       <c r="D272" s="0">
-        <v>31250</v>
+        <v>26350</v>
       </c>
     </row>
     <row r="273">
@@ -7138,10 +7144,10 @@
         <v>597</v>
       </c>
       <c r="C273" s="0" t="s">
-        <v>52</v>
+        <v>207</v>
       </c>
       <c r="D273" s="0">
-        <v>34.98</v>
+        <v>31250</v>
       </c>
     </row>
     <row r="274">
@@ -7152,7 +7158,7 @@
         <v>599</v>
       </c>
       <c r="C274" s="0" t="s">
-        <v>600</v>
+        <v>52</v>
       </c>
       <c r="D274" s="0">
         <v>34.98</v>
@@ -7160,27 +7166,27 @@
     </row>
     <row r="275">
       <c r="A275" s="0" t="s">
+        <v>600</v>
+      </c>
+      <c r="B275" s="0" t="s">
         <v>601</v>
       </c>
-      <c r="B275" s="0" t="s">
+      <c r="C275" s="0" t="s">
         <v>602</v>
       </c>
-      <c r="C275" s="0" t="s">
-        <v>603</v>
-      </c>
       <c r="D275" s="0">
-        <v>65</v>
+        <v>34.98</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="0" t="s">
+        <v>603</v>
+      </c>
+      <c r="B276" s="0" t="s">
         <v>604</v>
       </c>
-      <c r="B276" s="0" t="s">
+      <c r="C276" s="0" t="s">
         <v>605</v>
-      </c>
-      <c r="C276" s="0" t="s">
-        <v>52</v>
       </c>
       <c r="D276" s="0">
         <v>65</v>
@@ -7197,7 +7203,7 @@
         <v>52</v>
       </c>
       <c r="D277" s="0">
-        <v>92</v>
+        <v>65</v>
       </c>
     </row>
     <row r="278">
@@ -7211,7 +7217,7 @@
         <v>52</v>
       </c>
       <c r="D278" s="0">
-        <v>33</v>
+        <v>92</v>
       </c>
     </row>
     <row r="279">
@@ -7225,7 +7231,7 @@
         <v>52</v>
       </c>
       <c r="D279" s="0">
-        <v>54.8</v>
+        <v>33</v>
       </c>
     </row>
     <row r="280">
@@ -7236,10 +7242,10 @@
         <v>613</v>
       </c>
       <c r="C280" s="0" t="s">
-        <v>338</v>
+        <v>52</v>
       </c>
       <c r="D280" s="0">
-        <v>300</v>
+        <v>54.8</v>
       </c>
     </row>
     <row r="281">
@@ -7250,10 +7256,10 @@
         <v>615</v>
       </c>
       <c r="C281" s="0" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="D281" s="0">
-        <v>370</v>
+        <v>300</v>
       </c>
     </row>
     <row r="282">
@@ -7264,10 +7270,10 @@
         <v>617</v>
       </c>
       <c r="C282" s="0" t="s">
-        <v>359</v>
+        <v>341</v>
       </c>
       <c r="D282" s="0">
-        <v>450</v>
+        <v>370</v>
       </c>
     </row>
     <row r="283">
@@ -7278,7 +7284,7 @@
         <v>619</v>
       </c>
       <c r="C283" s="0" t="s">
-        <v>37</v>
+        <v>362</v>
       </c>
       <c r="D283" s="0">
         <v>450</v>
@@ -7292,7 +7298,7 @@
         <v>621</v>
       </c>
       <c r="C284" s="0" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="D284" s="0">
         <v>450</v>
@@ -7309,7 +7315,7 @@
         <v>15</v>
       </c>
       <c r="D285" s="0">
-        <v>1650</v>
+        <v>450</v>
       </c>
     </row>
     <row r="286">
@@ -7323,7 +7329,7 @@
         <v>15</v>
       </c>
       <c r="D286" s="0">
-        <v>2100</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="287">
@@ -7337,7 +7343,7 @@
         <v>15</v>
       </c>
       <c r="D287" s="0">
-        <v>1980</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="288">
@@ -7351,7 +7357,7 @@
         <v>15</v>
       </c>
       <c r="D288" s="0">
-        <v>2160</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="289">
@@ -7365,7 +7371,7 @@
         <v>15</v>
       </c>
       <c r="D289" s="0">
-        <v>1500</v>
+        <v>2160</v>
       </c>
     </row>
     <row r="290">
@@ -7379,7 +7385,7 @@
         <v>15</v>
       </c>
       <c r="D290" s="0">
-        <v>2600</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="291">
@@ -7393,7 +7399,7 @@
         <v>15</v>
       </c>
       <c r="D291" s="0">
-        <v>2000</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="292">
@@ -7407,7 +7413,7 @@
         <v>15</v>
       </c>
       <c r="D292" s="0">
-        <v>6700</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="293">
@@ -7421,7 +7427,7 @@
         <v>15</v>
       </c>
       <c r="D293" s="0">
-        <v>1650</v>
+        <v>6700</v>
       </c>
     </row>
     <row r="294">
@@ -7435,7 +7441,7 @@
         <v>15</v>
       </c>
       <c r="D294" s="0">
-        <v>1035</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="295">
@@ -7449,7 +7455,7 @@
         <v>15</v>
       </c>
       <c r="D295" s="0">
-        <v>2600</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="296">
@@ -7463,7 +7469,7 @@
         <v>15</v>
       </c>
       <c r="D296" s="0">
-        <v>2400</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="297">
@@ -7474,10 +7480,10 @@
         <v>647</v>
       </c>
       <c r="C297" s="0" t="s">
-        <v>140</v>
+        <v>15</v>
       </c>
       <c r="D297" s="0">
-        <v>4590</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="298">
@@ -7491,7 +7497,7 @@
         <v>140</v>
       </c>
       <c r="D298" s="0">
-        <v>2300</v>
+        <v>4590</v>
       </c>
     </row>
     <row r="299">
@@ -7505,7 +7511,7 @@
         <v>140</v>
       </c>
       <c r="D299" s="0">
-        <v>1150</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="300">
@@ -7516,10 +7522,10 @@
         <v>653</v>
       </c>
       <c r="C300" s="0" t="s">
-        <v>28</v>
+        <v>140</v>
       </c>
       <c r="D300" s="0">
-        <v>7655.2</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="301">
@@ -7530,10 +7536,10 @@
         <v>655</v>
       </c>
       <c r="C301" s="0" t="s">
-        <v>123</v>
+        <v>28</v>
       </c>
       <c r="D301" s="0">
-        <v>1790</v>
+        <v>7655.2</v>
       </c>
     </row>
     <row r="302">
@@ -7547,7 +7553,7 @@
         <v>123</v>
       </c>
       <c r="D302" s="0">
-        <v>3016.53</v>
+        <v>1790</v>
       </c>
     </row>
     <row r="303">
@@ -7561,7 +7567,7 @@
         <v>123</v>
       </c>
       <c r="D303" s="0">
-        <v>4800</v>
+        <v>3016.53</v>
       </c>
     </row>
     <row r="304">
@@ -7575,7 +7581,7 @@
         <v>123</v>
       </c>
       <c r="D304" s="0">
-        <v>4450</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="305">
@@ -7586,24 +7592,24 @@
         <v>663</v>
       </c>
       <c r="C305" s="0" t="s">
-        <v>664</v>
+        <v>123</v>
       </c>
       <c r="D305" s="0">
-        <v>0</v>
+        <v>4450</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="0" t="s">
+        <v>664</v>
+      </c>
+      <c r="B306" s="0" t="s">
         <v>665</v>
       </c>
-      <c r="B306" s="0" t="s">
+      <c r="C306" s="0" t="s">
         <v>666</v>
       </c>
-      <c r="C306" s="0" t="s">
-        <v>28</v>
-      </c>
       <c r="D306" s="0">
-        <v>494</v>
+        <v>0</v>
       </c>
     </row>
     <row r="307">
@@ -7617,7 +7623,7 @@
         <v>28</v>
       </c>
       <c r="D307" s="0">
-        <v>665.3</v>
+        <v>494</v>
       </c>
     </row>
     <row r="308">
@@ -7628,10 +7634,10 @@
         <v>670</v>
       </c>
       <c r="C308" s="0" t="s">
-        <v>92</v>
+        <v>28</v>
       </c>
       <c r="D308" s="0">
-        <v>33940.5</v>
+        <v>665.3</v>
       </c>
     </row>
     <row r="309">
@@ -7645,7 +7651,7 @@
         <v>92</v>
       </c>
       <c r="D309" s="0">
-        <v>4525.4</v>
+        <v>33940.5</v>
       </c>
     </row>
     <row r="310">
@@ -7656,10 +7662,10 @@
         <v>674</v>
       </c>
       <c r="C310" s="0" t="s">
-        <v>151</v>
+        <v>92</v>
       </c>
       <c r="D310" s="0">
-        <v>896</v>
+        <v>4525.4</v>
       </c>
     </row>
     <row r="311">
@@ -7670,10 +7676,10 @@
         <v>676</v>
       </c>
       <c r="C311" s="0" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="D311" s="0">
-        <v>1250</v>
+        <v>896</v>
       </c>
     </row>
     <row r="312">
@@ -7684,10 +7690,10 @@
         <v>678</v>
       </c>
       <c r="C312" s="0" t="s">
-        <v>92</v>
+        <v>140</v>
       </c>
       <c r="D312" s="0">
-        <v>332750</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="313">
@@ -7698,10 +7704,10 @@
         <v>680</v>
       </c>
       <c r="C313" s="0" t="s">
-        <v>202</v>
+        <v>92</v>
       </c>
       <c r="D313" s="0">
-        <v>17440</v>
+        <v>332750</v>
       </c>
     </row>
     <row r="314">
@@ -7715,7 +7721,7 @@
         <v>202</v>
       </c>
       <c r="D314" s="0">
-        <v>4390</v>
+        <v>17440</v>
       </c>
     </row>
     <row r="315">
@@ -7740,10 +7746,10 @@
         <v>686</v>
       </c>
       <c r="C316" s="0" t="s">
-        <v>281</v>
+        <v>202</v>
       </c>
       <c r="D316" s="0">
-        <v>2250</v>
+        <v>4390</v>
       </c>
     </row>
     <row r="317">
@@ -7754,10 +7760,10 @@
         <v>688</v>
       </c>
       <c r="C317" s="0" t="s">
-        <v>202</v>
+        <v>284</v>
       </c>
       <c r="D317" s="0">
-        <v>3355</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="318">
@@ -7768,10 +7774,10 @@
         <v>690</v>
       </c>
       <c r="C318" s="0" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="D318" s="0">
-        <v>7500</v>
+        <v>3355</v>
       </c>
     </row>
     <row r="319">
@@ -7782,10 +7788,10 @@
         <v>692</v>
       </c>
       <c r="C319" s="0" t="s">
-        <v>92</v>
+        <v>210</v>
       </c>
       <c r="D319" s="0">
-        <v>25289</v>
+        <v>7500</v>
       </c>
     </row>
     <row r="320">
@@ -7799,7 +7805,7 @@
         <v>92</v>
       </c>
       <c r="D320" s="0">
-        <v>252890</v>
+        <v>25289</v>
       </c>
     </row>
     <row r="321">
@@ -7810,10 +7816,10 @@
         <v>696</v>
       </c>
       <c r="C321" s="0" t="s">
-        <v>52</v>
+        <v>92</v>
       </c>
       <c r="D321" s="0">
-        <v>160</v>
+        <v>252890</v>
       </c>
     </row>
     <row r="322">
@@ -7824,10 +7830,10 @@
         <v>698</v>
       </c>
       <c r="C322" s="0" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="D322" s="0">
-        <v>285.6</v>
+        <v>160</v>
       </c>
     </row>
     <row r="323">
@@ -7841,7 +7847,7 @@
         <v>21</v>
       </c>
       <c r="D323" s="0">
-        <v>338</v>
+        <v>285.6</v>
       </c>
     </row>
     <row r="324">
@@ -7852,21 +7858,21 @@
         <v>702</v>
       </c>
       <c r="C324" s="0" t="s">
-        <v>703</v>
+        <v>21</v>
       </c>
       <c r="D324" s="0">
-        <v>770</v>
+        <v>338</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="0" t="s">
+        <v>703</v>
+      </c>
+      <c r="B325" s="0" t="s">
         <v>704</v>
       </c>
-      <c r="B325" s="0" t="s">
+      <c r="C325" s="0" t="s">
         <v>705</v>
-      </c>
-      <c r="C325" s="0" t="s">
-        <v>706</v>
       </c>
       <c r="D325" s="0">
         <v>770</v>
@@ -7874,16 +7880,16 @@
     </row>
     <row r="326">
       <c r="A326" s="0" t="s">
+        <v>706</v>
+      </c>
+      <c r="B326" s="0" t="s">
         <v>707</v>
       </c>
-      <c r="B326" s="0" t="s">
+      <c r="C326" s="0" t="s">
         <v>708</v>
       </c>
-      <c r="C326" s="0" t="s">
-        <v>15</v>
-      </c>
       <c r="D326" s="0">
-        <v>973.5</v>
+        <v>770</v>
       </c>
     </row>
     <row r="327">
@@ -7894,10 +7900,10 @@
         <v>710</v>
       </c>
       <c r="C327" s="0" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="D327" s="0">
-        <v>507.08</v>
+        <v>973.5</v>
       </c>
     </row>
     <row r="328">
@@ -7908,10 +7914,10 @@
         <v>712</v>
       </c>
       <c r="C328" s="0" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D328" s="0">
-        <v>450</v>
+        <v>507.08</v>
       </c>
     </row>
     <row r="329">
@@ -7922,10 +7928,10 @@
         <v>714</v>
       </c>
       <c r="C329" s="0" t="s">
-        <v>151</v>
+        <v>15</v>
       </c>
       <c r="D329" s="0">
-        <v>760</v>
+        <v>450</v>
       </c>
     </row>
     <row r="330">
@@ -7936,10 +7942,10 @@
         <v>716</v>
       </c>
       <c r="C330" s="0" t="s">
-        <v>281</v>
+        <v>151</v>
       </c>
       <c r="D330" s="0">
-        <v>5900</v>
+        <v>760</v>
       </c>
     </row>
     <row r="331">
@@ -7950,10 +7956,10 @@
         <v>718</v>
       </c>
       <c r="C331" s="0" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="D331" s="0">
-        <v>2900</v>
+        <v>5900</v>
       </c>
     </row>
     <row r="332">
@@ -7964,10 +7970,10 @@
         <v>720</v>
       </c>
       <c r="C332" s="0" t="s">
-        <v>140</v>
+        <v>284</v>
       </c>
       <c r="D332" s="0">
-        <v>890</v>
+        <v>2900</v>
       </c>
     </row>
     <row r="333">
@@ -7981,7 +7987,7 @@
         <v>140</v>
       </c>
       <c r="D333" s="0">
-        <v>594</v>
+        <v>890</v>
       </c>
     </row>
     <row r="334">
@@ -7995,7 +8001,7 @@
         <v>140</v>
       </c>
       <c r="D334" s="0">
-        <v>65</v>
+        <v>594</v>
       </c>
     </row>
     <row r="335">
@@ -8006,10 +8012,10 @@
         <v>726</v>
       </c>
       <c r="C335" s="0" t="s">
-        <v>92</v>
+        <v>140</v>
       </c>
       <c r="D335" s="0">
-        <v>11313.5</v>
+        <v>65</v>
       </c>
     </row>
     <row r="336">
@@ -8020,10 +8026,10 @@
         <v>728</v>
       </c>
       <c r="C336" s="0" t="s">
-        <v>34</v>
+        <v>92</v>
       </c>
       <c r="D336" s="0">
-        <v>420</v>
+        <v>11313.5</v>
       </c>
     </row>
     <row r="337">
@@ -8034,10 +8040,10 @@
         <v>730</v>
       </c>
       <c r="C337" s="0" t="s">
-        <v>359</v>
+        <v>34</v>
       </c>
       <c r="D337" s="0">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="338">
@@ -8048,10 +8054,10 @@
         <v>732</v>
       </c>
       <c r="C338" s="0" t="s">
-        <v>21</v>
+        <v>362</v>
       </c>
       <c r="D338" s="0">
-        <v>377</v>
+        <v>418</v>
       </c>
     </row>
     <row r="339">
@@ -8062,10 +8068,10 @@
         <v>734</v>
       </c>
       <c r="C339" s="0" t="s">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="D339" s="0">
-        <v>5780.66</v>
+        <v>377</v>
       </c>
     </row>
     <row r="340">
@@ -8076,10 +8082,10 @@
         <v>736</v>
       </c>
       <c r="C340" s="0" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="D340" s="0">
-        <v>898</v>
+        <v>5780.66</v>
       </c>
     </row>
     <row r="341">
@@ -8090,10 +8096,10 @@
         <v>738</v>
       </c>
       <c r="C341" s="0" t="s">
-        <v>123</v>
+        <v>70</v>
       </c>
       <c r="D341" s="0">
-        <v>4767</v>
+        <v>898</v>
       </c>
     </row>
     <row r="342">
@@ -8104,10 +8110,10 @@
         <v>740</v>
       </c>
       <c r="C342" s="0" t="s">
-        <v>34</v>
+        <v>123</v>
       </c>
       <c r="D342" s="0">
-        <v>650</v>
+        <v>4767</v>
       </c>
     </row>
     <row r="343">
@@ -8118,7 +8124,7 @@
         <v>742</v>
       </c>
       <c r="C343" s="0" t="s">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="D343" s="0">
         <v>650</v>
@@ -8132,10 +8138,10 @@
         <v>744</v>
       </c>
       <c r="C344" s="0" t="s">
-        <v>15</v>
+        <v>70</v>
       </c>
       <c r="D344" s="0">
-        <v>2178</v>
+        <v>650</v>
       </c>
     </row>
     <row r="345">
@@ -8146,10 +8152,10 @@
         <v>746</v>
       </c>
       <c r="C345" s="0" t="s">
-        <v>92</v>
+        <v>15</v>
       </c>
       <c r="D345" s="0">
-        <v>7986</v>
+        <v>2178</v>
       </c>
     </row>
     <row r="346">
@@ -8160,24 +8166,24 @@
         <v>748</v>
       </c>
       <c r="C346" s="0" t="s">
-        <v>749</v>
+        <v>92</v>
       </c>
       <c r="D346" s="0">
-        <v>1910</v>
+        <v>7986</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" s="0" t="s">
+        <v>749</v>
+      </c>
+      <c r="B347" s="0" t="s">
         <v>750</v>
       </c>
-      <c r="B347" s="0" t="s">
+      <c r="C347" s="0" t="s">
         <v>751</v>
       </c>
-      <c r="C347" s="0" t="s">
-        <v>151</v>
-      </c>
       <c r="D347" s="0">
-        <v>900</v>
+        <v>1910</v>
       </c>
     </row>
     <row r="348">
@@ -8188,10 +8194,10 @@
         <v>753</v>
       </c>
       <c r="C348" s="0" t="s">
-        <v>21</v>
+        <v>151</v>
       </c>
       <c r="D348" s="0">
-        <v>1722</v>
+        <v>900</v>
       </c>
     </row>
     <row r="349">
@@ -8202,10 +8208,10 @@
         <v>755</v>
       </c>
       <c r="C349" s="0" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="D349" s="0">
-        <v>59000</v>
+        <v>1722</v>
       </c>
     </row>
     <row r="350">
@@ -8216,10 +8222,10 @@
         <v>757</v>
       </c>
       <c r="C350" s="0" t="s">
-        <v>151</v>
+        <v>34</v>
       </c>
       <c r="D350" s="0">
-        <v>750</v>
+        <v>59000</v>
       </c>
     </row>
     <row r="351">
@@ -8233,7 +8239,7 @@
         <v>151</v>
       </c>
       <c r="D351" s="0">
-        <v>1212</v>
+        <v>750</v>
       </c>
     </row>
     <row r="352">
@@ -8247,7 +8253,7 @@
         <v>151</v>
       </c>
       <c r="D352" s="0">
-        <v>1300</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="353">
@@ -8261,7 +8267,7 @@
         <v>151</v>
       </c>
       <c r="D353" s="0">
-        <v>1500</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="354">
@@ -8275,7 +8281,7 @@
         <v>151</v>
       </c>
       <c r="D354" s="0">
-        <v>1400</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="355">
@@ -8286,10 +8292,10 @@
         <v>767</v>
       </c>
       <c r="C355" s="0" t="s">
-        <v>261</v>
+        <v>151</v>
       </c>
       <c r="D355" s="0">
-        <v>11959</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="356">
@@ -8300,10 +8306,10 @@
         <v>769</v>
       </c>
       <c r="C356" s="0" t="s">
-        <v>140</v>
+        <v>264</v>
       </c>
       <c r="D356" s="0">
-        <v>350</v>
+        <v>11959</v>
       </c>
     </row>
     <row r="357">
@@ -8314,10 +8320,10 @@
         <v>771</v>
       </c>
       <c r="C357" s="0" t="s">
-        <v>281</v>
+        <v>140</v>
       </c>
       <c r="D357" s="0">
-        <v>1450</v>
+        <v>350</v>
       </c>
     </row>
     <row r="358">
@@ -8328,10 +8334,10 @@
         <v>773</v>
       </c>
       <c r="C358" s="0" t="s">
-        <v>92</v>
+        <v>284</v>
       </c>
       <c r="D358" s="0">
-        <v>7320.5</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="359">
@@ -8342,10 +8348,10 @@
         <v>775</v>
       </c>
       <c r="C359" s="0" t="s">
-        <v>15</v>
+        <v>92</v>
       </c>
       <c r="D359" s="0">
-        <v>900</v>
+        <v>7320.5</v>
       </c>
     </row>
     <row r="360">
@@ -8356,10 +8362,10 @@
         <v>777</v>
       </c>
       <c r="C360" s="0" t="s">
-        <v>281</v>
+        <v>15</v>
       </c>
       <c r="D360" s="0">
-        <v>566</v>
+        <v>900</v>
       </c>
     </row>
     <row r="361">
@@ -8370,10 +8376,10 @@
         <v>779</v>
       </c>
       <c r="C361" s="0" t="s">
-        <v>469</v>
+        <v>284</v>
       </c>
       <c r="D361" s="0">
-        <v>64925</v>
+        <v>566</v>
       </c>
     </row>
     <row r="362">
@@ -8384,10 +8390,10 @@
         <v>781</v>
       </c>
       <c r="C362" s="0" t="s">
-        <v>15</v>
+        <v>472</v>
       </c>
       <c r="D362" s="0">
-        <v>1100</v>
+        <v>64925</v>
       </c>
     </row>
     <row r="363">
@@ -8398,10 +8404,10 @@
         <v>783</v>
       </c>
       <c r="C363" s="0" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="D363" s="0">
-        <v>1623</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="364">
@@ -8412,10 +8418,10 @@
         <v>785</v>
       </c>
       <c r="C364" s="0" t="s">
-        <v>140</v>
+        <v>21</v>
       </c>
       <c r="D364" s="0">
-        <v>1269</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="365">
@@ -8429,7 +8435,7 @@
         <v>140</v>
       </c>
       <c r="D365" s="0">
-        <v>4712</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="366">
@@ -8440,10 +8446,10 @@
         <v>789</v>
       </c>
       <c r="C366" s="0" t="s">
-        <v>28</v>
+        <v>140</v>
       </c>
       <c r="D366" s="0">
-        <v>1250</v>
+        <v>4712</v>
       </c>
     </row>
     <row r="367">
@@ -8457,7 +8463,7 @@
         <v>28</v>
       </c>
       <c r="D367" s="0">
-        <v>1986</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="368">
@@ -8468,10 +8474,10 @@
         <v>793</v>
       </c>
       <c r="C368" s="0" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="D368" s="0">
-        <v>450</v>
+        <v>1986</v>
       </c>
     </row>
     <row r="369">
@@ -8485,7 +8491,7 @@
         <v>15</v>
       </c>
       <c r="D369" s="0">
-        <v>825</v>
+        <v>450</v>
       </c>
     </row>
     <row r="370">
@@ -8510,10 +8516,10 @@
         <v>799</v>
       </c>
       <c r="C371" s="0" t="s">
-        <v>379</v>
+        <v>15</v>
       </c>
       <c r="D371" s="0">
-        <v>134775.6</v>
+        <v>825</v>
       </c>
     </row>
     <row r="372">
@@ -8524,10 +8530,10 @@
         <v>801</v>
       </c>
       <c r="C372" s="0" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="D372" s="0">
-        <v>175991.55</v>
+        <v>134775.6</v>
       </c>
     </row>
     <row r="373">
@@ -8538,10 +8544,10 @@
         <v>803</v>
       </c>
       <c r="C373" s="0" t="s">
-        <v>70</v>
+        <v>382</v>
       </c>
       <c r="D373" s="0">
-        <v>3427</v>
+        <v>175991.55</v>
       </c>
     </row>
     <row r="374">
@@ -8555,7 +8561,7 @@
         <v>70</v>
       </c>
       <c r="D374" s="0">
-        <v>10618</v>
+        <v>3427</v>
       </c>
     </row>
     <row r="375">
@@ -8566,10 +8572,10 @@
         <v>807</v>
       </c>
       <c r="C375" s="0" t="s">
-        <v>281</v>
+        <v>70</v>
       </c>
       <c r="D375" s="0">
-        <v>515</v>
+        <v>10618</v>
       </c>
     </row>
     <row r="376">
@@ -8580,7 +8586,7 @@
         <v>809</v>
       </c>
       <c r="C376" s="0" t="s">
-        <v>37</v>
+        <v>284</v>
       </c>
       <c r="D376" s="0">
         <v>515</v>
@@ -8594,10 +8600,10 @@
         <v>811</v>
       </c>
       <c r="C377" s="0" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="D377" s="0">
-        <v>10000</v>
+        <v>515</v>
       </c>
     </row>
     <row r="378">
@@ -8608,10 +8614,10 @@
         <v>813</v>
       </c>
       <c r="C378" s="0" t="s">
-        <v>469</v>
+        <v>52</v>
       </c>
       <c r="D378" s="0">
-        <v>207558.08</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="379">
@@ -8622,10 +8628,10 @@
         <v>815</v>
       </c>
       <c r="C379" s="0" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="D379" s="0">
-        <v>249069.69</v>
+        <v>207558.08</v>
       </c>
     </row>
     <row r="380">
@@ -8636,10 +8642,10 @@
         <v>817</v>
       </c>
       <c r="C380" s="0" t="s">
-        <v>70</v>
+        <v>472</v>
       </c>
       <c r="D380" s="0">
-        <v>10522</v>
+        <v>249069.69</v>
       </c>
     </row>
     <row r="381">
@@ -8653,7 +8659,7 @@
         <v>70</v>
       </c>
       <c r="D381" s="0">
-        <v>19481</v>
+        <v>10522</v>
       </c>
     </row>
     <row r="382">
@@ -8664,24 +8670,24 @@
         <v>821</v>
       </c>
       <c r="C382" s="0" t="s">
-        <v>822</v>
+        <v>70</v>
       </c>
       <c r="D382" s="0">
-        <v>1080</v>
+        <v>19481</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" s="0" t="s">
+        <v>822</v>
+      </c>
+      <c r="B383" s="0" t="s">
         <v>823</v>
       </c>
-      <c r="B383" s="0" t="s">
+      <c r="C383" s="0" t="s">
         <v>824</v>
       </c>
-      <c r="C383" s="0" t="s">
-        <v>18</v>
-      </c>
       <c r="D383" s="0">
-        <v>586.49</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="384">
@@ -8692,24 +8698,24 @@
         <v>826</v>
       </c>
       <c r="C384" s="0" t="s">
-        <v>827</v>
+        <v>18</v>
       </c>
       <c r="D384" s="0">
-        <v>520</v>
+        <v>586.49</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" s="0" t="s">
+        <v>827</v>
+      </c>
+      <c r="B385" s="0" t="s">
         <v>828</v>
       </c>
-      <c r="B385" s="0" t="s">
+      <c r="C385" s="0" t="s">
         <v>829</v>
       </c>
-      <c r="C385" s="0" t="s">
-        <v>827</v>
-      </c>
       <c r="D385" s="0">
-        <v>300</v>
+        <v>520</v>
       </c>
     </row>
     <row r="386">
@@ -8720,10 +8726,10 @@
         <v>831</v>
       </c>
       <c r="C386" s="0" t="s">
-        <v>15</v>
+        <v>829</v>
       </c>
       <c r="D386" s="0">
-        <v>2200</v>
+        <v>300</v>
       </c>
     </row>
     <row r="387">
@@ -8737,7 +8743,7 @@
         <v>15</v>
       </c>
       <c r="D387" s="0">
-        <v>2800</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="388">
@@ -8748,10 +8754,10 @@
         <v>835</v>
       </c>
       <c r="C388" s="0" t="s">
-        <v>92</v>
+        <v>15</v>
       </c>
       <c r="D388" s="0">
-        <v>5190.9</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="389">
@@ -8762,10 +8768,10 @@
         <v>837</v>
       </c>
       <c r="C389" s="0" t="s">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="D389" s="0">
-        <v>2969</v>
+        <v>5190.9</v>
       </c>
     </row>
     <row r="390">
@@ -8776,10 +8782,10 @@
         <v>839</v>
       </c>
       <c r="C390" s="0" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="D390" s="0">
-        <v>3800</v>
+        <v>2969</v>
       </c>
     </row>
     <row r="391">
@@ -8790,10 +8796,10 @@
         <v>841</v>
       </c>
       <c r="C391" s="0" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="D391" s="0">
-        <v>4000</v>
+        <v>3800</v>
       </c>
     </row>
     <row r="392">
@@ -8804,24 +8810,24 @@
         <v>843</v>
       </c>
       <c r="C392" s="0" t="s">
-        <v>844</v>
+        <v>15</v>
       </c>
       <c r="D392" s="0">
-        <v>3800</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" s="0" t="s">
+        <v>844</v>
+      </c>
+      <c r="B393" s="0" t="s">
         <v>845</v>
       </c>
-      <c r="B393" s="0" t="s">
+      <c r="C393" s="0" t="s">
         <v>846</v>
       </c>
-      <c r="C393" s="0" t="s">
-        <v>21</v>
-      </c>
       <c r="D393" s="0">
-        <v>353</v>
+        <v>3800</v>
       </c>
     </row>
     <row r="394">
@@ -8832,10 +8838,10 @@
         <v>848</v>
       </c>
       <c r="C394" s="0" t="s">
-        <v>110</v>
+        <v>21</v>
       </c>
       <c r="D394" s="0">
-        <v>1800</v>
+        <v>353</v>
       </c>
     </row>
     <row r="395">
@@ -8846,10 +8852,10 @@
         <v>850</v>
       </c>
       <c r="C395" s="0" t="s">
-        <v>15</v>
+        <v>110</v>
       </c>
       <c r="D395" s="0">
-        <v>2948</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="396">
@@ -8860,10 +8866,10 @@
         <v>852</v>
       </c>
       <c r="C396" s="0" t="s">
-        <v>92</v>
+        <v>15</v>
       </c>
       <c r="D396" s="0">
-        <v>146.41</v>
+        <v>2948</v>
       </c>
     </row>
     <row r="397">
@@ -8874,10 +8880,10 @@
         <v>854</v>
       </c>
       <c r="C397" s="0" t="s">
-        <v>207</v>
+        <v>92</v>
       </c>
       <c r="D397" s="0">
-        <v>65537</v>
+        <v>146.41</v>
       </c>
     </row>
     <row r="398">
@@ -8888,10 +8894,10 @@
         <v>856</v>
       </c>
       <c r="C398" s="0" t="s">
-        <v>140</v>
+        <v>210</v>
       </c>
       <c r="D398" s="0">
-        <v>4130.4</v>
+        <v>65537</v>
       </c>
     </row>
     <row r="399">
@@ -8905,7 +8911,7 @@
         <v>140</v>
       </c>
       <c r="D399" s="0">
-        <v>4283</v>
+        <v>4130.4</v>
       </c>
     </row>
     <row r="400">
@@ -8919,7 +8925,7 @@
         <v>140</v>
       </c>
       <c r="D400" s="0">
-        <v>6524.8</v>
+        <v>4283</v>
       </c>
     </row>
     <row r="401">
@@ -8930,10 +8936,10 @@
         <v>862</v>
       </c>
       <c r="C401" s="0" t="s">
-        <v>308</v>
+        <v>140</v>
       </c>
       <c r="D401" s="0">
-        <v>570</v>
+        <v>6524.8</v>
       </c>
     </row>
     <row r="402">
@@ -8944,10 +8950,10 @@
         <v>864</v>
       </c>
       <c r="C402" s="0" t="s">
-        <v>70</v>
+        <v>311</v>
       </c>
       <c r="D402" s="0">
-        <v>550</v>
+        <v>570</v>
       </c>
     </row>
     <row r="403">
@@ -8958,10 +8964,10 @@
         <v>866</v>
       </c>
       <c r="C403" s="0" t="s">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="D403" s="0">
-        <v>153</v>
+        <v>550</v>
       </c>
     </row>
     <row r="404">
@@ -8972,10 +8978,10 @@
         <v>868</v>
       </c>
       <c r="C404" s="0" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="D404" s="0">
-        <v>740.7</v>
+        <v>153</v>
       </c>
     </row>
     <row r="405">
@@ -8986,10 +8992,10 @@
         <v>870</v>
       </c>
       <c r="C405" s="0" t="s">
-        <v>59</v>
+        <v>28</v>
       </c>
       <c r="D405" s="0">
-        <v>101000</v>
+        <v>740.7</v>
       </c>
     </row>
     <row r="406">
@@ -9000,10 +9006,10 @@
         <v>872</v>
       </c>
       <c r="C406" s="0" t="s">
-        <v>123</v>
+        <v>59</v>
       </c>
       <c r="D406" s="0">
-        <v>6251</v>
+        <v>101000</v>
       </c>
     </row>
     <row r="407">
@@ -9014,10 +9020,10 @@
         <v>874</v>
       </c>
       <c r="C407" s="0" t="s">
-        <v>140</v>
+        <v>123</v>
       </c>
       <c r="D407" s="0">
-        <v>857.67</v>
+        <v>6251</v>
       </c>
     </row>
     <row r="408">
@@ -9028,10 +9034,10 @@
         <v>876</v>
       </c>
       <c r="C408" s="0" t="s">
-        <v>92</v>
+        <v>140</v>
       </c>
       <c r="D408" s="0">
-        <v>1164.66</v>
+        <v>857.67</v>
       </c>
     </row>
     <row r="409">
@@ -9042,10 +9048,10 @@
         <v>878</v>
       </c>
       <c r="C409" s="0" t="s">
-        <v>151</v>
+        <v>92</v>
       </c>
       <c r="D409" s="0">
-        <v>360</v>
+        <v>1164.66</v>
       </c>
     </row>
     <row r="410">
@@ -9059,7 +9065,7 @@
         <v>151</v>
       </c>
       <c r="D410" s="0">
-        <v>450</v>
+        <v>360</v>
       </c>
     </row>
     <row r="411">
@@ -9073,7 +9079,7 @@
         <v>151</v>
       </c>
       <c r="D411" s="0">
-        <v>2150</v>
+        <v>450</v>
       </c>
     </row>
     <row r="412">
@@ -9084,10 +9090,10 @@
         <v>884</v>
       </c>
       <c r="C412" s="0" t="s">
-        <v>580</v>
+        <v>151</v>
       </c>
       <c r="D412" s="0">
-        <v>25192.82</v>
+        <v>2150</v>
       </c>
     </row>
     <row r="413">
@@ -9098,10 +9104,10 @@
         <v>886</v>
       </c>
       <c r="C413" s="0" t="s">
-        <v>70</v>
+        <v>582</v>
       </c>
       <c r="D413" s="0">
-        <v>3500</v>
+        <v>25192.82</v>
       </c>
     </row>
     <row r="414">
@@ -9112,10 +9118,10 @@
         <v>888</v>
       </c>
       <c r="C414" s="0" t="s">
-        <v>175</v>
+        <v>70</v>
       </c>
       <c r="D414" s="0">
-        <v>600</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="415">
@@ -9126,24 +9132,24 @@
         <v>890</v>
       </c>
       <c r="C415" s="0" t="s">
-        <v>891</v>
+        <v>175</v>
       </c>
       <c r="D415" s="0">
-        <v>1080</v>
+        <v>600</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" s="0" t="s">
+        <v>891</v>
+      </c>
+      <c r="B416" s="0" t="s">
         <v>892</v>
       </c>
-      <c r="B416" s="0" t="s">
+      <c r="C416" s="0" t="s">
         <v>893</v>
       </c>
-      <c r="C416" s="0" t="s">
-        <v>338</v>
-      </c>
       <c r="D416" s="0">
-        <v>8628</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="417">
@@ -9154,10 +9160,10 @@
         <v>895</v>
       </c>
       <c r="C417" s="0" t="s">
-        <v>40</v>
+        <v>341</v>
       </c>
       <c r="D417" s="0">
-        <v>27991.54</v>
+        <v>8628</v>
       </c>
     </row>
     <row r="418">
@@ -9168,10 +9174,10 @@
         <v>897</v>
       </c>
       <c r="C418" s="0" t="s">
-        <v>140</v>
+        <v>40</v>
       </c>
       <c r="D418" s="0">
-        <v>1020</v>
+        <v>27991.54</v>
       </c>
     </row>
     <row r="419">
@@ -9185,7 +9191,7 @@
         <v>140</v>
       </c>
       <c r="D419" s="0">
-        <v>4106</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="420">
@@ -9196,10 +9202,10 @@
         <v>901</v>
       </c>
       <c r="C420" s="0" t="s">
-        <v>281</v>
+        <v>140</v>
       </c>
       <c r="D420" s="0">
-        <v>450</v>
+        <v>4106</v>
       </c>
     </row>
     <row r="421">
@@ -9210,10 +9216,10 @@
         <v>903</v>
       </c>
       <c r="C421" s="0" t="s">
-        <v>45</v>
+        <v>284</v>
       </c>
       <c r="D421" s="0">
-        <v>6344.43</v>
+        <v>450</v>
       </c>
     </row>
     <row r="422">
@@ -9227,7 +9233,7 @@
         <v>45</v>
       </c>
       <c r="D422" s="0">
-        <v>2862.28</v>
+        <v>6344.43</v>
       </c>
     </row>
     <row r="423">
@@ -9241,7 +9247,7 @@
         <v>45</v>
       </c>
       <c r="D423" s="0">
-        <v>2131.18</v>
+        <v>2862.28</v>
       </c>
     </row>
     <row r="424">
@@ -9255,7 +9261,7 @@
         <v>45</v>
       </c>
       <c r="D424" s="0">
-        <v>29795.68</v>
+        <v>2131.18</v>
       </c>
     </row>
     <row r="425">
@@ -9269,7 +9275,7 @@
         <v>45</v>
       </c>
       <c r="D425" s="0">
-        <v>2307.09</v>
+        <v>29795.68</v>
       </c>
     </row>
     <row r="426">
@@ -9283,7 +9289,7 @@
         <v>45</v>
       </c>
       <c r="D426" s="0">
-        <v>5249.48</v>
+        <v>2307.09</v>
       </c>
     </row>
     <row r="427">
@@ -9297,7 +9303,7 @@
         <v>45</v>
       </c>
       <c r="D427" s="0">
-        <v>4708</v>
+        <v>5249.48</v>
       </c>
     </row>
     <row r="428">
@@ -9308,10 +9314,10 @@
         <v>917</v>
       </c>
       <c r="C428" s="0" t="s">
-        <v>478</v>
+        <v>45</v>
       </c>
       <c r="D428" s="0">
-        <v>510</v>
+        <v>4708</v>
       </c>
     </row>
     <row r="429">
@@ -9322,7 +9328,7 @@
         <v>919</v>
       </c>
       <c r="C429" s="0" t="s">
-        <v>37</v>
+        <v>207</v>
       </c>
       <c r="D429" s="0">
         <v>510</v>
@@ -9336,21 +9342,21 @@
         <v>921</v>
       </c>
       <c r="C430" s="0" t="s">
-        <v>922</v>
+        <v>37</v>
       </c>
       <c r="D430" s="0">
-        <v>626</v>
+        <v>510</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" s="0" t="s">
+        <v>922</v>
+      </c>
+      <c r="B431" s="0" t="s">
         <v>923</v>
       </c>
-      <c r="B431" s="0" t="s">
+      <c r="C431" s="0" t="s">
         <v>924</v>
-      </c>
-      <c r="C431" s="0" t="s">
-        <v>922</v>
       </c>
       <c r="D431" s="0">
         <v>626</v>
@@ -9364,7 +9370,7 @@
         <v>926</v>
       </c>
       <c r="C432" s="0" t="s">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="D432" s="0">
         <v>626</v>
@@ -9378,10 +9384,10 @@
         <v>928</v>
       </c>
       <c r="C433" s="0" t="s">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="D433" s="0">
-        <v>342</v>
+        <v>626</v>
       </c>
     </row>
     <row r="434">
@@ -9392,7 +9398,7 @@
         <v>930</v>
       </c>
       <c r="C434" s="0" t="s">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="D434" s="0">
         <v>342</v>
@@ -9406,7 +9412,7 @@
         <v>932</v>
       </c>
       <c r="C435" s="0" t="s">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="D435" s="0">
         <v>342</v>
@@ -9420,10 +9426,10 @@
         <v>934</v>
       </c>
       <c r="C436" s="0" t="s">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="D436" s="0">
-        <v>0</v>
+        <v>342</v>
       </c>
     </row>
     <row r="437">
@@ -9434,7 +9440,7 @@
         <v>936</v>
       </c>
       <c r="C437" s="0" t="s">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="D437" s="0">
         <v>0</v>
@@ -9448,21 +9454,21 @@
         <v>938</v>
       </c>
       <c r="C438" s="0" t="s">
-        <v>939</v>
+        <v>924</v>
       </c>
       <c r="D438" s="0">
-        <v>453</v>
+        <v>0</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" s="0" t="s">
+        <v>939</v>
+      </c>
+      <c r="B439" s="0" t="s">
         <v>940</v>
       </c>
-      <c r="B439" s="0" t="s">
+      <c r="C439" s="0" t="s">
         <v>941</v>
-      </c>
-      <c r="C439" s="0" t="s">
-        <v>922</v>
       </c>
       <c r="D439" s="0">
         <v>453</v>
@@ -9476,10 +9482,10 @@
         <v>943</v>
       </c>
       <c r="C440" s="0" t="s">
-        <v>70</v>
+        <v>924</v>
       </c>
       <c r="D440" s="0">
-        <v>19322</v>
+        <v>453</v>
       </c>
     </row>
     <row r="441">
@@ -9490,10 +9496,10 @@
         <v>945</v>
       </c>
       <c r="C441" s="0" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="D441" s="0">
-        <v>430</v>
+        <v>19322</v>
       </c>
     </row>
     <row r="442">
@@ -9504,7 +9510,7 @@
         <v>947</v>
       </c>
       <c r="C442" s="0" t="s">
-        <v>281</v>
+        <v>34</v>
       </c>
       <c r="D442" s="0">
         <v>430</v>
@@ -9518,10 +9524,10 @@
         <v>949</v>
       </c>
       <c r="C443" s="0" t="s">
-        <v>115</v>
+        <v>284</v>
       </c>
       <c r="D443" s="0">
-        <v>14000</v>
+        <v>430</v>
       </c>
     </row>
     <row r="444">
@@ -9532,10 +9538,10 @@
         <v>951</v>
       </c>
       <c r="C444" s="0" t="s">
-        <v>140</v>
+        <v>115</v>
       </c>
       <c r="D444" s="0">
-        <v>15400</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="445">
@@ -9549,7 +9555,7 @@
         <v>140</v>
       </c>
       <c r="D445" s="0">
-        <v>3340</v>
+        <v>15400</v>
       </c>
     </row>
     <row r="446">
@@ -9560,10 +9566,10 @@
         <v>955</v>
       </c>
       <c r="C446" s="0" t="s">
-        <v>92</v>
+        <v>140</v>
       </c>
       <c r="D446" s="0">
-        <v>266200</v>
+        <v>3340</v>
       </c>
     </row>
     <row r="447">
@@ -9577,7 +9583,7 @@
         <v>92</v>
       </c>
       <c r="D447" s="0">
-        <v>194991.5</v>
+        <v>266200</v>
       </c>
     </row>
     <row r="448">
@@ -9591,7 +9597,7 @@
         <v>92</v>
       </c>
       <c r="D448" s="0">
-        <v>289492.5</v>
+        <v>194991.5</v>
       </c>
     </row>
     <row r="449">
@@ -9602,24 +9608,24 @@
         <v>961</v>
       </c>
       <c r="C449" s="0" t="s">
-        <v>962</v>
+        <v>92</v>
       </c>
       <c r="D449" s="0">
-        <v>13722.52</v>
+        <v>289492.5</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" s="0" t="s">
+        <v>962</v>
+      </c>
+      <c r="B450" s="0" t="s">
         <v>963</v>
       </c>
-      <c r="B450" s="0" t="s">
+      <c r="C450" s="0" t="s">
         <v>964</v>
       </c>
-      <c r="C450" s="0" t="s">
-        <v>962</v>
-      </c>
       <c r="D450" s="0">
-        <v>15072</v>
+        <v>13722.52</v>
       </c>
     </row>
     <row r="451">
@@ -9630,10 +9636,10 @@
         <v>966</v>
       </c>
       <c r="C451" s="0" t="s">
-        <v>962</v>
+        <v>964</v>
       </c>
       <c r="D451" s="0">
-        <v>6555.64</v>
+        <v>15072</v>
       </c>
     </row>
     <row r="452">
@@ -9644,10 +9650,10 @@
         <v>968</v>
       </c>
       <c r="C452" s="0" t="s">
-        <v>962</v>
+        <v>964</v>
       </c>
       <c r="D452" s="0">
-        <v>8964.61</v>
+        <v>6555.64</v>
       </c>
     </row>
     <row r="453">
@@ -9658,10 +9664,10 @@
         <v>970</v>
       </c>
       <c r="C453" s="0" t="s">
-        <v>962</v>
+        <v>964</v>
       </c>
       <c r="D453" s="0">
-        <v>11735</v>
+        <v>8964.61</v>
       </c>
     </row>
     <row r="454">
@@ -9672,10 +9678,10 @@
         <v>972</v>
       </c>
       <c r="C454" s="0" t="s">
-        <v>70</v>
+        <v>964</v>
       </c>
       <c r="D454" s="0">
-        <v>4276</v>
+        <v>11735</v>
       </c>
     </row>
     <row r="455">
@@ -9686,10 +9692,10 @@
         <v>974</v>
       </c>
       <c r="C455" s="0" t="s">
-        <v>140</v>
+        <v>70</v>
       </c>
       <c r="D455" s="0">
-        <v>3930</v>
+        <v>4276</v>
       </c>
     </row>
     <row r="456">
@@ -9700,10 +9706,10 @@
         <v>976</v>
       </c>
       <c r="C456" s="0" t="s">
-        <v>92</v>
+        <v>140</v>
       </c>
       <c r="D456" s="0">
-        <v>4392.3</v>
+        <v>3930</v>
       </c>
     </row>
     <row r="457">
@@ -9714,24 +9720,24 @@
         <v>978</v>
       </c>
       <c r="C457" s="0" t="s">
-        <v>979</v>
+        <v>92</v>
       </c>
       <c r="D457" s="0">
-        <v>5254.41</v>
+        <v>4392.3</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" s="0" t="s">
+        <v>979</v>
+      </c>
+      <c r="B458" s="0" t="s">
         <v>980</v>
       </c>
-      <c r="B458" s="0" t="s">
+      <c r="C458" s="0" t="s">
         <v>981</v>
       </c>
-      <c r="C458" s="0" t="s">
-        <v>52</v>
-      </c>
       <c r="D458" s="0">
-        <v>1297</v>
+        <v>5254.41</v>
       </c>
     </row>
     <row r="459">
@@ -9745,7 +9751,7 @@
         <v>52</v>
       </c>
       <c r="D459" s="0">
-        <v>298</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="460">
@@ -9759,7 +9765,7 @@
         <v>52</v>
       </c>
       <c r="D460" s="0">
-        <v>596</v>
+        <v>298</v>
       </c>
     </row>
     <row r="461">
@@ -9770,10 +9776,10 @@
         <v>987</v>
       </c>
       <c r="C461" s="0" t="s">
-        <v>376</v>
+        <v>52</v>
       </c>
       <c r="D461" s="0">
-        <v>65142.6</v>
+        <v>596</v>
       </c>
     </row>
     <row r="462">
@@ -9784,10 +9790,10 @@
         <v>989</v>
       </c>
       <c r="C462" s="0" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="D462" s="0">
-        <v>23482.7</v>
+        <v>65142.6</v>
       </c>
     </row>
     <row r="463">
@@ -9798,10 +9804,10 @@
         <v>991</v>
       </c>
       <c r="C463" s="0" t="s">
-        <v>28</v>
+        <v>379</v>
       </c>
       <c r="D463" s="0">
-        <v>6029.59</v>
+        <v>23482.7</v>
       </c>
     </row>
     <row r="464">
@@ -9812,10 +9818,10 @@
         <v>993</v>
       </c>
       <c r="C464" s="0" t="s">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="D464" s="0">
-        <v>12000</v>
+        <v>6029.59</v>
       </c>
     </row>
     <row r="465">
@@ -9829,7 +9835,7 @@
         <v>52</v>
       </c>
       <c r="D465" s="0">
-        <v>17425</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="466">
@@ -9840,66 +9846,66 @@
         <v>997</v>
       </c>
       <c r="C466" s="0" t="s">
-        <v>998</v>
+        <v>52</v>
       </c>
       <c r="D466" s="0">
-        <v>1958</v>
+        <v>17425</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" s="0" t="s">
+        <v>998</v>
+      </c>
+      <c r="B467" s="0" t="s">
         <v>999</v>
       </c>
-      <c r="B467" s="0" t="s">
+      <c r="C467" s="0" t="s">
         <v>1000</v>
       </c>
-      <c r="C467" s="0" t="s">
-        <v>1001</v>
-      </c>
       <c r="D467" s="0">
-        <v>2282.3</v>
+        <v>1958</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" s="0" t="s">
+        <v>1001</v>
+      </c>
+      <c r="B468" s="0" t="s">
         <v>1002</v>
       </c>
-      <c r="B468" s="0" t="s">
+      <c r="C468" s="0" t="s">
         <v>1003</v>
       </c>
-      <c r="C468" s="0" t="s">
-        <v>1004</v>
-      </c>
       <c r="D468" s="0">
-        <v>386</v>
+        <v>2282.3</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" s="0" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B469" s="0" t="s">
         <v>1005</v>
       </c>
-      <c r="B469" s="0" t="s">
+      <c r="C469" s="0" t="s">
         <v>1006</v>
       </c>
-      <c r="C469" s="0" t="s">
-        <v>1007</v>
-      </c>
       <c r="D469" s="0">
-        <v>385.4</v>
+        <v>386</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" s="0" t="s">
+        <v>1007</v>
+      </c>
+      <c r="B470" s="0" t="s">
         <v>1008</v>
       </c>
-      <c r="B470" s="0" t="s">
+      <c r="C470" s="0" t="s">
         <v>1009</v>
       </c>
-      <c r="C470" s="0" t="s">
-        <v>92</v>
-      </c>
       <c r="D470" s="0">
-        <v>296147.5</v>
+        <v>385.4</v>
       </c>
     </row>
     <row r="471">
@@ -9910,10 +9916,10 @@
         <v>1011</v>
       </c>
       <c r="C471" s="0" t="s">
-        <v>123</v>
+        <v>92</v>
       </c>
       <c r="D471" s="0">
-        <v>1890</v>
+        <v>296147.5</v>
       </c>
     </row>
     <row r="472">
@@ -9924,10 +9930,10 @@
         <v>1013</v>
       </c>
       <c r="C472" s="0" t="s">
-        <v>580</v>
+        <v>123</v>
       </c>
       <c r="D472" s="0">
-        <v>71176.4</v>
+        <v>1890</v>
       </c>
     </row>
     <row r="473">
@@ -9938,10 +9944,10 @@
         <v>1015</v>
       </c>
       <c r="C473" s="0" t="s">
-        <v>140</v>
+        <v>582</v>
       </c>
       <c r="D473" s="0">
-        <v>87</v>
+        <v>71176.4</v>
       </c>
     </row>
     <row r="474">
@@ -9952,10 +9958,10 @@
         <v>1017</v>
       </c>
       <c r="C474" s="0" t="s">
-        <v>70</v>
+        <v>140</v>
       </c>
       <c r="D474" s="0">
-        <v>950</v>
+        <v>89</v>
       </c>
     </row>
     <row r="475">
@@ -9966,10 +9972,10 @@
         <v>1019</v>
       </c>
       <c r="C475" s="0" t="s">
-        <v>469</v>
+        <v>70</v>
       </c>
       <c r="D475" s="0">
-        <v>342641</v>
+        <v>950</v>
       </c>
     </row>
     <row r="476">
@@ -9980,10 +9986,10 @@
         <v>1021</v>
       </c>
       <c r="C476" s="0" t="s">
-        <v>160</v>
+        <v>472</v>
       </c>
       <c r="D476" s="0">
-        <v>2200</v>
+        <v>342641</v>
       </c>
     </row>
     <row r="477">
@@ -9994,10 +10000,10 @@
         <v>1023</v>
       </c>
       <c r="C477" s="0" t="s">
-        <v>478</v>
+        <v>160</v>
       </c>
       <c r="D477" s="0">
-        <v>41000</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="478">
@@ -10008,10 +10014,10 @@
         <v>1025</v>
       </c>
       <c r="C478" s="0" t="s">
-        <v>70</v>
+        <v>207</v>
       </c>
       <c r="D478" s="0">
-        <v>5790</v>
+        <v>41000</v>
       </c>
     </row>
     <row r="479">
@@ -10022,10 +10028,10 @@
         <v>1027</v>
       </c>
       <c r="C479" s="0" t="s">
-        <v>922</v>
+        <v>70</v>
       </c>
       <c r="D479" s="0">
-        <v>880</v>
+        <v>5790</v>
       </c>
     </row>
     <row r="480">
@@ -10036,7 +10042,7 @@
         <v>1029</v>
       </c>
       <c r="C480" s="0" t="s">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="D480" s="0">
         <v>880</v>
@@ -10050,7 +10056,7 @@
         <v>1031</v>
       </c>
       <c r="C481" s="0" t="s">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="D481" s="0">
         <v>880</v>
@@ -10064,10 +10070,10 @@
         <v>1033</v>
       </c>
       <c r="C482" s="0" t="s">
-        <v>21</v>
+        <v>924</v>
       </c>
       <c r="D482" s="0">
-        <v>563.36</v>
+        <v>880</v>
       </c>
     </row>
     <row r="483">
@@ -10078,10 +10084,10 @@
         <v>1035</v>
       </c>
       <c r="C483" s="0" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D483" s="0">
-        <v>3520</v>
+        <v>563.36</v>
       </c>
     </row>
     <row r="484">
@@ -10095,7 +10101,7 @@
         <v>15</v>
       </c>
       <c r="D484" s="0">
-        <v>2600</v>
+        <v>3520</v>
       </c>
     </row>
     <row r="485">
@@ -10106,10 +10112,10 @@
         <v>1039</v>
       </c>
       <c r="C485" s="0" t="s">
-        <v>281</v>
+        <v>15</v>
       </c>
       <c r="D485" s="0">
-        <v>3700</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="486">
@@ -10120,10 +10126,10 @@
         <v>1041</v>
       </c>
       <c r="C486" s="0" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="D486" s="0">
-        <v>2600</v>
+        <v>3700</v>
       </c>
     </row>
     <row r="487">
@@ -10134,10 +10140,10 @@
         <v>1043</v>
       </c>
       <c r="C487" s="0" t="s">
-        <v>15</v>
+        <v>284</v>
       </c>
       <c r="D487" s="0">
-        <v>2235</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="488">
@@ -10151,7 +10157,7 @@
         <v>15</v>
       </c>
       <c r="D488" s="0">
-        <v>3850</v>
+        <v>2235</v>
       </c>
     </row>
     <row r="489">
@@ -10162,24 +10168,24 @@
         <v>1047</v>
       </c>
       <c r="C489" s="0" t="s">
-        <v>1048</v>
+        <v>15</v>
       </c>
       <c r="D489" s="0">
-        <v>1</v>
+        <v>3850</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" s="0" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B490" s="0" t="s">
         <v>1049</v>
       </c>
-      <c r="B490" s="0" t="s">
+      <c r="C490" s="0" t="s">
         <v>1050</v>
       </c>
-      <c r="C490" s="0" t="s">
-        <v>28</v>
-      </c>
       <c r="D490" s="0">
-        <v>15189</v>
+        <v>1</v>
       </c>
     </row>
     <row r="491">
@@ -10190,10 +10196,10 @@
         <v>1052</v>
       </c>
       <c r="C491" s="0" t="s">
-        <v>376</v>
+        <v>28</v>
       </c>
       <c r="D491" s="0">
-        <v>3859.93</v>
+        <v>15189</v>
       </c>
     </row>
     <row r="492">
@@ -10204,10 +10210,10 @@
         <v>1054</v>
       </c>
       <c r="C492" s="0" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="D492" s="0">
-        <v>11751.49</v>
+        <v>3859.93</v>
       </c>
     </row>
     <row r="493">
@@ -10218,10 +10224,10 @@
         <v>1056</v>
       </c>
       <c r="C493" s="0" t="s">
-        <v>338</v>
+        <v>379</v>
       </c>
       <c r="D493" s="0">
-        <v>6000</v>
+        <v>11751.49</v>
       </c>
     </row>
     <row r="494">
@@ -10232,10 +10238,10 @@
         <v>1058</v>
       </c>
       <c r="C494" s="0" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="D494" s="0">
-        <v>3000</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="495">
@@ -10246,10 +10252,10 @@
         <v>1060</v>
       </c>
       <c r="C495" s="0" t="s">
-        <v>37</v>
+        <v>341</v>
       </c>
       <c r="D495" s="0">
-        <v>618</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="496">
@@ -10260,24 +10266,24 @@
         <v>1062</v>
       </c>
       <c r="C496" s="0" t="s">
-        <v>1063</v>
+        <v>37</v>
       </c>
       <c r="D496" s="0">
-        <v>24600</v>
+        <v>618</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" s="0" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B497" s="0" t="s">
         <v>1064</v>
       </c>
-      <c r="B497" s="0" t="s">
+      <c r="C497" s="0" t="s">
         <v>1065</v>
       </c>
-      <c r="C497" s="0" t="s">
-        <v>105</v>
-      </c>
       <c r="D497" s="0">
-        <v>0</v>
+        <v>24600</v>
       </c>
     </row>
     <row r="498">
@@ -10288,10 +10294,10 @@
         <v>1067</v>
       </c>
       <c r="C498" s="0" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="D498" s="0">
-        <v>43590.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="499">
@@ -10302,10 +10308,10 @@
         <v>1069</v>
       </c>
       <c r="C499" s="0" t="s">
-        <v>469</v>
+        <v>92</v>
       </c>
       <c r="D499" s="0">
-        <v>207558.07</v>
+        <v>43590.25</v>
       </c>
     </row>
     <row r="500">
@@ -10316,10 +10322,10 @@
         <v>1071</v>
       </c>
       <c r="C500" s="0" t="s">
-        <v>376</v>
+        <v>472</v>
       </c>
       <c r="D500" s="0">
-        <v>77429.29</v>
+        <v>207558.07</v>
       </c>
     </row>
     <row r="501">
@@ -10330,10 +10336,10 @@
         <v>1073</v>
       </c>
       <c r="C501" s="0" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="D501" s="0">
-        <v>42913.42</v>
+        <v>77429.29</v>
       </c>
     </row>
     <row r="502">
@@ -10344,10 +10350,10 @@
         <v>1075</v>
       </c>
       <c r="C502" s="0" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="D502" s="0">
-        <v>88806.25</v>
+        <v>42913.42</v>
       </c>
     </row>
     <row r="503">
@@ -10358,10 +10364,10 @@
         <v>1077</v>
       </c>
       <c r="C503" s="0" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="D503" s="0">
-        <v>50781.52</v>
+        <v>88806.25</v>
       </c>
     </row>
     <row r="504">
@@ -10372,10 +10378,10 @@
         <v>1079</v>
       </c>
       <c r="C504" s="0" t="s">
-        <v>21</v>
+        <v>379</v>
       </c>
       <c r="D504" s="0">
-        <v>1600</v>
+        <v>50781.52</v>
       </c>
     </row>
     <row r="505">
@@ -10386,10 +10392,10 @@
         <v>1081</v>
       </c>
       <c r="C505" s="0" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D505" s="0">
-        <v>3521.4</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="506">
@@ -10403,7 +10409,7 @@
         <v>28</v>
       </c>
       <c r="D506" s="0">
-        <v>3987</v>
+        <v>3521.4</v>
       </c>
     </row>
     <row r="507">
@@ -10417,7 +10423,7 @@
         <v>28</v>
       </c>
       <c r="D507" s="0">
-        <v>4086.37</v>
+        <v>3987</v>
       </c>
     </row>
     <row r="508">
@@ -10431,7 +10437,7 @@
         <v>28</v>
       </c>
       <c r="D508" s="0">
-        <v>3382.65</v>
+        <v>4086.37</v>
       </c>
     </row>
     <row r="509">
@@ -10442,10 +10448,10 @@
         <v>1089</v>
       </c>
       <c r="C509" s="0" t="s">
-        <v>160</v>
+        <v>28</v>
       </c>
       <c r="D509" s="0">
-        <v>430</v>
+        <v>3382.65</v>
       </c>
     </row>
     <row r="510">
@@ -10456,9 +10462,23 @@
         <v>1091</v>
       </c>
       <c r="C510" s="0" t="s">
+        <v>160</v>
+      </c>
+      <c r="D510" s="0">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" s="0" t="s">
+        <v>1092</v>
+      </c>
+      <c r="B511" s="0" t="s">
+        <v>1093</v>
+      </c>
+      <c r="C511" s="0" t="s">
         <v>140</v>
       </c>
-      <c r="D510" s="0">
+      <c r="D511" s="0">
         <v>465</v>
       </c>
     </row>

--- a/price_list.xlsx
+++ b/price_list.xlsx
@@ -4151,7 +4151,7 @@
         <v>140</v>
       </c>
       <c r="D59" s="0">
-        <v>489.8</v>
+        <v>500</v>
       </c>
     </row>
     <row r="60">
@@ -4333,7 +4333,7 @@
         <v>140</v>
       </c>
       <c r="D72" s="0">
-        <v>649</v>
+        <v>700</v>
       </c>
     </row>
     <row r="73">
@@ -4935,7 +4935,7 @@
         <v>140</v>
       </c>
       <c r="D115" s="0">
-        <v>993</v>
+        <v>970</v>
       </c>
     </row>
     <row r="116">
@@ -5159,7 +5159,7 @@
         <v>140</v>
       </c>
       <c r="D131" s="0">
-        <v>2800</v>
+        <v>3100</v>
       </c>
     </row>
     <row r="132">
@@ -5173,7 +5173,7 @@
         <v>140</v>
       </c>
       <c r="D132" s="0">
-        <v>6536</v>
+        <v>6700</v>
       </c>
     </row>
     <row r="133">
@@ -6307,7 +6307,7 @@
         <v>472</v>
       </c>
       <c r="D213" s="0">
-        <v>60630</v>
+        <v>70443</v>
       </c>
     </row>
     <row r="214">
@@ -6965,7 +6965,7 @@
         <v>140</v>
       </c>
       <c r="D260" s="0">
-        <v>430</v>
+        <v>446</v>
       </c>
     </row>
     <row r="261">
@@ -6979,7 +6979,7 @@
         <v>140</v>
       </c>
       <c r="D261" s="0">
-        <v>373</v>
+        <v>370</v>
       </c>
     </row>
     <row r="262">
@@ -7049,7 +7049,7 @@
         <v>582</v>
       </c>
       <c r="D266" s="0">
-        <v>177940.1</v>
+        <v>189016.25</v>
       </c>
     </row>
     <row r="267">
@@ -7091,7 +7091,7 @@
         <v>472</v>
       </c>
       <c r="D269" s="0">
-        <v>227939.52</v>
+        <v>243315</v>
       </c>
     </row>
     <row r="270">
@@ -7105,7 +7105,7 @@
         <v>472</v>
       </c>
       <c r="D270" s="0">
-        <v>184488.7</v>
+        <v>196835</v>
       </c>
     </row>
     <row r="271">
@@ -7497,7 +7497,7 @@
         <v>140</v>
       </c>
       <c r="D298" s="0">
-        <v>4590</v>
+        <v>4730</v>
       </c>
     </row>
     <row r="299">
@@ -7511,7 +7511,7 @@
         <v>140</v>
       </c>
       <c r="D299" s="0">
-        <v>2300</v>
+        <v>2517</v>
       </c>
     </row>
     <row r="300">
@@ -7525,7 +7525,7 @@
         <v>140</v>
       </c>
       <c r="D300" s="0">
-        <v>1150</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="301">
@@ -7693,7 +7693,7 @@
         <v>140</v>
       </c>
       <c r="D312" s="0">
-        <v>1250</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="313">
@@ -7987,7 +7987,7 @@
         <v>140</v>
       </c>
       <c r="D333" s="0">
-        <v>890</v>
+        <v>935</v>
       </c>
     </row>
     <row r="334">
@@ -8001,7 +8001,7 @@
         <v>140</v>
       </c>
       <c r="D334" s="0">
-        <v>594</v>
+        <v>620</v>
       </c>
     </row>
     <row r="335">
@@ -8015,7 +8015,7 @@
         <v>140</v>
       </c>
       <c r="D335" s="0">
-        <v>65</v>
+        <v>73</v>
       </c>
     </row>
     <row r="336">
@@ -8323,7 +8323,7 @@
         <v>140</v>
       </c>
       <c r="D357" s="0">
-        <v>350</v>
+        <v>365</v>
       </c>
     </row>
     <row r="358">
@@ -8631,7 +8631,7 @@
         <v>472</v>
       </c>
       <c r="D379" s="0">
-        <v>207558.08</v>
+        <v>213700</v>
       </c>
     </row>
     <row r="380">
@@ -8645,7 +8645,7 @@
         <v>472</v>
       </c>
       <c r="D380" s="0">
-        <v>249069.69</v>
+        <v>257000</v>
       </c>
     </row>
     <row r="381">
@@ -9037,7 +9037,7 @@
         <v>140</v>
       </c>
       <c r="D408" s="0">
-        <v>857.67</v>
+        <v>883</v>
       </c>
     </row>
     <row r="409">
@@ -9555,7 +9555,7 @@
         <v>140</v>
       </c>
       <c r="D445" s="0">
-        <v>15400</v>
+        <v>12049</v>
       </c>
     </row>
     <row r="446">
@@ -9569,7 +9569,7 @@
         <v>140</v>
       </c>
       <c r="D446" s="0">
-        <v>3340</v>
+        <v>2895</v>
       </c>
     </row>
     <row r="447">
@@ -9947,7 +9947,7 @@
         <v>582</v>
       </c>
       <c r="D473" s="0">
-        <v>71176.4</v>
+        <v>83000</v>
       </c>
     </row>
     <row r="474">
@@ -9961,7 +9961,7 @@
         <v>140</v>
       </c>
       <c r="D474" s="0">
-        <v>89</v>
+        <v>99</v>
       </c>
     </row>
     <row r="475">
@@ -9989,7 +9989,7 @@
         <v>472</v>
       </c>
       <c r="D476" s="0">
-        <v>342641</v>
+        <v>398107</v>
       </c>
     </row>
     <row r="477">
@@ -10325,7 +10325,7 @@
         <v>472</v>
       </c>
       <c r="D500" s="0">
-        <v>207558.07</v>
+        <v>213700</v>
       </c>
     </row>
     <row r="501">
@@ -10479,7 +10479,7 @@
         <v>140</v>
       </c>
       <c r="D511" s="0">
-        <v>465</v>
+        <v>495</v>
       </c>
     </row>
   </sheetData>

--- a/price_list.xlsx
+++ b/price_list.xlsx
@@ -3591,7 +3591,7 @@
         <v>45</v>
       </c>
       <c r="D19" s="0">
-        <v>3853.39</v>
+        <v>3958.98</v>
       </c>
     </row>
     <row r="20">
@@ -3619,7 +3619,7 @@
         <v>45</v>
       </c>
       <c r="D21" s="0">
-        <v>31996.8</v>
+        <v>32755.59</v>
       </c>
     </row>
     <row r="22">
@@ -4907,7 +4907,7 @@
         <v>45</v>
       </c>
       <c r="D113" s="0">
-        <v>5771.79</v>
+        <v>5660.43</v>
       </c>
     </row>
     <row r="114">
@@ -6125,7 +6125,7 @@
         <v>45</v>
       </c>
       <c r="D200" s="0">
-        <v>4729.48</v>
+        <v>6127.17</v>
       </c>
     </row>
     <row r="201">
@@ -8085,7 +8085,7 @@
         <v>45</v>
       </c>
       <c r="D340" s="0">
-        <v>5780.66</v>
+        <v>5726.32</v>
       </c>
     </row>
     <row r="341">
@@ -9233,7 +9233,7 @@
         <v>45</v>
       </c>
       <c r="D422" s="0">
-        <v>6344.43</v>
+        <v>6518.32</v>
       </c>
     </row>
     <row r="423">
@@ -9247,7 +9247,7 @@
         <v>45</v>
       </c>
       <c r="D423" s="0">
-        <v>2862.28</v>
+        <v>2940.72</v>
       </c>
     </row>
     <row r="424">
@@ -9261,7 +9261,7 @@
         <v>45</v>
       </c>
       <c r="D424" s="0">
-        <v>2131.18</v>
+        <v>2090.06</v>
       </c>
     </row>
     <row r="425">
@@ -9275,7 +9275,7 @@
         <v>45</v>
       </c>
       <c r="D425" s="0">
-        <v>29795.68</v>
+        <v>30612.7</v>
       </c>
     </row>
     <row r="426">
@@ -9289,7 +9289,7 @@
         <v>45</v>
       </c>
       <c r="D426" s="0">
-        <v>2307.09</v>
+        <v>2370.33</v>
       </c>
     </row>
     <row r="427">
@@ -9303,7 +9303,7 @@
         <v>45</v>
       </c>
       <c r="D427" s="0">
-        <v>5249.48</v>
+        <v>6550.3</v>
       </c>
     </row>
     <row r="428">
@@ -9317,7 +9317,7 @@
         <v>45</v>
       </c>
       <c r="D428" s="0">
-        <v>4708</v>
+        <v>5277.18</v>
       </c>
     </row>
     <row r="429">

--- a/price_list.xlsx
+++ b/price_list.xlsx
@@ -5383,7 +5383,7 @@
         <v>31</v>
       </c>
       <c r="D147" s="0">
-        <v>700</v>
+        <v>550</v>
       </c>
     </row>
     <row r="148">
@@ -5397,7 +5397,7 @@
         <v>70</v>
       </c>
       <c r="D148" s="0">
-        <v>700</v>
+        <v>550</v>
       </c>
     </row>
     <row r="149">
@@ -5411,7 +5411,7 @@
         <v>34</v>
       </c>
       <c r="D149" s="0">
-        <v>700</v>
+        <v>550</v>
       </c>
     </row>
     <row r="150">
@@ -5481,7 +5481,7 @@
         <v>34</v>
       </c>
       <c r="D154" s="0">
-        <v>400</v>
+        <v>380</v>
       </c>
     </row>
     <row r="155">
@@ -5495,7 +5495,7 @@
         <v>70</v>
       </c>
       <c r="D155" s="0">
-        <v>410</v>
+        <v>380</v>
       </c>
     </row>
     <row r="156">
@@ -5607,7 +5607,7 @@
         <v>34</v>
       </c>
       <c r="D163" s="0">
-        <v>650</v>
+        <v>550</v>
       </c>
     </row>
     <row r="164">
@@ -5621,7 +5621,7 @@
         <v>151</v>
       </c>
       <c r="D164" s="0">
-        <v>650</v>
+        <v>550</v>
       </c>
     </row>
     <row r="165">
@@ -5635,7 +5635,7 @@
         <v>15</v>
       </c>
       <c r="D165" s="0">
-        <v>650</v>
+        <v>550</v>
       </c>
     </row>
     <row r="166">
@@ -8043,7 +8043,7 @@
         <v>34</v>
       </c>
       <c r="D337" s="0">
-        <v>420</v>
+        <v>400</v>
       </c>
     </row>
     <row r="338">
@@ -8057,7 +8057,7 @@
         <v>362</v>
       </c>
       <c r="D338" s="0">
-        <v>418</v>
+        <v>400</v>
       </c>
     </row>
     <row r="339">

--- a/price_list.xlsx
+++ b/price_list.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1094" uniqueCount="1094">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1120" uniqueCount="1120">
   <si>
     <t>Solo Activos</t>
   </si>
@@ -185,6 +185,21 @@
     <t>AGUJA HIPOD 40X8 21GX1 1/2" X 1 - 000023736</t>
   </si>
   <si>
+    <t>DAG00510</t>
+  </si>
+  <si>
+    <t>AGUJA HIPODERMICA SM 21 G X 1 (40/8) X 1 - DAG00510</t>
+  </si>
+  <si>
+    <t>SM</t>
+  </si>
+  <si>
+    <t>DAG00520</t>
+  </si>
+  <si>
+    <t>AGUJA HIPODERMICA SM 25G X 5/8 (16/5) X 1 - DAG00520</t>
+  </si>
+  <si>
     <t>000023594</t>
   </si>
   <si>
@@ -1469,12 +1484,57 @@
     <t>GRIPABEN T DESC. LIMON Y MIEL SOBRES X 5 X 5G - 000024189</t>
   </si>
   <si>
+    <t>000024726</t>
+  </si>
+  <si>
+    <t>GUANTE DE EXAMEN DE LATEX SP TALLE L x 100 - 000024726</t>
+  </si>
+  <si>
+    <t>SP</t>
+  </si>
+  <si>
+    <t>DGE00515</t>
+  </si>
+  <si>
+    <t>GUANTE DE EXAMEN DE LATEX SP TALLE M X 100 - DGE00515</t>
+  </si>
+  <si>
+    <t>DGE00510</t>
+  </si>
+  <si>
+    <t>GUANTE DE EXAMEN DE LATEX SP TALLE S X 100 - DGE00510</t>
+  </si>
+  <si>
+    <t>000024727</t>
+  </si>
+  <si>
+    <t>GUANTE DE EXAMEN DE NITRILO TALLE L x 100 - SP - 000024727</t>
+  </si>
+  <si>
     <t>000024406</t>
   </si>
   <si>
     <t>GUANTE DE EXAMEN DE NITRILO TALLE M X 100 - 000024406</t>
   </si>
   <si>
+    <t>000024723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GUANTE DE LATEX CIRUGIA ESTERILES N° 6.5  X PAR - SM - 000024723</t>
+  </si>
+  <si>
+    <t>000024724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GUANTE DE LATEX CIRUGIA ESTERILES N° 8   X PAR - SM - 000024724</t>
+  </si>
+  <si>
+    <t>000024725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GUANTE DE LATEX CIRUGIA ESTERILES N° 8.5   X PAR - SM - 000024725</t>
+  </si>
+  <si>
     <t>000023840</t>
   </si>
   <si>
@@ -1808,6 +1868,12 @@
     <t>IOPAMIRON 370mg F.Amp. EV. AC. x 50ml - 000001888</t>
   </si>
   <si>
+    <t>DJE00530</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JERINGA  10 ML  X 1 - SM - DJE00530</t>
+  </si>
+  <si>
     <t>000024331</t>
   </si>
   <si>
@@ -1820,9 +1886,6 @@
     <t>JERINGA 1 ML X 1 - SM - DJE00515</t>
   </si>
   <si>
-    <t>SM</t>
-  </si>
-  <si>
     <t>000024702</t>
   </si>
   <si>
@@ -1838,6 +1901,9 @@
     <t>JERINGA 10 ML PISTON SIN LATEX EUROMIX - 000023732</t>
   </si>
   <si>
+    <t>JERINGA 10ML SM X 1 - DJE00530</t>
+  </si>
+  <si>
     <t>000023815</t>
   </si>
   <si>
@@ -1856,6 +1922,12 @@
     <t>JERINGA 5 ML PISTON SIN LATEX EUROMIX - 000023731</t>
   </si>
   <si>
+    <t>000024073</t>
+  </si>
+  <si>
+    <t>JERINGA 5 ML PISTON SIN LATEX SM - 000024073</t>
+  </si>
+  <si>
     <t>000011914</t>
   </si>
   <si>
@@ -2508,6 +2580,12 @@
   </si>
   <si>
     <t>PARACETAMOL TEVA 500MG X 10 - 100005448</t>
+  </si>
+  <si>
+    <t>000020410</t>
+  </si>
+  <si>
+    <t>PASMODINA COMPUESTA Amp. x 5ml - 000020410</t>
   </si>
   <si>
     <t>000003885</t>
@@ -3359,7 +3437,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A2:D511"/>
+  <dimension ref="A2:D524"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
@@ -3675,7 +3753,7 @@
         <v>59</v>
       </c>
       <c r="D25" s="0">
-        <v>42000</v>
+        <v>12.3</v>
       </c>
     </row>
     <row r="26">
@@ -3686,10 +3764,10 @@
         <v>61</v>
       </c>
       <c r="C26" s="0" t="s">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="D26" s="0">
-        <v>162.86</v>
+        <v>12.3</v>
       </c>
     </row>
     <row r="27">
@@ -3703,7 +3781,7 @@
         <v>64</v>
       </c>
       <c r="D27" s="0">
-        <v>2158.2</v>
+        <v>42000</v>
       </c>
     </row>
     <row r="28">
@@ -3714,38 +3792,38 @@
         <v>66</v>
       </c>
       <c r="C28" s="0" t="s">
-        <v>67</v>
+        <v>28</v>
       </c>
       <c r="D28" s="0">
-        <v>2220</v>
+        <v>162.86</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="0" t="s">
+        <v>67</v>
+      </c>
+      <c r="B29" s="0" t="s">
         <v>68</v>
       </c>
-      <c r="B29" s="0" t="s">
+      <c r="C29" s="0" t="s">
         <v>69</v>
       </c>
-      <c r="C29" s="0" t="s">
-        <v>70</v>
-      </c>
       <c r="D29" s="0">
-        <v>5126</v>
+        <v>2158.2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="B30" s="0" t="s">
         <v>71</v>
       </c>
-      <c r="B30" s="0" t="s">
+      <c r="C30" s="0" t="s">
         <v>72</v>
       </c>
-      <c r="C30" s="0" t="s">
-        <v>70</v>
-      </c>
       <c r="D30" s="0">
-        <v>14813</v>
+        <v>2220</v>
       </c>
     </row>
     <row r="31">
@@ -3756,66 +3834,66 @@
         <v>74</v>
       </c>
       <c r="C31" s="0" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D31" s="0">
-        <v>4454</v>
+        <v>5126</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="0" t="s">
+        <v>76</v>
+      </c>
+      <c r="B32" s="0" t="s">
+        <v>77</v>
+      </c>
+      <c r="C32" s="0" t="s">
         <v>75</v>
       </c>
-      <c r="B32" s="0" t="s">
-        <v>76</v>
-      </c>
-      <c r="C32" s="0" t="s">
-        <v>18</v>
-      </c>
       <c r="D32" s="0">
-        <v>9630.7</v>
+        <v>14813</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="0" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C33" s="0" t="s">
-        <v>18</v>
+        <v>75</v>
       </c>
       <c r="D33" s="0">
-        <v>11127.74</v>
+        <v>4454</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="0" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C34" s="0" t="s">
         <v>18</v>
       </c>
       <c r="D34" s="0">
-        <v>2463.98</v>
+        <v>9630.7</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="0" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B35" s="0" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C35" s="0" t="s">
-        <v>83</v>
+        <v>18</v>
       </c>
       <c r="D35" s="0">
-        <v>10520</v>
+        <v>11127.74</v>
       </c>
     </row>
     <row r="36">
@@ -3829,7 +3907,7 @@
         <v>18</v>
       </c>
       <c r="D36" s="0">
-        <v>7352.97</v>
+        <v>2463.98</v>
       </c>
     </row>
     <row r="37">
@@ -3840,18 +3918,18 @@
         <v>87</v>
       </c>
       <c r="C37" s="0" t="s">
-        <v>18</v>
+        <v>88</v>
       </c>
       <c r="D37" s="0">
-        <v>10700.78</v>
+        <v>10520</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="0" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B38" s="0" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C38" s="0" t="s">
         <v>18</v>
@@ -3862,16 +3940,16 @@
     </row>
     <row r="39">
       <c r="A39" s="0" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B39" s="0" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C39" s="0" t="s">
-        <v>92</v>
+        <v>18</v>
       </c>
       <c r="D39" s="0">
-        <v>22627</v>
+        <v>10700.78</v>
       </c>
     </row>
     <row r="40">
@@ -3882,10 +3960,10 @@
         <v>94</v>
       </c>
       <c r="C40" s="0" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D40" s="0">
-        <v>750</v>
+        <v>7352.97</v>
       </c>
     </row>
     <row r="41">
@@ -3896,66 +3974,66 @@
         <v>96</v>
       </c>
       <c r="C41" s="0" t="s">
-        <v>37</v>
+        <v>97</v>
       </c>
       <c r="D41" s="0">
-        <v>750</v>
+        <v>22627</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="0" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B42" s="0" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C42" s="0" t="s">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="D42" s="0">
-        <v>2000</v>
+        <v>750</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="0" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B43" s="0" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C43" s="0" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="D43" s="0">
-        <v>431</v>
+        <v>750</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="0" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B44" s="0" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C44" s="0" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="D44" s="0">
-        <v>450</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="0" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B45" s="0" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C45" s="0" t="s">
-        <v>105</v>
+        <v>21</v>
       </c>
       <c r="D45" s="0">
-        <v>1312</v>
+        <v>431</v>
       </c>
     </row>
     <row r="46">
@@ -3966,10 +4044,10 @@
         <v>107</v>
       </c>
       <c r="C46" s="0" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D46" s="0">
-        <v>2900</v>
+        <v>450</v>
       </c>
     </row>
     <row r="47">
@@ -3983,7 +4061,7 @@
         <v>110</v>
       </c>
       <c r="D47" s="0">
-        <v>2687.98</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="48">
@@ -3994,10 +4072,10 @@
         <v>112</v>
       </c>
       <c r="C48" s="0" t="s">
-        <v>92</v>
+        <v>15</v>
       </c>
       <c r="D48" s="0">
-        <v>4525.4</v>
+        <v>2900</v>
       </c>
     </row>
     <row r="49">
@@ -4022,24 +4100,24 @@
         <v>117</v>
       </c>
       <c r="C50" s="0" t="s">
-        <v>118</v>
+        <v>97</v>
       </c>
       <c r="D50" s="0">
-        <v>2200</v>
+        <v>4525.4</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="0" t="s">
+        <v>118</v>
+      </c>
+      <c r="B51" s="0" t="s">
         <v>119</v>
       </c>
-      <c r="B51" s="0" t="s">
+      <c r="C51" s="0" t="s">
         <v>120</v>
       </c>
-      <c r="C51" s="0" t="s">
-        <v>34</v>
-      </c>
       <c r="D51" s="0">
-        <v>1300</v>
+        <v>2687.98</v>
       </c>
     </row>
     <row r="52">
@@ -4053,7 +4131,7 @@
         <v>123</v>
       </c>
       <c r="D52" s="0">
-        <v>1700</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="53">
@@ -4064,10 +4142,10 @@
         <v>125</v>
       </c>
       <c r="C53" s="0" t="s">
-        <v>92</v>
+        <v>34</v>
       </c>
       <c r="D53" s="0">
-        <v>35271.5</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="54">
@@ -4081,7 +4159,7 @@
         <v>128</v>
       </c>
       <c r="D54" s="0">
-        <v>38000</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="55">
@@ -4092,10 +4170,10 @@
         <v>130</v>
       </c>
       <c r="C55" s="0" t="s">
-        <v>70</v>
+        <v>97</v>
       </c>
       <c r="D55" s="0">
-        <v>3795</v>
+        <v>35271.5</v>
       </c>
     </row>
     <row r="56">
@@ -4109,7 +4187,7 @@
         <v>133</v>
       </c>
       <c r="D56" s="0">
-        <v>332</v>
+        <v>38000</v>
       </c>
     </row>
     <row r="57">
@@ -4120,10 +4198,10 @@
         <v>135</v>
       </c>
       <c r="C57" s="0" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="D57" s="0">
-        <v>110</v>
+        <v>3795</v>
       </c>
     </row>
     <row r="58">
@@ -4134,24 +4212,24 @@
         <v>137</v>
       </c>
       <c r="C58" s="0" t="s">
-        <v>123</v>
+        <v>138</v>
       </c>
       <c r="D58" s="0">
-        <v>3550</v>
+        <v>332</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="0" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B59" s="0" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C59" s="0" t="s">
-        <v>140</v>
+        <v>52</v>
       </c>
       <c r="D59" s="0">
-        <v>500</v>
+        <v>110</v>
       </c>
     </row>
     <row r="60">
@@ -4162,10 +4240,10 @@
         <v>142</v>
       </c>
       <c r="C60" s="0" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="D60" s="0">
-        <v>602</v>
+        <v>3550</v>
       </c>
     </row>
     <row r="61">
@@ -4176,52 +4254,52 @@
         <v>144</v>
       </c>
       <c r="C61" s="0" t="s">
-        <v>18</v>
+        <v>145</v>
       </c>
       <c r="D61" s="0">
-        <v>330</v>
+        <v>500</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="0" t="s">
+        <v>146</v>
+      </c>
+      <c r="B62" s="0" t="s">
+        <v>147</v>
+      </c>
+      <c r="C62" s="0" t="s">
         <v>145</v>
       </c>
-      <c r="B62" s="0" t="s">
-        <v>146</v>
-      </c>
-      <c r="C62" s="0" t="s">
-        <v>18</v>
-      </c>
       <c r="D62" s="0">
-        <v>508.5</v>
+        <v>602</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="0" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B63" s="0" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C63" s="0" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D63" s="0">
-        <v>484</v>
+        <v>330</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="0" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B64" s="0" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C64" s="0" t="s">
-        <v>151</v>
+        <v>18</v>
       </c>
       <c r="D64" s="0">
-        <v>410</v>
+        <v>508.5</v>
       </c>
     </row>
     <row r="65">
@@ -4232,10 +4310,10 @@
         <v>153</v>
       </c>
       <c r="C65" s="0" t="s">
-        <v>115</v>
+        <v>15</v>
       </c>
       <c r="D65" s="0">
-        <v>1080</v>
+        <v>484</v>
       </c>
     </row>
     <row r="66">
@@ -4246,38 +4324,38 @@
         <v>155</v>
       </c>
       <c r="C66" s="0" t="s">
-        <v>123</v>
+        <v>156</v>
       </c>
       <c r="D66" s="0">
-        <v>1080</v>
+        <v>410</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="0" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B67" s="0" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C67" s="0" t="s">
-        <v>15</v>
+        <v>120</v>
       </c>
       <c r="D67" s="0">
-        <v>3200</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="0" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B68" s="0" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C68" s="0" t="s">
-        <v>160</v>
+        <v>128</v>
       </c>
       <c r="D68" s="0">
-        <v>3800</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="69">
@@ -4288,10 +4366,10 @@
         <v>162</v>
       </c>
       <c r="C69" s="0" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="D69" s="0">
-        <v>9</v>
+        <v>3200</v>
       </c>
     </row>
     <row r="70">
@@ -4302,80 +4380,80 @@
         <v>164</v>
       </c>
       <c r="C70" s="0" t="s">
-        <v>52</v>
+        <v>165</v>
       </c>
       <c r="D70" s="0">
-        <v>9</v>
+        <v>3800</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="0" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B71" s="0" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C71" s="0" t="s">
         <v>52</v>
       </c>
       <c r="D71" s="0">
-        <v>1225</v>
+        <v>9</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="0" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B72" s="0" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C72" s="0" t="s">
-        <v>140</v>
+        <v>52</v>
       </c>
       <c r="D72" s="0">
-        <v>700</v>
+        <v>9</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="0" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B73" s="0" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C73" s="0" t="s">
-        <v>140</v>
+        <v>52</v>
       </c>
       <c r="D73" s="0">
-        <v>606</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="0" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B74" s="0" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C74" s="0" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="D74" s="0">
-        <v>6700</v>
+        <v>700</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="0" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B75" s="0" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C75" s="0" t="s">
-        <v>175</v>
+        <v>145</v>
       </c>
       <c r="D75" s="0">
-        <v>675</v>
+        <v>606</v>
       </c>
     </row>
     <row r="76">
@@ -4386,10 +4464,10 @@
         <v>177</v>
       </c>
       <c r="C76" s="0" t="s">
-        <v>15</v>
+        <v>145</v>
       </c>
       <c r="D76" s="0">
-        <v>1782</v>
+        <v>6700</v>
       </c>
     </row>
     <row r="77">
@@ -4400,80 +4478,80 @@
         <v>179</v>
       </c>
       <c r="C77" s="0" t="s">
-        <v>15</v>
+        <v>180</v>
       </c>
       <c r="D77" s="0">
-        <v>1400</v>
+        <v>675</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="0" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B78" s="0" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C78" s="0" t="s">
         <v>15</v>
       </c>
       <c r="D78" s="0">
-        <v>680</v>
+        <v>1782</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="0" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B79" s="0" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C79" s="0" t="s">
         <v>15</v>
       </c>
       <c r="D79" s="0">
-        <v>780</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="0" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B80" s="0" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C80" s="0" t="s">
         <v>15</v>
       </c>
       <c r="D80" s="0">
-        <v>2580</v>
+        <v>680</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="0" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B81" s="0" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C81" s="0" t="s">
         <v>15</v>
       </c>
       <c r="D81" s="0">
-        <v>1100</v>
+        <v>780</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="0" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B82" s="0" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C82" s="0" t="s">
-        <v>190</v>
+        <v>15</v>
       </c>
       <c r="D82" s="0">
-        <v>2450</v>
+        <v>2580</v>
       </c>
     </row>
     <row r="83">
@@ -4484,10 +4562,10 @@
         <v>192</v>
       </c>
       <c r="C83" s="0" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="D83" s="0">
-        <v>362</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="84">
@@ -4498,38 +4576,38 @@
         <v>194</v>
       </c>
       <c r="C84" s="0" t="s">
-        <v>21</v>
+        <v>195</v>
       </c>
       <c r="D84" s="0">
-        <v>33.7</v>
+        <v>2450</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="0" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B85" s="0" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C85" s="0" t="s">
-        <v>123</v>
+        <v>52</v>
       </c>
       <c r="D85" s="0">
-        <v>1080</v>
+        <v>362</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="0" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B86" s="0" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C86" s="0" t="s">
-        <v>199</v>
+        <v>21</v>
       </c>
       <c r="D86" s="0">
-        <v>0</v>
+        <v>33.7</v>
       </c>
     </row>
     <row r="87">
@@ -4540,24 +4618,24 @@
         <v>201</v>
       </c>
       <c r="C87" s="0" t="s">
-        <v>202</v>
+        <v>128</v>
       </c>
       <c r="D87" s="0">
-        <v>5650</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="0" t="s">
+        <v>202</v>
+      </c>
+      <c r="B88" s="0" t="s">
         <v>203</v>
       </c>
-      <c r="B88" s="0" t="s">
+      <c r="C88" s="0" t="s">
         <v>204</v>
       </c>
-      <c r="C88" s="0" t="s">
-        <v>202</v>
-      </c>
       <c r="D88" s="0">
-        <v>2590</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -4571,7 +4649,7 @@
         <v>207</v>
       </c>
       <c r="D89" s="0">
-        <v>2595</v>
+        <v>5650</v>
       </c>
     </row>
     <row r="90">
@@ -4582,24 +4660,24 @@
         <v>209</v>
       </c>
       <c r="C90" s="0" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="D90" s="0">
-        <v>3000</v>
+        <v>2590</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="0" t="s">
+        <v>210</v>
+      </c>
+      <c r="B91" s="0" t="s">
         <v>211</v>
       </c>
-      <c r="B91" s="0" t="s">
+      <c r="C91" s="0" t="s">
         <v>212</v>
       </c>
-      <c r="C91" s="0" t="s">
-        <v>210</v>
-      </c>
       <c r="D91" s="0">
-        <v>3000</v>
+        <v>2595</v>
       </c>
     </row>
     <row r="92">
@@ -4610,102 +4688,102 @@
         <v>214</v>
       </c>
       <c r="C92" s="0" t="s">
-        <v>110</v>
+        <v>215</v>
       </c>
       <c r="D92" s="0">
-        <v>1770</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="0" t="s">
+        <v>216</v>
+      </c>
+      <c r="B93" s="0" t="s">
+        <v>217</v>
+      </c>
+      <c r="C93" s="0" t="s">
         <v>215</v>
       </c>
-      <c r="B93" s="0" t="s">
-        <v>216</v>
-      </c>
-      <c r="C93" s="0" t="s">
-        <v>70</v>
-      </c>
       <c r="D93" s="0">
-        <v>900</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="0" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B94" s="0" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C94" s="0" t="s">
-        <v>140</v>
+        <v>115</v>
       </c>
       <c r="D94" s="0">
-        <v>720.72</v>
+        <v>1770</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="0" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B95" s="0" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C95" s="0" t="s">
-        <v>140</v>
+        <v>75</v>
       </c>
       <c r="D95" s="0">
-        <v>613.76</v>
+        <v>900</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="0" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B96" s="0" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C96" s="0" t="s">
-        <v>52</v>
+        <v>145</v>
       </c>
       <c r="D96" s="0">
-        <v>190</v>
+        <v>720.72</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="0" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B97" s="0" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C97" s="0" t="s">
-        <v>52</v>
+        <v>145</v>
       </c>
       <c r="D97" s="0">
-        <v>180</v>
+        <v>613.76</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="0" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B98" s="0" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C98" s="0" t="s">
         <v>52</v>
       </c>
       <c r="D98" s="0">
-        <v>180</v>
+        <v>190</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="0" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B99" s="0" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C99" s="0" t="s">
         <v>52</v>
@@ -4716,114 +4794,114 @@
     </row>
     <row r="100">
       <c r="A100" s="0" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B100" s="0" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C100" s="0" t="s">
         <v>52</v>
       </c>
       <c r="D100" s="0">
-        <v>190</v>
+        <v>180</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="0" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B101" s="0" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C101" s="0" t="s">
-        <v>15</v>
+        <v>52</v>
       </c>
       <c r="D101" s="0">
-        <v>1760</v>
+        <v>180</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="0" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B102" s="0" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C102" s="0" t="s">
-        <v>18</v>
+        <v>52</v>
       </c>
       <c r="D102" s="0">
-        <v>1117.4</v>
+        <v>190</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="0" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B103" s="0" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C103" s="0" t="s">
-        <v>92</v>
+        <v>15</v>
       </c>
       <c r="D103" s="0">
-        <v>3274.24</v>
+        <v>1760</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="0" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B104" s="0" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C104" s="0" t="s">
-        <v>92</v>
+        <v>18</v>
       </c>
       <c r="D104" s="0">
-        <v>2475.72</v>
+        <v>1117.4</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="0" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B105" s="0" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C105" s="0" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="D105" s="0">
-        <v>3713.58</v>
+        <v>3274.24</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="0" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B106" s="0" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C106" s="0" t="s">
-        <v>118</v>
+        <v>97</v>
       </c>
       <c r="D106" s="0">
-        <v>1810</v>
+        <v>2475.72</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="0" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B107" s="0" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C107" s="0" t="s">
-        <v>245</v>
+        <v>97</v>
       </c>
       <c r="D107" s="0">
-        <v>1800</v>
+        <v>3713.58</v>
       </c>
     </row>
     <row r="108">
@@ -4834,10 +4912,10 @@
         <v>247</v>
       </c>
       <c r="C108" s="0" t="s">
-        <v>15</v>
+        <v>123</v>
       </c>
       <c r="D108" s="0">
-        <v>1600</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="109">
@@ -4848,7 +4926,7 @@
         <v>249</v>
       </c>
       <c r="C109" s="0" t="s">
-        <v>15</v>
+        <v>250</v>
       </c>
       <c r="D109" s="0">
         <v>1800</v>
@@ -4856,13 +4934,13 @@
     </row>
     <row r="110">
       <c r="A110" s="0" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B110" s="0" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C110" s="0" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="D110" s="0">
         <v>1600</v>
@@ -4870,27 +4948,27 @@
     </row>
     <row r="111">
       <c r="A111" s="0" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B111" s="0" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C111" s="0" t="s">
-        <v>118</v>
+        <v>15</v>
       </c>
       <c r="D111" s="0">
-        <v>1900</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="0" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B112" s="0" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C112" s="0" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="D112" s="0">
         <v>1600</v>
@@ -4898,58 +4976,58 @@
     </row>
     <row r="113">
       <c r="A113" s="0" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B113" s="0" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C113" s="0" t="s">
-        <v>45</v>
+        <v>123</v>
       </c>
       <c r="D113" s="0">
-        <v>5660.43</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="0" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B114" s="0" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C114" s="0" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D114" s="0">
-        <v>975</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="0" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B115" s="0" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C115" s="0" t="s">
-        <v>140</v>
+        <v>45</v>
       </c>
       <c r="D115" s="0">
-        <v>970</v>
+        <v>5660.43</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="0" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B116" s="0" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C116" s="0" t="s">
-        <v>264</v>
+        <v>18</v>
       </c>
       <c r="D116" s="0">
-        <v>2800</v>
+        <v>975</v>
       </c>
     </row>
     <row r="117">
@@ -4960,10 +5038,10 @@
         <v>266</v>
       </c>
       <c r="C117" s="0" t="s">
-        <v>264</v>
+        <v>145</v>
       </c>
       <c r="D117" s="0">
-        <v>4525.4</v>
+        <v>970</v>
       </c>
     </row>
     <row r="118">
@@ -4974,80 +5052,80 @@
         <v>268</v>
       </c>
       <c r="C118" s="0" t="s">
-        <v>21</v>
+        <v>269</v>
       </c>
       <c r="D118" s="0">
-        <v>2954</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="0" t="s">
+        <v>270</v>
+      </c>
+      <c r="B119" s="0" t="s">
+        <v>271</v>
+      </c>
+      <c r="C119" s="0" t="s">
         <v>269</v>
       </c>
-      <c r="B119" s="0" t="s">
-        <v>270</v>
-      </c>
-      <c r="C119" s="0" t="s">
-        <v>92</v>
-      </c>
       <c r="D119" s="0">
-        <v>11313.5</v>
+        <v>4525.4</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="0" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B120" s="0" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C120" s="0" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="D120" s="0">
-        <v>2200</v>
+        <v>2954</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="0" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B121" s="0" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C121" s="0" t="s">
-        <v>37</v>
+        <v>97</v>
       </c>
       <c r="D121" s="0">
-        <v>2400</v>
+        <v>11313.5</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="0" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B122" s="0" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C122" s="0" t="s">
-        <v>92</v>
+        <v>34</v>
       </c>
       <c r="D122" s="0">
-        <v>212.96</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="0" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B123" s="0" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C123" s="0" t="s">
-        <v>279</v>
+        <v>37</v>
       </c>
       <c r="D123" s="0">
-        <v>0</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="124">
@@ -5058,10 +5136,10 @@
         <v>281</v>
       </c>
       <c r="C124" s="0" t="s">
-        <v>279</v>
+        <v>97</v>
       </c>
       <c r="D124" s="0">
-        <v>0</v>
+        <v>212.96</v>
       </c>
     </row>
     <row r="125">
@@ -5075,7 +5153,7 @@
         <v>284</v>
       </c>
       <c r="D125" s="0">
-        <v>520</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -5086,10 +5164,10 @@
         <v>286</v>
       </c>
       <c r="C126" s="0" t="s">
-        <v>34</v>
+        <v>284</v>
       </c>
       <c r="D126" s="0">
-        <v>520</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -5100,52 +5178,52 @@
         <v>288</v>
       </c>
       <c r="C127" s="0" t="s">
-        <v>52</v>
+        <v>289</v>
       </c>
       <c r="D127" s="0">
-        <v>22</v>
+        <v>520</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="0" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B128" s="0" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C128" s="0" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="D128" s="0">
-        <v>3200</v>
+        <v>520</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="0" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B129" s="0" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C129" s="0" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="D129" s="0">
-        <v>7377.5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="0" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B130" s="0" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C130" s="0" t="s">
-        <v>295</v>
+        <v>15</v>
       </c>
       <c r="D130" s="0">
-        <v>16095</v>
+        <v>3200</v>
       </c>
     </row>
     <row r="131">
@@ -5156,10 +5234,10 @@
         <v>297</v>
       </c>
       <c r="C131" s="0" t="s">
-        <v>140</v>
+        <v>28</v>
       </c>
       <c r="D131" s="0">
-        <v>3100</v>
+        <v>7377.5</v>
       </c>
     </row>
     <row r="132">
@@ -5170,52 +5248,52 @@
         <v>299</v>
       </c>
       <c r="C132" s="0" t="s">
-        <v>140</v>
+        <v>300</v>
       </c>
       <c r="D132" s="0">
-        <v>6700</v>
+        <v>16095</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="0" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B133" s="0" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C133" s="0" t="s">
-        <v>15</v>
+        <v>145</v>
       </c>
       <c r="D133" s="0">
-        <v>4200</v>
+        <v>3100</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="0" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B134" s="0" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C134" s="0" t="s">
-        <v>15</v>
+        <v>145</v>
       </c>
       <c r="D134" s="0">
-        <v>1050</v>
+        <v>6700</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="0" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B135" s="0" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C135" s="0" t="s">
-        <v>306</v>
+        <v>15</v>
       </c>
       <c r="D135" s="0">
-        <v>3350</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="136">
@@ -5226,10 +5304,10 @@
         <v>308</v>
       </c>
       <c r="C136" s="0" t="s">
-        <v>123</v>
+        <v>15</v>
       </c>
       <c r="D136" s="0">
-        <v>3350</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="137">
@@ -5243,7 +5321,7 @@
         <v>311</v>
       </c>
       <c r="D137" s="0">
-        <v>0</v>
+        <v>3350</v>
       </c>
     </row>
     <row r="138">
@@ -5254,10 +5332,10 @@
         <v>313</v>
       </c>
       <c r="C138" s="0" t="s">
-        <v>18</v>
+        <v>128</v>
       </c>
       <c r="D138" s="0">
-        <v>589.9</v>
+        <v>3350</v>
       </c>
     </row>
     <row r="139">
@@ -5268,38 +5346,38 @@
         <v>315</v>
       </c>
       <c r="C139" s="0" t="s">
-        <v>15</v>
+        <v>316</v>
       </c>
       <c r="D139" s="0">
-        <v>1600</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="0" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B140" s="0" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C140" s="0" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D140" s="0">
-        <v>2000</v>
+        <v>589.9</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="0" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B141" s="0" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C141" s="0" t="s">
-        <v>320</v>
+        <v>15</v>
       </c>
       <c r="D141" s="0">
-        <v>2728</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="142">
@@ -5310,10 +5388,10 @@
         <v>322</v>
       </c>
       <c r="C142" s="0" t="s">
-        <v>70</v>
+        <v>15</v>
       </c>
       <c r="D142" s="0">
-        <v>0</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="143">
@@ -5324,91 +5402,91 @@
         <v>324</v>
       </c>
       <c r="C143" s="0" t="s">
-        <v>70</v>
+        <v>325</v>
       </c>
       <c r="D143" s="0">
-        <v>88248.3</v>
+        <v>2728</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="0" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B144" s="0" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C144" s="0" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="D144" s="0">
-        <v>1785</v>
+        <v>0</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="0" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B145" s="0" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C145" s="0" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="D145" s="0">
-        <v>2058</v>
+        <v>88248.3</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="0" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B146" s="0" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C146" s="0" t="s">
-        <v>15</v>
+        <v>52</v>
       </c>
       <c r="D146" s="0">
-        <v>1270</v>
+        <v>1785</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="0" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B147" s="0" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C147" s="0" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="D147" s="0">
-        <v>550</v>
+        <v>2058</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="0" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B148" s="0" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C148" s="0" t="s">
-        <v>70</v>
+        <v>15</v>
       </c>
       <c r="D148" s="0">
-        <v>550</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="0" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B149" s="0" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C149" s="0" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D149" s="0">
         <v>550</v>
@@ -5416,30 +5494,30 @@
     </row>
     <row r="150">
       <c r="A150" s="0" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B150" s="0" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C150" s="0" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="D150" s="0">
-        <v>1663.75</v>
+        <v>550</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="0" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B151" s="0" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C151" s="0" t="s">
-        <v>341</v>
+        <v>34</v>
       </c>
       <c r="D151" s="0">
-        <v>4500</v>
+        <v>550</v>
       </c>
     </row>
     <row r="152">
@@ -5450,10 +5528,10 @@
         <v>343</v>
       </c>
       <c r="C152" s="0" t="s">
-        <v>34</v>
+        <v>97</v>
       </c>
       <c r="D152" s="0">
-        <v>390</v>
+        <v>1663.75</v>
       </c>
     </row>
     <row r="153">
@@ -5464,122 +5542,122 @@
         <v>345</v>
       </c>
       <c r="C153" s="0" t="s">
-        <v>15</v>
+        <v>346</v>
       </c>
       <c r="D153" s="0">
-        <v>500</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="0" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B154" s="0" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C154" s="0" t="s">
         <v>34</v>
       </c>
       <c r="D154" s="0">
-        <v>380</v>
+        <v>390</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="0" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B155" s="0" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C155" s="0" t="s">
-        <v>70</v>
+        <v>15</v>
       </c>
       <c r="D155" s="0">
-        <v>380</v>
+        <v>500</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="0" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B156" s="0" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C156" s="0" t="s">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="D156" s="0">
-        <v>580</v>
+        <v>380</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="0" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B157" s="0" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C157" s="0" t="s">
-        <v>15</v>
+        <v>75</v>
       </c>
       <c r="D157" s="0">
-        <v>572</v>
+        <v>380</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="0" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B158" s="0" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C158" s="0" t="s">
-        <v>28</v>
+        <v>75</v>
       </c>
       <c r="D158" s="0">
-        <v>106950.8</v>
+        <v>580</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="0" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B159" s="0" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C159" s="0" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="D159" s="0">
-        <v>118372.7</v>
+        <v>572</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="0" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B160" s="0" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C160" s="0" t="s">
         <v>28</v>
       </c>
       <c r="D160" s="0">
-        <v>140178.2</v>
+        <v>106950.8</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="0" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B161" s="0" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C161" s="0" t="s">
-        <v>362</v>
+        <v>28</v>
       </c>
       <c r="D161" s="0">
-        <v>650</v>
+        <v>118372.7</v>
       </c>
     </row>
     <row r="162">
@@ -5590,10 +5668,10 @@
         <v>364</v>
       </c>
       <c r="C162" s="0" t="s">
-        <v>110</v>
+        <v>28</v>
       </c>
       <c r="D162" s="0">
-        <v>1590</v>
+        <v>140178.2</v>
       </c>
     </row>
     <row r="163">
@@ -5604,35 +5682,35 @@
         <v>366</v>
       </c>
       <c r="C163" s="0" t="s">
-        <v>34</v>
+        <v>367</v>
       </c>
       <c r="D163" s="0">
-        <v>550</v>
+        <v>650</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="0" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B164" s="0" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C164" s="0" t="s">
-        <v>151</v>
+        <v>115</v>
       </c>
       <c r="D164" s="0">
-        <v>550</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="0" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B165" s="0" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C165" s="0" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="D165" s="0">
         <v>550</v>
@@ -5640,58 +5718,58 @@
     </row>
     <row r="166">
       <c r="A166" s="0" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B166" s="0" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C166" s="0" t="s">
-        <v>15</v>
+        <v>156</v>
       </c>
       <c r="D166" s="0">
-        <v>1700</v>
+        <v>550</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="0" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B167" s="0" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C167" s="0" t="s">
         <v>15</v>
       </c>
       <c r="D167" s="0">
-        <v>0</v>
+        <v>550</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="0" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B168" s="0" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C168" s="0" t="s">
-        <v>115</v>
+        <v>15</v>
       </c>
       <c r="D168" s="0">
-        <v>1290</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="0" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B169" s="0" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C169" s="0" t="s">
-        <v>379</v>
+        <v>15</v>
       </c>
       <c r="D169" s="0">
-        <v>55058.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="170">
@@ -5702,24 +5780,24 @@
         <v>381</v>
       </c>
       <c r="C170" s="0" t="s">
-        <v>382</v>
+        <v>120</v>
       </c>
       <c r="D170" s="0">
-        <v>104695.98</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="0" t="s">
+        <v>382</v>
+      </c>
+      <c r="B171" s="0" t="s">
         <v>383</v>
       </c>
-      <c r="B171" s="0" t="s">
+      <c r="C171" s="0" t="s">
         <v>384</v>
       </c>
-      <c r="C171" s="0" t="s">
-        <v>382</v>
-      </c>
       <c r="D171" s="0">
-        <v>80478.92</v>
+        <v>55058.9</v>
       </c>
     </row>
     <row r="172">
@@ -5730,66 +5808,66 @@
         <v>386</v>
       </c>
       <c r="C172" s="0" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="D172" s="0">
-        <v>92546.68</v>
+        <v>104695.98</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="0" t="s">
+        <v>388</v>
+      </c>
+      <c r="B173" s="0" t="s">
+        <v>389</v>
+      </c>
+      <c r="C173" s="0" t="s">
         <v>387</v>
       </c>
-      <c r="B173" s="0" t="s">
-        <v>388</v>
-      </c>
-      <c r="C173" s="0" t="s">
-        <v>28</v>
-      </c>
       <c r="D173" s="0">
-        <v>972.9</v>
+        <v>80478.92</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="0" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B174" s="0" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C174" s="0" t="s">
-        <v>28</v>
+        <v>387</v>
       </c>
       <c r="D174" s="0">
-        <v>265.3</v>
+        <v>92546.68</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="0" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B175" s="0" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C175" s="0" t="s">
         <v>28</v>
       </c>
       <c r="D175" s="0">
-        <v>2908.78</v>
+        <v>972.9</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="0" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B176" s="0" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C176" s="0" t="s">
-        <v>395</v>
+        <v>28</v>
       </c>
       <c r="D176" s="0">
-        <v>61</v>
+        <v>265.3</v>
       </c>
     </row>
     <row r="177">
@@ -5800,10 +5878,10 @@
         <v>397</v>
       </c>
       <c r="C177" s="0" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="D177" s="0">
-        <v>270</v>
+        <v>2908.78</v>
       </c>
     </row>
     <row r="178">
@@ -5814,304 +5892,304 @@
         <v>399</v>
       </c>
       <c r="C178" s="0" t="s">
-        <v>151</v>
+        <v>400</v>
       </c>
       <c r="D178" s="0">
-        <v>257</v>
+        <v>61</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="0" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B179" s="0" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C179" s="0" t="s">
-        <v>140</v>
+        <v>18</v>
       </c>
       <c r="D179" s="0">
-        <v>2859</v>
+        <v>270</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="0" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B180" s="0" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C180" s="0" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="D180" s="0">
-        <v>3573.45</v>
+        <v>257</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="0" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B181" s="0" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C181" s="0" t="s">
-        <v>123</v>
+        <v>145</v>
       </c>
       <c r="D181" s="0">
-        <v>5218</v>
+        <v>2859</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="0" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B182" s="0" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C182" s="0" t="s">
-        <v>379</v>
+        <v>145</v>
       </c>
       <c r="D182" s="0">
-        <v>37527.35</v>
+        <v>3573.45</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="0" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B183" s="0" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C183" s="0" t="s">
-        <v>18</v>
+        <v>128</v>
       </c>
       <c r="D183" s="0">
-        <v>825.18</v>
+        <v>5218</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="0" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B184" s="0" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C184" s="0" t="s">
-        <v>18</v>
+        <v>384</v>
       </c>
       <c r="D184" s="0">
-        <v>2687.98</v>
+        <v>37527.35</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="0" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B185" s="0" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C185" s="0" t="s">
         <v>18</v>
       </c>
       <c r="D185" s="0">
-        <v>6764.67</v>
+        <v>825.18</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="0" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B186" s="0" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C186" s="0" t="s">
         <v>18</v>
       </c>
       <c r="D186" s="0">
-        <v>353.46</v>
+        <v>2687.98</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="0" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B187" s="0" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C187" s="0" t="s">
         <v>18</v>
       </c>
       <c r="D187" s="0">
-        <v>10799.76</v>
+        <v>6764.67</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="0" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B188" s="0" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C188" s="0" t="s">
         <v>18</v>
       </c>
       <c r="D188" s="0">
-        <v>3939.57</v>
+        <v>353.46</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="0" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B189" s="0" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C189" s="0" t="s">
         <v>18</v>
       </c>
       <c r="D189" s="0">
-        <v>412.8</v>
+        <v>10799.76</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="0" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B190" s="0" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C190" s="0" t="s">
         <v>18</v>
       </c>
       <c r="D190" s="0">
-        <v>2184.81</v>
+        <v>3939.57</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="0" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B191" s="0" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C191" s="0" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D191" s="0">
-        <v>9748.5</v>
+        <v>412.8</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="0" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B192" s="0" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C192" s="0" t="s">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="D192" s="0">
-        <v>430</v>
+        <v>2184.81</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="0" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B193" s="0" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C193" s="0" t="s">
-        <v>70</v>
+        <v>28</v>
       </c>
       <c r="D193" s="0">
-        <v>800</v>
+        <v>9748.5</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="0" t="s">
+        <v>431</v>
+      </c>
+      <c r="B194" s="0" t="s">
+        <v>432</v>
+      </c>
+      <c r="C194" s="0" t="s">
+        <v>75</v>
+      </c>
+      <c r="D194" s="0">
         <v>430</v>
-      </c>
-      <c r="B194" s="0" t="s">
-        <v>431</v>
-      </c>
-      <c r="C194" s="0" t="s">
-        <v>245</v>
-      </c>
-      <c r="D194" s="0">
-        <v>2040</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="0" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B195" s="0" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C195" s="0" t="s">
-        <v>245</v>
+        <v>75</v>
       </c>
       <c r="D195" s="0">
-        <v>1380</v>
+        <v>800</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="0" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B196" s="0" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C196" s="0" t="s">
-        <v>379</v>
+        <v>250</v>
       </c>
       <c r="D196" s="0">
-        <v>236458.17</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="0" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B197" s="0" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C197" s="0" t="s">
-        <v>28</v>
+        <v>250</v>
       </c>
       <c r="D197" s="0">
-        <v>317.2</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="0" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B198" s="0" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C198" s="0" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="D198" s="0">
-        <v>25100</v>
+        <v>236458.17</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="0" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B199" s="0" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C199" s="0" t="s">
-        <v>442</v>
+        <v>28</v>
       </c>
       <c r="D199" s="0">
-        <v>20900</v>
+        <v>317.2</v>
       </c>
     </row>
     <row r="200">
@@ -6122,10 +6200,10 @@
         <v>444</v>
       </c>
       <c r="C200" s="0" t="s">
-        <v>45</v>
+        <v>384</v>
       </c>
       <c r="D200" s="0">
-        <v>6127.17</v>
+        <v>25100</v>
       </c>
     </row>
     <row r="201">
@@ -6136,122 +6214,122 @@
         <v>446</v>
       </c>
       <c r="C201" s="0" t="s">
-        <v>21</v>
+        <v>447</v>
       </c>
       <c r="D201" s="0">
-        <v>1104.46</v>
+        <v>20900</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="0" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B202" s="0" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C202" s="0" t="s">
-        <v>92</v>
+        <v>45</v>
       </c>
       <c r="D202" s="0">
-        <v>11646.25</v>
+        <v>6127.17</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="0" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B203" s="0" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C203" s="0" t="s">
-        <v>123</v>
+        <v>21</v>
       </c>
       <c r="D203" s="0">
-        <v>6072</v>
+        <v>1104.46</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="0" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B204" s="0" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C204" s="0" t="s">
-        <v>70</v>
+        <v>97</v>
       </c>
       <c r="D204" s="0">
-        <v>400</v>
+        <v>11646.25</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="0" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B205" s="0" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C205" s="0" t="s">
-        <v>21</v>
+        <v>128</v>
       </c>
       <c r="D205" s="0">
-        <v>409</v>
+        <v>6072</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="0" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B206" s="0" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C206" s="0" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="D206" s="0">
-        <v>10748</v>
+        <v>400</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="0" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B207" s="0" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C207" s="0" t="s">
-        <v>64</v>
+        <v>21</v>
       </c>
       <c r="D207" s="0">
-        <v>12898</v>
+        <v>409</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="0" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B208" s="0" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C208" s="0" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="D208" s="0">
-        <v>2000</v>
+        <v>10748</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="0" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B209" s="0" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C209" s="0" t="s">
-        <v>463</v>
+        <v>69</v>
       </c>
       <c r="D209" s="0">
-        <v>0</v>
+        <v>12898</v>
       </c>
     </row>
     <row r="210">
@@ -6262,10 +6340,10 @@
         <v>465</v>
       </c>
       <c r="C210" s="0" t="s">
-        <v>15</v>
+        <v>52</v>
       </c>
       <c r="D210" s="0">
-        <v>490</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="211">
@@ -6276,7 +6354,7 @@
         <v>467</v>
       </c>
       <c r="C211" s="0" t="s">
-        <v>34</v>
+        <v>468</v>
       </c>
       <c r="D211" s="0">
         <v>0</v>
@@ -6284,30 +6362,30 @@
     </row>
     <row r="212">
       <c r="A212" s="0" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B212" s="0" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C212" s="0" t="s">
-        <v>160</v>
+        <v>15</v>
       </c>
       <c r="D212" s="0">
-        <v>25171.1</v>
+        <v>490</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="0" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B213" s="0" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C213" s="0" t="s">
-        <v>472</v>
+        <v>34</v>
       </c>
       <c r="D213" s="0">
-        <v>70443</v>
+        <v>0</v>
       </c>
     </row>
     <row r="214">
@@ -6318,10 +6396,10 @@
         <v>474</v>
       </c>
       <c r="C214" s="0" t="s">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="D214" s="0">
-        <v>1800</v>
+        <v>25171.1</v>
       </c>
     </row>
     <row r="215">
@@ -6332,220 +6410,220 @@
         <v>476</v>
       </c>
       <c r="C215" s="0" t="s">
-        <v>34</v>
+        <v>477</v>
       </c>
       <c r="D215" s="0">
-        <v>0</v>
+        <v>70443</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="0" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B216" s="0" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C216" s="0" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="D216" s="0">
-        <v>492.2</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="0" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B217" s="0" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C217" s="0" t="s">
-        <v>207</v>
+        <v>34</v>
       </c>
       <c r="D217" s="0">
-        <v>495</v>
+        <v>0</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="0" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B218" s="0" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C218" s="0" t="s">
-        <v>18</v>
+        <v>145</v>
       </c>
       <c r="D218" s="0">
-        <v>1819.72</v>
+        <v>492.2</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="0" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B219" s="0" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C219" s="0" t="s">
-        <v>18</v>
+        <v>212</v>
       </c>
       <c r="D219" s="0">
-        <v>4391.81</v>
+        <v>495</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="0" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B220" s="0" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C220" s="0" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="D220" s="0">
-        <v>4700</v>
+        <v>1819.72</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="0" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B221" s="0" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C221" s="0" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="D221" s="0">
-        <v>4670</v>
+        <v>4391.81</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="0" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B222" s="0" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C222" s="0" t="s">
-        <v>52</v>
+        <v>492</v>
       </c>
       <c r="D222" s="0">
-        <v>4670</v>
+        <v>4100</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="0" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="B223" s="0" t="s">
+        <v>494</v>
+      </c>
+      <c r="C223" s="0" t="s">
         <v>492</v>
       </c>
-      <c r="C223" s="0" t="s">
-        <v>52</v>
-      </c>
       <c r="D223" s="0">
-        <v>4670</v>
+        <v>4100</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="0" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="B224" s="0" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="C224" s="0" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="D224" s="0">
-        <v>265</v>
+        <v>4100</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="0" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B225" s="0" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C225" s="0" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="D225" s="0">
-        <v>265</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="0" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B226" s="0" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C226" s="0" t="s">
-        <v>495</v>
+        <v>52</v>
       </c>
       <c r="D226" s="0">
-        <v>265</v>
+        <v>4700</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="0" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B227" s="0" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C227" s="0" t="s">
-        <v>495</v>
+        <v>59</v>
       </c>
       <c r="D227" s="0">
-        <v>265</v>
+        <v>235</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="0" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B228" s="0" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C228" s="0" t="s">
-        <v>495</v>
+        <v>59</v>
       </c>
       <c r="D228" s="0">
-        <v>265</v>
+        <v>235</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="0" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B229" s="0" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C229" s="0" t="s">
-        <v>495</v>
+        <v>59</v>
       </c>
       <c r="D229" s="0">
-        <v>265</v>
+        <v>235</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="0" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B230" s="0" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C230" s="0" t="s">
-        <v>508</v>
+        <v>52</v>
       </c>
       <c r="D230" s="0">
-        <v>4700</v>
+        <v>4670</v>
       </c>
     </row>
     <row r="231">
@@ -6556,38 +6634,38 @@
         <v>510</v>
       </c>
       <c r="C231" s="0" t="s">
-        <v>511</v>
+        <v>52</v>
       </c>
       <c r="D231" s="0">
-        <v>4700</v>
+        <v>4670</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="0" t="s">
+        <v>511</v>
+      </c>
+      <c r="B232" s="0" t="s">
         <v>512</v>
-      </c>
-      <c r="B232" s="0" t="s">
-        <v>513</v>
       </c>
       <c r="C232" s="0" t="s">
         <v>52</v>
       </c>
       <c r="D232" s="0">
-        <v>4700</v>
+        <v>4670</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="0" t="s">
+        <v>513</v>
+      </c>
+      <c r="B233" s="0" t="s">
         <v>514</v>
       </c>
-      <c r="B233" s="0" t="s">
+      <c r="C233" s="0" t="s">
         <v>515</v>
       </c>
-      <c r="C233" s="0" t="s">
-        <v>52</v>
-      </c>
       <c r="D233" s="0">
-        <v>597</v>
+        <v>265</v>
       </c>
     </row>
     <row r="234">
@@ -6598,10 +6676,10 @@
         <v>517</v>
       </c>
       <c r="C234" s="0" t="s">
-        <v>52</v>
+        <v>515</v>
       </c>
       <c r="D234" s="0">
-        <v>223</v>
+        <v>265</v>
       </c>
     </row>
     <row r="235">
@@ -6612,10 +6690,10 @@
         <v>519</v>
       </c>
       <c r="C235" s="0" t="s">
-        <v>52</v>
+        <v>515</v>
       </c>
       <c r="D235" s="0">
-        <v>247</v>
+        <v>265</v>
       </c>
     </row>
     <row r="236">
@@ -6626,10 +6704,10 @@
         <v>521</v>
       </c>
       <c r="C236" s="0" t="s">
-        <v>37</v>
+        <v>515</v>
       </c>
       <c r="D236" s="0">
-        <v>5600</v>
+        <v>265</v>
       </c>
     </row>
     <row r="237">
@@ -6640,10 +6718,10 @@
         <v>523</v>
       </c>
       <c r="C237" s="0" t="s">
-        <v>151</v>
+        <v>515</v>
       </c>
       <c r="D237" s="0">
-        <v>6000</v>
+        <v>265</v>
       </c>
     </row>
     <row r="238">
@@ -6654,10 +6732,10 @@
         <v>525</v>
       </c>
       <c r="C238" s="0" t="s">
-        <v>70</v>
+        <v>515</v>
       </c>
       <c r="D238" s="0">
-        <v>80000</v>
+        <v>265</v>
       </c>
     </row>
     <row r="239">
@@ -6668,472 +6746,472 @@
         <v>527</v>
       </c>
       <c r="C239" s="0" t="s">
-        <v>70</v>
+        <v>528</v>
       </c>
       <c r="D239" s="0">
-        <v>90000</v>
+        <v>4700</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="0" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B240" s="0" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C240" s="0" t="s">
-        <v>70</v>
+        <v>531</v>
       </c>
       <c r="D240" s="0">
-        <v>110000</v>
+        <v>4700</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="0" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="B241" s="0" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="C241" s="0" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="D241" s="0">
-        <v>900</v>
+        <v>4700</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="0" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="B242" s="0" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="C242" s="0" t="s">
-        <v>15</v>
+        <v>52</v>
       </c>
       <c r="D242" s="0">
-        <v>1100</v>
+        <v>597</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="0" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="B243" s="0" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="C243" s="0" t="s">
-        <v>15</v>
+        <v>52</v>
       </c>
       <c r="D243" s="0">
-        <v>2500</v>
+        <v>223</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="0" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="B244" s="0" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="C244" s="0" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="D244" s="0">
-        <v>14608.16</v>
+        <v>247</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="0" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="B245" s="0" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="C245" s="0" t="s">
-        <v>151</v>
+        <v>37</v>
       </c>
       <c r="D245" s="0">
-        <v>700</v>
+        <v>5600</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="0" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="B246" s="0" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="C246" s="0" t="s">
-        <v>37</v>
+        <v>156</v>
       </c>
       <c r="D246" s="0">
-        <v>700</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="0" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="B247" s="0" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="C247" s="0" t="s">
-        <v>284</v>
+        <v>75</v>
       </c>
       <c r="D247" s="0">
-        <v>450</v>
+        <v>80000</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="0" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="B248" s="0" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="C248" s="0" t="s">
-        <v>15</v>
+        <v>75</v>
       </c>
       <c r="D248" s="0">
-        <v>555</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="0" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="B249" s="0" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="C249" s="0" t="s">
-        <v>15</v>
+        <v>75</v>
       </c>
       <c r="D249" s="0">
-        <v>825</v>
+        <v>110000</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="0" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="B250" s="0" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="C250" s="0" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="D250" s="0">
-        <v>36.3</v>
+        <v>900</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="0" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="B251" s="0" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="C251" s="0" t="s">
         <v>15</v>
       </c>
       <c r="D251" s="0">
-        <v>544.5</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="0" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="B252" s="0" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="C252" s="0" t="s">
         <v>15</v>
       </c>
       <c r="D252" s="0">
-        <v>750</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="0" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="B253" s="0" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="C253" s="0" t="s">
-        <v>151</v>
+        <v>28</v>
       </c>
       <c r="D253" s="0">
-        <v>1130</v>
+        <v>14608.16</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="0" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="B254" s="0" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="C254" s="0" t="s">
-        <v>52</v>
+        <v>156</v>
       </c>
       <c r="D254" s="0">
-        <v>4510</v>
+        <v>700</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="0" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="B255" s="0" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="C255" s="0" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="D255" s="0">
-        <v>4510</v>
+        <v>700</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="0" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="B256" s="0" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="C256" s="0" t="s">
-        <v>52</v>
+        <v>289</v>
       </c>
       <c r="D256" s="0">
-        <v>4510</v>
+        <v>450</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="0" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="B257" s="0" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="C257" s="0" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="D257" s="0">
-        <v>4510</v>
+        <v>555</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="0" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="B258" s="0" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="C258" s="0" t="s">
         <v>15</v>
       </c>
       <c r="D258" s="0">
-        <v>902</v>
+        <v>825</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="0" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="B259" s="0" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="C259" s="0" t="s">
         <v>15</v>
       </c>
       <c r="D259" s="0">
-        <v>880</v>
+        <v>36.3</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="0" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="B260" s="0" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="C260" s="0" t="s">
-        <v>140</v>
+        <v>15</v>
       </c>
       <c r="D260" s="0">
-        <v>446</v>
+        <v>544.5</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="0" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="B261" s="0" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="C261" s="0" t="s">
-        <v>140</v>
+        <v>15</v>
       </c>
       <c r="D261" s="0">
-        <v>370</v>
+        <v>750</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="0" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="B262" s="0" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="C262" s="0" t="s">
-        <v>18</v>
+        <v>156</v>
       </c>
       <c r="D262" s="0">
-        <v>300</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="0" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="B263" s="0" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="C263" s="0" t="s">
-        <v>18</v>
+        <v>52</v>
       </c>
       <c r="D263" s="0">
-        <v>420</v>
+        <v>4510</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="0" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="B264" s="0" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="C264" s="0" t="s">
-        <v>18</v>
+        <v>52</v>
       </c>
       <c r="D264" s="0">
-        <v>760</v>
+        <v>4510</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="0" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="B265" s="0" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="C265" s="0" t="s">
-        <v>18</v>
+        <v>52</v>
       </c>
       <c r="D265" s="0">
-        <v>820</v>
+        <v>4510</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="0" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="B266" s="0" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="C266" s="0" t="s">
-        <v>582</v>
+        <v>52</v>
       </c>
       <c r="D266" s="0">
-        <v>189016.25</v>
+        <v>4510</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="0" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B267" s="0" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C267" s="0" t="s">
-        <v>70</v>
+        <v>15</v>
       </c>
       <c r="D267" s="0">
-        <v>28000</v>
+        <v>902</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="0" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B268" s="0" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C268" s="0" t="s">
-        <v>70</v>
+        <v>15</v>
       </c>
       <c r="D268" s="0">
-        <v>34000</v>
+        <v>880</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="0" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B269" s="0" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C269" s="0" t="s">
-        <v>472</v>
+        <v>145</v>
       </c>
       <c r="D269" s="0">
-        <v>243315</v>
+        <v>446</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="0" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B270" s="0" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C270" s="0" t="s">
-        <v>472</v>
+        <v>145</v>
       </c>
       <c r="D270" s="0">
-        <v>196835</v>
+        <v>370</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="0" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B271" s="0" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C271" s="0" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D271" s="0">
-        <v>1760</v>
+        <v>300</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="0" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B272" s="0" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C272" s="0" t="s">
-        <v>595</v>
+        <v>18</v>
       </c>
       <c r="D272" s="0">
-        <v>26350</v>
+        <v>420</v>
       </c>
     </row>
     <row r="273">
@@ -7144,10 +7222,10 @@
         <v>597</v>
       </c>
       <c r="C273" s="0" t="s">
-        <v>207</v>
+        <v>18</v>
       </c>
       <c r="D273" s="0">
-        <v>31250</v>
+        <v>760</v>
       </c>
     </row>
     <row r="274">
@@ -7158,10 +7236,10 @@
         <v>599</v>
       </c>
       <c r="C274" s="0" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="D274" s="0">
-        <v>34.98</v>
+        <v>820</v>
       </c>
     </row>
     <row r="275">
@@ -7175,7 +7253,7 @@
         <v>602</v>
       </c>
       <c r="D275" s="0">
-        <v>34.98</v>
+        <v>189016.25</v>
       </c>
     </row>
     <row r="276">
@@ -7186,80 +7264,80 @@
         <v>604</v>
       </c>
       <c r="C276" s="0" t="s">
-        <v>605</v>
+        <v>75</v>
       </c>
       <c r="D276" s="0">
-        <v>65</v>
+        <v>28000</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="0" t="s">
+        <v>605</v>
+      </c>
+      <c r="B277" s="0" t="s">
         <v>606</v>
       </c>
-      <c r="B277" s="0" t="s">
-        <v>607</v>
-      </c>
       <c r="C277" s="0" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="D277" s="0">
-        <v>65</v>
+        <v>34000</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="0" t="s">
+        <v>607</v>
+      </c>
+      <c r="B278" s="0" t="s">
         <v>608</v>
       </c>
-      <c r="B278" s="0" t="s">
-        <v>609</v>
-      </c>
       <c r="C278" s="0" t="s">
-        <v>52</v>
+        <v>477</v>
       </c>
       <c r="D278" s="0">
-        <v>92</v>
+        <v>243315</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="0" t="s">
+        <v>609</v>
+      </c>
+      <c r="B279" s="0" t="s">
         <v>610</v>
       </c>
-      <c r="B279" s="0" t="s">
-        <v>611</v>
-      </c>
       <c r="C279" s="0" t="s">
-        <v>52</v>
+        <v>477</v>
       </c>
       <c r="D279" s="0">
-        <v>33</v>
+        <v>196835</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="0" t="s">
+        <v>611</v>
+      </c>
+      <c r="B280" s="0" t="s">
         <v>612</v>
       </c>
-      <c r="B280" s="0" t="s">
-        <v>613</v>
-      </c>
       <c r="C280" s="0" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="D280" s="0">
-        <v>54.8</v>
+        <v>1760</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="0" t="s">
+        <v>613</v>
+      </c>
+      <c r="B281" s="0" t="s">
         <v>614</v>
       </c>
-      <c r="B281" s="0" t="s">
+      <c r="C281" s="0" t="s">
         <v>615</v>
       </c>
-      <c r="C281" s="0" t="s">
-        <v>341</v>
-      </c>
       <c r="D281" s="0">
-        <v>300</v>
+        <v>26350</v>
       </c>
     </row>
     <row r="282">
@@ -7270,10 +7348,10 @@
         <v>617</v>
       </c>
       <c r="C282" s="0" t="s">
-        <v>341</v>
+        <v>212</v>
       </c>
       <c r="D282" s="0">
-        <v>370</v>
+        <v>31250</v>
       </c>
     </row>
     <row r="283">
@@ -7284,10 +7362,10 @@
         <v>619</v>
       </c>
       <c r="C283" s="0" t="s">
-        <v>362</v>
+        <v>59</v>
       </c>
       <c r="D283" s="0">
-        <v>450</v>
+        <v>69</v>
       </c>
     </row>
     <row r="284">
@@ -7298,10 +7376,10 @@
         <v>621</v>
       </c>
       <c r="C284" s="0" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="D284" s="0">
-        <v>450</v>
+        <v>34.98</v>
       </c>
     </row>
     <row r="285">
@@ -7312,10 +7390,10 @@
         <v>623</v>
       </c>
       <c r="C285" s="0" t="s">
-        <v>15</v>
+        <v>59</v>
       </c>
       <c r="D285" s="0">
-        <v>450</v>
+        <v>34.98</v>
       </c>
     </row>
     <row r="286">
@@ -7326,38 +7404,38 @@
         <v>625</v>
       </c>
       <c r="C286" s="0" t="s">
-        <v>15</v>
+        <v>626</v>
       </c>
       <c r="D286" s="0">
-        <v>1650</v>
+        <v>65</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="0" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B287" s="0" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C287" s="0" t="s">
-        <v>15</v>
+        <v>52</v>
       </c>
       <c r="D287" s="0">
-        <v>2100</v>
+        <v>65</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="0" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
       <c r="B288" s="0" t="s">
         <v>629</v>
       </c>
       <c r="C288" s="0" t="s">
-        <v>15</v>
+        <v>59</v>
       </c>
       <c r="D288" s="0">
-        <v>1980</v>
+        <v>0</v>
       </c>
     </row>
     <row r="289">
@@ -7368,10 +7446,10 @@
         <v>631</v>
       </c>
       <c r="C289" s="0" t="s">
-        <v>15</v>
+        <v>52</v>
       </c>
       <c r="D289" s="0">
-        <v>2160</v>
+        <v>92</v>
       </c>
     </row>
     <row r="290">
@@ -7382,10 +7460,10 @@
         <v>633</v>
       </c>
       <c r="C290" s="0" t="s">
-        <v>15</v>
+        <v>52</v>
       </c>
       <c r="D290" s="0">
-        <v>1300</v>
+        <v>33</v>
       </c>
     </row>
     <row r="291">
@@ -7396,10 +7474,10 @@
         <v>635</v>
       </c>
       <c r="C291" s="0" t="s">
-        <v>15</v>
+        <v>52</v>
       </c>
       <c r="D291" s="0">
-        <v>2600</v>
+        <v>54.8</v>
       </c>
     </row>
     <row r="292">
@@ -7410,10 +7488,10 @@
         <v>637</v>
       </c>
       <c r="C292" s="0" t="s">
-        <v>15</v>
+        <v>59</v>
       </c>
       <c r="D292" s="0">
-        <v>2000</v>
+        <v>44</v>
       </c>
     </row>
     <row r="293">
@@ -7424,10 +7502,10 @@
         <v>639</v>
       </c>
       <c r="C293" s="0" t="s">
-        <v>15</v>
+        <v>346</v>
       </c>
       <c r="D293" s="0">
-        <v>6700</v>
+        <v>300</v>
       </c>
     </row>
     <row r="294">
@@ -7438,10 +7516,10 @@
         <v>641</v>
       </c>
       <c r="C294" s="0" t="s">
-        <v>15</v>
+        <v>346</v>
       </c>
       <c r="D294" s="0">
-        <v>1650</v>
+        <v>370</v>
       </c>
     </row>
     <row r="295">
@@ -7452,10 +7530,10 @@
         <v>643</v>
       </c>
       <c r="C295" s="0" t="s">
-        <v>15</v>
+        <v>367</v>
       </c>
       <c r="D295" s="0">
-        <v>1035</v>
+        <v>450</v>
       </c>
     </row>
     <row r="296">
@@ -7466,10 +7544,10 @@
         <v>645</v>
       </c>
       <c r="C296" s="0" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="D296" s="0">
-        <v>2600</v>
+        <v>450</v>
       </c>
     </row>
     <row r="297">
@@ -7483,7 +7561,7 @@
         <v>15</v>
       </c>
       <c r="D297" s="0">
-        <v>2400</v>
+        <v>450</v>
       </c>
     </row>
     <row r="298">
@@ -7494,10 +7572,10 @@
         <v>649</v>
       </c>
       <c r="C298" s="0" t="s">
-        <v>140</v>
+        <v>15</v>
       </c>
       <c r="D298" s="0">
-        <v>4730</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="299">
@@ -7508,10 +7586,10 @@
         <v>651</v>
       </c>
       <c r="C299" s="0" t="s">
-        <v>140</v>
+        <v>15</v>
       </c>
       <c r="D299" s="0">
-        <v>2517</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="300">
@@ -7522,10 +7600,10 @@
         <v>653</v>
       </c>
       <c r="C300" s="0" t="s">
-        <v>140</v>
+        <v>15</v>
       </c>
       <c r="D300" s="0">
-        <v>1190</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="301">
@@ -7536,10 +7614,10 @@
         <v>655</v>
       </c>
       <c r="C301" s="0" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="D301" s="0">
-        <v>7655.2</v>
+        <v>2160</v>
       </c>
     </row>
     <row r="302">
@@ -7550,10 +7628,10 @@
         <v>657</v>
       </c>
       <c r="C302" s="0" t="s">
-        <v>123</v>
+        <v>15</v>
       </c>
       <c r="D302" s="0">
-        <v>1790</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="303">
@@ -7564,10 +7642,10 @@
         <v>659</v>
       </c>
       <c r="C303" s="0" t="s">
-        <v>123</v>
+        <v>15</v>
       </c>
       <c r="D303" s="0">
-        <v>3016.53</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="304">
@@ -7578,10 +7656,10 @@
         <v>661</v>
       </c>
       <c r="C304" s="0" t="s">
-        <v>123</v>
+        <v>15</v>
       </c>
       <c r="D304" s="0">
-        <v>4800</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="305">
@@ -7592,10 +7670,10 @@
         <v>663</v>
       </c>
       <c r="C305" s="0" t="s">
-        <v>123</v>
+        <v>15</v>
       </c>
       <c r="D305" s="0">
-        <v>4450</v>
+        <v>6700</v>
       </c>
     </row>
     <row r="306">
@@ -7606,178 +7684,178 @@
         <v>665</v>
       </c>
       <c r="C306" s="0" t="s">
-        <v>666</v>
+        <v>15</v>
       </c>
       <c r="D306" s="0">
-        <v>0</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="0" t="s">
+        <v>666</v>
+      </c>
+      <c r="B307" s="0" t="s">
         <v>667</v>
       </c>
-      <c r="B307" s="0" t="s">
-        <v>668</v>
-      </c>
       <c r="C307" s="0" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="D307" s="0">
-        <v>494</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="0" t="s">
+        <v>668</v>
+      </c>
+      <c r="B308" s="0" t="s">
         <v>669</v>
       </c>
-      <c r="B308" s="0" t="s">
-        <v>670</v>
-      </c>
       <c r="C308" s="0" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="D308" s="0">
-        <v>665.3</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="0" t="s">
+        <v>670</v>
+      </c>
+      <c r="B309" s="0" t="s">
         <v>671</v>
       </c>
-      <c r="B309" s="0" t="s">
-        <v>672</v>
-      </c>
       <c r="C309" s="0" t="s">
-        <v>92</v>
+        <v>15</v>
       </c>
       <c r="D309" s="0">
-        <v>33940.5</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="0" t="s">
+        <v>672</v>
+      </c>
+      <c r="B310" s="0" t="s">
         <v>673</v>
       </c>
-      <c r="B310" s="0" t="s">
-        <v>674</v>
-      </c>
       <c r="C310" s="0" t="s">
-        <v>92</v>
+        <v>145</v>
       </c>
       <c r="D310" s="0">
-        <v>4525.4</v>
+        <v>4730</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="0" t="s">
+        <v>674</v>
+      </c>
+      <c r="B311" s="0" t="s">
         <v>675</v>
       </c>
-      <c r="B311" s="0" t="s">
-        <v>676</v>
-      </c>
       <c r="C311" s="0" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="D311" s="0">
-        <v>896</v>
+        <v>2517</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="0" t="s">
+        <v>676</v>
+      </c>
+      <c r="B312" s="0" t="s">
         <v>677</v>
       </c>
-      <c r="B312" s="0" t="s">
-        <v>678</v>
-      </c>
       <c r="C312" s="0" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="D312" s="0">
-        <v>1125</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="0" t="s">
+        <v>678</v>
+      </c>
+      <c r="B313" s="0" t="s">
         <v>679</v>
       </c>
-      <c r="B313" s="0" t="s">
-        <v>680</v>
-      </c>
       <c r="C313" s="0" t="s">
-        <v>92</v>
+        <v>28</v>
       </c>
       <c r="D313" s="0">
-        <v>332750</v>
+        <v>7655.2</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="0" t="s">
+        <v>680</v>
+      </c>
+      <c r="B314" s="0" t="s">
         <v>681</v>
       </c>
-      <c r="B314" s="0" t="s">
-        <v>682</v>
-      </c>
       <c r="C314" s="0" t="s">
-        <v>202</v>
+        <v>128</v>
       </c>
       <c r="D314" s="0">
-        <v>17440</v>
+        <v>1790</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="0" t="s">
+        <v>682</v>
+      </c>
+      <c r="B315" s="0" t="s">
         <v>683</v>
       </c>
-      <c r="B315" s="0" t="s">
-        <v>684</v>
-      </c>
       <c r="C315" s="0" t="s">
-        <v>202</v>
+        <v>128</v>
       </c>
       <c r="D315" s="0">
-        <v>4390</v>
+        <v>3016.53</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="0" t="s">
+        <v>684</v>
+      </c>
+      <c r="B316" s="0" t="s">
         <v>685</v>
       </c>
-      <c r="B316" s="0" t="s">
-        <v>686</v>
-      </c>
       <c r="C316" s="0" t="s">
-        <v>202</v>
+        <v>128</v>
       </c>
       <c r="D316" s="0">
-        <v>4390</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="0" t="s">
+        <v>686</v>
+      </c>
+      <c r="B317" s="0" t="s">
         <v>687</v>
       </c>
-      <c r="B317" s="0" t="s">
-        <v>688</v>
-      </c>
       <c r="C317" s="0" t="s">
-        <v>284</v>
+        <v>128</v>
       </c>
       <c r="D317" s="0">
-        <v>2250</v>
+        <v>4450</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="0" t="s">
+        <v>688</v>
+      </c>
+      <c r="B318" s="0" t="s">
         <v>689</v>
       </c>
-      <c r="B318" s="0" t="s">
+      <c r="C318" s="0" t="s">
         <v>690</v>
       </c>
-      <c r="C318" s="0" t="s">
-        <v>202</v>
-      </c>
       <c r="D318" s="0">
-        <v>3355</v>
+        <v>0</v>
       </c>
     </row>
     <row r="319">
@@ -7788,10 +7866,10 @@
         <v>692</v>
       </c>
       <c r="C319" s="0" t="s">
-        <v>210</v>
+        <v>28</v>
       </c>
       <c r="D319" s="0">
-        <v>7500</v>
+        <v>494</v>
       </c>
     </row>
     <row r="320">
@@ -7802,10 +7880,10 @@
         <v>694</v>
       </c>
       <c r="C320" s="0" t="s">
-        <v>92</v>
+        <v>28</v>
       </c>
       <c r="D320" s="0">
-        <v>25289</v>
+        <v>665.3</v>
       </c>
     </row>
     <row r="321">
@@ -7816,10 +7894,10 @@
         <v>696</v>
       </c>
       <c r="C321" s="0" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="D321" s="0">
-        <v>252890</v>
+        <v>33940.5</v>
       </c>
     </row>
     <row r="322">
@@ -7830,10 +7908,10 @@
         <v>698</v>
       </c>
       <c r="C322" s="0" t="s">
-        <v>52</v>
+        <v>97</v>
       </c>
       <c r="D322" s="0">
-        <v>160</v>
+        <v>4525.4</v>
       </c>
     </row>
     <row r="323">
@@ -7844,10 +7922,10 @@
         <v>700</v>
       </c>
       <c r="C323" s="0" t="s">
-        <v>21</v>
+        <v>156</v>
       </c>
       <c r="D323" s="0">
-        <v>285.6</v>
+        <v>896</v>
       </c>
     </row>
     <row r="324">
@@ -7858,10 +7936,10 @@
         <v>702</v>
       </c>
       <c r="C324" s="0" t="s">
-        <v>21</v>
+        <v>145</v>
       </c>
       <c r="D324" s="0">
-        <v>338</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="325">
@@ -7872,192 +7950,192 @@
         <v>704</v>
       </c>
       <c r="C325" s="0" t="s">
-        <v>705</v>
+        <v>97</v>
       </c>
       <c r="D325" s="0">
-        <v>770</v>
+        <v>332750</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="0" t="s">
+        <v>705</v>
+      </c>
+      <c r="B326" s="0" t="s">
         <v>706</v>
       </c>
-      <c r="B326" s="0" t="s">
-        <v>707</v>
-      </c>
       <c r="C326" s="0" t="s">
-        <v>708</v>
+        <v>207</v>
       </c>
       <c r="D326" s="0">
-        <v>770</v>
+        <v>17440</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="0" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="B327" s="0" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="C327" s="0" t="s">
-        <v>15</v>
+        <v>207</v>
       </c>
       <c r="D327" s="0">
-        <v>973.5</v>
+        <v>4390</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="0" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="B328" s="0" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="C328" s="0" t="s">
-        <v>21</v>
+        <v>207</v>
       </c>
       <c r="D328" s="0">
-        <v>507.08</v>
+        <v>4390</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="0" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="B329" s="0" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="C329" s="0" t="s">
-        <v>15</v>
+        <v>289</v>
       </c>
       <c r="D329" s="0">
-        <v>450</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="0" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="B330" s="0" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="C330" s="0" t="s">
-        <v>151</v>
+        <v>207</v>
       </c>
       <c r="D330" s="0">
-        <v>760</v>
+        <v>3355</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="0" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="B331" s="0" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="C331" s="0" t="s">
-        <v>284</v>
+        <v>215</v>
       </c>
       <c r="D331" s="0">
-        <v>5900</v>
+        <v>7500</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="0" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="B332" s="0" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="C332" s="0" t="s">
-        <v>284</v>
+        <v>97</v>
       </c>
       <c r="D332" s="0">
-        <v>2900</v>
+        <v>25289</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="0" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="B333" s="0" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="C333" s="0" t="s">
-        <v>140</v>
+        <v>97</v>
       </c>
       <c r="D333" s="0">
-        <v>935</v>
+        <v>252890</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="0" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="B334" s="0" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="C334" s="0" t="s">
-        <v>140</v>
+        <v>52</v>
       </c>
       <c r="D334" s="0">
-        <v>620</v>
+        <v>160</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="0" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="B335" s="0" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="C335" s="0" t="s">
-        <v>140</v>
+        <v>21</v>
       </c>
       <c r="D335" s="0">
-        <v>73</v>
+        <v>285.6</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" s="0" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="B336" s="0" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="C336" s="0" t="s">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="D336" s="0">
-        <v>11313.5</v>
+        <v>338</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" s="0" t="s">
+        <v>727</v>
+      </c>
+      <c r="B337" s="0" t="s">
+        <v>728</v>
+      </c>
+      <c r="C337" s="0" t="s">
         <v>729</v>
       </c>
-      <c r="B337" s="0" t="s">
-        <v>730</v>
-      </c>
-      <c r="C337" s="0" t="s">
-        <v>34</v>
-      </c>
       <c r="D337" s="0">
-        <v>400</v>
+        <v>770</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" s="0" t="s">
+        <v>730</v>
+      </c>
+      <c r="B338" s="0" t="s">
         <v>731</v>
       </c>
-      <c r="B338" s="0" t="s">
+      <c r="C338" s="0" t="s">
         <v>732</v>
       </c>
-      <c r="C338" s="0" t="s">
-        <v>362</v>
-      </c>
       <c r="D338" s="0">
-        <v>400</v>
+        <v>770</v>
       </c>
     </row>
     <row r="339">
@@ -8068,10 +8146,10 @@
         <v>734</v>
       </c>
       <c r="C339" s="0" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="D339" s="0">
-        <v>377</v>
+        <v>973.5</v>
       </c>
     </row>
     <row r="340">
@@ -8082,10 +8160,10 @@
         <v>736</v>
       </c>
       <c r="C340" s="0" t="s">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="D340" s="0">
-        <v>5726.32</v>
+        <v>507.08</v>
       </c>
     </row>
     <row r="341">
@@ -8096,10 +8174,10 @@
         <v>738</v>
       </c>
       <c r="C341" s="0" t="s">
-        <v>70</v>
+        <v>15</v>
       </c>
       <c r="D341" s="0">
-        <v>898</v>
+        <v>450</v>
       </c>
     </row>
     <row r="342">
@@ -8110,10 +8188,10 @@
         <v>740</v>
       </c>
       <c r="C342" s="0" t="s">
-        <v>123</v>
+        <v>156</v>
       </c>
       <c r="D342" s="0">
-        <v>4767</v>
+        <v>760</v>
       </c>
     </row>
     <row r="343">
@@ -8124,10 +8202,10 @@
         <v>742</v>
       </c>
       <c r="C343" s="0" t="s">
-        <v>34</v>
+        <v>289</v>
       </c>
       <c r="D343" s="0">
-        <v>650</v>
+        <v>5900</v>
       </c>
     </row>
     <row r="344">
@@ -8138,10 +8216,10 @@
         <v>744</v>
       </c>
       <c r="C344" s="0" t="s">
-        <v>70</v>
+        <v>289</v>
       </c>
       <c r="D344" s="0">
-        <v>650</v>
+        <v>2900</v>
       </c>
     </row>
     <row r="345">
@@ -8152,10 +8230,10 @@
         <v>746</v>
       </c>
       <c r="C345" s="0" t="s">
-        <v>15</v>
+        <v>145</v>
       </c>
       <c r="D345" s="0">
-        <v>2178</v>
+        <v>935</v>
       </c>
     </row>
     <row r="346">
@@ -8166,10 +8244,10 @@
         <v>748</v>
       </c>
       <c r="C346" s="0" t="s">
-        <v>92</v>
+        <v>145</v>
       </c>
       <c r="D346" s="0">
-        <v>7986</v>
+        <v>620</v>
       </c>
     </row>
     <row r="347">
@@ -8180,178 +8258,178 @@
         <v>750</v>
       </c>
       <c r="C347" s="0" t="s">
-        <v>751</v>
+        <v>145</v>
       </c>
       <c r="D347" s="0">
-        <v>1910</v>
+        <v>73</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" s="0" t="s">
+        <v>751</v>
+      </c>
+      <c r="B348" s="0" t="s">
         <v>752</v>
       </c>
-      <c r="B348" s="0" t="s">
-        <v>753</v>
-      </c>
       <c r="C348" s="0" t="s">
-        <v>151</v>
+        <v>97</v>
       </c>
       <c r="D348" s="0">
-        <v>900</v>
+        <v>11313.5</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" s="0" t="s">
+        <v>753</v>
+      </c>
+      <c r="B349" s="0" t="s">
         <v>754</v>
       </c>
-      <c r="B349" s="0" t="s">
-        <v>755</v>
-      </c>
       <c r="C349" s="0" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="D349" s="0">
-        <v>1722</v>
+        <v>400</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" s="0" t="s">
+        <v>755</v>
+      </c>
+      <c r="B350" s="0" t="s">
         <v>756</v>
       </c>
-      <c r="B350" s="0" t="s">
-        <v>757</v>
-      </c>
       <c r="C350" s="0" t="s">
-        <v>34</v>
+        <v>367</v>
       </c>
       <c r="D350" s="0">
-        <v>59000</v>
+        <v>400</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" s="0" t="s">
+        <v>757</v>
+      </c>
+      <c r="B351" s="0" t="s">
         <v>758</v>
       </c>
-      <c r="B351" s="0" t="s">
-        <v>759</v>
-      </c>
       <c r="C351" s="0" t="s">
-        <v>151</v>
+        <v>21</v>
       </c>
       <c r="D351" s="0">
-        <v>750</v>
+        <v>377</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" s="0" t="s">
+        <v>759</v>
+      </c>
+      <c r="B352" s="0" t="s">
         <v>760</v>
       </c>
-      <c r="B352" s="0" t="s">
-        <v>761</v>
-      </c>
       <c r="C352" s="0" t="s">
-        <v>151</v>
+        <v>45</v>
       </c>
       <c r="D352" s="0">
-        <v>1212</v>
+        <v>5726.32</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" s="0" t="s">
+        <v>761</v>
+      </c>
+      <c r="B353" s="0" t="s">
         <v>762</v>
       </c>
-      <c r="B353" s="0" t="s">
-        <v>763</v>
-      </c>
       <c r="C353" s="0" t="s">
-        <v>151</v>
+        <v>75</v>
       </c>
       <c r="D353" s="0">
-        <v>1300</v>
+        <v>898</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" s="0" t="s">
+        <v>763</v>
+      </c>
+      <c r="B354" s="0" t="s">
         <v>764</v>
       </c>
-      <c r="B354" s="0" t="s">
-        <v>765</v>
-      </c>
       <c r="C354" s="0" t="s">
-        <v>151</v>
+        <v>128</v>
       </c>
       <c r="D354" s="0">
-        <v>1500</v>
+        <v>4767</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" s="0" t="s">
+        <v>765</v>
+      </c>
+      <c r="B355" s="0" t="s">
         <v>766</v>
       </c>
-      <c r="B355" s="0" t="s">
-        <v>767</v>
-      </c>
       <c r="C355" s="0" t="s">
-        <v>151</v>
+        <v>34</v>
       </c>
       <c r="D355" s="0">
-        <v>1400</v>
+        <v>650</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" s="0" t="s">
+        <v>767</v>
+      </c>
+      <c r="B356" s="0" t="s">
         <v>768</v>
       </c>
-      <c r="B356" s="0" t="s">
-        <v>769</v>
-      </c>
       <c r="C356" s="0" t="s">
-        <v>264</v>
+        <v>75</v>
       </c>
       <c r="D356" s="0">
-        <v>11959</v>
+        <v>650</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" s="0" t="s">
+        <v>769</v>
+      </c>
+      <c r="B357" s="0" t="s">
         <v>770</v>
       </c>
-      <c r="B357" s="0" t="s">
-        <v>771</v>
-      </c>
       <c r="C357" s="0" t="s">
-        <v>140</v>
+        <v>15</v>
       </c>
       <c r="D357" s="0">
-        <v>365</v>
+        <v>2178</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" s="0" t="s">
+        <v>771</v>
+      </c>
+      <c r="B358" s="0" t="s">
         <v>772</v>
       </c>
-      <c r="B358" s="0" t="s">
-        <v>773</v>
-      </c>
       <c r="C358" s="0" t="s">
-        <v>284</v>
+        <v>97</v>
       </c>
       <c r="D358" s="0">
-        <v>1450</v>
+        <v>7986</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" s="0" t="s">
+        <v>773</v>
+      </c>
+      <c r="B359" s="0" t="s">
         <v>774</v>
       </c>
-      <c r="B359" s="0" t="s">
+      <c r="C359" s="0" t="s">
         <v>775</v>
       </c>
-      <c r="C359" s="0" t="s">
-        <v>92</v>
-      </c>
       <c r="D359" s="0">
-        <v>7320.5</v>
+        <v>1910</v>
       </c>
     </row>
     <row r="360">
@@ -8362,7 +8440,7 @@
         <v>777</v>
       </c>
       <c r="C360" s="0" t="s">
-        <v>15</v>
+        <v>156</v>
       </c>
       <c r="D360" s="0">
         <v>900</v>
@@ -8376,10 +8454,10 @@
         <v>779</v>
       </c>
       <c r="C361" s="0" t="s">
-        <v>284</v>
+        <v>21</v>
       </c>
       <c r="D361" s="0">
-        <v>566</v>
+        <v>1722</v>
       </c>
     </row>
     <row r="362">
@@ -8390,10 +8468,10 @@
         <v>781</v>
       </c>
       <c r="C362" s="0" t="s">
-        <v>472</v>
+        <v>34</v>
       </c>
       <c r="D362" s="0">
-        <v>64925</v>
+        <v>59000</v>
       </c>
     </row>
     <row r="363">
@@ -8404,10 +8482,10 @@
         <v>783</v>
       </c>
       <c r="C363" s="0" t="s">
-        <v>15</v>
+        <v>156</v>
       </c>
       <c r="D363" s="0">
-        <v>1100</v>
+        <v>750</v>
       </c>
     </row>
     <row r="364">
@@ -8418,10 +8496,10 @@
         <v>785</v>
       </c>
       <c r="C364" s="0" t="s">
-        <v>21</v>
+        <v>156</v>
       </c>
       <c r="D364" s="0">
-        <v>1623</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="365">
@@ -8432,10 +8510,10 @@
         <v>787</v>
       </c>
       <c r="C365" s="0" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="D365" s="0">
-        <v>1269</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="366">
@@ -8446,10 +8524,10 @@
         <v>789</v>
       </c>
       <c r="C366" s="0" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="D366" s="0">
-        <v>4712</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="367">
@@ -8460,10 +8538,10 @@
         <v>791</v>
       </c>
       <c r="C367" s="0" t="s">
-        <v>28</v>
+        <v>156</v>
       </c>
       <c r="D367" s="0">
-        <v>1250</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="368">
@@ -8474,10 +8552,10 @@
         <v>793</v>
       </c>
       <c r="C368" s="0" t="s">
-        <v>28</v>
+        <v>269</v>
       </c>
       <c r="D368" s="0">
-        <v>1986</v>
+        <v>11959</v>
       </c>
     </row>
     <row r="369">
@@ -8488,10 +8566,10 @@
         <v>795</v>
       </c>
       <c r="C369" s="0" t="s">
-        <v>15</v>
+        <v>145</v>
       </c>
       <c r="D369" s="0">
-        <v>450</v>
+        <v>365</v>
       </c>
     </row>
     <row r="370">
@@ -8502,10 +8580,10 @@
         <v>797</v>
       </c>
       <c r="C370" s="0" t="s">
-        <v>15</v>
+        <v>289</v>
       </c>
       <c r="D370" s="0">
-        <v>825</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="371">
@@ -8516,10 +8594,10 @@
         <v>799</v>
       </c>
       <c r="C371" s="0" t="s">
-        <v>15</v>
+        <v>97</v>
       </c>
       <c r="D371" s="0">
-        <v>825</v>
+        <v>7320.5</v>
       </c>
     </row>
     <row r="372">
@@ -8530,10 +8608,10 @@
         <v>801</v>
       </c>
       <c r="C372" s="0" t="s">
-        <v>382</v>
+        <v>15</v>
       </c>
       <c r="D372" s="0">
-        <v>134775.6</v>
+        <v>900</v>
       </c>
     </row>
     <row r="373">
@@ -8544,10 +8622,10 @@
         <v>803</v>
       </c>
       <c r="C373" s="0" t="s">
-        <v>382</v>
+        <v>289</v>
       </c>
       <c r="D373" s="0">
-        <v>175991.55</v>
+        <v>566</v>
       </c>
     </row>
     <row r="374">
@@ -8558,10 +8636,10 @@
         <v>805</v>
       </c>
       <c r="C374" s="0" t="s">
-        <v>70</v>
+        <v>477</v>
       </c>
       <c r="D374" s="0">
-        <v>3427</v>
+        <v>64925</v>
       </c>
     </row>
     <row r="375">
@@ -8572,10 +8650,10 @@
         <v>807</v>
       </c>
       <c r="C375" s="0" t="s">
-        <v>70</v>
+        <v>15</v>
       </c>
       <c r="D375" s="0">
-        <v>10618</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="376">
@@ -8586,10 +8664,10 @@
         <v>809</v>
       </c>
       <c r="C376" s="0" t="s">
-        <v>284</v>
+        <v>21</v>
       </c>
       <c r="D376" s="0">
-        <v>515</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="377">
@@ -8600,10 +8678,10 @@
         <v>811</v>
       </c>
       <c r="C377" s="0" t="s">
-        <v>37</v>
+        <v>145</v>
       </c>
       <c r="D377" s="0">
-        <v>515</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="378">
@@ -8614,10 +8692,10 @@
         <v>813</v>
       </c>
       <c r="C378" s="0" t="s">
-        <v>52</v>
+        <v>145</v>
       </c>
       <c r="D378" s="0">
-        <v>10000</v>
+        <v>4712</v>
       </c>
     </row>
     <row r="379">
@@ -8628,10 +8706,10 @@
         <v>815</v>
       </c>
       <c r="C379" s="0" t="s">
-        <v>472</v>
+        <v>28</v>
       </c>
       <c r="D379" s="0">
-        <v>213700</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="380">
@@ -8642,10 +8720,10 @@
         <v>817</v>
       </c>
       <c r="C380" s="0" t="s">
-        <v>472</v>
+        <v>28</v>
       </c>
       <c r="D380" s="0">
-        <v>257000</v>
+        <v>1986</v>
       </c>
     </row>
     <row r="381">
@@ -8656,10 +8734,10 @@
         <v>819</v>
       </c>
       <c r="C381" s="0" t="s">
-        <v>70</v>
+        <v>15</v>
       </c>
       <c r="D381" s="0">
-        <v>10522</v>
+        <v>450</v>
       </c>
     </row>
     <row r="382">
@@ -8670,10 +8748,10 @@
         <v>821</v>
       </c>
       <c r="C382" s="0" t="s">
-        <v>70</v>
+        <v>15</v>
       </c>
       <c r="D382" s="0">
-        <v>19481</v>
+        <v>825</v>
       </c>
     </row>
     <row r="383">
@@ -8684,332 +8762,332 @@
         <v>823</v>
       </c>
       <c r="C383" s="0" t="s">
-        <v>824</v>
+        <v>15</v>
       </c>
       <c r="D383" s="0">
-        <v>1080</v>
+        <v>825</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" s="0" t="s">
+        <v>824</v>
+      </c>
+      <c r="B384" s="0" t="s">
         <v>825</v>
       </c>
-      <c r="B384" s="0" t="s">
-        <v>826</v>
-      </c>
       <c r="C384" s="0" t="s">
-        <v>18</v>
+        <v>387</v>
       </c>
       <c r="D384" s="0">
-        <v>586.49</v>
+        <v>134775.6</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" s="0" t="s">
+        <v>826</v>
+      </c>
+      <c r="B385" s="0" t="s">
         <v>827</v>
       </c>
-      <c r="B385" s="0" t="s">
-        <v>828</v>
-      </c>
       <c r="C385" s="0" t="s">
-        <v>829</v>
+        <v>387</v>
       </c>
       <c r="D385" s="0">
-        <v>520</v>
+        <v>175991.55</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" s="0" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="B386" s="0" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="C386" s="0" t="s">
-        <v>829</v>
+        <v>75</v>
       </c>
       <c r="D386" s="0">
-        <v>300</v>
+        <v>3427</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" s="0" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="B387" s="0" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="C387" s="0" t="s">
-        <v>15</v>
+        <v>75</v>
       </c>
       <c r="D387" s="0">
-        <v>2200</v>
+        <v>10618</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" s="0" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="B388" s="0" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="C388" s="0" t="s">
-        <v>15</v>
+        <v>289</v>
       </c>
       <c r="D388" s="0">
-        <v>2800</v>
+        <v>515</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" s="0" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="B389" s="0" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="C389" s="0" t="s">
-        <v>92</v>
+        <v>37</v>
       </c>
       <c r="D389" s="0">
-        <v>5190.9</v>
+        <v>515</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" s="0" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="B390" s="0" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="C390" s="0" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="D390" s="0">
-        <v>2969</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" s="0" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="B391" s="0" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="C391" s="0" t="s">
-        <v>34</v>
+        <v>477</v>
       </c>
       <c r="D391" s="0">
-        <v>3800</v>
+        <v>213700</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" s="0" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="B392" s="0" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="C392" s="0" t="s">
-        <v>15</v>
+        <v>477</v>
       </c>
       <c r="D392" s="0">
-        <v>4000</v>
+        <v>257000</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" s="0" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="B393" s="0" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="C393" s="0" t="s">
-        <v>846</v>
+        <v>75</v>
       </c>
       <c r="D393" s="0">
-        <v>3800</v>
+        <v>10522</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" s="0" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
       <c r="B394" s="0" t="s">
-        <v>848</v>
+        <v>845</v>
       </c>
       <c r="C394" s="0" t="s">
-        <v>21</v>
+        <v>75</v>
       </c>
       <c r="D394" s="0">
-        <v>353</v>
+        <v>19481</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" s="0" t="s">
-        <v>849</v>
+        <v>846</v>
       </c>
       <c r="B395" s="0" t="s">
-        <v>850</v>
+        <v>847</v>
       </c>
       <c r="C395" s="0" t="s">
-        <v>110</v>
+        <v>848</v>
       </c>
       <c r="D395" s="0">
-        <v>1800</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" s="0" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="B396" s="0" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="C396" s="0" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D396" s="0">
-        <v>2948</v>
+        <v>586.49</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" s="0" t="s">
+        <v>851</v>
+      </c>
+      <c r="B397" s="0" t="s">
+        <v>852</v>
+      </c>
+      <c r="C397" s="0" t="s">
         <v>853</v>
       </c>
-      <c r="B397" s="0" t="s">
-        <v>854</v>
-      </c>
-      <c r="C397" s="0" t="s">
-        <v>92</v>
-      </c>
       <c r="D397" s="0">
-        <v>146.41</v>
+        <v>520</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" s="0" t="s">
+        <v>854</v>
+      </c>
+      <c r="B398" s="0" t="s">
         <v>855</v>
       </c>
-      <c r="B398" s="0" t="s">
-        <v>856</v>
-      </c>
       <c r="C398" s="0" t="s">
-        <v>210</v>
+        <v>853</v>
       </c>
       <c r="D398" s="0">
-        <v>65537</v>
+        <v>300</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" s="0" t="s">
+        <v>856</v>
+      </c>
+      <c r="B399" s="0" t="s">
         <v>857</v>
       </c>
-      <c r="B399" s="0" t="s">
-        <v>858</v>
-      </c>
       <c r="C399" s="0" t="s">
-        <v>140</v>
+        <v>34</v>
       </c>
       <c r="D399" s="0">
-        <v>4130.4</v>
+        <v>630</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" s="0" t="s">
+        <v>858</v>
+      </c>
+      <c r="B400" s="0" t="s">
         <v>859</v>
       </c>
-      <c r="B400" s="0" t="s">
-        <v>860</v>
-      </c>
       <c r="C400" s="0" t="s">
-        <v>140</v>
+        <v>15</v>
       </c>
       <c r="D400" s="0">
-        <v>4283</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" s="0" t="s">
+        <v>860</v>
+      </c>
+      <c r="B401" s="0" t="s">
         <v>861</v>
       </c>
-      <c r="B401" s="0" t="s">
-        <v>862</v>
-      </c>
       <c r="C401" s="0" t="s">
-        <v>140</v>
+        <v>15</v>
       </c>
       <c r="D401" s="0">
-        <v>6524.8</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" s="0" t="s">
+        <v>862</v>
+      </c>
+      <c r="B402" s="0" t="s">
         <v>863</v>
       </c>
-      <c r="B402" s="0" t="s">
-        <v>864</v>
-      </c>
       <c r="C402" s="0" t="s">
-        <v>311</v>
+        <v>97</v>
       </c>
       <c r="D402" s="0">
-        <v>570</v>
+        <v>5190.9</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" s="0" t="s">
+        <v>864</v>
+      </c>
+      <c r="B403" s="0" t="s">
         <v>865</v>
       </c>
-      <c r="B403" s="0" t="s">
-        <v>866</v>
-      </c>
       <c r="C403" s="0" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D403" s="0">
-        <v>550</v>
+        <v>2969</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" s="0" t="s">
+        <v>866</v>
+      </c>
+      <c r="B404" s="0" t="s">
         <v>867</v>
       </c>
-      <c r="B404" s="0" t="s">
-        <v>868</v>
-      </c>
       <c r="C404" s="0" t="s">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="D404" s="0">
-        <v>153</v>
+        <v>3800</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" s="0" t="s">
+        <v>868</v>
+      </c>
+      <c r="B405" s="0" t="s">
         <v>869</v>
       </c>
-      <c r="B405" s="0" t="s">
-        <v>870</v>
-      </c>
       <c r="C405" s="0" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="D405" s="0">
-        <v>740.7</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" s="0" t="s">
+        <v>870</v>
+      </c>
+      <c r="B406" s="0" t="s">
         <v>871</v>
       </c>
-      <c r="B406" s="0" t="s">
+      <c r="C406" s="0" t="s">
         <v>872</v>
       </c>
-      <c r="C406" s="0" t="s">
-        <v>59</v>
-      </c>
       <c r="D406" s="0">
-        <v>101000</v>
+        <v>3800</v>
       </c>
     </row>
     <row r="407">
@@ -9020,10 +9098,10 @@
         <v>874</v>
       </c>
       <c r="C407" s="0" t="s">
-        <v>123</v>
+        <v>21</v>
       </c>
       <c r="D407" s="0">
-        <v>6251</v>
+        <v>353</v>
       </c>
     </row>
     <row r="408">
@@ -9034,10 +9112,10 @@
         <v>876</v>
       </c>
       <c r="C408" s="0" t="s">
-        <v>140</v>
+        <v>115</v>
       </c>
       <c r="D408" s="0">
-        <v>883</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="409">
@@ -9048,10 +9126,10 @@
         <v>878</v>
       </c>
       <c r="C409" s="0" t="s">
-        <v>92</v>
+        <v>15</v>
       </c>
       <c r="D409" s="0">
-        <v>1164.66</v>
+        <v>2948</v>
       </c>
     </row>
     <row r="410">
@@ -9062,10 +9140,10 @@
         <v>880</v>
       </c>
       <c r="C410" s="0" t="s">
-        <v>151</v>
+        <v>97</v>
       </c>
       <c r="D410" s="0">
-        <v>360</v>
+        <v>146.41</v>
       </c>
     </row>
     <row r="411">
@@ -9076,10 +9154,10 @@
         <v>882</v>
       </c>
       <c r="C411" s="0" t="s">
-        <v>151</v>
+        <v>215</v>
       </c>
       <c r="D411" s="0">
-        <v>450</v>
+        <v>65537</v>
       </c>
     </row>
     <row r="412">
@@ -9090,10 +9168,10 @@
         <v>884</v>
       </c>
       <c r="C412" s="0" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="D412" s="0">
-        <v>2150</v>
+        <v>4130.4</v>
       </c>
     </row>
     <row r="413">
@@ -9104,10 +9182,10 @@
         <v>886</v>
       </c>
       <c r="C413" s="0" t="s">
-        <v>582</v>
+        <v>145</v>
       </c>
       <c r="D413" s="0">
-        <v>25192.82</v>
+        <v>4283</v>
       </c>
     </row>
     <row r="414">
@@ -9118,10 +9196,10 @@
         <v>888</v>
       </c>
       <c r="C414" s="0" t="s">
-        <v>70</v>
+        <v>145</v>
       </c>
       <c r="D414" s="0">
-        <v>3500</v>
+        <v>6524.8</v>
       </c>
     </row>
     <row r="415">
@@ -9132,10 +9210,10 @@
         <v>890</v>
       </c>
       <c r="C415" s="0" t="s">
-        <v>175</v>
+        <v>316</v>
       </c>
       <c r="D415" s="0">
-        <v>600</v>
+        <v>570</v>
       </c>
     </row>
     <row r="416">
@@ -9146,192 +9224,192 @@
         <v>892</v>
       </c>
       <c r="C416" s="0" t="s">
-        <v>893</v>
+        <v>75</v>
       </c>
       <c r="D416" s="0">
-        <v>1080</v>
+        <v>550</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" s="0" t="s">
+        <v>893</v>
+      </c>
+      <c r="B417" s="0" t="s">
         <v>894</v>
       </c>
-      <c r="B417" s="0" t="s">
-        <v>895</v>
-      </c>
       <c r="C417" s="0" t="s">
-        <v>341</v>
+        <v>52</v>
       </c>
       <c r="D417" s="0">
-        <v>8628</v>
+        <v>153</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" s="0" t="s">
+        <v>895</v>
+      </c>
+      <c r="B418" s="0" t="s">
         <v>896</v>
       </c>
-      <c r="B418" s="0" t="s">
-        <v>897</v>
-      </c>
       <c r="C418" s="0" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="D418" s="0">
-        <v>27991.54</v>
+        <v>740.7</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" s="0" t="s">
+        <v>897</v>
+      </c>
+      <c r="B419" s="0" t="s">
         <v>898</v>
       </c>
-      <c r="B419" s="0" t="s">
-        <v>899</v>
-      </c>
       <c r="C419" s="0" t="s">
-        <v>140</v>
+        <v>64</v>
       </c>
       <c r="D419" s="0">
-        <v>1020</v>
+        <v>101000</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" s="0" t="s">
+        <v>899</v>
+      </c>
+      <c r="B420" s="0" t="s">
         <v>900</v>
       </c>
-      <c r="B420" s="0" t="s">
-        <v>901</v>
-      </c>
       <c r="C420" s="0" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="D420" s="0">
-        <v>4106</v>
+        <v>6251</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" s="0" t="s">
+        <v>901</v>
+      </c>
+      <c r="B421" s="0" t="s">
         <v>902</v>
       </c>
-      <c r="B421" s="0" t="s">
-        <v>903</v>
-      </c>
       <c r="C421" s="0" t="s">
-        <v>284</v>
+        <v>145</v>
       </c>
       <c r="D421" s="0">
-        <v>450</v>
+        <v>883</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" s="0" t="s">
+        <v>903</v>
+      </c>
+      <c r="B422" s="0" t="s">
         <v>904</v>
       </c>
-      <c r="B422" s="0" t="s">
-        <v>905</v>
-      </c>
       <c r="C422" s="0" t="s">
-        <v>45</v>
+        <v>97</v>
       </c>
       <c r="D422" s="0">
-        <v>6518.32</v>
+        <v>1164.66</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" s="0" t="s">
+        <v>905</v>
+      </c>
+      <c r="B423" s="0" t="s">
         <v>906</v>
       </c>
-      <c r="B423" s="0" t="s">
-        <v>907</v>
-      </c>
       <c r="C423" s="0" t="s">
-        <v>45</v>
+        <v>156</v>
       </c>
       <c r="D423" s="0">
-        <v>2940.72</v>
+        <v>360</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" s="0" t="s">
+        <v>907</v>
+      </c>
+      <c r="B424" s="0" t="s">
         <v>908</v>
       </c>
-      <c r="B424" s="0" t="s">
-        <v>909</v>
-      </c>
       <c r="C424" s="0" t="s">
-        <v>45</v>
+        <v>156</v>
       </c>
       <c r="D424" s="0">
-        <v>2090.06</v>
+        <v>450</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" s="0" t="s">
+        <v>909</v>
+      </c>
+      <c r="B425" s="0" t="s">
         <v>910</v>
       </c>
-      <c r="B425" s="0" t="s">
-        <v>911</v>
-      </c>
       <c r="C425" s="0" t="s">
-        <v>45</v>
+        <v>156</v>
       </c>
       <c r="D425" s="0">
-        <v>30612.7</v>
+        <v>2150</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" s="0" t="s">
+        <v>911</v>
+      </c>
+      <c r="B426" s="0" t="s">
         <v>912</v>
       </c>
-      <c r="B426" s="0" t="s">
-        <v>913</v>
-      </c>
       <c r="C426" s="0" t="s">
-        <v>45</v>
+        <v>602</v>
       </c>
       <c r="D426" s="0">
-        <v>2370.33</v>
+        <v>25192.82</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" s="0" t="s">
+        <v>913</v>
+      </c>
+      <c r="B427" s="0" t="s">
         <v>914</v>
       </c>
-      <c r="B427" s="0" t="s">
-        <v>915</v>
-      </c>
       <c r="C427" s="0" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="D427" s="0">
-        <v>6550.3</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" s="0" t="s">
+        <v>915</v>
+      </c>
+      <c r="B428" s="0" t="s">
         <v>916</v>
       </c>
-      <c r="B428" s="0" t="s">
-        <v>917</v>
-      </c>
       <c r="C428" s="0" t="s">
-        <v>45</v>
+        <v>180</v>
       </c>
       <c r="D428" s="0">
-        <v>5277.18</v>
+        <v>600</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" s="0" t="s">
+        <v>917</v>
+      </c>
+      <c r="B429" s="0" t="s">
         <v>918</v>
       </c>
-      <c r="B429" s="0" t="s">
+      <c r="C429" s="0" t="s">
         <v>919</v>
       </c>
-      <c r="C429" s="0" t="s">
-        <v>207</v>
-      </c>
       <c r="D429" s="0">
-        <v>510</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="430">
@@ -9342,10 +9420,10 @@
         <v>921</v>
       </c>
       <c r="C430" s="0" t="s">
-        <v>37</v>
+        <v>346</v>
       </c>
       <c r="D430" s="0">
-        <v>510</v>
+        <v>8628</v>
       </c>
     </row>
     <row r="431">
@@ -9356,738 +9434,738 @@
         <v>923</v>
       </c>
       <c r="C431" s="0" t="s">
-        <v>924</v>
+        <v>40</v>
       </c>
       <c r="D431" s="0">
-        <v>626</v>
+        <v>27991.54</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" s="0" t="s">
+        <v>924</v>
+      </c>
+      <c r="B432" s="0" t="s">
         <v>925</v>
       </c>
-      <c r="B432" s="0" t="s">
-        <v>926</v>
-      </c>
       <c r="C432" s="0" t="s">
-        <v>924</v>
+        <v>145</v>
       </c>
       <c r="D432" s="0">
-        <v>626</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" s="0" t="s">
+        <v>926</v>
+      </c>
+      <c r="B433" s="0" t="s">
         <v>927</v>
       </c>
-      <c r="B433" s="0" t="s">
-        <v>928</v>
-      </c>
       <c r="C433" s="0" t="s">
-        <v>924</v>
+        <v>145</v>
       </c>
       <c r="D433" s="0">
-        <v>626</v>
+        <v>4106</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" s="0" t="s">
+        <v>928</v>
+      </c>
+      <c r="B434" s="0" t="s">
         <v>929</v>
       </c>
-      <c r="B434" s="0" t="s">
-        <v>930</v>
-      </c>
       <c r="C434" s="0" t="s">
-        <v>924</v>
+        <v>289</v>
       </c>
       <c r="D434" s="0">
-        <v>342</v>
+        <v>450</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" s="0" t="s">
+        <v>930</v>
+      </c>
+      <c r="B435" s="0" t="s">
         <v>931</v>
       </c>
-      <c r="B435" s="0" t="s">
-        <v>932</v>
-      </c>
       <c r="C435" s="0" t="s">
-        <v>924</v>
+        <v>45</v>
       </c>
       <c r="D435" s="0">
-        <v>342</v>
+        <v>6518.32</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" s="0" t="s">
+        <v>932</v>
+      </c>
+      <c r="B436" s="0" t="s">
         <v>933</v>
       </c>
-      <c r="B436" s="0" t="s">
-        <v>934</v>
-      </c>
       <c r="C436" s="0" t="s">
-        <v>924</v>
+        <v>45</v>
       </c>
       <c r="D436" s="0">
-        <v>342</v>
+        <v>2940.72</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" s="0" t="s">
+        <v>934</v>
+      </c>
+      <c r="B437" s="0" t="s">
         <v>935</v>
       </c>
-      <c r="B437" s="0" t="s">
-        <v>936</v>
-      </c>
       <c r="C437" s="0" t="s">
-        <v>924</v>
+        <v>45</v>
       </c>
       <c r="D437" s="0">
-        <v>0</v>
+        <v>2090.06</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" s="0" t="s">
+        <v>936</v>
+      </c>
+      <c r="B438" s="0" t="s">
         <v>937</v>
       </c>
-      <c r="B438" s="0" t="s">
-        <v>938</v>
-      </c>
       <c r="C438" s="0" t="s">
-        <v>924</v>
+        <v>45</v>
       </c>
       <c r="D438" s="0">
-        <v>0</v>
+        <v>30612.7</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" s="0" t="s">
+        <v>938</v>
+      </c>
+      <c r="B439" s="0" t="s">
         <v>939</v>
       </c>
-      <c r="B439" s="0" t="s">
-        <v>940</v>
-      </c>
       <c r="C439" s="0" t="s">
-        <v>941</v>
+        <v>45</v>
       </c>
       <c r="D439" s="0">
-        <v>453</v>
+        <v>2370.33</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" s="0" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
       <c r="B440" s="0" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
       <c r="C440" s="0" t="s">
-        <v>924</v>
+        <v>45</v>
       </c>
       <c r="D440" s="0">
-        <v>453</v>
+        <v>6550.3</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" s="0" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="B441" s="0" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="C441" s="0" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="D441" s="0">
-        <v>19322</v>
+        <v>5277.18</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" s="0" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
       <c r="B442" s="0" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="C442" s="0" t="s">
-        <v>34</v>
+        <v>212</v>
       </c>
       <c r="D442" s="0">
-        <v>430</v>
+        <v>510</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" s="0" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
       <c r="B443" s="0" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
       <c r="C443" s="0" t="s">
-        <v>284</v>
+        <v>37</v>
       </c>
       <c r="D443" s="0">
-        <v>430</v>
+        <v>510</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" s="0" t="s">
+        <v>948</v>
+      </c>
+      <c r="B444" s="0" t="s">
+        <v>949</v>
+      </c>
+      <c r="C444" s="0" t="s">
         <v>950</v>
       </c>
-      <c r="B444" s="0" t="s">
-        <v>951</v>
-      </c>
-      <c r="C444" s="0" t="s">
-        <v>115</v>
-      </c>
       <c r="D444" s="0">
-        <v>14000</v>
+        <v>626</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" s="0" t="s">
+        <v>951</v>
+      </c>
+      <c r="B445" s="0" t="s">
         <v>952</v>
       </c>
-      <c r="B445" s="0" t="s">
-        <v>953</v>
-      </c>
       <c r="C445" s="0" t="s">
-        <v>140</v>
+        <v>950</v>
       </c>
       <c r="D445" s="0">
-        <v>12049</v>
+        <v>626</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" s="0" t="s">
+        <v>953</v>
+      </c>
+      <c r="B446" s="0" t="s">
         <v>954</v>
       </c>
-      <c r="B446" s="0" t="s">
-        <v>955</v>
-      </c>
       <c r="C446" s="0" t="s">
-        <v>140</v>
+        <v>950</v>
       </c>
       <c r="D446" s="0">
-        <v>2895</v>
+        <v>626</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" s="0" t="s">
+        <v>955</v>
+      </c>
+      <c r="B447" s="0" t="s">
         <v>956</v>
       </c>
-      <c r="B447" s="0" t="s">
-        <v>957</v>
-      </c>
       <c r="C447" s="0" t="s">
-        <v>92</v>
+        <v>950</v>
       </c>
       <c r="D447" s="0">
-        <v>266200</v>
+        <v>342</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" s="0" t="s">
+        <v>957</v>
+      </c>
+      <c r="B448" s="0" t="s">
         <v>958</v>
       </c>
-      <c r="B448" s="0" t="s">
-        <v>959</v>
-      </c>
       <c r="C448" s="0" t="s">
-        <v>92</v>
+        <v>950</v>
       </c>
       <c r="D448" s="0">
-        <v>194991.5</v>
+        <v>342</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" s="0" t="s">
+        <v>959</v>
+      </c>
+      <c r="B449" s="0" t="s">
         <v>960</v>
       </c>
-      <c r="B449" s="0" t="s">
-        <v>961</v>
-      </c>
       <c r="C449" s="0" t="s">
-        <v>92</v>
+        <v>950</v>
       </c>
       <c r="D449" s="0">
-        <v>289492.5</v>
+        <v>342</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" s="0" t="s">
+        <v>961</v>
+      </c>
+      <c r="B450" s="0" t="s">
         <v>962</v>
       </c>
-      <c r="B450" s="0" t="s">
-        <v>963</v>
-      </c>
       <c r="C450" s="0" t="s">
-        <v>964</v>
+        <v>950</v>
       </c>
       <c r="D450" s="0">
-        <v>13722.52</v>
+        <v>0</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" s="0" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="B451" s="0" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
       <c r="C451" s="0" t="s">
-        <v>964</v>
+        <v>950</v>
       </c>
       <c r="D451" s="0">
-        <v>15072</v>
+        <v>0</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" s="0" t="s">
+        <v>965</v>
+      </c>
+      <c r="B452" s="0" t="s">
+        <v>966</v>
+      </c>
+      <c r="C452" s="0" t="s">
         <v>967</v>
       </c>
-      <c r="B452" s="0" t="s">
-        <v>968</v>
-      </c>
-      <c r="C452" s="0" t="s">
-        <v>964</v>
-      </c>
       <c r="D452" s="0">
-        <v>6555.64</v>
+        <v>453</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" s="0" t="s">
+        <v>968</v>
+      </c>
+      <c r="B453" s="0" t="s">
         <v>969</v>
       </c>
-      <c r="B453" s="0" t="s">
-        <v>970</v>
-      </c>
       <c r="C453" s="0" t="s">
-        <v>964</v>
+        <v>950</v>
       </c>
       <c r="D453" s="0">
-        <v>8964.61</v>
+        <v>453</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" s="0" t="s">
+        <v>970</v>
+      </c>
+      <c r="B454" s="0" t="s">
         <v>971</v>
       </c>
-      <c r="B454" s="0" t="s">
-        <v>972</v>
-      </c>
       <c r="C454" s="0" t="s">
-        <v>964</v>
+        <v>75</v>
       </c>
       <c r="D454" s="0">
-        <v>11735</v>
+        <v>19322</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" s="0" t="s">
+        <v>972</v>
+      </c>
+      <c r="B455" s="0" t="s">
         <v>973</v>
       </c>
-      <c r="B455" s="0" t="s">
-        <v>974</v>
-      </c>
       <c r="C455" s="0" t="s">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="D455" s="0">
-        <v>4276</v>
+        <v>430</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" s="0" t="s">
+        <v>974</v>
+      </c>
+      <c r="B456" s="0" t="s">
         <v>975</v>
       </c>
-      <c r="B456" s="0" t="s">
-        <v>976</v>
-      </c>
       <c r="C456" s="0" t="s">
-        <v>140</v>
+        <v>289</v>
       </c>
       <c r="D456" s="0">
-        <v>3930</v>
+        <v>430</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" s="0" t="s">
+        <v>976</v>
+      </c>
+      <c r="B457" s="0" t="s">
         <v>977</v>
       </c>
-      <c r="B457" s="0" t="s">
-        <v>978</v>
-      </c>
       <c r="C457" s="0" t="s">
-        <v>92</v>
+        <v>120</v>
       </c>
       <c r="D457" s="0">
-        <v>4392.3</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" s="0" t="s">
+        <v>978</v>
+      </c>
+      <c r="B458" s="0" t="s">
         <v>979</v>
       </c>
-      <c r="B458" s="0" t="s">
-        <v>980</v>
-      </c>
       <c r="C458" s="0" t="s">
-        <v>981</v>
+        <v>145</v>
       </c>
       <c r="D458" s="0">
-        <v>5254.41</v>
+        <v>12049</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" s="0" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="B459" s="0" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="C459" s="0" t="s">
-        <v>52</v>
+        <v>145</v>
       </c>
       <c r="D459" s="0">
-        <v>1297</v>
+        <v>2895</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" s="0" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
       <c r="B460" s="0" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="C460" s="0" t="s">
-        <v>52</v>
+        <v>97</v>
       </c>
       <c r="D460" s="0">
-        <v>298</v>
+        <v>266200</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" s="0" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="B461" s="0" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="C461" s="0" t="s">
-        <v>52</v>
+        <v>97</v>
       </c>
       <c r="D461" s="0">
-        <v>596</v>
+        <v>194991.5</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" s="0" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="B462" s="0" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="C462" s="0" t="s">
-        <v>379</v>
+        <v>97</v>
       </c>
       <c r="D462" s="0">
-        <v>65142.6</v>
+        <v>289492.5</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" s="0" t="s">
+        <v>988</v>
+      </c>
+      <c r="B463" s="0" t="s">
+        <v>989</v>
+      </c>
+      <c r="C463" s="0" t="s">
         <v>990</v>
       </c>
-      <c r="B463" s="0" t="s">
-        <v>991</v>
-      </c>
-      <c r="C463" s="0" t="s">
-        <v>379</v>
-      </c>
       <c r="D463" s="0">
-        <v>23482.7</v>
+        <v>13722.52</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" s="0" t="s">
+        <v>991</v>
+      </c>
+      <c r="B464" s="0" t="s">
         <v>992</v>
       </c>
-      <c r="B464" s="0" t="s">
-        <v>993</v>
-      </c>
       <c r="C464" s="0" t="s">
-        <v>28</v>
+        <v>990</v>
       </c>
       <c r="D464" s="0">
-        <v>6029.59</v>
+        <v>15072</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" s="0" t="s">
+        <v>993</v>
+      </c>
+      <c r="B465" s="0" t="s">
         <v>994</v>
       </c>
-      <c r="B465" s="0" t="s">
-        <v>995</v>
-      </c>
       <c r="C465" s="0" t="s">
-        <v>52</v>
+        <v>990</v>
       </c>
       <c r="D465" s="0">
-        <v>12000</v>
+        <v>6555.64</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" s="0" t="s">
+        <v>995</v>
+      </c>
+      <c r="B466" s="0" t="s">
         <v>996</v>
       </c>
-      <c r="B466" s="0" t="s">
-        <v>997</v>
-      </c>
       <c r="C466" s="0" t="s">
-        <v>52</v>
+        <v>990</v>
       </c>
       <c r="D466" s="0">
-        <v>17425</v>
+        <v>8964.61</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" s="0" t="s">
+        <v>997</v>
+      </c>
+      <c r="B467" s="0" t="s">
         <v>998</v>
       </c>
-      <c r="B467" s="0" t="s">
-        <v>999</v>
-      </c>
       <c r="C467" s="0" t="s">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="D467" s="0">
-        <v>1958</v>
+        <v>11735</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" s="0" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="B468" s="0" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="C468" s="0" t="s">
-        <v>1003</v>
+        <v>75</v>
       </c>
       <c r="D468" s="0">
-        <v>2282.3</v>
+        <v>4276</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" s="0" t="s">
-        <v>1004</v>
+        <v>1001</v>
       </c>
       <c r="B469" s="0" t="s">
-        <v>1005</v>
+        <v>1002</v>
       </c>
       <c r="C469" s="0" t="s">
-        <v>1006</v>
+        <v>145</v>
       </c>
       <c r="D469" s="0">
-        <v>386</v>
+        <v>3930</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" s="0" t="s">
-        <v>1007</v>
+        <v>1003</v>
       </c>
       <c r="B470" s="0" t="s">
-        <v>1008</v>
+        <v>1004</v>
       </c>
       <c r="C470" s="0" t="s">
-        <v>1009</v>
+        <v>97</v>
       </c>
       <c r="D470" s="0">
-        <v>385.4</v>
+        <v>4392.3</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" s="0" t="s">
-        <v>1010</v>
+        <v>1005</v>
       </c>
       <c r="B471" s="0" t="s">
-        <v>1011</v>
+        <v>1006</v>
       </c>
       <c r="C471" s="0" t="s">
-        <v>92</v>
+        <v>1007</v>
       </c>
       <c r="D471" s="0">
-        <v>296147.5</v>
+        <v>5254.41</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" s="0" t="s">
-        <v>1012</v>
+        <v>1008</v>
       </c>
       <c r="B472" s="0" t="s">
-        <v>1013</v>
+        <v>1009</v>
       </c>
       <c r="C472" s="0" t="s">
-        <v>123</v>
+        <v>52</v>
       </c>
       <c r="D472" s="0">
-        <v>1890</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" s="0" t="s">
-        <v>1014</v>
+        <v>1010</v>
       </c>
       <c r="B473" s="0" t="s">
-        <v>1015</v>
+        <v>1011</v>
       </c>
       <c r="C473" s="0" t="s">
-        <v>582</v>
+        <v>52</v>
       </c>
       <c r="D473" s="0">
-        <v>83000</v>
+        <v>298</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" s="0" t="s">
-        <v>1016</v>
+        <v>1012</v>
       </c>
       <c r="B474" s="0" t="s">
-        <v>1017</v>
+        <v>1013</v>
       </c>
       <c r="C474" s="0" t="s">
-        <v>140</v>
+        <v>52</v>
       </c>
       <c r="D474" s="0">
-        <v>99</v>
+        <v>596</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" s="0" t="s">
-        <v>1018</v>
+        <v>1014</v>
       </c>
       <c r="B475" s="0" t="s">
-        <v>1019</v>
+        <v>1015</v>
       </c>
       <c r="C475" s="0" t="s">
-        <v>70</v>
+        <v>384</v>
       </c>
       <c r="D475" s="0">
-        <v>950</v>
+        <v>65142.6</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" s="0" t="s">
-        <v>1020</v>
+        <v>1016</v>
       </c>
       <c r="B476" s="0" t="s">
-        <v>1021</v>
+        <v>1017</v>
       </c>
       <c r="C476" s="0" t="s">
-        <v>472</v>
+        <v>384</v>
       </c>
       <c r="D476" s="0">
-        <v>398107</v>
+        <v>23482.7</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" s="0" t="s">
-        <v>1022</v>
+        <v>1018</v>
       </c>
       <c r="B477" s="0" t="s">
-        <v>1023</v>
+        <v>1019</v>
       </c>
       <c r="C477" s="0" t="s">
-        <v>160</v>
+        <v>28</v>
       </c>
       <c r="D477" s="0">
-        <v>2200</v>
+        <v>6029.59</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" s="0" t="s">
-        <v>1024</v>
+        <v>1020</v>
       </c>
       <c r="B478" s="0" t="s">
-        <v>1025</v>
+        <v>1021</v>
       </c>
       <c r="C478" s="0" t="s">
-        <v>207</v>
+        <v>52</v>
       </c>
       <c r="D478" s="0">
-        <v>41000</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" s="0" t="s">
-        <v>1026</v>
+        <v>1022</v>
       </c>
       <c r="B479" s="0" t="s">
-        <v>1027</v>
+        <v>1023</v>
       </c>
       <c r="C479" s="0" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="D479" s="0">
-        <v>5790</v>
+        <v>17425</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" s="0" t="s">
-        <v>1028</v>
+        <v>1024</v>
       </c>
       <c r="B480" s="0" t="s">
-        <v>1029</v>
+        <v>1025</v>
       </c>
       <c r="C480" s="0" t="s">
-        <v>924</v>
+        <v>1026</v>
       </c>
       <c r="D480" s="0">
-        <v>880</v>
+        <v>1958</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" s="0" t="s">
-        <v>1030</v>
+        <v>1027</v>
       </c>
       <c r="B481" s="0" t="s">
-        <v>1031</v>
+        <v>1028</v>
       </c>
       <c r="C481" s="0" t="s">
-        <v>924</v>
+        <v>1029</v>
       </c>
       <c r="D481" s="0">
-        <v>880</v>
+        <v>2282.3</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" s="0" t="s">
+        <v>1030</v>
+      </c>
+      <c r="B482" s="0" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C482" s="0" t="s">
         <v>1032</v>
       </c>
-      <c r="B482" s="0" t="s">
-        <v>1033</v>
-      </c>
-      <c r="C482" s="0" t="s">
-        <v>924</v>
-      </c>
       <c r="D482" s="0">
-        <v>880</v>
+        <v>386</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" s="0" t="s">
+        <v>1033</v>
+      </c>
+      <c r="B483" s="0" t="s">
         <v>1034</v>
       </c>
-      <c r="B483" s="0" t="s">
+      <c r="C483" s="0" t="s">
         <v>1035</v>
       </c>
-      <c r="C483" s="0" t="s">
-        <v>21</v>
-      </c>
       <c r="D483" s="0">
-        <v>563.36</v>
+        <v>385.4</v>
       </c>
     </row>
     <row r="484">
@@ -10098,10 +10176,10 @@
         <v>1037</v>
       </c>
       <c r="C484" s="0" t="s">
-        <v>15</v>
+        <v>97</v>
       </c>
       <c r="D484" s="0">
-        <v>3520</v>
+        <v>296147.5</v>
       </c>
     </row>
     <row r="485">
@@ -10112,10 +10190,10 @@
         <v>1039</v>
       </c>
       <c r="C485" s="0" t="s">
-        <v>15</v>
+        <v>128</v>
       </c>
       <c r="D485" s="0">
-        <v>2600</v>
+        <v>1890</v>
       </c>
     </row>
     <row r="486">
@@ -10126,10 +10204,10 @@
         <v>1041</v>
       </c>
       <c r="C486" s="0" t="s">
-        <v>284</v>
+        <v>602</v>
       </c>
       <c r="D486" s="0">
-        <v>3700</v>
+        <v>83000</v>
       </c>
     </row>
     <row r="487">
@@ -10140,10 +10218,10 @@
         <v>1043</v>
       </c>
       <c r="C487" s="0" t="s">
-        <v>284</v>
+        <v>145</v>
       </c>
       <c r="D487" s="0">
-        <v>2600</v>
+        <v>99</v>
       </c>
     </row>
     <row r="488">
@@ -10154,10 +10232,10 @@
         <v>1045</v>
       </c>
       <c r="C488" s="0" t="s">
-        <v>15</v>
+        <v>75</v>
       </c>
       <c r="D488" s="0">
-        <v>2235</v>
+        <v>950</v>
       </c>
     </row>
     <row r="489">
@@ -10168,10 +10246,10 @@
         <v>1047</v>
       </c>
       <c r="C489" s="0" t="s">
-        <v>15</v>
+        <v>477</v>
       </c>
       <c r="D489" s="0">
-        <v>3850</v>
+        <v>398107</v>
       </c>
     </row>
     <row r="490">
@@ -10182,290 +10260,290 @@
         <v>1049</v>
       </c>
       <c r="C490" s="0" t="s">
-        <v>1050</v>
+        <v>165</v>
       </c>
       <c r="D490" s="0">
-        <v>1</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" s="0" t="s">
+        <v>1050</v>
+      </c>
+      <c r="B491" s="0" t="s">
         <v>1051</v>
       </c>
-      <c r="B491" s="0" t="s">
-        <v>1052</v>
-      </c>
       <c r="C491" s="0" t="s">
-        <v>28</v>
+        <v>212</v>
       </c>
       <c r="D491" s="0">
-        <v>15189</v>
+        <v>41000</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" s="0" t="s">
+        <v>1052</v>
+      </c>
+      <c r="B492" s="0" t="s">
         <v>1053</v>
       </c>
-      <c r="B492" s="0" t="s">
-        <v>1054</v>
-      </c>
       <c r="C492" s="0" t="s">
-        <v>379</v>
+        <v>75</v>
       </c>
       <c r="D492" s="0">
-        <v>3859.93</v>
+        <v>5790</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" s="0" t="s">
+        <v>1054</v>
+      </c>
+      <c r="B493" s="0" t="s">
         <v>1055</v>
       </c>
-      <c r="B493" s="0" t="s">
-        <v>1056</v>
-      </c>
       <c r="C493" s="0" t="s">
-        <v>379</v>
+        <v>950</v>
       </c>
       <c r="D493" s="0">
-        <v>11751.49</v>
+        <v>880</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" s="0" t="s">
+        <v>1056</v>
+      </c>
+      <c r="B494" s="0" t="s">
         <v>1057</v>
       </c>
-      <c r="B494" s="0" t="s">
-        <v>1058</v>
-      </c>
       <c r="C494" s="0" t="s">
-        <v>341</v>
+        <v>950</v>
       </c>
       <c r="D494" s="0">
-        <v>6000</v>
+        <v>880</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" s="0" t="s">
+        <v>1058</v>
+      </c>
+      <c r="B495" s="0" t="s">
         <v>1059</v>
       </c>
-      <c r="B495" s="0" t="s">
-        <v>1060</v>
-      </c>
       <c r="C495" s="0" t="s">
-        <v>341</v>
+        <v>950</v>
       </c>
       <c r="D495" s="0">
-        <v>3000</v>
+        <v>880</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" s="0" t="s">
+        <v>1060</v>
+      </c>
+      <c r="B496" s="0" t="s">
         <v>1061</v>
       </c>
-      <c r="B496" s="0" t="s">
-        <v>1062</v>
-      </c>
       <c r="C496" s="0" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="D496" s="0">
-        <v>618</v>
+        <v>563.36</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" s="0" t="s">
+        <v>1062</v>
+      </c>
+      <c r="B497" s="0" t="s">
         <v>1063</v>
       </c>
-      <c r="B497" s="0" t="s">
-        <v>1064</v>
-      </c>
       <c r="C497" s="0" t="s">
-        <v>1065</v>
+        <v>15</v>
       </c>
       <c r="D497" s="0">
-        <v>24600</v>
+        <v>3520</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" s="0" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
       <c r="B498" s="0" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="C498" s="0" t="s">
-        <v>105</v>
+        <v>15</v>
       </c>
       <c r="D498" s="0">
-        <v>0</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" s="0" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="B499" s="0" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="C499" s="0" t="s">
-        <v>92</v>
+        <v>289</v>
       </c>
       <c r="D499" s="0">
-        <v>43590.25</v>
+        <v>3700</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" s="0" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="B500" s="0" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="C500" s="0" t="s">
-        <v>472</v>
+        <v>289</v>
       </c>
       <c r="D500" s="0">
-        <v>213700</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" s="0" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="B501" s="0" t="s">
-        <v>1073</v>
+        <v>1071</v>
       </c>
       <c r="C501" s="0" t="s">
-        <v>379</v>
+        <v>15</v>
       </c>
       <c r="D501" s="0">
-        <v>77429.29</v>
+        <v>2235</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" s="0" t="s">
-        <v>1074</v>
+        <v>1072</v>
       </c>
       <c r="B502" s="0" t="s">
-        <v>1075</v>
+        <v>1073</v>
       </c>
       <c r="C502" s="0" t="s">
-        <v>379</v>
+        <v>15</v>
       </c>
       <c r="D502" s="0">
-        <v>42913.42</v>
+        <v>3850</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" s="0" t="s">
+        <v>1074</v>
+      </c>
+      <c r="B503" s="0" t="s">
+        <v>1075</v>
+      </c>
+      <c r="C503" s="0" t="s">
         <v>1076</v>
       </c>
-      <c r="B503" s="0" t="s">
-        <v>1077</v>
-      </c>
-      <c r="C503" s="0" t="s">
-        <v>379</v>
-      </c>
       <c r="D503" s="0">
-        <v>88806.25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" s="0" t="s">
+        <v>1077</v>
+      </c>
+      <c r="B504" s="0" t="s">
         <v>1078</v>
       </c>
-      <c r="B504" s="0" t="s">
-        <v>1079</v>
-      </c>
       <c r="C504" s="0" t="s">
-        <v>379</v>
+        <v>28</v>
       </c>
       <c r="D504" s="0">
-        <v>50781.52</v>
+        <v>15189</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" s="0" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B505" s="0" t="s">
         <v>1080</v>
       </c>
-      <c r="B505" s="0" t="s">
-        <v>1081</v>
-      </c>
       <c r="C505" s="0" t="s">
-        <v>21</v>
+        <v>384</v>
       </c>
       <c r="D505" s="0">
-        <v>1600</v>
+        <v>3859.93</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" s="0" t="s">
+        <v>1081</v>
+      </c>
+      <c r="B506" s="0" t="s">
         <v>1082</v>
       </c>
-      <c r="B506" s="0" t="s">
-        <v>1083</v>
-      </c>
       <c r="C506" s="0" t="s">
-        <v>28</v>
+        <v>384</v>
       </c>
       <c r="D506" s="0">
-        <v>3521.4</v>
+        <v>11751.49</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" s="0" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B507" s="0" t="s">
         <v>1084</v>
       </c>
-      <c r="B507" s="0" t="s">
-        <v>1085</v>
-      </c>
       <c r="C507" s="0" t="s">
-        <v>28</v>
+        <v>346</v>
       </c>
       <c r="D507" s="0">
-        <v>3987</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" s="0" t="s">
+        <v>1085</v>
+      </c>
+      <c r="B508" s="0" t="s">
         <v>1086</v>
       </c>
-      <c r="B508" s="0" t="s">
-        <v>1087</v>
-      </c>
       <c r="C508" s="0" t="s">
-        <v>28</v>
+        <v>346</v>
       </c>
       <c r="D508" s="0">
-        <v>4086.37</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" s="0" t="s">
+        <v>1087</v>
+      </c>
+      <c r="B509" s="0" t="s">
         <v>1088</v>
       </c>
-      <c r="B509" s="0" t="s">
-        <v>1089</v>
-      </c>
       <c r="C509" s="0" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="D509" s="0">
-        <v>3382.65</v>
+        <v>618</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" s="0" t="s">
+        <v>1089</v>
+      </c>
+      <c r="B510" s="0" t="s">
         <v>1090</v>
       </c>
-      <c r="B510" s="0" t="s">
+      <c r="C510" s="0" t="s">
         <v>1091</v>
       </c>
-      <c r="C510" s="0" t="s">
-        <v>160</v>
-      </c>
       <c r="D510" s="0">
-        <v>430</v>
+        <v>24600</v>
       </c>
     </row>
     <row r="511">
@@ -10476,9 +10554,191 @@
         <v>1093</v>
       </c>
       <c r="C511" s="0" t="s">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="D511" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" s="0" t="s">
+        <v>1094</v>
+      </c>
+      <c r="B512" s="0" t="s">
+        <v>1095</v>
+      </c>
+      <c r="C512" s="0" t="s">
+        <v>97</v>
+      </c>
+      <c r="D512" s="0">
+        <v>43590.25</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" s="0" t="s">
+        <v>1096</v>
+      </c>
+      <c r="B513" s="0" t="s">
+        <v>1097</v>
+      </c>
+      <c r="C513" s="0" t="s">
+        <v>477</v>
+      </c>
+      <c r="D513" s="0">
+        <v>213700</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" s="0" t="s">
+        <v>1098</v>
+      </c>
+      <c r="B514" s="0" t="s">
+        <v>1099</v>
+      </c>
+      <c r="C514" s="0" t="s">
+        <v>384</v>
+      </c>
+      <c r="D514" s="0">
+        <v>77429.29</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" s="0" t="s">
+        <v>1100</v>
+      </c>
+      <c r="B515" s="0" t="s">
+        <v>1101</v>
+      </c>
+      <c r="C515" s="0" t="s">
+        <v>384</v>
+      </c>
+      <c r="D515" s="0">
+        <v>42913.42</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="0" t="s">
+        <v>1102</v>
+      </c>
+      <c r="B516" s="0" t="s">
+        <v>1103</v>
+      </c>
+      <c r="C516" s="0" t="s">
+        <v>384</v>
+      </c>
+      <c r="D516" s="0">
+        <v>88806.25</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" s="0" t="s">
+        <v>1104</v>
+      </c>
+      <c r="B517" s="0" t="s">
+        <v>1105</v>
+      </c>
+      <c r="C517" s="0" t="s">
+        <v>384</v>
+      </c>
+      <c r="D517" s="0">
+        <v>50781.52</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" s="0" t="s">
+        <v>1106</v>
+      </c>
+      <c r="B518" s="0" t="s">
+        <v>1107</v>
+      </c>
+      <c r="C518" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="D518" s="0">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" s="0" t="s">
+        <v>1108</v>
+      </c>
+      <c r="B519" s="0" t="s">
+        <v>1109</v>
+      </c>
+      <c r="C519" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="D519" s="0">
+        <v>3521.4</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" s="0" t="s">
+        <v>1110</v>
+      </c>
+      <c r="B520" s="0" t="s">
+        <v>1111</v>
+      </c>
+      <c r="C520" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="D520" s="0">
+        <v>3987</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" s="0" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B521" s="0" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C521" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="D521" s="0">
+        <v>4086.37</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" s="0" t="s">
+        <v>1114</v>
+      </c>
+      <c r="B522" s="0" t="s">
+        <v>1115</v>
+      </c>
+      <c r="C522" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="D522" s="0">
+        <v>3382.65</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" s="0" t="s">
+        <v>1116</v>
+      </c>
+      <c r="B523" s="0" t="s">
+        <v>1117</v>
+      </c>
+      <c r="C523" s="0" t="s">
+        <v>165</v>
+      </c>
+      <c r="D523" s="0">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" s="0" t="s">
+        <v>1118</v>
+      </c>
+      <c r="B524" s="0" t="s">
+        <v>1119</v>
+      </c>
+      <c r="C524" s="0" t="s">
+        <v>145</v>
+      </c>
+      <c r="D524" s="0">
         <v>495</v>
       </c>
     </row>

--- a/price_list.xlsx
+++ b/price_list.xlsx
@@ -3669,7 +3669,7 @@
         <v>45</v>
       </c>
       <c r="D19" s="0">
-        <v>3958.98</v>
+        <v>3886.27</v>
       </c>
     </row>
     <row r="20">
@@ -3697,7 +3697,7 @@
         <v>45</v>
       </c>
       <c r="D21" s="0">
-        <v>32755.59</v>
+        <v>32153.98</v>
       </c>
     </row>
     <row r="22">
@@ -5013,7 +5013,7 @@
         <v>45</v>
       </c>
       <c r="D115" s="0">
-        <v>5660.43</v>
+        <v>5556.47</v>
       </c>
     </row>
     <row r="116">
@@ -6231,7 +6231,7 @@
         <v>45</v>
       </c>
       <c r="D202" s="0">
-        <v>6127.17</v>
+        <v>6014.63</v>
       </c>
     </row>
     <row r="203">
@@ -8331,7 +8331,7 @@
         <v>45</v>
       </c>
       <c r="D352" s="0">
-        <v>5726.32</v>
+        <v>5621.15</v>
       </c>
     </row>
     <row r="353">
@@ -9493,7 +9493,7 @@
         <v>45</v>
       </c>
       <c r="D435" s="0">
-        <v>6518.32</v>
+        <v>6398.6</v>
       </c>
     </row>
     <row r="436">
@@ -9507,7 +9507,7 @@
         <v>45</v>
       </c>
       <c r="D436" s="0">
-        <v>2940.72</v>
+        <v>2886.7</v>
       </c>
     </row>
     <row r="437">
@@ -9521,7 +9521,7 @@
         <v>45</v>
       </c>
       <c r="D437" s="0">
-        <v>2090.06</v>
+        <v>2050.95</v>
       </c>
     </row>
     <row r="438">
@@ -9535,7 +9535,7 @@
         <v>45</v>
       </c>
       <c r="D438" s="0">
-        <v>30612.7</v>
+        <v>30050.45</v>
       </c>
     </row>
     <row r="439">
@@ -9549,7 +9549,7 @@
         <v>45</v>
       </c>
       <c r="D439" s="0">
-        <v>2370.33</v>
+        <v>2326.8</v>
       </c>
     </row>
     <row r="440">
@@ -9563,7 +9563,7 @@
         <v>45</v>
       </c>
       <c r="D440" s="0">
-        <v>6550.3</v>
+        <v>6429.95</v>
       </c>
     </row>
     <row r="441">
@@ -9577,7 +9577,7 @@
         <v>45</v>
       </c>
       <c r="D441" s="0">
-        <v>5277.18</v>
+        <v>5180.26</v>
       </c>
     </row>
     <row r="442">

--- a/price_list.xlsx
+++ b/price_list.xlsx
@@ -3977,7 +3977,7 @@
         <v>97</v>
       </c>
       <c r="D41" s="0">
-        <v>22627</v>
+        <v>23958</v>
       </c>
     </row>
     <row r="42">
@@ -4173,7 +4173,7 @@
         <v>97</v>
       </c>
       <c r="D55" s="0">
-        <v>35271.5</v>
+        <v>36602.5</v>
       </c>
     </row>
     <row r="56">
@@ -7953,7 +7953,7 @@
         <v>97</v>
       </c>
       <c r="D325" s="0">
-        <v>332750</v>
+        <v>342732.5</v>
       </c>
     </row>
     <row r="326">
@@ -8051,7 +8051,7 @@
         <v>97</v>
       </c>
       <c r="D332" s="0">
-        <v>25289</v>
+        <v>26620</v>
       </c>
     </row>
     <row r="333">
@@ -8065,7 +8065,7 @@
         <v>97</v>
       </c>
       <c r="D333" s="0">
-        <v>252890</v>
+        <v>266200</v>
       </c>
     </row>
     <row r="334">

--- a/price_list.xlsx
+++ b/price_list.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1120" uniqueCount="1120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1122" uniqueCount="1122">
   <si>
     <t>Solo Activos</t>
   </si>
@@ -1293,6 +1293,12 @@
   </si>
   <si>
     <t>FABOGESIC DICLO 75MG X 15 COMPR - 000024490</t>
+  </si>
+  <si>
+    <t>000024722</t>
+  </si>
+  <si>
+    <t>FABOGESIC PLEN 50/4MG X 10 COMPR - RELAX - SAVANT - 000024722</t>
   </si>
   <si>
     <t>000024436</t>
@@ -3437,7 +3443,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A2:D524"/>
+  <dimension ref="A2:D525"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
@@ -6091,7 +6097,7 @@
         <v>18</v>
       </c>
       <c r="D192" s="0">
-        <v>2184.81</v>
+        <v>320</v>
       </c>
     </row>
     <row r="193">
@@ -6102,10 +6108,10 @@
         <v>430</v>
       </c>
       <c r="C193" s="0" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D193" s="0">
-        <v>9748.5</v>
+        <v>2184.81</v>
       </c>
     </row>
     <row r="194">
@@ -6116,10 +6122,10 @@
         <v>432</v>
       </c>
       <c r="C194" s="0" t="s">
-        <v>75</v>
+        <v>28</v>
       </c>
       <c r="D194" s="0">
-        <v>430</v>
+        <v>9748.5</v>
       </c>
     </row>
     <row r="195">
@@ -6133,7 +6139,7 @@
         <v>75</v>
       </c>
       <c r="D195" s="0">
-        <v>800</v>
+        <v>430</v>
       </c>
     </row>
     <row r="196">
@@ -6144,10 +6150,10 @@
         <v>436</v>
       </c>
       <c r="C196" s="0" t="s">
-        <v>250</v>
+        <v>75</v>
       </c>
       <c r="D196" s="0">
-        <v>2040</v>
+        <v>800</v>
       </c>
     </row>
     <row r="197">
@@ -6161,7 +6167,7 @@
         <v>250</v>
       </c>
       <c r="D197" s="0">
-        <v>1380</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="198">
@@ -6172,10 +6178,10 @@
         <v>440</v>
       </c>
       <c r="C198" s="0" t="s">
-        <v>384</v>
+        <v>250</v>
       </c>
       <c r="D198" s="0">
-        <v>236458.17</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="199">
@@ -6186,10 +6192,10 @@
         <v>442</v>
       </c>
       <c r="C199" s="0" t="s">
-        <v>28</v>
+        <v>384</v>
       </c>
       <c r="D199" s="0">
-        <v>317.2</v>
+        <v>236458.17</v>
       </c>
     </row>
     <row r="200">
@@ -6200,10 +6206,10 @@
         <v>444</v>
       </c>
       <c r="C200" s="0" t="s">
-        <v>384</v>
+        <v>28</v>
       </c>
       <c r="D200" s="0">
-        <v>25100</v>
+        <v>317.2</v>
       </c>
     </row>
     <row r="201">
@@ -6214,24 +6220,24 @@
         <v>446</v>
       </c>
       <c r="C201" s="0" t="s">
-        <v>447</v>
+        <v>384</v>
       </c>
       <c r="D201" s="0">
-        <v>20900</v>
+        <v>25100</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="0" t="s">
+        <v>447</v>
+      </c>
+      <c r="B202" s="0" t="s">
         <v>448</v>
       </c>
-      <c r="B202" s="0" t="s">
+      <c r="C202" s="0" t="s">
         <v>449</v>
       </c>
-      <c r="C202" s="0" t="s">
-        <v>45</v>
-      </c>
       <c r="D202" s="0">
-        <v>6014.63</v>
+        <v>20900</v>
       </c>
     </row>
     <row r="203">
@@ -6242,10 +6248,10 @@
         <v>451</v>
       </c>
       <c r="C203" s="0" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="D203" s="0">
-        <v>1104.46</v>
+        <v>6014.63</v>
       </c>
     </row>
     <row r="204">
@@ -6256,10 +6262,10 @@
         <v>453</v>
       </c>
       <c r="C204" s="0" t="s">
-        <v>97</v>
+        <v>21</v>
       </c>
       <c r="D204" s="0">
-        <v>11646.25</v>
+        <v>1104.46</v>
       </c>
     </row>
     <row r="205">
@@ -6270,10 +6276,10 @@
         <v>455</v>
       </c>
       <c r="C205" s="0" t="s">
-        <v>128</v>
+        <v>97</v>
       </c>
       <c r="D205" s="0">
-        <v>6072</v>
+        <v>11646.25</v>
       </c>
     </row>
     <row r="206">
@@ -6284,10 +6290,10 @@
         <v>457</v>
       </c>
       <c r="C206" s="0" t="s">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="D206" s="0">
-        <v>400</v>
+        <v>6072</v>
       </c>
     </row>
     <row r="207">
@@ -6298,10 +6304,10 @@
         <v>459</v>
       </c>
       <c r="C207" s="0" t="s">
-        <v>21</v>
+        <v>75</v>
       </c>
       <c r="D207" s="0">
-        <v>409</v>
+        <v>400</v>
       </c>
     </row>
     <row r="208">
@@ -6312,10 +6318,10 @@
         <v>461</v>
       </c>
       <c r="C208" s="0" t="s">
-        <v>69</v>
+        <v>21</v>
       </c>
       <c r="D208" s="0">
-        <v>10748</v>
+        <v>409</v>
       </c>
     </row>
     <row r="209">
@@ -6329,7 +6335,7 @@
         <v>69</v>
       </c>
       <c r="D209" s="0">
-        <v>12898</v>
+        <v>10748</v>
       </c>
     </row>
     <row r="210">
@@ -6340,10 +6346,10 @@
         <v>465</v>
       </c>
       <c r="C210" s="0" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="D210" s="0">
-        <v>2000</v>
+        <v>12898</v>
       </c>
     </row>
     <row r="211">
@@ -6354,24 +6360,24 @@
         <v>467</v>
       </c>
       <c r="C211" s="0" t="s">
-        <v>468</v>
+        <v>52</v>
       </c>
       <c r="D211" s="0">
-        <v>0</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="0" t="s">
+        <v>468</v>
+      </c>
+      <c r="B212" s="0" t="s">
         <v>469</v>
       </c>
-      <c r="B212" s="0" t="s">
+      <c r="C212" s="0" t="s">
         <v>470</v>
       </c>
-      <c r="C212" s="0" t="s">
-        <v>15</v>
-      </c>
       <c r="D212" s="0">
-        <v>490</v>
+        <v>0</v>
       </c>
     </row>
     <row r="213">
@@ -6382,10 +6388,10 @@
         <v>472</v>
       </c>
       <c r="C213" s="0" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="D213" s="0">
-        <v>0</v>
+        <v>490</v>
       </c>
     </row>
     <row r="214">
@@ -6396,10 +6402,10 @@
         <v>474</v>
       </c>
       <c r="C214" s="0" t="s">
-        <v>165</v>
+        <v>34</v>
       </c>
       <c r="D214" s="0">
-        <v>25171.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="215">
@@ -6410,24 +6416,24 @@
         <v>476</v>
       </c>
       <c r="C215" s="0" t="s">
-        <v>477</v>
+        <v>165</v>
       </c>
       <c r="D215" s="0">
-        <v>70443</v>
+        <v>25171.1</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="0" t="s">
+        <v>477</v>
+      </c>
+      <c r="B216" s="0" t="s">
         <v>478</v>
       </c>
-      <c r="B216" s="0" t="s">
+      <c r="C216" s="0" t="s">
         <v>479</v>
       </c>
-      <c r="C216" s="0" t="s">
-        <v>156</v>
-      </c>
       <c r="D216" s="0">
-        <v>1800</v>
+        <v>70443</v>
       </c>
     </row>
     <row r="217">
@@ -6438,10 +6444,10 @@
         <v>481</v>
       </c>
       <c r="C217" s="0" t="s">
-        <v>34</v>
+        <v>156</v>
       </c>
       <c r="D217" s="0">
-        <v>0</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="218">
@@ -6452,10 +6458,10 @@
         <v>483</v>
       </c>
       <c r="C218" s="0" t="s">
-        <v>145</v>
+        <v>34</v>
       </c>
       <c r="D218" s="0">
-        <v>492.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="219">
@@ -6466,10 +6472,10 @@
         <v>485</v>
       </c>
       <c r="C219" s="0" t="s">
-        <v>212</v>
+        <v>145</v>
       </c>
       <c r="D219" s="0">
-        <v>495</v>
+        <v>492.2</v>
       </c>
     </row>
     <row r="220">
@@ -6480,10 +6486,10 @@
         <v>487</v>
       </c>
       <c r="C220" s="0" t="s">
-        <v>18</v>
+        <v>212</v>
       </c>
       <c r="D220" s="0">
-        <v>1819.72</v>
+        <v>495</v>
       </c>
     </row>
     <row r="221">
@@ -6497,7 +6503,7 @@
         <v>18</v>
       </c>
       <c r="D221" s="0">
-        <v>4391.81</v>
+        <v>1819.72</v>
       </c>
     </row>
     <row r="222">
@@ -6508,21 +6514,21 @@
         <v>491</v>
       </c>
       <c r="C222" s="0" t="s">
-        <v>492</v>
+        <v>18</v>
       </c>
       <c r="D222" s="0">
-        <v>4100</v>
+        <v>4391.81</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="0" t="s">
+        <v>492</v>
+      </c>
+      <c r="B223" s="0" t="s">
         <v>493</v>
       </c>
-      <c r="B223" s="0" t="s">
+      <c r="C223" s="0" t="s">
         <v>494</v>
-      </c>
-      <c r="C223" s="0" t="s">
-        <v>492</v>
       </c>
       <c r="D223" s="0">
         <v>4100</v>
@@ -6536,7 +6542,7 @@
         <v>496</v>
       </c>
       <c r="C224" s="0" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="D224" s="0">
         <v>4100</v>
@@ -6550,10 +6556,10 @@
         <v>498</v>
       </c>
       <c r="C225" s="0" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="D225" s="0">
-        <v>4200</v>
+        <v>4100</v>
       </c>
     </row>
     <row r="226">
@@ -6564,10 +6570,10 @@
         <v>500</v>
       </c>
       <c r="C226" s="0" t="s">
-        <v>52</v>
+        <v>494</v>
       </c>
       <c r="D226" s="0">
-        <v>4700</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="227">
@@ -6578,10 +6584,10 @@
         <v>502</v>
       </c>
       <c r="C227" s="0" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="D227" s="0">
-        <v>235</v>
+        <v>4700</v>
       </c>
     </row>
     <row r="228">
@@ -6620,10 +6626,10 @@
         <v>508</v>
       </c>
       <c r="C230" s="0" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="D230" s="0">
-        <v>4670</v>
+        <v>235</v>
       </c>
     </row>
     <row r="231">
@@ -6662,21 +6668,21 @@
         <v>514</v>
       </c>
       <c r="C233" s="0" t="s">
-        <v>515</v>
+        <v>52</v>
       </c>
       <c r="D233" s="0">
-        <v>265</v>
+        <v>4670</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="0" t="s">
+        <v>515</v>
+      </c>
+      <c r="B234" s="0" t="s">
         <v>516</v>
       </c>
-      <c r="B234" s="0" t="s">
+      <c r="C234" s="0" t="s">
         <v>517</v>
-      </c>
-      <c r="C234" s="0" t="s">
-        <v>515</v>
       </c>
       <c r="D234" s="0">
         <v>265</v>
@@ -6690,7 +6696,7 @@
         <v>519</v>
       </c>
       <c r="C235" s="0" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="D235" s="0">
         <v>265</v>
@@ -6704,7 +6710,7 @@
         <v>521</v>
       </c>
       <c r="C236" s="0" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="D236" s="0">
         <v>265</v>
@@ -6718,7 +6724,7 @@
         <v>523</v>
       </c>
       <c r="C237" s="0" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="D237" s="0">
         <v>265</v>
@@ -6732,7 +6738,7 @@
         <v>525</v>
       </c>
       <c r="C238" s="0" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="D238" s="0">
         <v>265</v>
@@ -6746,21 +6752,21 @@
         <v>527</v>
       </c>
       <c r="C239" s="0" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="D239" s="0">
-        <v>4700</v>
+        <v>265</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="0" t="s">
+        <v>528</v>
+      </c>
+      <c r="B240" s="0" t="s">
         <v>529</v>
       </c>
-      <c r="B240" s="0" t="s">
+      <c r="C240" s="0" t="s">
         <v>530</v>
-      </c>
-      <c r="C240" s="0" t="s">
-        <v>531</v>
       </c>
       <c r="D240" s="0">
         <v>4700</v>
@@ -6768,13 +6774,13 @@
     </row>
     <row r="241">
       <c r="A241" s="0" t="s">
+        <v>531</v>
+      </c>
+      <c r="B241" s="0" t="s">
         <v>532</v>
       </c>
-      <c r="B241" s="0" t="s">
+      <c r="C241" s="0" t="s">
         <v>533</v>
-      </c>
-      <c r="C241" s="0" t="s">
-        <v>52</v>
       </c>
       <c r="D241" s="0">
         <v>4700</v>
@@ -6791,7 +6797,7 @@
         <v>52</v>
       </c>
       <c r="D242" s="0">
-        <v>597</v>
+        <v>4700</v>
       </c>
     </row>
     <row r="243">
@@ -6805,7 +6811,7 @@
         <v>52</v>
       </c>
       <c r="D243" s="0">
-        <v>223</v>
+        <v>597</v>
       </c>
     </row>
     <row r="244">
@@ -6819,7 +6825,7 @@
         <v>52</v>
       </c>
       <c r="D244" s="0">
-        <v>247</v>
+        <v>223</v>
       </c>
     </row>
     <row r="245">
@@ -6830,10 +6836,10 @@
         <v>541</v>
       </c>
       <c r="C245" s="0" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="D245" s="0">
-        <v>5600</v>
+        <v>247</v>
       </c>
     </row>
     <row r="246">
@@ -6844,10 +6850,10 @@
         <v>543</v>
       </c>
       <c r="C246" s="0" t="s">
-        <v>156</v>
+        <v>37</v>
       </c>
       <c r="D246" s="0">
-        <v>6000</v>
+        <v>5600</v>
       </c>
     </row>
     <row r="247">
@@ -6858,10 +6864,10 @@
         <v>545</v>
       </c>
       <c r="C247" s="0" t="s">
-        <v>75</v>
+        <v>156</v>
       </c>
       <c r="D247" s="0">
-        <v>80000</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="248">
@@ -6875,7 +6881,7 @@
         <v>75</v>
       </c>
       <c r="D248" s="0">
-        <v>90000</v>
+        <v>80000</v>
       </c>
     </row>
     <row r="249">
@@ -6889,7 +6895,7 @@
         <v>75</v>
       </c>
       <c r="D249" s="0">
-        <v>110000</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="250">
@@ -6900,10 +6906,10 @@
         <v>551</v>
       </c>
       <c r="C250" s="0" t="s">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="D250" s="0">
-        <v>900</v>
+        <v>110000</v>
       </c>
     </row>
     <row r="251">
@@ -6914,10 +6920,10 @@
         <v>553</v>
       </c>
       <c r="C251" s="0" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="D251" s="0">
-        <v>1100</v>
+        <v>900</v>
       </c>
     </row>
     <row r="252">
@@ -6931,7 +6937,7 @@
         <v>15</v>
       </c>
       <c r="D252" s="0">
-        <v>2500</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="253">
@@ -6942,10 +6948,10 @@
         <v>557</v>
       </c>
       <c r="C253" s="0" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="D253" s="0">
-        <v>14608.16</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="254">
@@ -6956,10 +6962,10 @@
         <v>559</v>
       </c>
       <c r="C254" s="0" t="s">
-        <v>156</v>
+        <v>28</v>
       </c>
       <c r="D254" s="0">
-        <v>700</v>
+        <v>14608.16</v>
       </c>
     </row>
     <row r="255">
@@ -6970,7 +6976,7 @@
         <v>561</v>
       </c>
       <c r="C255" s="0" t="s">
-        <v>37</v>
+        <v>156</v>
       </c>
       <c r="D255" s="0">
         <v>700</v>
@@ -6984,10 +6990,10 @@
         <v>563</v>
       </c>
       <c r="C256" s="0" t="s">
-        <v>289</v>
+        <v>37</v>
       </c>
       <c r="D256" s="0">
-        <v>450</v>
+        <v>700</v>
       </c>
     </row>
     <row r="257">
@@ -6998,10 +7004,10 @@
         <v>565</v>
       </c>
       <c r="C257" s="0" t="s">
-        <v>15</v>
+        <v>289</v>
       </c>
       <c r="D257" s="0">
-        <v>555</v>
+        <v>450</v>
       </c>
     </row>
     <row r="258">
@@ -7015,7 +7021,7 @@
         <v>15</v>
       </c>
       <c r="D258" s="0">
-        <v>825</v>
+        <v>555</v>
       </c>
     </row>
     <row r="259">
@@ -7029,7 +7035,7 @@
         <v>15</v>
       </c>
       <c r="D259" s="0">
-        <v>36.3</v>
+        <v>825</v>
       </c>
     </row>
     <row r="260">
@@ -7043,7 +7049,7 @@
         <v>15</v>
       </c>
       <c r="D260" s="0">
-        <v>544.5</v>
+        <v>36.3</v>
       </c>
     </row>
     <row r="261">
@@ -7057,7 +7063,7 @@
         <v>15</v>
       </c>
       <c r="D261" s="0">
-        <v>750</v>
+        <v>544.5</v>
       </c>
     </row>
     <row r="262">
@@ -7068,10 +7074,10 @@
         <v>575</v>
       </c>
       <c r="C262" s="0" t="s">
-        <v>156</v>
+        <v>15</v>
       </c>
       <c r="D262" s="0">
-        <v>1130</v>
+        <v>750</v>
       </c>
     </row>
     <row r="263">
@@ -7082,10 +7088,10 @@
         <v>577</v>
       </c>
       <c r="C263" s="0" t="s">
-        <v>52</v>
+        <v>156</v>
       </c>
       <c r="D263" s="0">
-        <v>4510</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="264">
@@ -7138,10 +7144,10 @@
         <v>585</v>
       </c>
       <c r="C267" s="0" t="s">
-        <v>15</v>
+        <v>52</v>
       </c>
       <c r="D267" s="0">
-        <v>902</v>
+        <v>4510</v>
       </c>
     </row>
     <row r="268">
@@ -7155,7 +7161,7 @@
         <v>15</v>
       </c>
       <c r="D268" s="0">
-        <v>880</v>
+        <v>902</v>
       </c>
     </row>
     <row r="269">
@@ -7166,10 +7172,10 @@
         <v>589</v>
       </c>
       <c r="C269" s="0" t="s">
-        <v>145</v>
+        <v>15</v>
       </c>
       <c r="D269" s="0">
-        <v>446</v>
+        <v>880</v>
       </c>
     </row>
     <row r="270">
@@ -7183,7 +7189,7 @@
         <v>145</v>
       </c>
       <c r="D270" s="0">
-        <v>370</v>
+        <v>446</v>
       </c>
     </row>
     <row r="271">
@@ -7194,10 +7200,10 @@
         <v>593</v>
       </c>
       <c r="C271" s="0" t="s">
-        <v>18</v>
+        <v>145</v>
       </c>
       <c r="D271" s="0">
-        <v>300</v>
+        <v>370</v>
       </c>
     </row>
     <row r="272">
@@ -7211,7 +7217,7 @@
         <v>18</v>
       </c>
       <c r="D272" s="0">
-        <v>420</v>
+        <v>300</v>
       </c>
     </row>
     <row r="273">
@@ -7225,7 +7231,7 @@
         <v>18</v>
       </c>
       <c r="D273" s="0">
-        <v>760</v>
+        <v>420</v>
       </c>
     </row>
     <row r="274">
@@ -7239,7 +7245,7 @@
         <v>18</v>
       </c>
       <c r="D274" s="0">
-        <v>820</v>
+        <v>760</v>
       </c>
     </row>
     <row r="275">
@@ -7250,24 +7256,24 @@
         <v>601</v>
       </c>
       <c r="C275" s="0" t="s">
-        <v>602</v>
+        <v>18</v>
       </c>
       <c r="D275" s="0">
-        <v>189016.25</v>
+        <v>820</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="0" t="s">
+        <v>602</v>
+      </c>
+      <c r="B276" s="0" t="s">
         <v>603</v>
       </c>
-      <c r="B276" s="0" t="s">
+      <c r="C276" s="0" t="s">
         <v>604</v>
       </c>
-      <c r="C276" s="0" t="s">
-        <v>75</v>
-      </c>
       <c r="D276" s="0">
-        <v>28000</v>
+        <v>189016.25</v>
       </c>
     </row>
     <row r="277">
@@ -7281,7 +7287,7 @@
         <v>75</v>
       </c>
       <c r="D277" s="0">
-        <v>34000</v>
+        <v>28000</v>
       </c>
     </row>
     <row r="278">
@@ -7292,10 +7298,10 @@
         <v>608</v>
       </c>
       <c r="C278" s="0" t="s">
-        <v>477</v>
+        <v>75</v>
       </c>
       <c r="D278" s="0">
-        <v>243315</v>
+        <v>34000</v>
       </c>
     </row>
     <row r="279">
@@ -7306,10 +7312,10 @@
         <v>610</v>
       </c>
       <c r="C279" s="0" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="D279" s="0">
-        <v>196835</v>
+        <v>243315</v>
       </c>
     </row>
     <row r="280">
@@ -7320,10 +7326,10 @@
         <v>612</v>
       </c>
       <c r="C280" s="0" t="s">
-        <v>15</v>
+        <v>479</v>
       </c>
       <c r="D280" s="0">
-        <v>1760</v>
+        <v>196835</v>
       </c>
     </row>
     <row r="281">
@@ -7334,24 +7340,24 @@
         <v>614</v>
       </c>
       <c r="C281" s="0" t="s">
-        <v>615</v>
+        <v>15</v>
       </c>
       <c r="D281" s="0">
-        <v>26350</v>
+        <v>1760</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="0" t="s">
+        <v>615</v>
+      </c>
+      <c r="B282" s="0" t="s">
         <v>616</v>
       </c>
-      <c r="B282" s="0" t="s">
+      <c r="C282" s="0" t="s">
         <v>617</v>
       </c>
-      <c r="C282" s="0" t="s">
-        <v>212</v>
-      </c>
       <c r="D282" s="0">
-        <v>31250</v>
+        <v>26350</v>
       </c>
     </row>
     <row r="283">
@@ -7362,10 +7368,10 @@
         <v>619</v>
       </c>
       <c r="C283" s="0" t="s">
-        <v>59</v>
+        <v>212</v>
       </c>
       <c r="D283" s="0">
-        <v>69</v>
+        <v>31250</v>
       </c>
     </row>
     <row r="284">
@@ -7376,10 +7382,10 @@
         <v>621</v>
       </c>
       <c r="C284" s="0" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="D284" s="0">
-        <v>34.98</v>
+        <v>69</v>
       </c>
     </row>
     <row r="285">
@@ -7390,7 +7396,7 @@
         <v>623</v>
       </c>
       <c r="C285" s="0" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="D285" s="0">
         <v>34.98</v>
@@ -7404,21 +7410,21 @@
         <v>625</v>
       </c>
       <c r="C286" s="0" t="s">
-        <v>626</v>
+        <v>59</v>
       </c>
       <c r="D286" s="0">
-        <v>65</v>
+        <v>34.98</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="0" t="s">
+        <v>626</v>
+      </c>
+      <c r="B287" s="0" t="s">
         <v>627</v>
       </c>
-      <c r="B287" s="0" t="s">
+      <c r="C287" s="0" t="s">
         <v>628</v>
-      </c>
-      <c r="C287" s="0" t="s">
-        <v>52</v>
       </c>
       <c r="D287" s="0">
         <v>65</v>
@@ -7426,30 +7432,30 @@
     </row>
     <row r="288">
       <c r="A288" s="0" t="s">
-        <v>618</v>
+        <v>629</v>
       </c>
       <c r="B288" s="0" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C288" s="0" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="D288" s="0">
-        <v>0</v>
+        <v>65</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="0" t="s">
-        <v>630</v>
+        <v>620</v>
       </c>
       <c r="B289" s="0" t="s">
         <v>631</v>
       </c>
       <c r="C289" s="0" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="D289" s="0">
-        <v>92</v>
+        <v>0</v>
       </c>
     </row>
     <row r="290">
@@ -7463,7 +7469,7 @@
         <v>52</v>
       </c>
       <c r="D290" s="0">
-        <v>33</v>
+        <v>92</v>
       </c>
     </row>
     <row r="291">
@@ -7477,7 +7483,7 @@
         <v>52</v>
       </c>
       <c r="D291" s="0">
-        <v>54.8</v>
+        <v>33</v>
       </c>
     </row>
     <row r="292">
@@ -7488,10 +7494,10 @@
         <v>637</v>
       </c>
       <c r="C292" s="0" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="D292" s="0">
-        <v>44</v>
+        <v>54.8</v>
       </c>
     </row>
     <row r="293">
@@ -7502,10 +7508,10 @@
         <v>639</v>
       </c>
       <c r="C293" s="0" t="s">
-        <v>346</v>
+        <v>59</v>
       </c>
       <c r="D293" s="0">
-        <v>300</v>
+        <v>44</v>
       </c>
     </row>
     <row r="294">
@@ -7519,7 +7525,7 @@
         <v>346</v>
       </c>
       <c r="D294" s="0">
-        <v>370</v>
+        <v>300</v>
       </c>
     </row>
     <row r="295">
@@ -7530,10 +7536,10 @@
         <v>643</v>
       </c>
       <c r="C295" s="0" t="s">
-        <v>367</v>
+        <v>346</v>
       </c>
       <c r="D295" s="0">
-        <v>450</v>
+        <v>370</v>
       </c>
     </row>
     <row r="296">
@@ -7544,7 +7550,7 @@
         <v>645</v>
       </c>
       <c r="C296" s="0" t="s">
-        <v>37</v>
+        <v>367</v>
       </c>
       <c r="D296" s="0">
         <v>450</v>
@@ -7558,7 +7564,7 @@
         <v>647</v>
       </c>
       <c r="C297" s="0" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="D297" s="0">
         <v>450</v>
@@ -7575,7 +7581,7 @@
         <v>15</v>
       </c>
       <c r="D298" s="0">
-        <v>1650</v>
+        <v>450</v>
       </c>
     </row>
     <row r="299">
@@ -7589,7 +7595,7 @@
         <v>15</v>
       </c>
       <c r="D299" s="0">
-        <v>2100</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="300">
@@ -7603,7 +7609,7 @@
         <v>15</v>
       </c>
       <c r="D300" s="0">
-        <v>1980</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="301">
@@ -7617,7 +7623,7 @@
         <v>15</v>
       </c>
       <c r="D301" s="0">
-        <v>2160</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="302">
@@ -7631,7 +7637,7 @@
         <v>15</v>
       </c>
       <c r="D302" s="0">
-        <v>1300</v>
+        <v>2160</v>
       </c>
     </row>
     <row r="303">
@@ -7645,7 +7651,7 @@
         <v>15</v>
       </c>
       <c r="D303" s="0">
-        <v>2600</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="304">
@@ -7659,7 +7665,7 @@
         <v>15</v>
       </c>
       <c r="D304" s="0">
-        <v>2000</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="305">
@@ -7673,7 +7679,7 @@
         <v>15</v>
       </c>
       <c r="D305" s="0">
-        <v>6700</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="306">
@@ -7687,7 +7693,7 @@
         <v>15</v>
       </c>
       <c r="D306" s="0">
-        <v>1650</v>
+        <v>6700</v>
       </c>
     </row>
     <row r="307">
@@ -7701,7 +7707,7 @@
         <v>15</v>
       </c>
       <c r="D307" s="0">
-        <v>1035</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="308">
@@ -7715,7 +7721,7 @@
         <v>15</v>
       </c>
       <c r="D308" s="0">
-        <v>2600</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="309">
@@ -7729,7 +7735,7 @@
         <v>15</v>
       </c>
       <c r="D309" s="0">
-        <v>2400</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="310">
@@ -7740,10 +7746,10 @@
         <v>673</v>
       </c>
       <c r="C310" s="0" t="s">
-        <v>145</v>
+        <v>15</v>
       </c>
       <c r="D310" s="0">
-        <v>4730</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="311">
@@ -7757,7 +7763,7 @@
         <v>145</v>
       </c>
       <c r="D311" s="0">
-        <v>2517</v>
+        <v>4730</v>
       </c>
     </row>
     <row r="312">
@@ -7771,7 +7777,7 @@
         <v>145</v>
       </c>
       <c r="D312" s="0">
-        <v>1190</v>
+        <v>2517</v>
       </c>
     </row>
     <row r="313">
@@ -7782,10 +7788,10 @@
         <v>679</v>
       </c>
       <c r="C313" s="0" t="s">
-        <v>28</v>
+        <v>145</v>
       </c>
       <c r="D313" s="0">
-        <v>7655.2</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="314">
@@ -7796,10 +7802,10 @@
         <v>681</v>
       </c>
       <c r="C314" s="0" t="s">
-        <v>128</v>
+        <v>28</v>
       </c>
       <c r="D314" s="0">
-        <v>1790</v>
+        <v>7655.2</v>
       </c>
     </row>
     <row r="315">
@@ -7813,7 +7819,7 @@
         <v>128</v>
       </c>
       <c r="D315" s="0">
-        <v>3016.53</v>
+        <v>1790</v>
       </c>
     </row>
     <row r="316">
@@ -7827,7 +7833,7 @@
         <v>128</v>
       </c>
       <c r="D316" s="0">
-        <v>4800</v>
+        <v>3016.53</v>
       </c>
     </row>
     <row r="317">
@@ -7841,7 +7847,7 @@
         <v>128</v>
       </c>
       <c r="D317" s="0">
-        <v>4450</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="318">
@@ -7852,24 +7858,24 @@
         <v>689</v>
       </c>
       <c r="C318" s="0" t="s">
-        <v>690</v>
+        <v>128</v>
       </c>
       <c r="D318" s="0">
-        <v>0</v>
+        <v>4450</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="0" t="s">
+        <v>690</v>
+      </c>
+      <c r="B319" s="0" t="s">
         <v>691</v>
       </c>
-      <c r="B319" s="0" t="s">
+      <c r="C319" s="0" t="s">
         <v>692</v>
       </c>
-      <c r="C319" s="0" t="s">
-        <v>28</v>
-      </c>
       <c r="D319" s="0">
-        <v>494</v>
+        <v>0</v>
       </c>
     </row>
     <row r="320">
@@ -7883,7 +7889,7 @@
         <v>28</v>
       </c>
       <c r="D320" s="0">
-        <v>665.3</v>
+        <v>494</v>
       </c>
     </row>
     <row r="321">
@@ -7894,10 +7900,10 @@
         <v>696</v>
       </c>
       <c r="C321" s="0" t="s">
-        <v>97</v>
+        <v>28</v>
       </c>
       <c r="D321" s="0">
-        <v>33940.5</v>
+        <v>665.3</v>
       </c>
     </row>
     <row r="322">
@@ -7911,7 +7917,7 @@
         <v>97</v>
       </c>
       <c r="D322" s="0">
-        <v>4525.4</v>
+        <v>33940.5</v>
       </c>
     </row>
     <row r="323">
@@ -7922,10 +7928,10 @@
         <v>700</v>
       </c>
       <c r="C323" s="0" t="s">
-        <v>156</v>
+        <v>97</v>
       </c>
       <c r="D323" s="0">
-        <v>896</v>
+        <v>4525.4</v>
       </c>
     </row>
     <row r="324">
@@ -7936,10 +7942,10 @@
         <v>702</v>
       </c>
       <c r="C324" s="0" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="D324" s="0">
-        <v>1125</v>
+        <v>896</v>
       </c>
     </row>
     <row r="325">
@@ -7950,10 +7956,10 @@
         <v>704</v>
       </c>
       <c r="C325" s="0" t="s">
-        <v>97</v>
+        <v>145</v>
       </c>
       <c r="D325" s="0">
-        <v>342732.5</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="326">
@@ -7964,10 +7970,10 @@
         <v>706</v>
       </c>
       <c r="C326" s="0" t="s">
-        <v>207</v>
+        <v>97</v>
       </c>
       <c r="D326" s="0">
-        <v>17440</v>
+        <v>342732.5</v>
       </c>
     </row>
     <row r="327">
@@ -7981,7 +7987,7 @@
         <v>207</v>
       </c>
       <c r="D327" s="0">
-        <v>4390</v>
+        <v>17440</v>
       </c>
     </row>
     <row r="328">
@@ -8006,10 +8012,10 @@
         <v>712</v>
       </c>
       <c r="C329" s="0" t="s">
-        <v>289</v>
+        <v>207</v>
       </c>
       <c r="D329" s="0">
-        <v>2250</v>
+        <v>4390</v>
       </c>
     </row>
     <row r="330">
@@ -8020,10 +8026,10 @@
         <v>714</v>
       </c>
       <c r="C330" s="0" t="s">
-        <v>207</v>
+        <v>289</v>
       </c>
       <c r="D330" s="0">
-        <v>3355</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="331">
@@ -8034,10 +8040,10 @@
         <v>716</v>
       </c>
       <c r="C331" s="0" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="D331" s="0">
-        <v>7500</v>
+        <v>3355</v>
       </c>
     </row>
     <row r="332">
@@ -8048,10 +8054,10 @@
         <v>718</v>
       </c>
       <c r="C332" s="0" t="s">
-        <v>97</v>
+        <v>215</v>
       </c>
       <c r="D332" s="0">
-        <v>26620</v>
+        <v>7500</v>
       </c>
     </row>
     <row r="333">
@@ -8065,7 +8071,7 @@
         <v>97</v>
       </c>
       <c r="D333" s="0">
-        <v>266200</v>
+        <v>26620</v>
       </c>
     </row>
     <row r="334">
@@ -8076,10 +8082,10 @@
         <v>722</v>
       </c>
       <c r="C334" s="0" t="s">
-        <v>52</v>
+        <v>97</v>
       </c>
       <c r="D334" s="0">
-        <v>160</v>
+        <v>266200</v>
       </c>
     </row>
     <row r="335">
@@ -8090,10 +8096,10 @@
         <v>724</v>
       </c>
       <c r="C335" s="0" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="D335" s="0">
-        <v>285.6</v>
+        <v>160</v>
       </c>
     </row>
     <row r="336">
@@ -8107,7 +8113,7 @@
         <v>21</v>
       </c>
       <c r="D336" s="0">
-        <v>338</v>
+        <v>285.6</v>
       </c>
     </row>
     <row r="337">
@@ -8118,21 +8124,21 @@
         <v>728</v>
       </c>
       <c r="C337" s="0" t="s">
-        <v>729</v>
+        <v>21</v>
       </c>
       <c r="D337" s="0">
-        <v>770</v>
+        <v>338</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" s="0" t="s">
+        <v>729</v>
+      </c>
+      <c r="B338" s="0" t="s">
         <v>730</v>
       </c>
-      <c r="B338" s="0" t="s">
+      <c r="C338" s="0" t="s">
         <v>731</v>
-      </c>
-      <c r="C338" s="0" t="s">
-        <v>732</v>
       </c>
       <c r="D338" s="0">
         <v>770</v>
@@ -8140,16 +8146,16 @@
     </row>
     <row r="339">
       <c r="A339" s="0" t="s">
+        <v>732</v>
+      </c>
+      <c r="B339" s="0" t="s">
         <v>733</v>
       </c>
-      <c r="B339" s="0" t="s">
+      <c r="C339" s="0" t="s">
         <v>734</v>
       </c>
-      <c r="C339" s="0" t="s">
-        <v>15</v>
-      </c>
       <c r="D339" s="0">
-        <v>973.5</v>
+        <v>770</v>
       </c>
     </row>
     <row r="340">
@@ -8160,10 +8166,10 @@
         <v>736</v>
       </c>
       <c r="C340" s="0" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="D340" s="0">
-        <v>507.08</v>
+        <v>973.5</v>
       </c>
     </row>
     <row r="341">
@@ -8174,10 +8180,10 @@
         <v>738</v>
       </c>
       <c r="C341" s="0" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D341" s="0">
-        <v>450</v>
+        <v>507.08</v>
       </c>
     </row>
     <row r="342">
@@ -8188,10 +8194,10 @@
         <v>740</v>
       </c>
       <c r="C342" s="0" t="s">
-        <v>156</v>
+        <v>15</v>
       </c>
       <c r="D342" s="0">
-        <v>760</v>
+        <v>450</v>
       </c>
     </row>
     <row r="343">
@@ -8202,10 +8208,10 @@
         <v>742</v>
       </c>
       <c r="C343" s="0" t="s">
-        <v>289</v>
+        <v>156</v>
       </c>
       <c r="D343" s="0">
-        <v>5900</v>
+        <v>760</v>
       </c>
     </row>
     <row r="344">
@@ -8219,7 +8225,7 @@
         <v>289</v>
       </c>
       <c r="D344" s="0">
-        <v>2900</v>
+        <v>5900</v>
       </c>
     </row>
     <row r="345">
@@ -8230,10 +8236,10 @@
         <v>746</v>
       </c>
       <c r="C345" s="0" t="s">
-        <v>145</v>
+        <v>289</v>
       </c>
       <c r="D345" s="0">
-        <v>935</v>
+        <v>2900</v>
       </c>
     </row>
     <row r="346">
@@ -8247,7 +8253,7 @@
         <v>145</v>
       </c>
       <c r="D346" s="0">
-        <v>620</v>
+        <v>935</v>
       </c>
     </row>
     <row r="347">
@@ -8261,7 +8267,7 @@
         <v>145</v>
       </c>
       <c r="D347" s="0">
-        <v>73</v>
+        <v>620</v>
       </c>
     </row>
     <row r="348">
@@ -8272,10 +8278,10 @@
         <v>752</v>
       </c>
       <c r="C348" s="0" t="s">
-        <v>97</v>
+        <v>145</v>
       </c>
       <c r="D348" s="0">
-        <v>11313.5</v>
+        <v>73</v>
       </c>
     </row>
     <row r="349">
@@ -8286,10 +8292,10 @@
         <v>754</v>
       </c>
       <c r="C349" s="0" t="s">
-        <v>34</v>
+        <v>97</v>
       </c>
       <c r="D349" s="0">
-        <v>400</v>
+        <v>11313.5</v>
       </c>
     </row>
     <row r="350">
@@ -8300,7 +8306,7 @@
         <v>756</v>
       </c>
       <c r="C350" s="0" t="s">
-        <v>367</v>
+        <v>34</v>
       </c>
       <c r="D350" s="0">
         <v>400</v>
@@ -8314,10 +8320,10 @@
         <v>758</v>
       </c>
       <c r="C351" s="0" t="s">
-        <v>21</v>
+        <v>367</v>
       </c>
       <c r="D351" s="0">
-        <v>377</v>
+        <v>400</v>
       </c>
     </row>
     <row r="352">
@@ -8328,10 +8334,10 @@
         <v>760</v>
       </c>
       <c r="C352" s="0" t="s">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="D352" s="0">
-        <v>5621.15</v>
+        <v>377</v>
       </c>
     </row>
     <row r="353">
@@ -8342,10 +8348,10 @@
         <v>762</v>
       </c>
       <c r="C353" s="0" t="s">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="D353" s="0">
-        <v>898</v>
+        <v>5621.15</v>
       </c>
     </row>
     <row r="354">
@@ -8356,10 +8362,10 @@
         <v>764</v>
       </c>
       <c r="C354" s="0" t="s">
-        <v>128</v>
+        <v>75</v>
       </c>
       <c r="D354" s="0">
-        <v>4767</v>
+        <v>898</v>
       </c>
     </row>
     <row r="355">
@@ -8370,10 +8376,10 @@
         <v>766</v>
       </c>
       <c r="C355" s="0" t="s">
-        <v>34</v>
+        <v>128</v>
       </c>
       <c r="D355" s="0">
-        <v>650</v>
+        <v>4767</v>
       </c>
     </row>
     <row r="356">
@@ -8384,7 +8390,7 @@
         <v>768</v>
       </c>
       <c r="C356" s="0" t="s">
-        <v>75</v>
+        <v>34</v>
       </c>
       <c r="D356" s="0">
         <v>650</v>
@@ -8398,10 +8404,10 @@
         <v>770</v>
       </c>
       <c r="C357" s="0" t="s">
-        <v>15</v>
+        <v>75</v>
       </c>
       <c r="D357" s="0">
-        <v>2178</v>
+        <v>650</v>
       </c>
     </row>
     <row r="358">
@@ -8412,10 +8418,10 @@
         <v>772</v>
       </c>
       <c r="C358" s="0" t="s">
-        <v>97</v>
+        <v>15</v>
       </c>
       <c r="D358" s="0">
-        <v>7986</v>
+        <v>2178</v>
       </c>
     </row>
     <row r="359">
@@ -8426,24 +8432,24 @@
         <v>774</v>
       </c>
       <c r="C359" s="0" t="s">
-        <v>775</v>
+        <v>97</v>
       </c>
       <c r="D359" s="0">
-        <v>1910</v>
+        <v>7986</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" s="0" t="s">
+        <v>775</v>
+      </c>
+      <c r="B360" s="0" t="s">
         <v>776</v>
       </c>
-      <c r="B360" s="0" t="s">
+      <c r="C360" s="0" t="s">
         <v>777</v>
       </c>
-      <c r="C360" s="0" t="s">
-        <v>156</v>
-      </c>
       <c r="D360" s="0">
-        <v>900</v>
+        <v>1910</v>
       </c>
     </row>
     <row r="361">
@@ -8454,10 +8460,10 @@
         <v>779</v>
       </c>
       <c r="C361" s="0" t="s">
-        <v>21</v>
+        <v>156</v>
       </c>
       <c r="D361" s="0">
-        <v>1722</v>
+        <v>900</v>
       </c>
     </row>
     <row r="362">
@@ -8468,10 +8474,10 @@
         <v>781</v>
       </c>
       <c r="C362" s="0" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="D362" s="0">
-        <v>59000</v>
+        <v>1722</v>
       </c>
     </row>
     <row r="363">
@@ -8482,10 +8488,10 @@
         <v>783</v>
       </c>
       <c r="C363" s="0" t="s">
-        <v>156</v>
+        <v>34</v>
       </c>
       <c r="D363" s="0">
-        <v>750</v>
+        <v>59000</v>
       </c>
     </row>
     <row r="364">
@@ -8499,7 +8505,7 @@
         <v>156</v>
       </c>
       <c r="D364" s="0">
-        <v>1212</v>
+        <v>750</v>
       </c>
     </row>
     <row r="365">
@@ -8513,7 +8519,7 @@
         <v>156</v>
       </c>
       <c r="D365" s="0">
-        <v>1300</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="366">
@@ -8527,7 +8533,7 @@
         <v>156</v>
       </c>
       <c r="D366" s="0">
-        <v>1500</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="367">
@@ -8541,7 +8547,7 @@
         <v>156</v>
       </c>
       <c r="D367" s="0">
-        <v>1400</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="368">
@@ -8552,10 +8558,10 @@
         <v>793</v>
       </c>
       <c r="C368" s="0" t="s">
-        <v>269</v>
+        <v>156</v>
       </c>
       <c r="D368" s="0">
-        <v>11959</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="369">
@@ -8566,10 +8572,10 @@
         <v>795</v>
       </c>
       <c r="C369" s="0" t="s">
-        <v>145</v>
+        <v>269</v>
       </c>
       <c r="D369" s="0">
-        <v>365</v>
+        <v>11959</v>
       </c>
     </row>
     <row r="370">
@@ -8580,10 +8586,10 @@
         <v>797</v>
       </c>
       <c r="C370" s="0" t="s">
-        <v>289</v>
+        <v>145</v>
       </c>
       <c r="D370" s="0">
-        <v>1450</v>
+        <v>365</v>
       </c>
     </row>
     <row r="371">
@@ -8594,10 +8600,10 @@
         <v>799</v>
       </c>
       <c r="C371" s="0" t="s">
-        <v>97</v>
+        <v>289</v>
       </c>
       <c r="D371" s="0">
-        <v>7320.5</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="372">
@@ -8608,10 +8614,10 @@
         <v>801</v>
       </c>
       <c r="C372" s="0" t="s">
-        <v>15</v>
+        <v>97</v>
       </c>
       <c r="D372" s="0">
-        <v>900</v>
+        <v>7320.5</v>
       </c>
     </row>
     <row r="373">
@@ -8622,10 +8628,10 @@
         <v>803</v>
       </c>
       <c r="C373" s="0" t="s">
-        <v>289</v>
+        <v>15</v>
       </c>
       <c r="D373" s="0">
-        <v>566</v>
+        <v>900</v>
       </c>
     </row>
     <row r="374">
@@ -8636,10 +8642,10 @@
         <v>805</v>
       </c>
       <c r="C374" s="0" t="s">
-        <v>477</v>
+        <v>289</v>
       </c>
       <c r="D374" s="0">
-        <v>64925</v>
+        <v>566</v>
       </c>
     </row>
     <row r="375">
@@ -8650,10 +8656,10 @@
         <v>807</v>
       </c>
       <c r="C375" s="0" t="s">
-        <v>15</v>
+        <v>479</v>
       </c>
       <c r="D375" s="0">
-        <v>1100</v>
+        <v>64925</v>
       </c>
     </row>
     <row r="376">
@@ -8664,10 +8670,10 @@
         <v>809</v>
       </c>
       <c r="C376" s="0" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="D376" s="0">
-        <v>1623</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="377">
@@ -8678,10 +8684,10 @@
         <v>811</v>
       </c>
       <c r="C377" s="0" t="s">
-        <v>145</v>
+        <v>21</v>
       </c>
       <c r="D377" s="0">
-        <v>1269</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="378">
@@ -8695,7 +8701,7 @@
         <v>145</v>
       </c>
       <c r="D378" s="0">
-        <v>4712</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="379">
@@ -8706,10 +8712,10 @@
         <v>815</v>
       </c>
       <c r="C379" s="0" t="s">
-        <v>28</v>
+        <v>145</v>
       </c>
       <c r="D379" s="0">
-        <v>1250</v>
+        <v>4712</v>
       </c>
     </row>
     <row r="380">
@@ -8723,7 +8729,7 @@
         <v>28</v>
       </c>
       <c r="D380" s="0">
-        <v>1986</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="381">
@@ -8734,10 +8740,10 @@
         <v>819</v>
       </c>
       <c r="C381" s="0" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="D381" s="0">
-        <v>450</v>
+        <v>1986</v>
       </c>
     </row>
     <row r="382">
@@ -8751,7 +8757,7 @@
         <v>15</v>
       </c>
       <c r="D382" s="0">
-        <v>825</v>
+        <v>450</v>
       </c>
     </row>
     <row r="383">
@@ -8776,10 +8782,10 @@
         <v>825</v>
       </c>
       <c r="C384" s="0" t="s">
-        <v>387</v>
+        <v>15</v>
       </c>
       <c r="D384" s="0">
-        <v>134775.6</v>
+        <v>825</v>
       </c>
     </row>
     <row r="385">
@@ -8793,7 +8799,7 @@
         <v>387</v>
       </c>
       <c r="D385" s="0">
-        <v>175991.55</v>
+        <v>134775.6</v>
       </c>
     </row>
     <row r="386">
@@ -8804,10 +8810,10 @@
         <v>829</v>
       </c>
       <c r="C386" s="0" t="s">
-        <v>75</v>
+        <v>387</v>
       </c>
       <c r="D386" s="0">
-        <v>3427</v>
+        <v>175991.55</v>
       </c>
     </row>
     <row r="387">
@@ -8821,7 +8827,7 @@
         <v>75</v>
       </c>
       <c r="D387" s="0">
-        <v>10618</v>
+        <v>3427</v>
       </c>
     </row>
     <row r="388">
@@ -8832,10 +8838,10 @@
         <v>833</v>
       </c>
       <c r="C388" s="0" t="s">
-        <v>289</v>
+        <v>75</v>
       </c>
       <c r="D388" s="0">
-        <v>515</v>
+        <v>10618</v>
       </c>
     </row>
     <row r="389">
@@ -8846,7 +8852,7 @@
         <v>835</v>
       </c>
       <c r="C389" s="0" t="s">
-        <v>37</v>
+        <v>289</v>
       </c>
       <c r="D389" s="0">
         <v>515</v>
@@ -8860,10 +8866,10 @@
         <v>837</v>
       </c>
       <c r="C390" s="0" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="D390" s="0">
-        <v>10000</v>
+        <v>515</v>
       </c>
     </row>
     <row r="391">
@@ -8874,10 +8880,10 @@
         <v>839</v>
       </c>
       <c r="C391" s="0" t="s">
-        <v>477</v>
+        <v>52</v>
       </c>
       <c r="D391" s="0">
-        <v>213700</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="392">
@@ -8888,10 +8894,10 @@
         <v>841</v>
       </c>
       <c r="C392" s="0" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="D392" s="0">
-        <v>257000</v>
+        <v>213700</v>
       </c>
     </row>
     <row r="393">
@@ -8902,10 +8908,10 @@
         <v>843</v>
       </c>
       <c r="C393" s="0" t="s">
-        <v>75</v>
+        <v>479</v>
       </c>
       <c r="D393" s="0">
-        <v>10522</v>
+        <v>257000</v>
       </c>
     </row>
     <row r="394">
@@ -8919,7 +8925,7 @@
         <v>75</v>
       </c>
       <c r="D394" s="0">
-        <v>19481</v>
+        <v>10522</v>
       </c>
     </row>
     <row r="395">
@@ -8930,24 +8936,24 @@
         <v>847</v>
       </c>
       <c r="C395" s="0" t="s">
-        <v>848</v>
+        <v>75</v>
       </c>
       <c r="D395" s="0">
-        <v>1080</v>
+        <v>19481</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" s="0" t="s">
+        <v>848</v>
+      </c>
+      <c r="B396" s="0" t="s">
         <v>849</v>
       </c>
-      <c r="B396" s="0" t="s">
+      <c r="C396" s="0" t="s">
         <v>850</v>
       </c>
-      <c r="C396" s="0" t="s">
-        <v>18</v>
-      </c>
       <c r="D396" s="0">
-        <v>586.49</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="397">
@@ -8958,24 +8964,24 @@
         <v>852</v>
       </c>
       <c r="C397" s="0" t="s">
-        <v>853</v>
+        <v>18</v>
       </c>
       <c r="D397" s="0">
-        <v>520</v>
+        <v>586.49</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" s="0" t="s">
+        <v>853</v>
+      </c>
+      <c r="B398" s="0" t="s">
         <v>854</v>
       </c>
-      <c r="B398" s="0" t="s">
+      <c r="C398" s="0" t="s">
         <v>855</v>
       </c>
-      <c r="C398" s="0" t="s">
-        <v>853</v>
-      </c>
       <c r="D398" s="0">
-        <v>300</v>
+        <v>520</v>
       </c>
     </row>
     <row r="399">
@@ -8986,10 +8992,10 @@
         <v>857</v>
       </c>
       <c r="C399" s="0" t="s">
-        <v>34</v>
+        <v>855</v>
       </c>
       <c r="D399" s="0">
-        <v>630</v>
+        <v>300</v>
       </c>
     </row>
     <row r="400">
@@ -9000,10 +9006,10 @@
         <v>859</v>
       </c>
       <c r="C400" s="0" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="D400" s="0">
-        <v>2200</v>
+        <v>630</v>
       </c>
     </row>
     <row r="401">
@@ -9017,7 +9023,7 @@
         <v>15</v>
       </c>
       <c r="D401" s="0">
-        <v>2800</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="402">
@@ -9028,10 +9034,10 @@
         <v>863</v>
       </c>
       <c r="C402" s="0" t="s">
-        <v>97</v>
+        <v>15</v>
       </c>
       <c r="D402" s="0">
-        <v>5190.9</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="403">
@@ -9042,10 +9048,10 @@
         <v>865</v>
       </c>
       <c r="C403" s="0" t="s">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="D403" s="0">
-        <v>2969</v>
+        <v>5190.9</v>
       </c>
     </row>
     <row r="404">
@@ -9056,10 +9062,10 @@
         <v>867</v>
       </c>
       <c r="C404" s="0" t="s">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="D404" s="0">
-        <v>3800</v>
+        <v>2969</v>
       </c>
     </row>
     <row r="405">
@@ -9070,10 +9076,10 @@
         <v>869</v>
       </c>
       <c r="C405" s="0" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="D405" s="0">
-        <v>4000</v>
+        <v>3800</v>
       </c>
     </row>
     <row r="406">
@@ -9084,24 +9090,24 @@
         <v>871</v>
       </c>
       <c r="C406" s="0" t="s">
-        <v>872</v>
+        <v>15</v>
       </c>
       <c r="D406" s="0">
-        <v>3800</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" s="0" t="s">
+        <v>872</v>
+      </c>
+      <c r="B407" s="0" t="s">
         <v>873</v>
       </c>
-      <c r="B407" s="0" t="s">
+      <c r="C407" s="0" t="s">
         <v>874</v>
       </c>
-      <c r="C407" s="0" t="s">
-        <v>21</v>
-      </c>
       <c r="D407" s="0">
-        <v>353</v>
+        <v>3800</v>
       </c>
     </row>
     <row r="408">
@@ -9112,10 +9118,10 @@
         <v>876</v>
       </c>
       <c r="C408" s="0" t="s">
-        <v>115</v>
+        <v>21</v>
       </c>
       <c r="D408" s="0">
-        <v>1800</v>
+        <v>353</v>
       </c>
     </row>
     <row r="409">
@@ -9126,10 +9132,10 @@
         <v>878</v>
       </c>
       <c r="C409" s="0" t="s">
-        <v>15</v>
+        <v>115</v>
       </c>
       <c r="D409" s="0">
-        <v>2948</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="410">
@@ -9140,10 +9146,10 @@
         <v>880</v>
       </c>
       <c r="C410" s="0" t="s">
-        <v>97</v>
+        <v>15</v>
       </c>
       <c r="D410" s="0">
-        <v>146.41</v>
+        <v>2948</v>
       </c>
     </row>
     <row r="411">
@@ -9154,10 +9160,10 @@
         <v>882</v>
       </c>
       <c r="C411" s="0" t="s">
-        <v>215</v>
+        <v>97</v>
       </c>
       <c r="D411" s="0">
-        <v>65537</v>
+        <v>146.41</v>
       </c>
     </row>
     <row r="412">
@@ -9168,10 +9174,10 @@
         <v>884</v>
       </c>
       <c r="C412" s="0" t="s">
-        <v>145</v>
+        <v>215</v>
       </c>
       <c r="D412" s="0">
-        <v>4130.4</v>
+        <v>65537</v>
       </c>
     </row>
     <row r="413">
@@ -9185,7 +9191,7 @@
         <v>145</v>
       </c>
       <c r="D413" s="0">
-        <v>4283</v>
+        <v>4130.4</v>
       </c>
     </row>
     <row r="414">
@@ -9199,7 +9205,7 @@
         <v>145</v>
       </c>
       <c r="D414" s="0">
-        <v>6524.8</v>
+        <v>4283</v>
       </c>
     </row>
     <row r="415">
@@ -9210,10 +9216,10 @@
         <v>890</v>
       </c>
       <c r="C415" s="0" t="s">
-        <v>316</v>
+        <v>145</v>
       </c>
       <c r="D415" s="0">
-        <v>570</v>
+        <v>6524.8</v>
       </c>
     </row>
     <row r="416">
@@ -9224,10 +9230,10 @@
         <v>892</v>
       </c>
       <c r="C416" s="0" t="s">
-        <v>75</v>
+        <v>316</v>
       </c>
       <c r="D416" s="0">
-        <v>550</v>
+        <v>570</v>
       </c>
     </row>
     <row r="417">
@@ -9238,10 +9244,10 @@
         <v>894</v>
       </c>
       <c r="C417" s="0" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="D417" s="0">
-        <v>153</v>
+        <v>550</v>
       </c>
     </row>
     <row r="418">
@@ -9252,10 +9258,10 @@
         <v>896</v>
       </c>
       <c r="C418" s="0" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="D418" s="0">
-        <v>740.7</v>
+        <v>153</v>
       </c>
     </row>
     <row r="419">
@@ -9266,10 +9272,10 @@
         <v>898</v>
       </c>
       <c r="C419" s="0" t="s">
-        <v>64</v>
+        <v>28</v>
       </c>
       <c r="D419" s="0">
-        <v>101000</v>
+        <v>740.7</v>
       </c>
     </row>
     <row r="420">
@@ -9280,10 +9286,10 @@
         <v>900</v>
       </c>
       <c r="C420" s="0" t="s">
-        <v>128</v>
+        <v>64</v>
       </c>
       <c r="D420" s="0">
-        <v>6251</v>
+        <v>101000</v>
       </c>
     </row>
     <row r="421">
@@ -9294,10 +9300,10 @@
         <v>902</v>
       </c>
       <c r="C421" s="0" t="s">
-        <v>145</v>
+        <v>128</v>
       </c>
       <c r="D421" s="0">
-        <v>883</v>
+        <v>6251</v>
       </c>
     </row>
     <row r="422">
@@ -9308,10 +9314,10 @@
         <v>904</v>
       </c>
       <c r="C422" s="0" t="s">
-        <v>97</v>
+        <v>145</v>
       </c>
       <c r="D422" s="0">
-        <v>1164.66</v>
+        <v>883</v>
       </c>
     </row>
     <row r="423">
@@ -9322,10 +9328,10 @@
         <v>906</v>
       </c>
       <c r="C423" s="0" t="s">
-        <v>156</v>
+        <v>97</v>
       </c>
       <c r="D423" s="0">
-        <v>360</v>
+        <v>1164.66</v>
       </c>
     </row>
     <row r="424">
@@ -9339,7 +9345,7 @@
         <v>156</v>
       </c>
       <c r="D424" s="0">
-        <v>450</v>
+        <v>360</v>
       </c>
     </row>
     <row r="425">
@@ -9353,7 +9359,7 @@
         <v>156</v>
       </c>
       <c r="D425" s="0">
-        <v>2150</v>
+        <v>450</v>
       </c>
     </row>
     <row r="426">
@@ -9364,10 +9370,10 @@
         <v>912</v>
       </c>
       <c r="C426" s="0" t="s">
-        <v>602</v>
+        <v>156</v>
       </c>
       <c r="D426" s="0">
-        <v>25192.82</v>
+        <v>2150</v>
       </c>
     </row>
     <row r="427">
@@ -9378,10 +9384,10 @@
         <v>914</v>
       </c>
       <c r="C427" s="0" t="s">
-        <v>75</v>
+        <v>604</v>
       </c>
       <c r="D427" s="0">
-        <v>3500</v>
+        <v>25192.82</v>
       </c>
     </row>
     <row r="428">
@@ -9392,10 +9398,10 @@
         <v>916</v>
       </c>
       <c r="C428" s="0" t="s">
-        <v>180</v>
+        <v>75</v>
       </c>
       <c r="D428" s="0">
-        <v>600</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="429">
@@ -9406,24 +9412,24 @@
         <v>918</v>
       </c>
       <c r="C429" s="0" t="s">
-        <v>919</v>
+        <v>180</v>
       </c>
       <c r="D429" s="0">
-        <v>1080</v>
+        <v>600</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" s="0" t="s">
+        <v>919</v>
+      </c>
+      <c r="B430" s="0" t="s">
         <v>920</v>
       </c>
-      <c r="B430" s="0" t="s">
+      <c r="C430" s="0" t="s">
         <v>921</v>
       </c>
-      <c r="C430" s="0" t="s">
-        <v>346</v>
-      </c>
       <c r="D430" s="0">
-        <v>8628</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="431">
@@ -9434,10 +9440,10 @@
         <v>923</v>
       </c>
       <c r="C431" s="0" t="s">
-        <v>40</v>
+        <v>346</v>
       </c>
       <c r="D431" s="0">
-        <v>27991.54</v>
+        <v>8628</v>
       </c>
     </row>
     <row r="432">
@@ -9448,10 +9454,10 @@
         <v>925</v>
       </c>
       <c r="C432" s="0" t="s">
-        <v>145</v>
+        <v>40</v>
       </c>
       <c r="D432" s="0">
-        <v>1020</v>
+        <v>27991.54</v>
       </c>
     </row>
     <row r="433">
@@ -9465,7 +9471,7 @@
         <v>145</v>
       </c>
       <c r="D433" s="0">
-        <v>4106</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="434">
@@ -9476,10 +9482,10 @@
         <v>929</v>
       </c>
       <c r="C434" s="0" t="s">
-        <v>289</v>
+        <v>145</v>
       </c>
       <c r="D434" s="0">
-        <v>450</v>
+        <v>4106</v>
       </c>
     </row>
     <row r="435">
@@ -9490,10 +9496,10 @@
         <v>931</v>
       </c>
       <c r="C435" s="0" t="s">
-        <v>45</v>
+        <v>289</v>
       </c>
       <c r="D435" s="0">
-        <v>6398.6</v>
+        <v>450</v>
       </c>
     </row>
     <row r="436">
@@ -9507,7 +9513,7 @@
         <v>45</v>
       </c>
       <c r="D436" s="0">
-        <v>2886.7</v>
+        <v>6398.6</v>
       </c>
     </row>
     <row r="437">
@@ -9521,7 +9527,7 @@
         <v>45</v>
       </c>
       <c r="D437" s="0">
-        <v>2050.95</v>
+        <v>2886.7</v>
       </c>
     </row>
     <row r="438">
@@ -9535,7 +9541,7 @@
         <v>45</v>
       </c>
       <c r="D438" s="0">
-        <v>30050.45</v>
+        <v>2050.95</v>
       </c>
     </row>
     <row r="439">
@@ -9549,7 +9555,7 @@
         <v>45</v>
       </c>
       <c r="D439" s="0">
-        <v>2326.8</v>
+        <v>30050.45</v>
       </c>
     </row>
     <row r="440">
@@ -9563,7 +9569,7 @@
         <v>45</v>
       </c>
       <c r="D440" s="0">
-        <v>6429.95</v>
+        <v>2326.8</v>
       </c>
     </row>
     <row r="441">
@@ -9577,7 +9583,7 @@
         <v>45</v>
       </c>
       <c r="D441" s="0">
-        <v>5180.26</v>
+        <v>6429.95</v>
       </c>
     </row>
     <row r="442">
@@ -9588,10 +9594,10 @@
         <v>945</v>
       </c>
       <c r="C442" s="0" t="s">
-        <v>212</v>
+        <v>45</v>
       </c>
       <c r="D442" s="0">
-        <v>510</v>
+        <v>5180.26</v>
       </c>
     </row>
     <row r="443">
@@ -9602,7 +9608,7 @@
         <v>947</v>
       </c>
       <c r="C443" s="0" t="s">
-        <v>37</v>
+        <v>212</v>
       </c>
       <c r="D443" s="0">
         <v>510</v>
@@ -9616,21 +9622,21 @@
         <v>949</v>
       </c>
       <c r="C444" s="0" t="s">
-        <v>950</v>
+        <v>37</v>
       </c>
       <c r="D444" s="0">
-        <v>626</v>
+        <v>510</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" s="0" t="s">
+        <v>950</v>
+      </c>
+      <c r="B445" s="0" t="s">
         <v>951</v>
       </c>
-      <c r="B445" s="0" t="s">
+      <c r="C445" s="0" t="s">
         <v>952</v>
-      </c>
-      <c r="C445" s="0" t="s">
-        <v>950</v>
       </c>
       <c r="D445" s="0">
         <v>626</v>
@@ -9644,7 +9650,7 @@
         <v>954</v>
       </c>
       <c r="C446" s="0" t="s">
-        <v>950</v>
+        <v>952</v>
       </c>
       <c r="D446" s="0">
         <v>626</v>
@@ -9658,10 +9664,10 @@
         <v>956</v>
       </c>
       <c r="C447" s="0" t="s">
-        <v>950</v>
+        <v>952</v>
       </c>
       <c r="D447" s="0">
-        <v>342</v>
+        <v>626</v>
       </c>
     </row>
     <row r="448">
@@ -9672,7 +9678,7 @@
         <v>958</v>
       </c>
       <c r="C448" s="0" t="s">
-        <v>950</v>
+        <v>952</v>
       </c>
       <c r="D448" s="0">
         <v>342</v>
@@ -9686,7 +9692,7 @@
         <v>960</v>
       </c>
       <c r="C449" s="0" t="s">
-        <v>950</v>
+        <v>952</v>
       </c>
       <c r="D449" s="0">
         <v>342</v>
@@ -9700,10 +9706,10 @@
         <v>962</v>
       </c>
       <c r="C450" s="0" t="s">
-        <v>950</v>
+        <v>952</v>
       </c>
       <c r="D450" s="0">
-        <v>0</v>
+        <v>342</v>
       </c>
     </row>
     <row r="451">
@@ -9714,7 +9720,7 @@
         <v>964</v>
       </c>
       <c r="C451" s="0" t="s">
-        <v>950</v>
+        <v>952</v>
       </c>
       <c r="D451" s="0">
         <v>0</v>
@@ -9728,21 +9734,21 @@
         <v>966</v>
       </c>
       <c r="C452" s="0" t="s">
-        <v>967</v>
+        <v>952</v>
       </c>
       <c r="D452" s="0">
-        <v>453</v>
+        <v>0</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" s="0" t="s">
+        <v>967</v>
+      </c>
+      <c r="B453" s="0" t="s">
         <v>968</v>
       </c>
-      <c r="B453" s="0" t="s">
+      <c r="C453" s="0" t="s">
         <v>969</v>
-      </c>
-      <c r="C453" s="0" t="s">
-        <v>950</v>
       </c>
       <c r="D453" s="0">
         <v>453</v>
@@ -9756,10 +9762,10 @@
         <v>971</v>
       </c>
       <c r="C454" s="0" t="s">
-        <v>75</v>
+        <v>952</v>
       </c>
       <c r="D454" s="0">
-        <v>19322</v>
+        <v>453</v>
       </c>
     </row>
     <row r="455">
@@ -9770,10 +9776,10 @@
         <v>973</v>
       </c>
       <c r="C455" s="0" t="s">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="D455" s="0">
-        <v>430</v>
+        <v>19322</v>
       </c>
     </row>
     <row r="456">
@@ -9784,7 +9790,7 @@
         <v>975</v>
       </c>
       <c r="C456" s="0" t="s">
-        <v>289</v>
+        <v>34</v>
       </c>
       <c r="D456" s="0">
         <v>430</v>
@@ -9798,10 +9804,10 @@
         <v>977</v>
       </c>
       <c r="C457" s="0" t="s">
-        <v>120</v>
+        <v>289</v>
       </c>
       <c r="D457" s="0">
-        <v>14000</v>
+        <v>430</v>
       </c>
     </row>
     <row r="458">
@@ -9812,10 +9818,10 @@
         <v>979</v>
       </c>
       <c r="C458" s="0" t="s">
-        <v>145</v>
+        <v>120</v>
       </c>
       <c r="D458" s="0">
-        <v>12049</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="459">
@@ -9829,7 +9835,7 @@
         <v>145</v>
       </c>
       <c r="D459" s="0">
-        <v>2895</v>
+        <v>12049</v>
       </c>
     </row>
     <row r="460">
@@ -9840,10 +9846,10 @@
         <v>983</v>
       </c>
       <c r="C460" s="0" t="s">
-        <v>97</v>
+        <v>145</v>
       </c>
       <c r="D460" s="0">
-        <v>266200</v>
+        <v>2895</v>
       </c>
     </row>
     <row r="461">
@@ -9857,7 +9863,7 @@
         <v>97</v>
       </c>
       <c r="D461" s="0">
-        <v>194991.5</v>
+        <v>266200</v>
       </c>
     </row>
     <row r="462">
@@ -9871,7 +9877,7 @@
         <v>97</v>
       </c>
       <c r="D462" s="0">
-        <v>289492.5</v>
+        <v>194991.5</v>
       </c>
     </row>
     <row r="463">
@@ -9882,24 +9888,24 @@
         <v>989</v>
       </c>
       <c r="C463" s="0" t="s">
-        <v>990</v>
+        <v>97</v>
       </c>
       <c r="D463" s="0">
-        <v>13722.52</v>
+        <v>289492.5</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" s="0" t="s">
+        <v>990</v>
+      </c>
+      <c r="B464" s="0" t="s">
         <v>991</v>
       </c>
-      <c r="B464" s="0" t="s">
+      <c r="C464" s="0" t="s">
         <v>992</v>
       </c>
-      <c r="C464" s="0" t="s">
-        <v>990</v>
-      </c>
       <c r="D464" s="0">
-        <v>15072</v>
+        <v>13722.52</v>
       </c>
     </row>
     <row r="465">
@@ -9910,10 +9916,10 @@
         <v>994</v>
       </c>
       <c r="C465" s="0" t="s">
-        <v>990</v>
+        <v>992</v>
       </c>
       <c r="D465" s="0">
-        <v>6555.64</v>
+        <v>15072</v>
       </c>
     </row>
     <row r="466">
@@ -9924,10 +9930,10 @@
         <v>996</v>
       </c>
       <c r="C466" s="0" t="s">
-        <v>990</v>
+        <v>992</v>
       </c>
       <c r="D466" s="0">
-        <v>8964.61</v>
+        <v>6555.64</v>
       </c>
     </row>
     <row r="467">
@@ -9938,10 +9944,10 @@
         <v>998</v>
       </c>
       <c r="C467" s="0" t="s">
-        <v>990</v>
+        <v>992</v>
       </c>
       <c r="D467" s="0">
-        <v>11735</v>
+        <v>8964.61</v>
       </c>
     </row>
     <row r="468">
@@ -9952,10 +9958,10 @@
         <v>1000</v>
       </c>
       <c r="C468" s="0" t="s">
-        <v>75</v>
+        <v>992</v>
       </c>
       <c r="D468" s="0">
-        <v>4276</v>
+        <v>11735</v>
       </c>
     </row>
     <row r="469">
@@ -9966,10 +9972,10 @@
         <v>1002</v>
       </c>
       <c r="C469" s="0" t="s">
-        <v>145</v>
+        <v>75</v>
       </c>
       <c r="D469" s="0">
-        <v>3930</v>
+        <v>4276</v>
       </c>
     </row>
     <row r="470">
@@ -9980,10 +9986,10 @@
         <v>1004</v>
       </c>
       <c r="C470" s="0" t="s">
-        <v>97</v>
+        <v>145</v>
       </c>
       <c r="D470" s="0">
-        <v>4392.3</v>
+        <v>3930</v>
       </c>
     </row>
     <row r="471">
@@ -9994,24 +10000,24 @@
         <v>1006</v>
       </c>
       <c r="C471" s="0" t="s">
-        <v>1007</v>
+        <v>97</v>
       </c>
       <c r="D471" s="0">
-        <v>5254.41</v>
+        <v>4392.3</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" s="0" t="s">
+        <v>1007</v>
+      </c>
+      <c r="B472" s="0" t="s">
         <v>1008</v>
       </c>
-      <c r="B472" s="0" t="s">
+      <c r="C472" s="0" t="s">
         <v>1009</v>
       </c>
-      <c r="C472" s="0" t="s">
-        <v>52</v>
-      </c>
       <c r="D472" s="0">
-        <v>1297</v>
+        <v>5254.41</v>
       </c>
     </row>
     <row r="473">
@@ -10025,7 +10031,7 @@
         <v>52</v>
       </c>
       <c r="D473" s="0">
-        <v>298</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="474">
@@ -10039,7 +10045,7 @@
         <v>52</v>
       </c>
       <c r="D474" s="0">
-        <v>596</v>
+        <v>298</v>
       </c>
     </row>
     <row r="475">
@@ -10050,10 +10056,10 @@
         <v>1015</v>
       </c>
       <c r="C475" s="0" t="s">
-        <v>384</v>
+        <v>52</v>
       </c>
       <c r="D475" s="0">
-        <v>65142.6</v>
+        <v>596</v>
       </c>
     </row>
     <row r="476">
@@ -10067,7 +10073,7 @@
         <v>384</v>
       </c>
       <c r="D476" s="0">
-        <v>23482.7</v>
+        <v>65142.6</v>
       </c>
     </row>
     <row r="477">
@@ -10078,10 +10084,10 @@
         <v>1019</v>
       </c>
       <c r="C477" s="0" t="s">
-        <v>28</v>
+        <v>384</v>
       </c>
       <c r="D477" s="0">
-        <v>6029.59</v>
+        <v>23482.7</v>
       </c>
     </row>
     <row r="478">
@@ -10092,10 +10098,10 @@
         <v>1021</v>
       </c>
       <c r="C478" s="0" t="s">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="D478" s="0">
-        <v>12000</v>
+        <v>6029.59</v>
       </c>
     </row>
     <row r="479">
@@ -10109,7 +10115,7 @@
         <v>52</v>
       </c>
       <c r="D479" s="0">
-        <v>17425</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="480">
@@ -10120,66 +10126,66 @@
         <v>1025</v>
       </c>
       <c r="C480" s="0" t="s">
-        <v>1026</v>
+        <v>52</v>
       </c>
       <c r="D480" s="0">
-        <v>1958</v>
+        <v>17425</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" s="0" t="s">
+        <v>1026</v>
+      </c>
+      <c r="B481" s="0" t="s">
         <v>1027</v>
       </c>
-      <c r="B481" s="0" t="s">
+      <c r="C481" s="0" t="s">
         <v>1028</v>
       </c>
-      <c r="C481" s="0" t="s">
-        <v>1029</v>
-      </c>
       <c r="D481" s="0">
-        <v>2282.3</v>
+        <v>1958</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" s="0" t="s">
+        <v>1029</v>
+      </c>
+      <c r="B482" s="0" t="s">
         <v>1030</v>
       </c>
-      <c r="B482" s="0" t="s">
+      <c r="C482" s="0" t="s">
         <v>1031</v>
       </c>
-      <c r="C482" s="0" t="s">
-        <v>1032</v>
-      </c>
       <c r="D482" s="0">
-        <v>386</v>
+        <v>2282.3</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" s="0" t="s">
+        <v>1032</v>
+      </c>
+      <c r="B483" s="0" t="s">
         <v>1033</v>
       </c>
-      <c r="B483" s="0" t="s">
+      <c r="C483" s="0" t="s">
         <v>1034</v>
       </c>
-      <c r="C483" s="0" t="s">
-        <v>1035</v>
-      </c>
       <c r="D483" s="0">
-        <v>385.4</v>
+        <v>386</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" s="0" t="s">
+        <v>1035</v>
+      </c>
+      <c r="B484" s="0" t="s">
         <v>1036</v>
       </c>
-      <c r="B484" s="0" t="s">
+      <c r="C484" s="0" t="s">
         <v>1037</v>
       </c>
-      <c r="C484" s="0" t="s">
-        <v>97</v>
-      </c>
       <c r="D484" s="0">
-        <v>296147.5</v>
+        <v>385.4</v>
       </c>
     </row>
     <row r="485">
@@ -10190,10 +10196,10 @@
         <v>1039</v>
       </c>
       <c r="C485" s="0" t="s">
-        <v>128</v>
+        <v>97</v>
       </c>
       <c r="D485" s="0">
-        <v>1890</v>
+        <v>296147.5</v>
       </c>
     </row>
     <row r="486">
@@ -10204,10 +10210,10 @@
         <v>1041</v>
       </c>
       <c r="C486" s="0" t="s">
-        <v>602</v>
+        <v>128</v>
       </c>
       <c r="D486" s="0">
-        <v>83000</v>
+        <v>1890</v>
       </c>
     </row>
     <row r="487">
@@ -10218,10 +10224,10 @@
         <v>1043</v>
       </c>
       <c r="C487" s="0" t="s">
-        <v>145</v>
+        <v>604</v>
       </c>
       <c r="D487" s="0">
-        <v>99</v>
+        <v>83000</v>
       </c>
     </row>
     <row r="488">
@@ -10232,10 +10238,10 @@
         <v>1045</v>
       </c>
       <c r="C488" s="0" t="s">
-        <v>75</v>
+        <v>145</v>
       </c>
       <c r="D488" s="0">
-        <v>950</v>
+        <v>99</v>
       </c>
     </row>
     <row r="489">
@@ -10246,10 +10252,10 @@
         <v>1047</v>
       </c>
       <c r="C489" s="0" t="s">
-        <v>477</v>
+        <v>75</v>
       </c>
       <c r="D489" s="0">
-        <v>398107</v>
+        <v>950</v>
       </c>
     </row>
     <row r="490">
@@ -10260,10 +10266,10 @@
         <v>1049</v>
       </c>
       <c r="C490" s="0" t="s">
-        <v>165</v>
+        <v>479</v>
       </c>
       <c r="D490" s="0">
-        <v>2200</v>
+        <v>398107</v>
       </c>
     </row>
     <row r="491">
@@ -10274,10 +10280,10 @@
         <v>1051</v>
       </c>
       <c r="C491" s="0" t="s">
-        <v>212</v>
+        <v>165</v>
       </c>
       <c r="D491" s="0">
-        <v>41000</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="492">
@@ -10288,10 +10294,10 @@
         <v>1053</v>
       </c>
       <c r="C492" s="0" t="s">
-        <v>75</v>
+        <v>212</v>
       </c>
       <c r="D492" s="0">
-        <v>5790</v>
+        <v>41000</v>
       </c>
     </row>
     <row r="493">
@@ -10302,10 +10308,10 @@
         <v>1055</v>
       </c>
       <c r="C493" s="0" t="s">
-        <v>950</v>
+        <v>75</v>
       </c>
       <c r="D493" s="0">
-        <v>880</v>
+        <v>5790</v>
       </c>
     </row>
     <row r="494">
@@ -10316,7 +10322,7 @@
         <v>1057</v>
       </c>
       <c r="C494" s="0" t="s">
-        <v>950</v>
+        <v>952</v>
       </c>
       <c r="D494" s="0">
         <v>880</v>
@@ -10330,7 +10336,7 @@
         <v>1059</v>
       </c>
       <c r="C495" s="0" t="s">
-        <v>950</v>
+        <v>952</v>
       </c>
       <c r="D495" s="0">
         <v>880</v>
@@ -10344,10 +10350,10 @@
         <v>1061</v>
       </c>
       <c r="C496" s="0" t="s">
-        <v>21</v>
+        <v>952</v>
       </c>
       <c r="D496" s="0">
-        <v>563.36</v>
+        <v>880</v>
       </c>
     </row>
     <row r="497">
@@ -10358,10 +10364,10 @@
         <v>1063</v>
       </c>
       <c r="C497" s="0" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D497" s="0">
-        <v>3520</v>
+        <v>563.36</v>
       </c>
     </row>
     <row r="498">
@@ -10375,7 +10381,7 @@
         <v>15</v>
       </c>
       <c r="D498" s="0">
-        <v>2600</v>
+        <v>3520</v>
       </c>
     </row>
     <row r="499">
@@ -10386,10 +10392,10 @@
         <v>1067</v>
       </c>
       <c r="C499" s="0" t="s">
-        <v>289</v>
+        <v>15</v>
       </c>
       <c r="D499" s="0">
-        <v>3700</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="500">
@@ -10403,7 +10409,7 @@
         <v>289</v>
       </c>
       <c r="D500" s="0">
-        <v>2600</v>
+        <v>3700</v>
       </c>
     </row>
     <row r="501">
@@ -10414,10 +10420,10 @@
         <v>1071</v>
       </c>
       <c r="C501" s="0" t="s">
-        <v>15</v>
+        <v>289</v>
       </c>
       <c r="D501" s="0">
-        <v>2235</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="502">
@@ -10431,7 +10437,7 @@
         <v>15</v>
       </c>
       <c r="D502" s="0">
-        <v>3850</v>
+        <v>2235</v>
       </c>
     </row>
     <row r="503">
@@ -10442,24 +10448,24 @@
         <v>1075</v>
       </c>
       <c r="C503" s="0" t="s">
-        <v>1076</v>
+        <v>15</v>
       </c>
       <c r="D503" s="0">
-        <v>1</v>
+        <v>3850</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" s="0" t="s">
+        <v>1076</v>
+      </c>
+      <c r="B504" s="0" t="s">
         <v>1077</v>
       </c>
-      <c r="B504" s="0" t="s">
+      <c r="C504" s="0" t="s">
         <v>1078</v>
       </c>
-      <c r="C504" s="0" t="s">
-        <v>28</v>
-      </c>
       <c r="D504" s="0">
-        <v>15189</v>
+        <v>1</v>
       </c>
     </row>
     <row r="505">
@@ -10470,10 +10476,10 @@
         <v>1080</v>
       </c>
       <c r="C505" s="0" t="s">
-        <v>384</v>
+        <v>28</v>
       </c>
       <c r="D505" s="0">
-        <v>3859.93</v>
+        <v>15189</v>
       </c>
     </row>
     <row r="506">
@@ -10487,7 +10493,7 @@
         <v>384</v>
       </c>
       <c r="D506" s="0">
-        <v>11751.49</v>
+        <v>3859.93</v>
       </c>
     </row>
     <row r="507">
@@ -10498,10 +10504,10 @@
         <v>1084</v>
       </c>
       <c r="C507" s="0" t="s">
-        <v>346</v>
+        <v>384</v>
       </c>
       <c r="D507" s="0">
-        <v>6000</v>
+        <v>11751.49</v>
       </c>
     </row>
     <row r="508">
@@ -10515,7 +10521,7 @@
         <v>346</v>
       </c>
       <c r="D508" s="0">
-        <v>3000</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="509">
@@ -10526,10 +10532,10 @@
         <v>1088</v>
       </c>
       <c r="C509" s="0" t="s">
-        <v>37</v>
+        <v>346</v>
       </c>
       <c r="D509" s="0">
-        <v>618</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="510">
@@ -10540,24 +10546,24 @@
         <v>1090</v>
       </c>
       <c r="C510" s="0" t="s">
-        <v>1091</v>
+        <v>37</v>
       </c>
       <c r="D510" s="0">
-        <v>24600</v>
+        <v>618</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" s="0" t="s">
+        <v>1091</v>
+      </c>
+      <c r="B511" s="0" t="s">
         <v>1092</v>
       </c>
-      <c r="B511" s="0" t="s">
+      <c r="C511" s="0" t="s">
         <v>1093</v>
       </c>
-      <c r="C511" s="0" t="s">
-        <v>110</v>
-      </c>
       <c r="D511" s="0">
-        <v>0</v>
+        <v>24600</v>
       </c>
     </row>
     <row r="512">
@@ -10568,10 +10574,10 @@
         <v>1095</v>
       </c>
       <c r="C512" s="0" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="D512" s="0">
-        <v>43590.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="513">
@@ -10582,10 +10588,10 @@
         <v>1097</v>
       </c>
       <c r="C513" s="0" t="s">
-        <v>477</v>
+        <v>97</v>
       </c>
       <c r="D513" s="0">
-        <v>213700</v>
+        <v>43590.25</v>
       </c>
     </row>
     <row r="514">
@@ -10596,10 +10602,10 @@
         <v>1099</v>
       </c>
       <c r="C514" s="0" t="s">
-        <v>384</v>
+        <v>479</v>
       </c>
       <c r="D514" s="0">
-        <v>77429.29</v>
+        <v>213700</v>
       </c>
     </row>
     <row r="515">
@@ -10613,7 +10619,7 @@
         <v>384</v>
       </c>
       <c r="D515" s="0">
-        <v>42913.42</v>
+        <v>77429.29</v>
       </c>
     </row>
     <row r="516">
@@ -10627,7 +10633,7 @@
         <v>384</v>
       </c>
       <c r="D516" s="0">
-        <v>88806.25</v>
+        <v>42913.42</v>
       </c>
     </row>
     <row r="517">
@@ -10641,7 +10647,7 @@
         <v>384</v>
       </c>
       <c r="D517" s="0">
-        <v>50781.52</v>
+        <v>88806.25</v>
       </c>
     </row>
     <row r="518">
@@ -10652,10 +10658,10 @@
         <v>1107</v>
       </c>
       <c r="C518" s="0" t="s">
-        <v>21</v>
+        <v>384</v>
       </c>
       <c r="D518" s="0">
-        <v>1600</v>
+        <v>50781.52</v>
       </c>
     </row>
     <row r="519">
@@ -10666,10 +10672,10 @@
         <v>1109</v>
       </c>
       <c r="C519" s="0" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D519" s="0">
-        <v>3521.4</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="520">
@@ -10683,7 +10689,7 @@
         <v>28</v>
       </c>
       <c r="D520" s="0">
-        <v>3987</v>
+        <v>3521.4</v>
       </c>
     </row>
     <row r="521">
@@ -10697,7 +10703,7 @@
         <v>28</v>
       </c>
       <c r="D521" s="0">
-        <v>4086.37</v>
+        <v>3987</v>
       </c>
     </row>
     <row r="522">
@@ -10711,7 +10717,7 @@
         <v>28</v>
       </c>
       <c r="D522" s="0">
-        <v>3382.65</v>
+        <v>4086.37</v>
       </c>
     </row>
     <row r="523">
@@ -10722,10 +10728,10 @@
         <v>1117</v>
       </c>
       <c r="C523" s="0" t="s">
-        <v>165</v>
+        <v>28</v>
       </c>
       <c r="D523" s="0">
-        <v>430</v>
+        <v>3382.65</v>
       </c>
     </row>
     <row r="524">
@@ -10736,9 +10742,23 @@
         <v>1119</v>
       </c>
       <c r="C524" s="0" t="s">
+        <v>165</v>
+      </c>
+      <c r="D524" s="0">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" s="0" t="s">
+        <v>1120</v>
+      </c>
+      <c r="B525" s="0" t="s">
+        <v>1121</v>
+      </c>
+      <c r="C525" s="0" t="s">
         <v>145</v>
       </c>
-      <c r="D524" s="0">
+      <c r="D525" s="0">
         <v>495</v>
       </c>
     </row>

--- a/price_list.xlsx
+++ b/price_list.xlsx
@@ -3815,7 +3815,7 @@
         <v>69</v>
       </c>
       <c r="D29" s="0">
-        <v>2158.2</v>
+        <v>2275</v>
       </c>
     </row>
     <row r="30">
@@ -3829,7 +3829,7 @@
         <v>72</v>
       </c>
       <c r="D30" s="0">
-        <v>2220</v>
+        <v>2275</v>
       </c>
     </row>
     <row r="31">

--- a/price_list.xlsx
+++ b/price_list.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1122" uniqueCount="1122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1124" uniqueCount="1124">
   <si>
     <t>Solo Activos</t>
   </si>
@@ -2307,6 +2307,12 @@
   </si>
   <si>
     <t xml:space="preserve">METRONIDAZOL DENVER FARMA 500MG COMP. X   10 - 000022239</t>
+  </si>
+  <si>
+    <t>000024247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">METRONIDAZOL VANNIER 500MG  X 10 COMPRIMIDOS - 000024247</t>
   </si>
   <si>
     <t>000022207</t>
@@ -3443,7 +3449,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A2:D525"/>
+  <dimension ref="A2:D526"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
@@ -6895,7 +6901,7 @@
         <v>75</v>
       </c>
       <c r="D249" s="0">
-        <v>90000</v>
+        <v>110000</v>
       </c>
     </row>
     <row r="250">
@@ -6909,7 +6915,7 @@
         <v>75</v>
       </c>
       <c r="D250" s="0">
-        <v>110000</v>
+        <v>130000</v>
       </c>
     </row>
     <row r="251">
@@ -8376,10 +8382,10 @@
         <v>766</v>
       </c>
       <c r="C355" s="0" t="s">
-        <v>128</v>
+        <v>21</v>
       </c>
       <c r="D355" s="0">
-        <v>4767</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="356">
@@ -8390,10 +8396,10 @@
         <v>768</v>
       </c>
       <c r="C356" s="0" t="s">
-        <v>34</v>
+        <v>128</v>
       </c>
       <c r="D356" s="0">
-        <v>650</v>
+        <v>4767</v>
       </c>
     </row>
     <row r="357">
@@ -8404,7 +8410,7 @@
         <v>770</v>
       </c>
       <c r="C357" s="0" t="s">
-        <v>75</v>
+        <v>34</v>
       </c>
       <c r="D357" s="0">
         <v>650</v>
@@ -8418,10 +8424,10 @@
         <v>772</v>
       </c>
       <c r="C358" s="0" t="s">
-        <v>15</v>
+        <v>75</v>
       </c>
       <c r="D358" s="0">
-        <v>2178</v>
+        <v>650</v>
       </c>
     </row>
     <row r="359">
@@ -8432,10 +8438,10 @@
         <v>774</v>
       </c>
       <c r="C359" s="0" t="s">
-        <v>97</v>
+        <v>15</v>
       </c>
       <c r="D359" s="0">
-        <v>7986</v>
+        <v>2178</v>
       </c>
     </row>
     <row r="360">
@@ -8446,24 +8452,24 @@
         <v>776</v>
       </c>
       <c r="C360" s="0" t="s">
-        <v>777</v>
+        <v>97</v>
       </c>
       <c r="D360" s="0">
-        <v>1910</v>
+        <v>7986</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" s="0" t="s">
+        <v>777</v>
+      </c>
+      <c r="B361" s="0" t="s">
         <v>778</v>
       </c>
-      <c r="B361" s="0" t="s">
+      <c r="C361" s="0" t="s">
         <v>779</v>
       </c>
-      <c r="C361" s="0" t="s">
-        <v>156</v>
-      </c>
       <c r="D361" s="0">
-        <v>900</v>
+        <v>1910</v>
       </c>
     </row>
     <row r="362">
@@ -8474,10 +8480,10 @@
         <v>781</v>
       </c>
       <c r="C362" s="0" t="s">
-        <v>21</v>
+        <v>156</v>
       </c>
       <c r="D362" s="0">
-        <v>1722</v>
+        <v>900</v>
       </c>
     </row>
     <row r="363">
@@ -8488,10 +8494,10 @@
         <v>783</v>
       </c>
       <c r="C363" s="0" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="D363" s="0">
-        <v>59000</v>
+        <v>1722</v>
       </c>
     </row>
     <row r="364">
@@ -8502,10 +8508,10 @@
         <v>785</v>
       </c>
       <c r="C364" s="0" t="s">
-        <v>156</v>
+        <v>34</v>
       </c>
       <c r="D364" s="0">
-        <v>750</v>
+        <v>59000</v>
       </c>
     </row>
     <row r="365">
@@ -8519,7 +8525,7 @@
         <v>156</v>
       </c>
       <c r="D365" s="0">
-        <v>1212</v>
+        <v>750</v>
       </c>
     </row>
     <row r="366">
@@ -8533,7 +8539,7 @@
         <v>156</v>
       </c>
       <c r="D366" s="0">
-        <v>1300</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="367">
@@ -8547,7 +8553,7 @@
         <v>156</v>
       </c>
       <c r="D367" s="0">
-        <v>1500</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="368">
@@ -8561,7 +8567,7 @@
         <v>156</v>
       </c>
       <c r="D368" s="0">
-        <v>1400</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="369">
@@ -8572,10 +8578,10 @@
         <v>795</v>
       </c>
       <c r="C369" s="0" t="s">
-        <v>269</v>
+        <v>156</v>
       </c>
       <c r="D369" s="0">
-        <v>11959</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="370">
@@ -8586,10 +8592,10 @@
         <v>797</v>
       </c>
       <c r="C370" s="0" t="s">
-        <v>145</v>
+        <v>269</v>
       </c>
       <c r="D370" s="0">
-        <v>365</v>
+        <v>11959</v>
       </c>
     </row>
     <row r="371">
@@ -8600,10 +8606,10 @@
         <v>799</v>
       </c>
       <c r="C371" s="0" t="s">
-        <v>289</v>
+        <v>145</v>
       </c>
       <c r="D371" s="0">
-        <v>1450</v>
+        <v>365</v>
       </c>
     </row>
     <row r="372">
@@ -8614,10 +8620,10 @@
         <v>801</v>
       </c>
       <c r="C372" s="0" t="s">
-        <v>97</v>
+        <v>289</v>
       </c>
       <c r="D372" s="0">
-        <v>7320.5</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="373">
@@ -8628,10 +8634,10 @@
         <v>803</v>
       </c>
       <c r="C373" s="0" t="s">
-        <v>15</v>
+        <v>97</v>
       </c>
       <c r="D373" s="0">
-        <v>900</v>
+        <v>7320.5</v>
       </c>
     </row>
     <row r="374">
@@ -8642,10 +8648,10 @@
         <v>805</v>
       </c>
       <c r="C374" s="0" t="s">
-        <v>289</v>
+        <v>15</v>
       </c>
       <c r="D374" s="0">
-        <v>566</v>
+        <v>900</v>
       </c>
     </row>
     <row r="375">
@@ -8656,10 +8662,10 @@
         <v>807</v>
       </c>
       <c r="C375" s="0" t="s">
-        <v>479</v>
+        <v>289</v>
       </c>
       <c r="D375" s="0">
-        <v>64925</v>
+        <v>566</v>
       </c>
     </row>
     <row r="376">
@@ -8670,10 +8676,10 @@
         <v>809</v>
       </c>
       <c r="C376" s="0" t="s">
-        <v>15</v>
+        <v>479</v>
       </c>
       <c r="D376" s="0">
-        <v>1100</v>
+        <v>64925</v>
       </c>
     </row>
     <row r="377">
@@ -8684,10 +8690,10 @@
         <v>811</v>
       </c>
       <c r="C377" s="0" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="D377" s="0">
-        <v>1623</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="378">
@@ -8698,10 +8704,10 @@
         <v>813</v>
       </c>
       <c r="C378" s="0" t="s">
-        <v>145</v>
+        <v>21</v>
       </c>
       <c r="D378" s="0">
-        <v>1269</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="379">
@@ -8715,7 +8721,7 @@
         <v>145</v>
       </c>
       <c r="D379" s="0">
-        <v>4712</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="380">
@@ -8726,10 +8732,10 @@
         <v>817</v>
       </c>
       <c r="C380" s="0" t="s">
-        <v>28</v>
+        <v>145</v>
       </c>
       <c r="D380" s="0">
-        <v>1250</v>
+        <v>4712</v>
       </c>
     </row>
     <row r="381">
@@ -8743,7 +8749,7 @@
         <v>28</v>
       </c>
       <c r="D381" s="0">
-        <v>1986</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="382">
@@ -8754,10 +8760,10 @@
         <v>821</v>
       </c>
       <c r="C382" s="0" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="D382" s="0">
-        <v>450</v>
+        <v>1986</v>
       </c>
     </row>
     <row r="383">
@@ -8771,7 +8777,7 @@
         <v>15</v>
       </c>
       <c r="D383" s="0">
-        <v>825</v>
+        <v>450</v>
       </c>
     </row>
     <row r="384">
@@ -8796,10 +8802,10 @@
         <v>827</v>
       </c>
       <c r="C385" s="0" t="s">
-        <v>387</v>
+        <v>15</v>
       </c>
       <c r="D385" s="0">
-        <v>134775.6</v>
+        <v>825</v>
       </c>
     </row>
     <row r="386">
@@ -8813,7 +8819,7 @@
         <v>387</v>
       </c>
       <c r="D386" s="0">
-        <v>175991.55</v>
+        <v>134775.6</v>
       </c>
     </row>
     <row r="387">
@@ -8824,10 +8830,10 @@
         <v>831</v>
       </c>
       <c r="C387" s="0" t="s">
-        <v>75</v>
+        <v>387</v>
       </c>
       <c r="D387" s="0">
-        <v>3427</v>
+        <v>175991.55</v>
       </c>
     </row>
     <row r="388">
@@ -8841,7 +8847,7 @@
         <v>75</v>
       </c>
       <c r="D388" s="0">
-        <v>10618</v>
+        <v>3427</v>
       </c>
     </row>
     <row r="389">
@@ -8852,10 +8858,10 @@
         <v>835</v>
       </c>
       <c r="C389" s="0" t="s">
-        <v>289</v>
+        <v>75</v>
       </c>
       <c r="D389" s="0">
-        <v>515</v>
+        <v>10618</v>
       </c>
     </row>
     <row r="390">
@@ -8866,7 +8872,7 @@
         <v>837</v>
       </c>
       <c r="C390" s="0" t="s">
-        <v>37</v>
+        <v>289</v>
       </c>
       <c r="D390" s="0">
         <v>515</v>
@@ -8880,10 +8886,10 @@
         <v>839</v>
       </c>
       <c r="C391" s="0" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="D391" s="0">
-        <v>10000</v>
+        <v>515</v>
       </c>
     </row>
     <row r="392">
@@ -8894,10 +8900,10 @@
         <v>841</v>
       </c>
       <c r="C392" s="0" t="s">
-        <v>479</v>
+        <v>52</v>
       </c>
       <c r="D392" s="0">
-        <v>213700</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="393">
@@ -8911,7 +8917,7 @@
         <v>479</v>
       </c>
       <c r="D393" s="0">
-        <v>257000</v>
+        <v>213700</v>
       </c>
     </row>
     <row r="394">
@@ -8922,10 +8928,10 @@
         <v>845</v>
       </c>
       <c r="C394" s="0" t="s">
-        <v>75</v>
+        <v>479</v>
       </c>
       <c r="D394" s="0">
-        <v>10522</v>
+        <v>257000</v>
       </c>
     </row>
     <row r="395">
@@ -8939,7 +8945,7 @@
         <v>75</v>
       </c>
       <c r="D395" s="0">
-        <v>19481</v>
+        <v>10522</v>
       </c>
     </row>
     <row r="396">
@@ -8950,24 +8956,24 @@
         <v>849</v>
       </c>
       <c r="C396" s="0" t="s">
-        <v>850</v>
+        <v>75</v>
       </c>
       <c r="D396" s="0">
-        <v>1080</v>
+        <v>19481</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" s="0" t="s">
+        <v>850</v>
+      </c>
+      <c r="B397" s="0" t="s">
         <v>851</v>
       </c>
-      <c r="B397" s="0" t="s">
+      <c r="C397" s="0" t="s">
         <v>852</v>
       </c>
-      <c r="C397" s="0" t="s">
-        <v>18</v>
-      </c>
       <c r="D397" s="0">
-        <v>586.49</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="398">
@@ -8978,24 +8984,24 @@
         <v>854</v>
       </c>
       <c r="C398" s="0" t="s">
-        <v>855</v>
+        <v>18</v>
       </c>
       <c r="D398" s="0">
-        <v>520</v>
+        <v>586.49</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" s="0" t="s">
+        <v>855</v>
+      </c>
+      <c r="B399" s="0" t="s">
         <v>856</v>
       </c>
-      <c r="B399" s="0" t="s">
+      <c r="C399" s="0" t="s">
         <v>857</v>
       </c>
-      <c r="C399" s="0" t="s">
-        <v>855</v>
-      </c>
       <c r="D399" s="0">
-        <v>300</v>
+        <v>520</v>
       </c>
     </row>
     <row r="400">
@@ -9006,10 +9012,10 @@
         <v>859</v>
       </c>
       <c r="C400" s="0" t="s">
-        <v>34</v>
+        <v>857</v>
       </c>
       <c r="D400" s="0">
-        <v>630</v>
+        <v>300</v>
       </c>
     </row>
     <row r="401">
@@ -9020,10 +9026,10 @@
         <v>861</v>
       </c>
       <c r="C401" s="0" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="D401" s="0">
-        <v>2200</v>
+        <v>630</v>
       </c>
     </row>
     <row r="402">
@@ -9037,7 +9043,7 @@
         <v>15</v>
       </c>
       <c r="D402" s="0">
-        <v>2800</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="403">
@@ -9048,10 +9054,10 @@
         <v>865</v>
       </c>
       <c r="C403" s="0" t="s">
-        <v>97</v>
+        <v>15</v>
       </c>
       <c r="D403" s="0">
-        <v>5190.9</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="404">
@@ -9062,10 +9068,10 @@
         <v>867</v>
       </c>
       <c r="C404" s="0" t="s">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="D404" s="0">
-        <v>2969</v>
+        <v>5190.9</v>
       </c>
     </row>
     <row r="405">
@@ -9076,10 +9082,10 @@
         <v>869</v>
       </c>
       <c r="C405" s="0" t="s">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="D405" s="0">
-        <v>3800</v>
+        <v>2969</v>
       </c>
     </row>
     <row r="406">
@@ -9090,10 +9096,10 @@
         <v>871</v>
       </c>
       <c r="C406" s="0" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="D406" s="0">
-        <v>4000</v>
+        <v>3800</v>
       </c>
     </row>
     <row r="407">
@@ -9104,24 +9110,24 @@
         <v>873</v>
       </c>
       <c r="C407" s="0" t="s">
-        <v>874</v>
+        <v>15</v>
       </c>
       <c r="D407" s="0">
-        <v>3800</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" s="0" t="s">
+        <v>874</v>
+      </c>
+      <c r="B408" s="0" t="s">
         <v>875</v>
       </c>
-      <c r="B408" s="0" t="s">
+      <c r="C408" s="0" t="s">
         <v>876</v>
       </c>
-      <c r="C408" s="0" t="s">
-        <v>21</v>
-      </c>
       <c r="D408" s="0">
-        <v>353</v>
+        <v>3800</v>
       </c>
     </row>
     <row r="409">
@@ -9132,10 +9138,10 @@
         <v>878</v>
       </c>
       <c r="C409" s="0" t="s">
-        <v>115</v>
+        <v>21</v>
       </c>
       <c r="D409" s="0">
-        <v>1800</v>
+        <v>353</v>
       </c>
     </row>
     <row r="410">
@@ -9146,10 +9152,10 @@
         <v>880</v>
       </c>
       <c r="C410" s="0" t="s">
-        <v>15</v>
+        <v>115</v>
       </c>
       <c r="D410" s="0">
-        <v>2948</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="411">
@@ -9160,10 +9166,10 @@
         <v>882</v>
       </c>
       <c r="C411" s="0" t="s">
-        <v>97</v>
+        <v>15</v>
       </c>
       <c r="D411" s="0">
-        <v>146.41</v>
+        <v>2948</v>
       </c>
     </row>
     <row r="412">
@@ -9174,10 +9180,10 @@
         <v>884</v>
       </c>
       <c r="C412" s="0" t="s">
-        <v>215</v>
+        <v>97</v>
       </c>
       <c r="D412" s="0">
-        <v>65537</v>
+        <v>146.41</v>
       </c>
     </row>
     <row r="413">
@@ -9188,10 +9194,10 @@
         <v>886</v>
       </c>
       <c r="C413" s="0" t="s">
-        <v>145</v>
+        <v>215</v>
       </c>
       <c r="D413" s="0">
-        <v>4130.4</v>
+        <v>65537</v>
       </c>
     </row>
     <row r="414">
@@ -9205,7 +9211,7 @@
         <v>145</v>
       </c>
       <c r="D414" s="0">
-        <v>4283</v>
+        <v>4130.4</v>
       </c>
     </row>
     <row r="415">
@@ -9219,7 +9225,7 @@
         <v>145</v>
       </c>
       <c r="D415" s="0">
-        <v>6524.8</v>
+        <v>4283</v>
       </c>
     </row>
     <row r="416">
@@ -9230,10 +9236,10 @@
         <v>892</v>
       </c>
       <c r="C416" s="0" t="s">
-        <v>316</v>
+        <v>145</v>
       </c>
       <c r="D416" s="0">
-        <v>570</v>
+        <v>6524.8</v>
       </c>
     </row>
     <row r="417">
@@ -9244,10 +9250,10 @@
         <v>894</v>
       </c>
       <c r="C417" s="0" t="s">
-        <v>75</v>
+        <v>316</v>
       </c>
       <c r="D417" s="0">
-        <v>550</v>
+        <v>570</v>
       </c>
     </row>
     <row r="418">
@@ -9258,10 +9264,10 @@
         <v>896</v>
       </c>
       <c r="C418" s="0" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="D418" s="0">
-        <v>153</v>
+        <v>550</v>
       </c>
     </row>
     <row r="419">
@@ -9272,10 +9278,10 @@
         <v>898</v>
       </c>
       <c r="C419" s="0" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="D419" s="0">
-        <v>740.7</v>
+        <v>153</v>
       </c>
     </row>
     <row r="420">
@@ -9286,10 +9292,10 @@
         <v>900</v>
       </c>
       <c r="C420" s="0" t="s">
-        <v>64</v>
+        <v>28</v>
       </c>
       <c r="D420" s="0">
-        <v>101000</v>
+        <v>740.7</v>
       </c>
     </row>
     <row r="421">
@@ -9300,10 +9306,10 @@
         <v>902</v>
       </c>
       <c r="C421" s="0" t="s">
-        <v>128</v>
+        <v>64</v>
       </c>
       <c r="D421" s="0">
-        <v>6251</v>
+        <v>101000</v>
       </c>
     </row>
     <row r="422">
@@ -9314,10 +9320,10 @@
         <v>904</v>
       </c>
       <c r="C422" s="0" t="s">
-        <v>145</v>
+        <v>128</v>
       </c>
       <c r="D422" s="0">
-        <v>883</v>
+        <v>6251</v>
       </c>
     </row>
     <row r="423">
@@ -9328,10 +9334,10 @@
         <v>906</v>
       </c>
       <c r="C423" s="0" t="s">
-        <v>97</v>
+        <v>145</v>
       </c>
       <c r="D423" s="0">
-        <v>1164.66</v>
+        <v>883</v>
       </c>
     </row>
     <row r="424">
@@ -9342,10 +9348,10 @@
         <v>908</v>
       </c>
       <c r="C424" s="0" t="s">
-        <v>156</v>
+        <v>97</v>
       </c>
       <c r="D424" s="0">
-        <v>360</v>
+        <v>1164.66</v>
       </c>
     </row>
     <row r="425">
@@ -9359,7 +9365,7 @@
         <v>156</v>
       </c>
       <c r="D425" s="0">
-        <v>450</v>
+        <v>360</v>
       </c>
     </row>
     <row r="426">
@@ -9373,7 +9379,7 @@
         <v>156</v>
       </c>
       <c r="D426" s="0">
-        <v>2150</v>
+        <v>450</v>
       </c>
     </row>
     <row r="427">
@@ -9384,10 +9390,10 @@
         <v>914</v>
       </c>
       <c r="C427" s="0" t="s">
-        <v>604</v>
+        <v>156</v>
       </c>
       <c r="D427" s="0">
-        <v>25192.82</v>
+        <v>2150</v>
       </c>
     </row>
     <row r="428">
@@ -9398,10 +9404,10 @@
         <v>916</v>
       </c>
       <c r="C428" s="0" t="s">
-        <v>75</v>
+        <v>604</v>
       </c>
       <c r="D428" s="0">
-        <v>3500</v>
+        <v>25192.82</v>
       </c>
     </row>
     <row r="429">
@@ -9412,10 +9418,10 @@
         <v>918</v>
       </c>
       <c r="C429" s="0" t="s">
-        <v>180</v>
+        <v>75</v>
       </c>
       <c r="D429" s="0">
-        <v>600</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="430">
@@ -9426,24 +9432,24 @@
         <v>920</v>
       </c>
       <c r="C430" s="0" t="s">
-        <v>921</v>
+        <v>180</v>
       </c>
       <c r="D430" s="0">
-        <v>1080</v>
+        <v>600</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" s="0" t="s">
+        <v>921</v>
+      </c>
+      <c r="B431" s="0" t="s">
         <v>922</v>
       </c>
-      <c r="B431" s="0" t="s">
+      <c r="C431" s="0" t="s">
         <v>923</v>
       </c>
-      <c r="C431" s="0" t="s">
-        <v>346</v>
-      </c>
       <c r="D431" s="0">
-        <v>8628</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="432">
@@ -9454,10 +9460,10 @@
         <v>925</v>
       </c>
       <c r="C432" s="0" t="s">
-        <v>40</v>
+        <v>346</v>
       </c>
       <c r="D432" s="0">
-        <v>27991.54</v>
+        <v>8628</v>
       </c>
     </row>
     <row r="433">
@@ -9468,10 +9474,10 @@
         <v>927</v>
       </c>
       <c r="C433" s="0" t="s">
-        <v>145</v>
+        <v>40</v>
       </c>
       <c r="D433" s="0">
-        <v>1020</v>
+        <v>27991.54</v>
       </c>
     </row>
     <row r="434">
@@ -9485,7 +9491,7 @@
         <v>145</v>
       </c>
       <c r="D434" s="0">
-        <v>4106</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="435">
@@ -9496,10 +9502,10 @@
         <v>931</v>
       </c>
       <c r="C435" s="0" t="s">
-        <v>289</v>
+        <v>145</v>
       </c>
       <c r="D435" s="0">
-        <v>450</v>
+        <v>4106</v>
       </c>
     </row>
     <row r="436">
@@ -9510,10 +9516,10 @@
         <v>933</v>
       </c>
       <c r="C436" s="0" t="s">
-        <v>45</v>
+        <v>289</v>
       </c>
       <c r="D436" s="0">
-        <v>6398.6</v>
+        <v>450</v>
       </c>
     </row>
     <row r="437">
@@ -9527,7 +9533,7 @@
         <v>45</v>
       </c>
       <c r="D437" s="0">
-        <v>2886.7</v>
+        <v>6398.6</v>
       </c>
     </row>
     <row r="438">
@@ -9541,7 +9547,7 @@
         <v>45</v>
       </c>
       <c r="D438" s="0">
-        <v>2050.95</v>
+        <v>2886.7</v>
       </c>
     </row>
     <row r="439">
@@ -9555,7 +9561,7 @@
         <v>45</v>
       </c>
       <c r="D439" s="0">
-        <v>30050.45</v>
+        <v>2050.95</v>
       </c>
     </row>
     <row r="440">
@@ -9569,7 +9575,7 @@
         <v>45</v>
       </c>
       <c r="D440" s="0">
-        <v>2326.8</v>
+        <v>30050.45</v>
       </c>
     </row>
     <row r="441">
@@ -9583,7 +9589,7 @@
         <v>45</v>
       </c>
       <c r="D441" s="0">
-        <v>6429.95</v>
+        <v>2326.8</v>
       </c>
     </row>
     <row r="442">
@@ -9597,7 +9603,7 @@
         <v>45</v>
       </c>
       <c r="D442" s="0">
-        <v>5180.26</v>
+        <v>6429.95</v>
       </c>
     </row>
     <row r="443">
@@ -9608,10 +9614,10 @@
         <v>947</v>
       </c>
       <c r="C443" s="0" t="s">
-        <v>212</v>
+        <v>45</v>
       </c>
       <c r="D443" s="0">
-        <v>510</v>
+        <v>5180.26</v>
       </c>
     </row>
     <row r="444">
@@ -9622,7 +9628,7 @@
         <v>949</v>
       </c>
       <c r="C444" s="0" t="s">
-        <v>37</v>
+        <v>212</v>
       </c>
       <c r="D444" s="0">
         <v>510</v>
@@ -9636,21 +9642,21 @@
         <v>951</v>
       </c>
       <c r="C445" s="0" t="s">
-        <v>952</v>
+        <v>37</v>
       </c>
       <c r="D445" s="0">
-        <v>626</v>
+        <v>510</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" s="0" t="s">
+        <v>952</v>
+      </c>
+      <c r="B446" s="0" t="s">
         <v>953</v>
       </c>
-      <c r="B446" s="0" t="s">
+      <c r="C446" s="0" t="s">
         <v>954</v>
-      </c>
-      <c r="C446" s="0" t="s">
-        <v>952</v>
       </c>
       <c r="D446" s="0">
         <v>626</v>
@@ -9664,7 +9670,7 @@
         <v>956</v>
       </c>
       <c r="C447" s="0" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="D447" s="0">
         <v>626</v>
@@ -9678,10 +9684,10 @@
         <v>958</v>
       </c>
       <c r="C448" s="0" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="D448" s="0">
-        <v>342</v>
+        <v>626</v>
       </c>
     </row>
     <row r="449">
@@ -9692,7 +9698,7 @@
         <v>960</v>
       </c>
       <c r="C449" s="0" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="D449" s="0">
         <v>342</v>
@@ -9706,7 +9712,7 @@
         <v>962</v>
       </c>
       <c r="C450" s="0" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="D450" s="0">
         <v>342</v>
@@ -9720,10 +9726,10 @@
         <v>964</v>
       </c>
       <c r="C451" s="0" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="D451" s="0">
-        <v>0</v>
+        <v>342</v>
       </c>
     </row>
     <row r="452">
@@ -9734,7 +9740,7 @@
         <v>966</v>
       </c>
       <c r="C452" s="0" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="D452" s="0">
         <v>0</v>
@@ -9748,21 +9754,21 @@
         <v>968</v>
       </c>
       <c r="C453" s="0" t="s">
-        <v>969</v>
+        <v>954</v>
       </c>
       <c r="D453" s="0">
-        <v>453</v>
+        <v>0</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" s="0" t="s">
+        <v>969</v>
+      </c>
+      <c r="B454" s="0" t="s">
         <v>970</v>
       </c>
-      <c r="B454" s="0" t="s">
+      <c r="C454" s="0" t="s">
         <v>971</v>
-      </c>
-      <c r="C454" s="0" t="s">
-        <v>952</v>
       </c>
       <c r="D454" s="0">
         <v>453</v>
@@ -9776,10 +9782,10 @@
         <v>973</v>
       </c>
       <c r="C455" s="0" t="s">
-        <v>75</v>
+        <v>954</v>
       </c>
       <c r="D455" s="0">
-        <v>19322</v>
+        <v>453</v>
       </c>
     </row>
     <row r="456">
@@ -9790,10 +9796,10 @@
         <v>975</v>
       </c>
       <c r="C456" s="0" t="s">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="D456" s="0">
-        <v>430</v>
+        <v>19322</v>
       </c>
     </row>
     <row r="457">
@@ -9804,7 +9810,7 @@
         <v>977</v>
       </c>
       <c r="C457" s="0" t="s">
-        <v>289</v>
+        <v>34</v>
       </c>
       <c r="D457" s="0">
         <v>430</v>
@@ -9818,10 +9824,10 @@
         <v>979</v>
       </c>
       <c r="C458" s="0" t="s">
-        <v>120</v>
+        <v>289</v>
       </c>
       <c r="D458" s="0">
-        <v>14000</v>
+        <v>430</v>
       </c>
     </row>
     <row r="459">
@@ -9832,10 +9838,10 @@
         <v>981</v>
       </c>
       <c r="C459" s="0" t="s">
-        <v>145</v>
+        <v>120</v>
       </c>
       <c r="D459" s="0">
-        <v>12049</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="460">
@@ -9849,7 +9855,7 @@
         <v>145</v>
       </c>
       <c r="D460" s="0">
-        <v>2895</v>
+        <v>12049</v>
       </c>
     </row>
     <row r="461">
@@ -9860,10 +9866,10 @@
         <v>985</v>
       </c>
       <c r="C461" s="0" t="s">
-        <v>97</v>
+        <v>145</v>
       </c>
       <c r="D461" s="0">
-        <v>266200</v>
+        <v>2895</v>
       </c>
     </row>
     <row r="462">
@@ -9877,7 +9883,7 @@
         <v>97</v>
       </c>
       <c r="D462" s="0">
-        <v>194991.5</v>
+        <v>266200</v>
       </c>
     </row>
     <row r="463">
@@ -9891,7 +9897,7 @@
         <v>97</v>
       </c>
       <c r="D463" s="0">
-        <v>289492.5</v>
+        <v>194991.5</v>
       </c>
     </row>
     <row r="464">
@@ -9902,24 +9908,24 @@
         <v>991</v>
       </c>
       <c r="C464" s="0" t="s">
-        <v>992</v>
+        <v>97</v>
       </c>
       <c r="D464" s="0">
-        <v>13722.52</v>
+        <v>289492.5</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" s="0" t="s">
+        <v>992</v>
+      </c>
+      <c r="B465" s="0" t="s">
         <v>993</v>
       </c>
-      <c r="B465" s="0" t="s">
+      <c r="C465" s="0" t="s">
         <v>994</v>
       </c>
-      <c r="C465" s="0" t="s">
-        <v>992</v>
-      </c>
       <c r="D465" s="0">
-        <v>15072</v>
+        <v>13722.52</v>
       </c>
     </row>
     <row r="466">
@@ -9930,10 +9936,10 @@
         <v>996</v>
       </c>
       <c r="C466" s="0" t="s">
-        <v>992</v>
+        <v>994</v>
       </c>
       <c r="D466" s="0">
-        <v>6555.64</v>
+        <v>15072</v>
       </c>
     </row>
     <row r="467">
@@ -9944,10 +9950,10 @@
         <v>998</v>
       </c>
       <c r="C467" s="0" t="s">
-        <v>992</v>
+        <v>994</v>
       </c>
       <c r="D467" s="0">
-        <v>8964.61</v>
+        <v>6555.64</v>
       </c>
     </row>
     <row r="468">
@@ -9958,10 +9964,10 @@
         <v>1000</v>
       </c>
       <c r="C468" s="0" t="s">
-        <v>992</v>
+        <v>994</v>
       </c>
       <c r="D468" s="0">
-        <v>11735</v>
+        <v>8964.61</v>
       </c>
     </row>
     <row r="469">
@@ -9972,10 +9978,10 @@
         <v>1002</v>
       </c>
       <c r="C469" s="0" t="s">
-        <v>75</v>
+        <v>994</v>
       </c>
       <c r="D469" s="0">
-        <v>4276</v>
+        <v>11735</v>
       </c>
     </row>
     <row r="470">
@@ -9986,10 +9992,10 @@
         <v>1004</v>
       </c>
       <c r="C470" s="0" t="s">
-        <v>145</v>
+        <v>75</v>
       </c>
       <c r="D470" s="0">
-        <v>3930</v>
+        <v>4276</v>
       </c>
     </row>
     <row r="471">
@@ -10000,10 +10006,10 @@
         <v>1006</v>
       </c>
       <c r="C471" s="0" t="s">
-        <v>97</v>
+        <v>145</v>
       </c>
       <c r="D471" s="0">
-        <v>4392.3</v>
+        <v>3930</v>
       </c>
     </row>
     <row r="472">
@@ -10014,24 +10020,24 @@
         <v>1008</v>
       </c>
       <c r="C472" s="0" t="s">
-        <v>1009</v>
+        <v>97</v>
       </c>
       <c r="D472" s="0">
-        <v>5254.41</v>
+        <v>4392.3</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" s="0" t="s">
+        <v>1009</v>
+      </c>
+      <c r="B473" s="0" t="s">
         <v>1010</v>
       </c>
-      <c r="B473" s="0" t="s">
+      <c r="C473" s="0" t="s">
         <v>1011</v>
       </c>
-      <c r="C473" s="0" t="s">
-        <v>52</v>
-      </c>
       <c r="D473" s="0">
-        <v>1297</v>
+        <v>5254.41</v>
       </c>
     </row>
     <row r="474">
@@ -10045,7 +10051,7 @@
         <v>52</v>
       </c>
       <c r="D474" s="0">
-        <v>298</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="475">
@@ -10059,7 +10065,7 @@
         <v>52</v>
       </c>
       <c r="D475" s="0">
-        <v>596</v>
+        <v>298</v>
       </c>
     </row>
     <row r="476">
@@ -10070,10 +10076,10 @@
         <v>1017</v>
       </c>
       <c r="C476" s="0" t="s">
-        <v>384</v>
+        <v>52</v>
       </c>
       <c r="D476" s="0">
-        <v>65142.6</v>
+        <v>596</v>
       </c>
     </row>
     <row r="477">
@@ -10087,7 +10093,7 @@
         <v>384</v>
       </c>
       <c r="D477" s="0">
-        <v>23482.7</v>
+        <v>65142.6</v>
       </c>
     </row>
     <row r="478">
@@ -10098,10 +10104,10 @@
         <v>1021</v>
       </c>
       <c r="C478" s="0" t="s">
-        <v>28</v>
+        <v>384</v>
       </c>
       <c r="D478" s="0">
-        <v>6029.59</v>
+        <v>23482.7</v>
       </c>
     </row>
     <row r="479">
@@ -10112,10 +10118,10 @@
         <v>1023</v>
       </c>
       <c r="C479" s="0" t="s">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="D479" s="0">
-        <v>12000</v>
+        <v>6029.59</v>
       </c>
     </row>
     <row r="480">
@@ -10129,7 +10135,7 @@
         <v>52</v>
       </c>
       <c r="D480" s="0">
-        <v>17425</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="481">
@@ -10140,66 +10146,66 @@
         <v>1027</v>
       </c>
       <c r="C481" s="0" t="s">
-        <v>1028</v>
+        <v>52</v>
       </c>
       <c r="D481" s="0">
-        <v>1958</v>
+        <v>17425</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" s="0" t="s">
+        <v>1028</v>
+      </c>
+      <c r="B482" s="0" t="s">
         <v>1029</v>
       </c>
-      <c r="B482" s="0" t="s">
+      <c r="C482" s="0" t="s">
         <v>1030</v>
       </c>
-      <c r="C482" s="0" t="s">
-        <v>1031</v>
-      </c>
       <c r="D482" s="0">
-        <v>2282.3</v>
+        <v>1958</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" s="0" t="s">
+        <v>1031</v>
+      </c>
+      <c r="B483" s="0" t="s">
         <v>1032</v>
       </c>
-      <c r="B483" s="0" t="s">
+      <c r="C483" s="0" t="s">
         <v>1033</v>
       </c>
-      <c r="C483" s="0" t="s">
-        <v>1034</v>
-      </c>
       <c r="D483" s="0">
-        <v>386</v>
+        <v>2282.3</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" s="0" t="s">
+        <v>1034</v>
+      </c>
+      <c r="B484" s="0" t="s">
         <v>1035</v>
       </c>
-      <c r="B484" s="0" t="s">
+      <c r="C484" s="0" t="s">
         <v>1036</v>
       </c>
-      <c r="C484" s="0" t="s">
-        <v>1037</v>
-      </c>
       <c r="D484" s="0">
-        <v>385.4</v>
+        <v>386</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" s="0" t="s">
+        <v>1037</v>
+      </c>
+      <c r="B485" s="0" t="s">
         <v>1038</v>
       </c>
-      <c r="B485" s="0" t="s">
+      <c r="C485" s="0" t="s">
         <v>1039</v>
       </c>
-      <c r="C485" s="0" t="s">
-        <v>97</v>
-      </c>
       <c r="D485" s="0">
-        <v>296147.5</v>
+        <v>385.4</v>
       </c>
     </row>
     <row r="486">
@@ -10210,10 +10216,10 @@
         <v>1041</v>
       </c>
       <c r="C486" s="0" t="s">
-        <v>128</v>
+        <v>97</v>
       </c>
       <c r="D486" s="0">
-        <v>1890</v>
+        <v>296147.5</v>
       </c>
     </row>
     <row r="487">
@@ -10224,10 +10230,10 @@
         <v>1043</v>
       </c>
       <c r="C487" s="0" t="s">
-        <v>604</v>
+        <v>128</v>
       </c>
       <c r="D487" s="0">
-        <v>83000</v>
+        <v>1890</v>
       </c>
     </row>
     <row r="488">
@@ -10238,10 +10244,10 @@
         <v>1045</v>
       </c>
       <c r="C488" s="0" t="s">
-        <v>145</v>
+        <v>604</v>
       </c>
       <c r="D488" s="0">
-        <v>99</v>
+        <v>83000</v>
       </c>
     </row>
     <row r="489">
@@ -10252,10 +10258,10 @@
         <v>1047</v>
       </c>
       <c r="C489" s="0" t="s">
-        <v>75</v>
+        <v>145</v>
       </c>
       <c r="D489" s="0">
-        <v>950</v>
+        <v>99</v>
       </c>
     </row>
     <row r="490">
@@ -10266,10 +10272,10 @@
         <v>1049</v>
       </c>
       <c r="C490" s="0" t="s">
-        <v>479</v>
+        <v>75</v>
       </c>
       <c r="D490" s="0">
-        <v>398107</v>
+        <v>950</v>
       </c>
     </row>
     <row r="491">
@@ -10280,10 +10286,10 @@
         <v>1051</v>
       </c>
       <c r="C491" s="0" t="s">
-        <v>165</v>
+        <v>479</v>
       </c>
       <c r="D491" s="0">
-        <v>2200</v>
+        <v>398107</v>
       </c>
     </row>
     <row r="492">
@@ -10294,10 +10300,10 @@
         <v>1053</v>
       </c>
       <c r="C492" s="0" t="s">
-        <v>212</v>
+        <v>165</v>
       </c>
       <c r="D492" s="0">
-        <v>41000</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="493">
@@ -10308,10 +10314,10 @@
         <v>1055</v>
       </c>
       <c r="C493" s="0" t="s">
-        <v>75</v>
+        <v>212</v>
       </c>
       <c r="D493" s="0">
-        <v>5790</v>
+        <v>41000</v>
       </c>
     </row>
     <row r="494">
@@ -10322,10 +10328,10 @@
         <v>1057</v>
       </c>
       <c r="C494" s="0" t="s">
-        <v>952</v>
+        <v>75</v>
       </c>
       <c r="D494" s="0">
-        <v>880</v>
+        <v>5790</v>
       </c>
     </row>
     <row r="495">
@@ -10336,7 +10342,7 @@
         <v>1059</v>
       </c>
       <c r="C495" s="0" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="D495" s="0">
         <v>880</v>
@@ -10350,7 +10356,7 @@
         <v>1061</v>
       </c>
       <c r="C496" s="0" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="D496" s="0">
         <v>880</v>
@@ -10364,10 +10370,10 @@
         <v>1063</v>
       </c>
       <c r="C497" s="0" t="s">
-        <v>21</v>
+        <v>954</v>
       </c>
       <c r="D497" s="0">
-        <v>563.36</v>
+        <v>880</v>
       </c>
     </row>
     <row r="498">
@@ -10378,10 +10384,10 @@
         <v>1065</v>
       </c>
       <c r="C498" s="0" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D498" s="0">
-        <v>3520</v>
+        <v>563.36</v>
       </c>
     </row>
     <row r="499">
@@ -10395,7 +10401,7 @@
         <v>15</v>
       </c>
       <c r="D499" s="0">
-        <v>2600</v>
+        <v>3520</v>
       </c>
     </row>
     <row r="500">
@@ -10406,10 +10412,10 @@
         <v>1069</v>
       </c>
       <c r="C500" s="0" t="s">
-        <v>289</v>
+        <v>15</v>
       </c>
       <c r="D500" s="0">
-        <v>3700</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="501">
@@ -10423,7 +10429,7 @@
         <v>289</v>
       </c>
       <c r="D501" s="0">
-        <v>2600</v>
+        <v>3700</v>
       </c>
     </row>
     <row r="502">
@@ -10434,10 +10440,10 @@
         <v>1073</v>
       </c>
       <c r="C502" s="0" t="s">
-        <v>15</v>
+        <v>289</v>
       </c>
       <c r="D502" s="0">
-        <v>2235</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="503">
@@ -10451,7 +10457,7 @@
         <v>15</v>
       </c>
       <c r="D503" s="0">
-        <v>3850</v>
+        <v>2235</v>
       </c>
     </row>
     <row r="504">
@@ -10462,24 +10468,24 @@
         <v>1077</v>
       </c>
       <c r="C504" s="0" t="s">
-        <v>1078</v>
+        <v>15</v>
       </c>
       <c r="D504" s="0">
-        <v>1</v>
+        <v>3850</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" s="0" t="s">
+        <v>1078</v>
+      </c>
+      <c r="B505" s="0" t="s">
         <v>1079</v>
       </c>
-      <c r="B505" s="0" t="s">
+      <c r="C505" s="0" t="s">
         <v>1080</v>
       </c>
-      <c r="C505" s="0" t="s">
-        <v>28</v>
-      </c>
       <c r="D505" s="0">
-        <v>15189</v>
+        <v>1</v>
       </c>
     </row>
     <row r="506">
@@ -10490,10 +10496,10 @@
         <v>1082</v>
       </c>
       <c r="C506" s="0" t="s">
-        <v>384</v>
+        <v>28</v>
       </c>
       <c r="D506" s="0">
-        <v>3859.93</v>
+        <v>15189</v>
       </c>
     </row>
     <row r="507">
@@ -10507,7 +10513,7 @@
         <v>384</v>
       </c>
       <c r="D507" s="0">
-        <v>11751.49</v>
+        <v>3859.93</v>
       </c>
     </row>
     <row r="508">
@@ -10518,10 +10524,10 @@
         <v>1086</v>
       </c>
       <c r="C508" s="0" t="s">
-        <v>346</v>
+        <v>384</v>
       </c>
       <c r="D508" s="0">
-        <v>6000</v>
+        <v>11751.49</v>
       </c>
     </row>
     <row r="509">
@@ -10535,7 +10541,7 @@
         <v>346</v>
       </c>
       <c r="D509" s="0">
-        <v>3000</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="510">
@@ -10546,10 +10552,10 @@
         <v>1090</v>
       </c>
       <c r="C510" s="0" t="s">
-        <v>37</v>
+        <v>346</v>
       </c>
       <c r="D510" s="0">
-        <v>618</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="511">
@@ -10560,24 +10566,24 @@
         <v>1092</v>
       </c>
       <c r="C511" s="0" t="s">
-        <v>1093</v>
+        <v>37</v>
       </c>
       <c r="D511" s="0">
-        <v>24600</v>
+        <v>618</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" s="0" t="s">
+        <v>1093</v>
+      </c>
+      <c r="B512" s="0" t="s">
         <v>1094</v>
       </c>
-      <c r="B512" s="0" t="s">
+      <c r="C512" s="0" t="s">
         <v>1095</v>
       </c>
-      <c r="C512" s="0" t="s">
-        <v>110</v>
-      </c>
       <c r="D512" s="0">
-        <v>0</v>
+        <v>24600</v>
       </c>
     </row>
     <row r="513">
@@ -10588,10 +10594,10 @@
         <v>1097</v>
       </c>
       <c r="C513" s="0" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="D513" s="0">
-        <v>43590.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="514">
@@ -10602,10 +10608,10 @@
         <v>1099</v>
       </c>
       <c r="C514" s="0" t="s">
-        <v>479</v>
+        <v>97</v>
       </c>
       <c r="D514" s="0">
-        <v>213700</v>
+        <v>43590.25</v>
       </c>
     </row>
     <row r="515">
@@ -10616,10 +10622,10 @@
         <v>1101</v>
       </c>
       <c r="C515" s="0" t="s">
-        <v>384</v>
+        <v>479</v>
       </c>
       <c r="D515" s="0">
-        <v>77429.29</v>
+        <v>213700</v>
       </c>
     </row>
     <row r="516">
@@ -10633,7 +10639,7 @@
         <v>384</v>
       </c>
       <c r="D516" s="0">
-        <v>42913.42</v>
+        <v>77429.29</v>
       </c>
     </row>
     <row r="517">
@@ -10647,7 +10653,7 @@
         <v>384</v>
       </c>
       <c r="D517" s="0">
-        <v>88806.25</v>
+        <v>42913.42</v>
       </c>
     </row>
     <row r="518">
@@ -10661,7 +10667,7 @@
         <v>384</v>
       </c>
       <c r="D518" s="0">
-        <v>50781.52</v>
+        <v>88806.25</v>
       </c>
     </row>
     <row r="519">
@@ -10672,10 +10678,10 @@
         <v>1109</v>
       </c>
       <c r="C519" s="0" t="s">
-        <v>21</v>
+        <v>384</v>
       </c>
       <c r="D519" s="0">
-        <v>1600</v>
+        <v>50781.52</v>
       </c>
     </row>
     <row r="520">
@@ -10686,10 +10692,10 @@
         <v>1111</v>
       </c>
       <c r="C520" s="0" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D520" s="0">
-        <v>3521.4</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="521">
@@ -10703,7 +10709,7 @@
         <v>28</v>
       </c>
       <c r="D521" s="0">
-        <v>3987</v>
+        <v>3521.4</v>
       </c>
     </row>
     <row r="522">
@@ -10717,7 +10723,7 @@
         <v>28</v>
       </c>
       <c r="D522" s="0">
-        <v>4086.37</v>
+        <v>3987</v>
       </c>
     </row>
     <row r="523">
@@ -10731,7 +10737,7 @@
         <v>28</v>
       </c>
       <c r="D523" s="0">
-        <v>3382.65</v>
+        <v>4086.37</v>
       </c>
     </row>
     <row r="524">
@@ -10742,10 +10748,10 @@
         <v>1119</v>
       </c>
       <c r="C524" s="0" t="s">
-        <v>165</v>
+        <v>28</v>
       </c>
       <c r="D524" s="0">
-        <v>430</v>
+        <v>3382.65</v>
       </c>
     </row>
     <row r="525">
@@ -10756,9 +10762,23 @@
         <v>1121</v>
       </c>
       <c r="C525" s="0" t="s">
+        <v>165</v>
+      </c>
+      <c r="D525" s="0">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" s="0" t="s">
+        <v>1122</v>
+      </c>
+      <c r="B526" s="0" t="s">
+        <v>1123</v>
+      </c>
+      <c r="C526" s="0" t="s">
         <v>145</v>
       </c>
-      <c r="D525" s="0">
+      <c r="D526" s="0">
         <v>495</v>
       </c>
     </row>

--- a/price_list.xlsx
+++ b/price_list.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1124" uniqueCount="1124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1133" uniqueCount="1133">
   <si>
     <t>Solo Activos</t>
   </si>
@@ -1004,6 +1004,12 @@
     <t>DENSULIN ISOFANA N 100UI LAP PRELL. X 5 X 3 ML - 000024265</t>
   </si>
   <si>
+    <t>000024655</t>
+  </si>
+  <si>
+    <t>DENSURAPID 100 U/ML LAP PRELL X 3 ML X 1 - 000024655</t>
+  </si>
+  <si>
     <t>000023935</t>
   </si>
   <si>
@@ -1241,6 +1247,18 @@
     <t>ESPASMO BIOTENK Gotas x 20ml - 000004740</t>
   </si>
   <si>
+    <t>000014584</t>
+  </si>
+  <si>
+    <t>ESPIMAX 100mg Comp. x 10 - 000014584</t>
+  </si>
+  <si>
+    <t>000014583</t>
+  </si>
+  <si>
+    <t>ESPIMAX 25mg Comp. x 10 - 000014583</t>
+  </si>
+  <si>
     <t>000020969</t>
   </si>
   <si>
@@ -2303,12 +2321,6 @@
     <t>METRONIDAZOL 100 ML - JAYOR - 000029046</t>
   </si>
   <si>
-    <t>000022239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">METRONIDAZOL DENVER FARMA 500MG COMP. X   10 - 000022239</t>
-  </si>
-  <si>
     <t>000024247</t>
   </si>
   <si>
@@ -2360,6 +2372,15 @@
     <t>NAMIR 200MG /100ML JBE. X 1 X 120ML - 000004882</t>
   </si>
   <si>
+    <t>000024730</t>
+  </si>
+  <si>
+    <t>NAPROXENO COMP 500 MG X 10 - IVAX TEVA - 000024730</t>
+  </si>
+  <si>
+    <t>IVAX</t>
+  </si>
+  <si>
     <t>000010079</t>
   </si>
   <si>
@@ -2970,6 +2991,12 @@
   </si>
   <si>
     <t>SUPER-O 100mg Comp. Rec. x 20 - 000024713</t>
+  </si>
+  <si>
+    <t>000020823</t>
+  </si>
+  <si>
+    <t>SUPER-O 50mg Comp. Rec. x 20 - 000020823</t>
   </si>
   <si>
     <t>000009961</t>
@@ -3449,7 +3476,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A2:D526"/>
+  <dimension ref="A2:D530"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
@@ -3569,7 +3596,7 @@
         <v>21</v>
       </c>
       <c r="D11" s="0">
-        <v>406.65</v>
+        <v>385</v>
       </c>
     </row>
     <row r="12">
@@ -3583,7 +3610,7 @@
         <v>21</v>
       </c>
       <c r="D12" s="0">
-        <v>453.6</v>
+        <v>520</v>
       </c>
     </row>
     <row r="13">
@@ -5431,7 +5458,7 @@
         <v>75</v>
       </c>
       <c r="D144" s="0">
-        <v>0</v>
+        <v>89185.6</v>
       </c>
     </row>
     <row r="145">
@@ -5445,7 +5472,7 @@
         <v>75</v>
       </c>
       <c r="D145" s="0">
-        <v>88248.3</v>
+        <v>89185.6</v>
       </c>
     </row>
     <row r="146">
@@ -5456,10 +5483,10 @@
         <v>331</v>
       </c>
       <c r="C146" s="0" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="D146" s="0">
-        <v>1785</v>
+        <v>126551.04</v>
       </c>
     </row>
     <row r="147">
@@ -5473,7 +5500,7 @@
         <v>52</v>
       </c>
       <c r="D147" s="0">
-        <v>2058</v>
+        <v>1785</v>
       </c>
     </row>
     <row r="148">
@@ -5484,10 +5511,10 @@
         <v>335</v>
       </c>
       <c r="C148" s="0" t="s">
-        <v>15</v>
+        <v>52</v>
       </c>
       <c r="D148" s="0">
-        <v>1270</v>
+        <v>2058</v>
       </c>
     </row>
     <row r="149">
@@ -5498,10 +5525,10 @@
         <v>337</v>
       </c>
       <c r="C149" s="0" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="D149" s="0">
-        <v>550</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="150">
@@ -5512,7 +5539,7 @@
         <v>339</v>
       </c>
       <c r="C150" s="0" t="s">
-        <v>75</v>
+        <v>31</v>
       </c>
       <c r="D150" s="0">
         <v>550</v>
@@ -5526,7 +5553,7 @@
         <v>341</v>
       </c>
       <c r="C151" s="0" t="s">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="D151" s="0">
         <v>550</v>
@@ -5540,10 +5567,10 @@
         <v>343</v>
       </c>
       <c r="C152" s="0" t="s">
-        <v>97</v>
+        <v>34</v>
       </c>
       <c r="D152" s="0">
-        <v>1663.75</v>
+        <v>550</v>
       </c>
     </row>
     <row r="153">
@@ -5554,24 +5581,24 @@
         <v>345</v>
       </c>
       <c r="C153" s="0" t="s">
-        <v>346</v>
+        <v>97</v>
       </c>
       <c r="D153" s="0">
-        <v>4500</v>
+        <v>1663.75</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="0" t="s">
+        <v>346</v>
+      </c>
+      <c r="B154" s="0" t="s">
         <v>347</v>
       </c>
-      <c r="B154" s="0" t="s">
+      <c r="C154" s="0" t="s">
         <v>348</v>
       </c>
-      <c r="C154" s="0" t="s">
-        <v>34</v>
-      </c>
       <c r="D154" s="0">
-        <v>390</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="155">
@@ -5582,10 +5609,10 @@
         <v>350</v>
       </c>
       <c r="C155" s="0" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="D155" s="0">
-        <v>500</v>
+        <v>390</v>
       </c>
     </row>
     <row r="156">
@@ -5596,10 +5623,10 @@
         <v>352</v>
       </c>
       <c r="C156" s="0" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="D156" s="0">
-        <v>380</v>
+        <v>500</v>
       </c>
     </row>
     <row r="157">
@@ -5610,7 +5637,7 @@
         <v>354</v>
       </c>
       <c r="C157" s="0" t="s">
-        <v>75</v>
+        <v>34</v>
       </c>
       <c r="D157" s="0">
         <v>380</v>
@@ -5627,7 +5654,7 @@
         <v>75</v>
       </c>
       <c r="D158" s="0">
-        <v>580</v>
+        <v>380</v>
       </c>
     </row>
     <row r="159">
@@ -5638,10 +5665,10 @@
         <v>358</v>
       </c>
       <c r="C159" s="0" t="s">
-        <v>15</v>
+        <v>75</v>
       </c>
       <c r="D159" s="0">
-        <v>572</v>
+        <v>580</v>
       </c>
     </row>
     <row r="160">
@@ -5652,10 +5679,10 @@
         <v>360</v>
       </c>
       <c r="C160" s="0" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="D160" s="0">
-        <v>106950.8</v>
+        <v>572</v>
       </c>
     </row>
     <row r="161">
@@ -5669,7 +5696,7 @@
         <v>28</v>
       </c>
       <c r="D161" s="0">
-        <v>118372.7</v>
+        <v>106950.8</v>
       </c>
     </row>
     <row r="162">
@@ -5683,7 +5710,7 @@
         <v>28</v>
       </c>
       <c r="D162" s="0">
-        <v>140178.2</v>
+        <v>118372.7</v>
       </c>
     </row>
     <row r="163">
@@ -5694,24 +5721,24 @@
         <v>366</v>
       </c>
       <c r="C163" s="0" t="s">
-        <v>367</v>
+        <v>28</v>
       </c>
       <c r="D163" s="0">
-        <v>650</v>
+        <v>140178.2</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="0" t="s">
+        <v>367</v>
+      </c>
+      <c r="B164" s="0" t="s">
         <v>368</v>
       </c>
-      <c r="B164" s="0" t="s">
+      <c r="C164" s="0" t="s">
         <v>369</v>
       </c>
-      <c r="C164" s="0" t="s">
-        <v>115</v>
-      </c>
       <c r="D164" s="0">
-        <v>1590</v>
+        <v>650</v>
       </c>
     </row>
     <row r="165">
@@ -5722,10 +5749,10 @@
         <v>371</v>
       </c>
       <c r="C165" s="0" t="s">
-        <v>34</v>
+        <v>115</v>
       </c>
       <c r="D165" s="0">
-        <v>550</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="166">
@@ -5736,7 +5763,7 @@
         <v>373</v>
       </c>
       <c r="C166" s="0" t="s">
-        <v>156</v>
+        <v>34</v>
       </c>
       <c r="D166" s="0">
         <v>550</v>
@@ -5750,7 +5777,7 @@
         <v>375</v>
       </c>
       <c r="C167" s="0" t="s">
-        <v>15</v>
+        <v>156</v>
       </c>
       <c r="D167" s="0">
         <v>550</v>
@@ -5767,7 +5794,7 @@
         <v>15</v>
       </c>
       <c r="D168" s="0">
-        <v>1700</v>
+        <v>550</v>
       </c>
     </row>
     <row r="169">
@@ -5781,7 +5808,7 @@
         <v>15</v>
       </c>
       <c r="D169" s="0">
-        <v>0</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="170">
@@ -5792,10 +5819,10 @@
         <v>381</v>
       </c>
       <c r="C170" s="0" t="s">
-        <v>120</v>
+        <v>15</v>
       </c>
       <c r="D170" s="0">
-        <v>1290</v>
+        <v>0</v>
       </c>
     </row>
     <row r="171">
@@ -5806,38 +5833,38 @@
         <v>383</v>
       </c>
       <c r="C171" s="0" t="s">
-        <v>384</v>
+        <v>120</v>
       </c>
       <c r="D171" s="0">
-        <v>55058.9</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="0" t="s">
+        <v>384</v>
+      </c>
+      <c r="B172" s="0" t="s">
         <v>385</v>
       </c>
-      <c r="B172" s="0" t="s">
+      <c r="C172" s="0" t="s">
         <v>386</v>
       </c>
-      <c r="C172" s="0" t="s">
-        <v>387</v>
-      </c>
       <c r="D172" s="0">
-        <v>104695.98</v>
+        <v>55058.9</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="0" t="s">
+        <v>387</v>
+      </c>
+      <c r="B173" s="0" t="s">
         <v>388</v>
       </c>
-      <c r="B173" s="0" t="s">
+      <c r="C173" s="0" t="s">
         <v>389</v>
       </c>
-      <c r="C173" s="0" t="s">
-        <v>387</v>
-      </c>
       <c r="D173" s="0">
-        <v>80478.92</v>
+        <v>104695.98</v>
       </c>
     </row>
     <row r="174">
@@ -5848,10 +5875,10 @@
         <v>391</v>
       </c>
       <c r="C174" s="0" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="D174" s="0">
-        <v>92546.68</v>
+        <v>80478.92</v>
       </c>
     </row>
     <row r="175">
@@ -5862,10 +5889,10 @@
         <v>393</v>
       </c>
       <c r="C175" s="0" t="s">
-        <v>28</v>
+        <v>389</v>
       </c>
       <c r="D175" s="0">
-        <v>972.9</v>
+        <v>92546.68</v>
       </c>
     </row>
     <row r="176">
@@ -5879,7 +5906,7 @@
         <v>28</v>
       </c>
       <c r="D176" s="0">
-        <v>265.3</v>
+        <v>972.9</v>
       </c>
     </row>
     <row r="177">
@@ -5893,7 +5920,7 @@
         <v>28</v>
       </c>
       <c r="D177" s="0">
-        <v>2908.78</v>
+        <v>265.3</v>
       </c>
     </row>
     <row r="178">
@@ -5904,24 +5931,24 @@
         <v>399</v>
       </c>
       <c r="C178" s="0" t="s">
-        <v>400</v>
+        <v>28</v>
       </c>
       <c r="D178" s="0">
-        <v>61</v>
+        <v>2908.78</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="0" t="s">
+        <v>400</v>
+      </c>
+      <c r="B179" s="0" t="s">
         <v>401</v>
       </c>
-      <c r="B179" s="0" t="s">
+      <c r="C179" s="0" t="s">
         <v>402</v>
       </c>
-      <c r="C179" s="0" t="s">
-        <v>18</v>
-      </c>
       <c r="D179" s="0">
-        <v>270</v>
+        <v>61</v>
       </c>
     </row>
     <row r="180">
@@ -5932,10 +5959,10 @@
         <v>404</v>
       </c>
       <c r="C180" s="0" t="s">
-        <v>156</v>
+        <v>18</v>
       </c>
       <c r="D180" s="0">
-        <v>257</v>
+        <v>270</v>
       </c>
     </row>
     <row r="181">
@@ -5946,10 +5973,10 @@
         <v>406</v>
       </c>
       <c r="C181" s="0" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="D181" s="0">
-        <v>2859</v>
+        <v>257</v>
       </c>
     </row>
     <row r="182">
@@ -5963,7 +5990,7 @@
         <v>145</v>
       </c>
       <c r="D182" s="0">
-        <v>3573.45</v>
+        <v>2859</v>
       </c>
     </row>
     <row r="183">
@@ -5974,10 +6001,10 @@
         <v>410</v>
       </c>
       <c r="C183" s="0" t="s">
-        <v>128</v>
+        <v>145</v>
       </c>
       <c r="D183" s="0">
-        <v>5218</v>
+        <v>3573.45</v>
       </c>
     </row>
     <row r="184">
@@ -5988,10 +6015,10 @@
         <v>412</v>
       </c>
       <c r="C184" s="0" t="s">
-        <v>384</v>
+        <v>15</v>
       </c>
       <c r="D184" s="0">
-        <v>37527.35</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="185">
@@ -6002,10 +6029,10 @@
         <v>414</v>
       </c>
       <c r="C185" s="0" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D185" s="0">
-        <v>825.18</v>
+        <v>750</v>
       </c>
     </row>
     <row r="186">
@@ -6016,10 +6043,10 @@
         <v>416</v>
       </c>
       <c r="C186" s="0" t="s">
-        <v>18</v>
+        <v>128</v>
       </c>
       <c r="D186" s="0">
-        <v>2687.98</v>
+        <v>5218</v>
       </c>
     </row>
     <row r="187">
@@ -6030,10 +6057,10 @@
         <v>418</v>
       </c>
       <c r="C187" s="0" t="s">
-        <v>18</v>
+        <v>386</v>
       </c>
       <c r="D187" s="0">
-        <v>6764.67</v>
+        <v>37527.35</v>
       </c>
     </row>
     <row r="188">
@@ -6047,7 +6074,7 @@
         <v>18</v>
       </c>
       <c r="D188" s="0">
-        <v>353.46</v>
+        <v>825.18</v>
       </c>
     </row>
     <row r="189">
@@ -6061,7 +6088,7 @@
         <v>18</v>
       </c>
       <c r="D189" s="0">
-        <v>10799.76</v>
+        <v>2687.98</v>
       </c>
     </row>
     <row r="190">
@@ -6075,7 +6102,7 @@
         <v>18</v>
       </c>
       <c r="D190" s="0">
-        <v>3939.57</v>
+        <v>6764.67</v>
       </c>
     </row>
     <row r="191">
@@ -6089,7 +6116,7 @@
         <v>18</v>
       </c>
       <c r="D191" s="0">
-        <v>412.8</v>
+        <v>353.46</v>
       </c>
     </row>
     <row r="192">
@@ -6103,7 +6130,7 @@
         <v>18</v>
       </c>
       <c r="D192" s="0">
-        <v>320</v>
+        <v>10799.76</v>
       </c>
     </row>
     <row r="193">
@@ -6117,7 +6144,7 @@
         <v>18</v>
       </c>
       <c r="D193" s="0">
-        <v>2184.81</v>
+        <v>3939.57</v>
       </c>
     </row>
     <row r="194">
@@ -6128,10 +6155,10 @@
         <v>432</v>
       </c>
       <c r="C194" s="0" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D194" s="0">
-        <v>9748.5</v>
+        <v>412.8</v>
       </c>
     </row>
     <row r="195">
@@ -6142,10 +6169,10 @@
         <v>434</v>
       </c>
       <c r="C195" s="0" t="s">
-        <v>75</v>
+        <v>18</v>
       </c>
       <c r="D195" s="0">
-        <v>430</v>
+        <v>320</v>
       </c>
     </row>
     <row r="196">
@@ -6156,10 +6183,10 @@
         <v>436</v>
       </c>
       <c r="C196" s="0" t="s">
-        <v>75</v>
+        <v>18</v>
       </c>
       <c r="D196" s="0">
-        <v>800</v>
+        <v>2184.81</v>
       </c>
     </row>
     <row r="197">
@@ -6170,10 +6197,10 @@
         <v>438</v>
       </c>
       <c r="C197" s="0" t="s">
-        <v>250</v>
+        <v>28</v>
       </c>
       <c r="D197" s="0">
-        <v>2040</v>
+        <v>9748.5</v>
       </c>
     </row>
     <row r="198">
@@ -6184,10 +6211,10 @@
         <v>440</v>
       </c>
       <c r="C198" s="0" t="s">
-        <v>250</v>
+        <v>75</v>
       </c>
       <c r="D198" s="0">
-        <v>1380</v>
+        <v>430</v>
       </c>
     </row>
     <row r="199">
@@ -6198,10 +6225,10 @@
         <v>442</v>
       </c>
       <c r="C199" s="0" t="s">
-        <v>384</v>
+        <v>75</v>
       </c>
       <c r="D199" s="0">
-        <v>236458.17</v>
+        <v>800</v>
       </c>
     </row>
     <row r="200">
@@ -6212,10 +6239,10 @@
         <v>444</v>
       </c>
       <c r="C200" s="0" t="s">
-        <v>28</v>
+        <v>250</v>
       </c>
       <c r="D200" s="0">
-        <v>317.2</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="201">
@@ -6226,10 +6253,10 @@
         <v>446</v>
       </c>
       <c r="C201" s="0" t="s">
-        <v>384</v>
+        <v>250</v>
       </c>
       <c r="D201" s="0">
-        <v>25100</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="202">
@@ -6240,52 +6267,52 @@
         <v>448</v>
       </c>
       <c r="C202" s="0" t="s">
-        <v>449</v>
+        <v>386</v>
       </c>
       <c r="D202" s="0">
-        <v>20900</v>
+        <v>236458.17</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="0" t="s">
+        <v>449</v>
+      </c>
+      <c r="B203" s="0" t="s">
         <v>450</v>
       </c>
-      <c r="B203" s="0" t="s">
-        <v>451</v>
-      </c>
       <c r="C203" s="0" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="D203" s="0">
-        <v>6014.63</v>
+        <v>317.2</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="0" t="s">
+        <v>451</v>
+      </c>
+      <c r="B204" s="0" t="s">
         <v>452</v>
       </c>
-      <c r="B204" s="0" t="s">
-        <v>453</v>
-      </c>
       <c r="C204" s="0" t="s">
-        <v>21</v>
+        <v>386</v>
       </c>
       <c r="D204" s="0">
-        <v>1104.46</v>
+        <v>25100</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="0" t="s">
+        <v>453</v>
+      </c>
+      <c r="B205" s="0" t="s">
         <v>454</v>
       </c>
-      <c r="B205" s="0" t="s">
+      <c r="C205" s="0" t="s">
         <v>455</v>
       </c>
-      <c r="C205" s="0" t="s">
-        <v>97</v>
-      </c>
       <c r="D205" s="0">
-        <v>11646.25</v>
+        <v>20900</v>
       </c>
     </row>
     <row r="206">
@@ -6296,10 +6323,10 @@
         <v>457</v>
       </c>
       <c r="C206" s="0" t="s">
-        <v>128</v>
+        <v>45</v>
       </c>
       <c r="D206" s="0">
-        <v>6072</v>
+        <v>6014.63</v>
       </c>
     </row>
     <row r="207">
@@ -6310,10 +6337,10 @@
         <v>459</v>
       </c>
       <c r="C207" s="0" t="s">
-        <v>75</v>
+        <v>21</v>
       </c>
       <c r="D207" s="0">
-        <v>400</v>
+        <v>1104.46</v>
       </c>
     </row>
     <row r="208">
@@ -6324,10 +6351,10 @@
         <v>461</v>
       </c>
       <c r="C208" s="0" t="s">
-        <v>21</v>
+        <v>97</v>
       </c>
       <c r="D208" s="0">
-        <v>409</v>
+        <v>11646.25</v>
       </c>
     </row>
     <row r="209">
@@ -6338,10 +6365,10 @@
         <v>463</v>
       </c>
       <c r="C209" s="0" t="s">
-        <v>69</v>
+        <v>128</v>
       </c>
       <c r="D209" s="0">
-        <v>10748</v>
+        <v>6072</v>
       </c>
     </row>
     <row r="210">
@@ -6352,10 +6379,10 @@
         <v>465</v>
       </c>
       <c r="C210" s="0" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="D210" s="0">
-        <v>12898</v>
+        <v>400</v>
       </c>
     </row>
     <row r="211">
@@ -6366,10 +6393,10 @@
         <v>467</v>
       </c>
       <c r="C211" s="0" t="s">
-        <v>52</v>
+        <v>21</v>
       </c>
       <c r="D211" s="0">
-        <v>2000</v>
+        <v>409</v>
       </c>
     </row>
     <row r="212">
@@ -6380,52 +6407,52 @@
         <v>469</v>
       </c>
       <c r="C212" s="0" t="s">
-        <v>470</v>
+        <v>69</v>
       </c>
       <c r="D212" s="0">
-        <v>0</v>
+        <v>10748</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="0" t="s">
+        <v>470</v>
+      </c>
+      <c r="B213" s="0" t="s">
         <v>471</v>
       </c>
-      <c r="B213" s="0" t="s">
-        <v>472</v>
-      </c>
       <c r="C213" s="0" t="s">
-        <v>15</v>
+        <v>69</v>
       </c>
       <c r="D213" s="0">
-        <v>490</v>
+        <v>12898</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="0" t="s">
+        <v>472</v>
+      </c>
+      <c r="B214" s="0" t="s">
         <v>473</v>
       </c>
-      <c r="B214" s="0" t="s">
-        <v>474</v>
-      </c>
       <c r="C214" s="0" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="D214" s="0">
-        <v>0</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="0" t="s">
+        <v>474</v>
+      </c>
+      <c r="B215" s="0" t="s">
         <v>475</v>
       </c>
-      <c r="B215" s="0" t="s">
+      <c r="C215" s="0" t="s">
         <v>476</v>
       </c>
-      <c r="C215" s="0" t="s">
-        <v>165</v>
-      </c>
       <c r="D215" s="0">
-        <v>25171.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="216">
@@ -6436,52 +6463,52 @@
         <v>478</v>
       </c>
       <c r="C216" s="0" t="s">
-        <v>479</v>
+        <v>15</v>
       </c>
       <c r="D216" s="0">
-        <v>70443</v>
+        <v>490</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="0" t="s">
+        <v>479</v>
+      </c>
+      <c r="B217" s="0" t="s">
         <v>480</v>
       </c>
-      <c r="B217" s="0" t="s">
-        <v>481</v>
-      </c>
       <c r="C217" s="0" t="s">
-        <v>156</v>
+        <v>34</v>
       </c>
       <c r="D217" s="0">
-        <v>1800</v>
+        <v>0</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="0" t="s">
+        <v>481</v>
+      </c>
+      <c r="B218" s="0" t="s">
         <v>482</v>
       </c>
-      <c r="B218" s="0" t="s">
-        <v>483</v>
-      </c>
       <c r="C218" s="0" t="s">
-        <v>34</v>
+        <v>165</v>
       </c>
       <c r="D218" s="0">
-        <v>0</v>
+        <v>25676.62</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="0" t="s">
+        <v>483</v>
+      </c>
+      <c r="B219" s="0" t="s">
         <v>484</v>
       </c>
-      <c r="B219" s="0" t="s">
+      <c r="C219" s="0" t="s">
         <v>485</v>
       </c>
-      <c r="C219" s="0" t="s">
-        <v>145</v>
-      </c>
       <c r="D219" s="0">
-        <v>492.2</v>
+        <v>70443</v>
       </c>
     </row>
     <row r="220">
@@ -6492,10 +6519,10 @@
         <v>487</v>
       </c>
       <c r="C220" s="0" t="s">
-        <v>212</v>
+        <v>156</v>
       </c>
       <c r="D220" s="0">
-        <v>495</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="221">
@@ -6506,10 +6533,10 @@
         <v>489</v>
       </c>
       <c r="C221" s="0" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="D221" s="0">
-        <v>1819.72</v>
+        <v>0</v>
       </c>
     </row>
     <row r="222">
@@ -6520,10 +6547,10 @@
         <v>491</v>
       </c>
       <c r="C222" s="0" t="s">
-        <v>18</v>
+        <v>145</v>
       </c>
       <c r="D222" s="0">
-        <v>4391.81</v>
+        <v>492.2</v>
       </c>
     </row>
     <row r="223">
@@ -6534,52 +6561,52 @@
         <v>493</v>
       </c>
       <c r="C223" s="0" t="s">
-        <v>494</v>
+        <v>212</v>
       </c>
       <c r="D223" s="0">
-        <v>4100</v>
+        <v>495</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="0" t="s">
+        <v>494</v>
+      </c>
+      <c r="B224" s="0" t="s">
         <v>495</v>
       </c>
-      <c r="B224" s="0" t="s">
-        <v>496</v>
-      </c>
       <c r="C224" s="0" t="s">
-        <v>494</v>
+        <v>18</v>
       </c>
       <c r="D224" s="0">
-        <v>4100</v>
+        <v>1819.72</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="0" t="s">
+        <v>496</v>
+      </c>
+      <c r="B225" s="0" t="s">
         <v>497</v>
       </c>
-      <c r="B225" s="0" t="s">
-        <v>498</v>
-      </c>
       <c r="C225" s="0" t="s">
-        <v>494</v>
+        <v>18</v>
       </c>
       <c r="D225" s="0">
-        <v>4100</v>
+        <v>4391.81</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="0" t="s">
+        <v>498</v>
+      </c>
+      <c r="B226" s="0" t="s">
         <v>499</v>
       </c>
-      <c r="B226" s="0" t="s">
+      <c r="C226" s="0" t="s">
         <v>500</v>
       </c>
-      <c r="C226" s="0" t="s">
-        <v>494</v>
-      </c>
       <c r="D226" s="0">
-        <v>4200</v>
+        <v>4100</v>
       </c>
     </row>
     <row r="227">
@@ -6590,10 +6617,10 @@
         <v>502</v>
       </c>
       <c r="C227" s="0" t="s">
-        <v>52</v>
+        <v>500</v>
       </c>
       <c r="D227" s="0">
-        <v>4700</v>
+        <v>4100</v>
       </c>
     </row>
     <row r="228">
@@ -6604,10 +6631,10 @@
         <v>504</v>
       </c>
       <c r="C228" s="0" t="s">
-        <v>59</v>
+        <v>500</v>
       </c>
       <c r="D228" s="0">
-        <v>235</v>
+        <v>4100</v>
       </c>
     </row>
     <row r="229">
@@ -6618,10 +6645,10 @@
         <v>506</v>
       </c>
       <c r="C229" s="0" t="s">
-        <v>59</v>
+        <v>500</v>
       </c>
       <c r="D229" s="0">
-        <v>235</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="230">
@@ -6632,10 +6659,10 @@
         <v>508</v>
       </c>
       <c r="C230" s="0" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="D230" s="0">
-        <v>235</v>
+        <v>4700</v>
       </c>
     </row>
     <row r="231">
@@ -6646,10 +6673,10 @@
         <v>510</v>
       </c>
       <c r="C231" s="0" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="D231" s="0">
-        <v>4670</v>
+        <v>235</v>
       </c>
     </row>
     <row r="232">
@@ -6660,10 +6687,10 @@
         <v>512</v>
       </c>
       <c r="C232" s="0" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="D232" s="0">
-        <v>4670</v>
+        <v>235</v>
       </c>
     </row>
     <row r="233">
@@ -6674,10 +6701,10 @@
         <v>514</v>
       </c>
       <c r="C233" s="0" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="D233" s="0">
-        <v>4670</v>
+        <v>235</v>
       </c>
     </row>
     <row r="234">
@@ -6688,49 +6715,49 @@
         <v>516</v>
       </c>
       <c r="C234" s="0" t="s">
-        <v>517</v>
+        <v>52</v>
       </c>
       <c r="D234" s="0">
-        <v>265</v>
+        <v>4670</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="0" t="s">
+        <v>517</v>
+      </c>
+      <c r="B235" s="0" t="s">
         <v>518</v>
       </c>
-      <c r="B235" s="0" t="s">
-        <v>519</v>
-      </c>
       <c r="C235" s="0" t="s">
-        <v>517</v>
+        <v>52</v>
       </c>
       <c r="D235" s="0">
-        <v>265</v>
+        <v>4670</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="0" t="s">
+        <v>519</v>
+      </c>
+      <c r="B236" s="0" t="s">
         <v>520</v>
       </c>
-      <c r="B236" s="0" t="s">
-        <v>521</v>
-      </c>
       <c r="C236" s="0" t="s">
-        <v>517</v>
+        <v>52</v>
       </c>
       <c r="D236" s="0">
-        <v>265</v>
+        <v>4670</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="0" t="s">
+        <v>521</v>
+      </c>
+      <c r="B237" s="0" t="s">
         <v>522</v>
       </c>
-      <c r="B237" s="0" t="s">
+      <c r="C237" s="0" t="s">
         <v>523</v>
-      </c>
-      <c r="C237" s="0" t="s">
-        <v>517</v>
       </c>
       <c r="D237" s="0">
         <v>265</v>
@@ -6744,7 +6771,7 @@
         <v>525</v>
       </c>
       <c r="C238" s="0" t="s">
-        <v>517</v>
+        <v>523</v>
       </c>
       <c r="D238" s="0">
         <v>265</v>
@@ -6758,7 +6785,7 @@
         <v>527</v>
       </c>
       <c r="C239" s="0" t="s">
-        <v>517</v>
+        <v>523</v>
       </c>
       <c r="D239" s="0">
         <v>265</v>
@@ -6772,66 +6799,66 @@
         <v>529</v>
       </c>
       <c r="C240" s="0" t="s">
-        <v>530</v>
+        <v>523</v>
       </c>
       <c r="D240" s="0">
-        <v>4700</v>
+        <v>265</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="0" t="s">
+        <v>530</v>
+      </c>
+      <c r="B241" s="0" t="s">
         <v>531</v>
       </c>
-      <c r="B241" s="0" t="s">
-        <v>532</v>
-      </c>
       <c r="C241" s="0" t="s">
-        <v>533</v>
+        <v>523</v>
       </c>
       <c r="D241" s="0">
-        <v>4700</v>
+        <v>265</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="0" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="B242" s="0" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="C242" s="0" t="s">
-        <v>52</v>
+        <v>523</v>
       </c>
       <c r="D242" s="0">
-        <v>4700</v>
+        <v>265</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="0" t="s">
+        <v>534</v>
+      </c>
+      <c r="B243" s="0" t="s">
+        <v>535</v>
+      </c>
+      <c r="C243" s="0" t="s">
         <v>536</v>
       </c>
-      <c r="B243" s="0" t="s">
-        <v>537</v>
-      </c>
-      <c r="C243" s="0" t="s">
-        <v>52</v>
-      </c>
       <c r="D243" s="0">
-        <v>597</v>
+        <v>4700</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="0" t="s">
+        <v>537</v>
+      </c>
+      <c r="B244" s="0" t="s">
         <v>538</v>
       </c>
-      <c r="B244" s="0" t="s">
+      <c r="C244" s="0" t="s">
         <v>539</v>
       </c>
-      <c r="C244" s="0" t="s">
-        <v>52</v>
-      </c>
       <c r="D244" s="0">
-        <v>223</v>
+        <v>4700</v>
       </c>
     </row>
     <row r="245">
@@ -6845,7 +6872,7 @@
         <v>52</v>
       </c>
       <c r="D245" s="0">
-        <v>247</v>
+        <v>4700</v>
       </c>
     </row>
     <row r="246">
@@ -6856,10 +6883,10 @@
         <v>543</v>
       </c>
       <c r="C246" s="0" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="D246" s="0">
-        <v>5600</v>
+        <v>597</v>
       </c>
     </row>
     <row r="247">
@@ -6870,10 +6897,10 @@
         <v>545</v>
       </c>
       <c r="C247" s="0" t="s">
-        <v>156</v>
+        <v>52</v>
       </c>
       <c r="D247" s="0">
-        <v>6000</v>
+        <v>223</v>
       </c>
     </row>
     <row r="248">
@@ -6884,10 +6911,10 @@
         <v>547</v>
       </c>
       <c r="C248" s="0" t="s">
-        <v>75</v>
+        <v>52</v>
       </c>
       <c r="D248" s="0">
-        <v>80000</v>
+        <v>247</v>
       </c>
     </row>
     <row r="249">
@@ -6898,10 +6925,10 @@
         <v>549</v>
       </c>
       <c r="C249" s="0" t="s">
-        <v>75</v>
+        <v>37</v>
       </c>
       <c r="D249" s="0">
-        <v>110000</v>
+        <v>5600</v>
       </c>
     </row>
     <row r="250">
@@ -6912,10 +6939,10 @@
         <v>551</v>
       </c>
       <c r="C250" s="0" t="s">
-        <v>75</v>
+        <v>156</v>
       </c>
       <c r="D250" s="0">
-        <v>130000</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="251">
@@ -6926,10 +6953,10 @@
         <v>553</v>
       </c>
       <c r="C251" s="0" t="s">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="D251" s="0">
-        <v>900</v>
+        <v>80000</v>
       </c>
     </row>
     <row r="252">
@@ -6940,10 +6967,10 @@
         <v>555</v>
       </c>
       <c r="C252" s="0" t="s">
-        <v>15</v>
+        <v>75</v>
       </c>
       <c r="D252" s="0">
-        <v>1100</v>
+        <v>110000</v>
       </c>
     </row>
     <row r="253">
@@ -6954,10 +6981,10 @@
         <v>557</v>
       </c>
       <c r="C253" s="0" t="s">
-        <v>15</v>
+        <v>75</v>
       </c>
       <c r="D253" s="0">
-        <v>2500</v>
+        <v>130000</v>
       </c>
     </row>
     <row r="254">
@@ -6968,10 +6995,10 @@
         <v>559</v>
       </c>
       <c r="C254" s="0" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D254" s="0">
-        <v>14608.16</v>
+        <v>900</v>
       </c>
     </row>
     <row r="255">
@@ -6982,10 +7009,10 @@
         <v>561</v>
       </c>
       <c r="C255" s="0" t="s">
-        <v>156</v>
+        <v>15</v>
       </c>
       <c r="D255" s="0">
-        <v>700</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="256">
@@ -6996,10 +7023,10 @@
         <v>563</v>
       </c>
       <c r="C256" s="0" t="s">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="D256" s="0">
-        <v>700</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="257">
@@ -7010,10 +7037,10 @@
         <v>565</v>
       </c>
       <c r="C257" s="0" t="s">
-        <v>289</v>
+        <v>28</v>
       </c>
       <c r="D257" s="0">
-        <v>450</v>
+        <v>14608.16</v>
       </c>
     </row>
     <row r="258">
@@ -7024,10 +7051,10 @@
         <v>567</v>
       </c>
       <c r="C258" s="0" t="s">
-        <v>15</v>
+        <v>156</v>
       </c>
       <c r="D258" s="0">
-        <v>555</v>
+        <v>700</v>
       </c>
     </row>
     <row r="259">
@@ -7038,10 +7065,10 @@
         <v>569</v>
       </c>
       <c r="C259" s="0" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="D259" s="0">
-        <v>825</v>
+        <v>700</v>
       </c>
     </row>
     <row r="260">
@@ -7052,10 +7079,10 @@
         <v>571</v>
       </c>
       <c r="C260" s="0" t="s">
-        <v>15</v>
+        <v>289</v>
       </c>
       <c r="D260" s="0">
-        <v>36.3</v>
+        <v>450</v>
       </c>
     </row>
     <row r="261">
@@ -7069,7 +7096,7 @@
         <v>15</v>
       </c>
       <c r="D261" s="0">
-        <v>544.5</v>
+        <v>555</v>
       </c>
     </row>
     <row r="262">
@@ -7083,7 +7110,7 @@
         <v>15</v>
       </c>
       <c r="D262" s="0">
-        <v>750</v>
+        <v>825</v>
       </c>
     </row>
     <row r="263">
@@ -7094,10 +7121,10 @@
         <v>577</v>
       </c>
       <c r="C263" s="0" t="s">
-        <v>156</v>
+        <v>15</v>
       </c>
       <c r="D263" s="0">
-        <v>1130</v>
+        <v>36.3</v>
       </c>
     </row>
     <row r="264">
@@ -7108,10 +7135,10 @@
         <v>579</v>
       </c>
       <c r="C264" s="0" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="D264" s="0">
-        <v>4510</v>
+        <v>544.5</v>
       </c>
     </row>
     <row r="265">
@@ -7122,10 +7149,10 @@
         <v>581</v>
       </c>
       <c r="C265" s="0" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="D265" s="0">
-        <v>4510</v>
+        <v>750</v>
       </c>
     </row>
     <row r="266">
@@ -7136,10 +7163,10 @@
         <v>583</v>
       </c>
       <c r="C266" s="0" t="s">
-        <v>52</v>
+        <v>156</v>
       </c>
       <c r="D266" s="0">
-        <v>4510</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="267">
@@ -7164,10 +7191,10 @@
         <v>587</v>
       </c>
       <c r="C268" s="0" t="s">
-        <v>15</v>
+        <v>52</v>
       </c>
       <c r="D268" s="0">
-        <v>902</v>
+        <v>4510</v>
       </c>
     </row>
     <row r="269">
@@ -7178,10 +7205,10 @@
         <v>589</v>
       </c>
       <c r="C269" s="0" t="s">
-        <v>15</v>
+        <v>52</v>
       </c>
       <c r="D269" s="0">
-        <v>880</v>
+        <v>4510</v>
       </c>
     </row>
     <row r="270">
@@ -7192,10 +7219,10 @@
         <v>591</v>
       </c>
       <c r="C270" s="0" t="s">
-        <v>145</v>
+        <v>52</v>
       </c>
       <c r="D270" s="0">
-        <v>446</v>
+        <v>4510</v>
       </c>
     </row>
     <row r="271">
@@ -7206,10 +7233,10 @@
         <v>593</v>
       </c>
       <c r="C271" s="0" t="s">
-        <v>145</v>
+        <v>15</v>
       </c>
       <c r="D271" s="0">
-        <v>370</v>
+        <v>902</v>
       </c>
     </row>
     <row r="272">
@@ -7220,10 +7247,10 @@
         <v>595</v>
       </c>
       <c r="C272" s="0" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D272" s="0">
-        <v>300</v>
+        <v>880</v>
       </c>
     </row>
     <row r="273">
@@ -7234,10 +7261,10 @@
         <v>597</v>
       </c>
       <c r="C273" s="0" t="s">
-        <v>18</v>
+        <v>145</v>
       </c>
       <c r="D273" s="0">
-        <v>420</v>
+        <v>446</v>
       </c>
     </row>
     <row r="274">
@@ -7248,10 +7275,10 @@
         <v>599</v>
       </c>
       <c r="C274" s="0" t="s">
-        <v>18</v>
+        <v>145</v>
       </c>
       <c r="D274" s="0">
-        <v>760</v>
+        <v>370</v>
       </c>
     </row>
     <row r="275">
@@ -7265,7 +7292,7 @@
         <v>18</v>
       </c>
       <c r="D275" s="0">
-        <v>820</v>
+        <v>300</v>
       </c>
     </row>
     <row r="276">
@@ -7276,52 +7303,52 @@
         <v>603</v>
       </c>
       <c r="C276" s="0" t="s">
-        <v>604</v>
+        <v>18</v>
       </c>
       <c r="D276" s="0">
-        <v>189016.25</v>
+        <v>420</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="0" t="s">
+        <v>604</v>
+      </c>
+      <c r="B277" s="0" t="s">
         <v>605</v>
       </c>
-      <c r="B277" s="0" t="s">
-        <v>606</v>
-      </c>
       <c r="C277" s="0" t="s">
-        <v>75</v>
+        <v>18</v>
       </c>
       <c r="D277" s="0">
-        <v>28000</v>
+        <v>760</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="0" t="s">
+        <v>606</v>
+      </c>
+      <c r="B278" s="0" t="s">
         <v>607</v>
       </c>
-      <c r="B278" s="0" t="s">
-        <v>608</v>
-      </c>
       <c r="C278" s="0" t="s">
-        <v>75</v>
+        <v>18</v>
       </c>
       <c r="D278" s="0">
-        <v>34000</v>
+        <v>820</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="0" t="s">
+        <v>608</v>
+      </c>
+      <c r="B279" s="0" t="s">
         <v>609</v>
       </c>
-      <c r="B279" s="0" t="s">
+      <c r="C279" s="0" t="s">
         <v>610</v>
       </c>
-      <c r="C279" s="0" t="s">
-        <v>479</v>
-      </c>
       <c r="D279" s="0">
-        <v>243315</v>
+        <v>189016.25</v>
       </c>
     </row>
     <row r="280">
@@ -7332,10 +7359,10 @@
         <v>612</v>
       </c>
       <c r="C280" s="0" t="s">
-        <v>479</v>
+        <v>75</v>
       </c>
       <c r="D280" s="0">
-        <v>196835</v>
+        <v>36000</v>
       </c>
     </row>
     <row r="281">
@@ -7346,10 +7373,10 @@
         <v>614</v>
       </c>
       <c r="C281" s="0" t="s">
-        <v>15</v>
+        <v>75</v>
       </c>
       <c r="D281" s="0">
-        <v>1760</v>
+        <v>42480</v>
       </c>
     </row>
     <row r="282">
@@ -7360,52 +7387,52 @@
         <v>616</v>
       </c>
       <c r="C282" s="0" t="s">
-        <v>617</v>
+        <v>485</v>
       </c>
       <c r="D282" s="0">
-        <v>26350</v>
+        <v>243315</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="0" t="s">
+        <v>617</v>
+      </c>
+      <c r="B283" s="0" t="s">
         <v>618</v>
       </c>
-      <c r="B283" s="0" t="s">
-        <v>619</v>
-      </c>
       <c r="C283" s="0" t="s">
-        <v>212</v>
+        <v>485</v>
       </c>
       <c r="D283" s="0">
-        <v>31250</v>
+        <v>196835</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="0" t="s">
+        <v>619</v>
+      </c>
+      <c r="B284" s="0" t="s">
         <v>620</v>
       </c>
-      <c r="B284" s="0" t="s">
-        <v>621</v>
-      </c>
       <c r="C284" s="0" t="s">
-        <v>59</v>
+        <v>15</v>
       </c>
       <c r="D284" s="0">
-        <v>69</v>
+        <v>1760</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="0" t="s">
+        <v>621</v>
+      </c>
+      <c r="B285" s="0" t="s">
         <v>622</v>
       </c>
-      <c r="B285" s="0" t="s">
+      <c r="C285" s="0" t="s">
         <v>623</v>
       </c>
-      <c r="C285" s="0" t="s">
-        <v>52</v>
-      </c>
       <c r="D285" s="0">
-        <v>34.98</v>
+        <v>26350</v>
       </c>
     </row>
     <row r="286">
@@ -7416,10 +7443,10 @@
         <v>625</v>
       </c>
       <c r="C286" s="0" t="s">
-        <v>59</v>
+        <v>212</v>
       </c>
       <c r="D286" s="0">
-        <v>34.98</v>
+        <v>31250</v>
       </c>
     </row>
     <row r="287">
@@ -7430,29 +7457,29 @@
         <v>627</v>
       </c>
       <c r="C287" s="0" t="s">
-        <v>628</v>
+        <v>59</v>
       </c>
       <c r="D287" s="0">
-        <v>65</v>
+        <v>69</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="0" t="s">
+        <v>628</v>
+      </c>
+      <c r="B288" s="0" t="s">
         <v>629</v>
-      </c>
-      <c r="B288" s="0" t="s">
-        <v>630</v>
       </c>
       <c r="C288" s="0" t="s">
         <v>52</v>
       </c>
       <c r="D288" s="0">
-        <v>65</v>
+        <v>34.98</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="0" t="s">
-        <v>620</v>
+        <v>630</v>
       </c>
       <c r="B289" s="0" t="s">
         <v>631</v>
@@ -7461,7 +7488,7 @@
         <v>59</v>
       </c>
       <c r="D289" s="0">
-        <v>0</v>
+        <v>34.98</v>
       </c>
     </row>
     <row r="290">
@@ -7472,38 +7499,38 @@
         <v>633</v>
       </c>
       <c r="C290" s="0" t="s">
-        <v>52</v>
+        <v>634</v>
       </c>
       <c r="D290" s="0">
-        <v>92</v>
+        <v>65</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="0" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B291" s="0" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="C291" s="0" t="s">
         <v>52</v>
       </c>
       <c r="D291" s="0">
-        <v>33</v>
+        <v>65</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="0" t="s">
-        <v>636</v>
+        <v>626</v>
       </c>
       <c r="B292" s="0" t="s">
         <v>637</v>
       </c>
       <c r="C292" s="0" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="D292" s="0">
-        <v>54.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="293">
@@ -7514,10 +7541,10 @@
         <v>639</v>
       </c>
       <c r="C293" s="0" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="D293" s="0">
-        <v>44</v>
+        <v>92</v>
       </c>
     </row>
     <row r="294">
@@ -7528,10 +7555,10 @@
         <v>641</v>
       </c>
       <c r="C294" s="0" t="s">
-        <v>346</v>
+        <v>52</v>
       </c>
       <c r="D294" s="0">
-        <v>300</v>
+        <v>33</v>
       </c>
     </row>
     <row r="295">
@@ -7542,10 +7569,10 @@
         <v>643</v>
       </c>
       <c r="C295" s="0" t="s">
-        <v>346</v>
+        <v>52</v>
       </c>
       <c r="D295" s="0">
-        <v>370</v>
+        <v>54.8</v>
       </c>
     </row>
     <row r="296">
@@ -7556,10 +7583,10 @@
         <v>645</v>
       </c>
       <c r="C296" s="0" t="s">
-        <v>367</v>
+        <v>59</v>
       </c>
       <c r="D296" s="0">
-        <v>450</v>
+        <v>44</v>
       </c>
     </row>
     <row r="297">
@@ -7570,10 +7597,10 @@
         <v>647</v>
       </c>
       <c r="C297" s="0" t="s">
-        <v>37</v>
+        <v>348</v>
       </c>
       <c r="D297" s="0">
-        <v>450</v>
+        <v>300</v>
       </c>
     </row>
     <row r="298">
@@ -7584,10 +7611,10 @@
         <v>649</v>
       </c>
       <c r="C298" s="0" t="s">
-        <v>15</v>
+        <v>348</v>
       </c>
       <c r="D298" s="0">
-        <v>450</v>
+        <v>370</v>
       </c>
     </row>
     <row r="299">
@@ -7598,10 +7625,10 @@
         <v>651</v>
       </c>
       <c r="C299" s="0" t="s">
-        <v>15</v>
+        <v>369</v>
       </c>
       <c r="D299" s="0">
-        <v>1650</v>
+        <v>450</v>
       </c>
     </row>
     <row r="300">
@@ -7612,10 +7639,10 @@
         <v>653</v>
       </c>
       <c r="C300" s="0" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="D300" s="0">
-        <v>2100</v>
+        <v>450</v>
       </c>
     </row>
     <row r="301">
@@ -7629,7 +7656,7 @@
         <v>15</v>
       </c>
       <c r="D301" s="0">
-        <v>1980</v>
+        <v>450</v>
       </c>
     </row>
     <row r="302">
@@ -7643,7 +7670,7 @@
         <v>15</v>
       </c>
       <c r="D302" s="0">
-        <v>2160</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="303">
@@ -7657,7 +7684,7 @@
         <v>15</v>
       </c>
       <c r="D303" s="0">
-        <v>1300</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="304">
@@ -7671,7 +7698,7 @@
         <v>15</v>
       </c>
       <c r="D304" s="0">
-        <v>2600</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="305">
@@ -7685,7 +7712,7 @@
         <v>15</v>
       </c>
       <c r="D305" s="0">
-        <v>2000</v>
+        <v>2160</v>
       </c>
     </row>
     <row r="306">
@@ -7699,7 +7726,7 @@
         <v>15</v>
       </c>
       <c r="D306" s="0">
-        <v>6700</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="307">
@@ -7713,7 +7740,7 @@
         <v>15</v>
       </c>
       <c r="D307" s="0">
-        <v>1650</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="308">
@@ -7727,7 +7754,7 @@
         <v>15</v>
       </c>
       <c r="D308" s="0">
-        <v>1035</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="309">
@@ -7741,7 +7768,7 @@
         <v>15</v>
       </c>
       <c r="D309" s="0">
-        <v>2600</v>
+        <v>6700</v>
       </c>
     </row>
     <row r="310">
@@ -7755,7 +7782,7 @@
         <v>15</v>
       </c>
       <c r="D310" s="0">
-        <v>2400</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="311">
@@ -7766,10 +7793,10 @@
         <v>675</v>
       </c>
       <c r="C311" s="0" t="s">
-        <v>145</v>
+        <v>15</v>
       </c>
       <c r="D311" s="0">
-        <v>4730</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="312">
@@ -7780,10 +7807,10 @@
         <v>677</v>
       </c>
       <c r="C312" s="0" t="s">
-        <v>145</v>
+        <v>15</v>
       </c>
       <c r="D312" s="0">
-        <v>2517</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="313">
@@ -7794,10 +7821,10 @@
         <v>679</v>
       </c>
       <c r="C313" s="0" t="s">
-        <v>145</v>
+        <v>15</v>
       </c>
       <c r="D313" s="0">
-        <v>1190</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="314">
@@ -7808,10 +7835,10 @@
         <v>681</v>
       </c>
       <c r="C314" s="0" t="s">
-        <v>28</v>
+        <v>145</v>
       </c>
       <c r="D314" s="0">
-        <v>7655.2</v>
+        <v>4730</v>
       </c>
     </row>
     <row r="315">
@@ -7822,10 +7849,10 @@
         <v>683</v>
       </c>
       <c r="C315" s="0" t="s">
-        <v>128</v>
+        <v>145</v>
       </c>
       <c r="D315" s="0">
-        <v>1790</v>
+        <v>2517</v>
       </c>
     </row>
     <row r="316">
@@ -7836,10 +7863,10 @@
         <v>685</v>
       </c>
       <c r="C316" s="0" t="s">
-        <v>128</v>
+        <v>145</v>
       </c>
       <c r="D316" s="0">
-        <v>3016.53</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="317">
@@ -7850,10 +7877,10 @@
         <v>687</v>
       </c>
       <c r="C317" s="0" t="s">
-        <v>128</v>
+        <v>28</v>
       </c>
       <c r="D317" s="0">
-        <v>4800</v>
+        <v>7655.2</v>
       </c>
     </row>
     <row r="318">
@@ -7867,7 +7894,7 @@
         <v>128</v>
       </c>
       <c r="D318" s="0">
-        <v>4450</v>
+        <v>1790</v>
       </c>
     </row>
     <row r="319">
@@ -7878,52 +7905,52 @@
         <v>691</v>
       </c>
       <c r="C319" s="0" t="s">
-        <v>692</v>
+        <v>128</v>
       </c>
       <c r="D319" s="0">
-        <v>0</v>
+        <v>3016.53</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="0" t="s">
+        <v>692</v>
+      </c>
+      <c r="B320" s="0" t="s">
         <v>693</v>
       </c>
-      <c r="B320" s="0" t="s">
-        <v>694</v>
-      </c>
       <c r="C320" s="0" t="s">
-        <v>28</v>
+        <v>128</v>
       </c>
       <c r="D320" s="0">
-        <v>494</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="0" t="s">
+        <v>694</v>
+      </c>
+      <c r="B321" s="0" t="s">
         <v>695</v>
       </c>
-      <c r="B321" s="0" t="s">
-        <v>696</v>
-      </c>
       <c r="C321" s="0" t="s">
-        <v>28</v>
+        <v>128</v>
       </c>
       <c r="D321" s="0">
-        <v>665.3</v>
+        <v>4450</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="0" t="s">
+        <v>696</v>
+      </c>
+      <c r="B322" s="0" t="s">
         <v>697</v>
       </c>
-      <c r="B322" s="0" t="s">
+      <c r="C322" s="0" t="s">
         <v>698</v>
       </c>
-      <c r="C322" s="0" t="s">
-        <v>97</v>
-      </c>
       <c r="D322" s="0">
-        <v>33940.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="323">
@@ -7934,10 +7961,10 @@
         <v>700</v>
       </c>
       <c r="C323" s="0" t="s">
-        <v>97</v>
+        <v>28</v>
       </c>
       <c r="D323" s="0">
-        <v>4525.4</v>
+        <v>494</v>
       </c>
     </row>
     <row r="324">
@@ -7948,10 +7975,10 @@
         <v>702</v>
       </c>
       <c r="C324" s="0" t="s">
-        <v>156</v>
+        <v>28</v>
       </c>
       <c r="D324" s="0">
-        <v>896</v>
+        <v>665.3</v>
       </c>
     </row>
     <row r="325">
@@ -7962,10 +7989,10 @@
         <v>704</v>
       </c>
       <c r="C325" s="0" t="s">
-        <v>145</v>
+        <v>97</v>
       </c>
       <c r="D325" s="0">
-        <v>1125</v>
+        <v>33940.5</v>
       </c>
     </row>
     <row r="326">
@@ -7979,7 +8006,7 @@
         <v>97</v>
       </c>
       <c r="D326" s="0">
-        <v>342732.5</v>
+        <v>4525.4</v>
       </c>
     </row>
     <row r="327">
@@ -7990,10 +8017,10 @@
         <v>708</v>
       </c>
       <c r="C327" s="0" t="s">
-        <v>207</v>
+        <v>156</v>
       </c>
       <c r="D327" s="0">
-        <v>17440</v>
+        <v>896</v>
       </c>
     </row>
     <row r="328">
@@ -8004,10 +8031,10 @@
         <v>710</v>
       </c>
       <c r="C328" s="0" t="s">
-        <v>207</v>
+        <v>145</v>
       </c>
       <c r="D328" s="0">
-        <v>4390</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="329">
@@ -8018,10 +8045,10 @@
         <v>712</v>
       </c>
       <c r="C329" s="0" t="s">
-        <v>207</v>
+        <v>97</v>
       </c>
       <c r="D329" s="0">
-        <v>4390</v>
+        <v>342732.5</v>
       </c>
     </row>
     <row r="330">
@@ -8032,10 +8059,10 @@
         <v>714</v>
       </c>
       <c r="C330" s="0" t="s">
-        <v>289</v>
+        <v>207</v>
       </c>
       <c r="D330" s="0">
-        <v>2250</v>
+        <v>17440</v>
       </c>
     </row>
     <row r="331">
@@ -8049,7 +8076,7 @@
         <v>207</v>
       </c>
       <c r="D331" s="0">
-        <v>3355</v>
+        <v>4390</v>
       </c>
     </row>
     <row r="332">
@@ -8060,10 +8087,10 @@
         <v>718</v>
       </c>
       <c r="C332" s="0" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="D332" s="0">
-        <v>7500</v>
+        <v>4390</v>
       </c>
     </row>
     <row r="333">
@@ -8074,10 +8101,10 @@
         <v>720</v>
       </c>
       <c r="C333" s="0" t="s">
-        <v>97</v>
+        <v>289</v>
       </c>
       <c r="D333" s="0">
-        <v>26620</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="334">
@@ -8088,10 +8115,10 @@
         <v>722</v>
       </c>
       <c r="C334" s="0" t="s">
-        <v>97</v>
+        <v>207</v>
       </c>
       <c r="D334" s="0">
-        <v>266200</v>
+        <v>3355</v>
       </c>
     </row>
     <row r="335">
@@ -8102,10 +8129,10 @@
         <v>724</v>
       </c>
       <c r="C335" s="0" t="s">
-        <v>52</v>
+        <v>215</v>
       </c>
       <c r="D335" s="0">
-        <v>160</v>
+        <v>7500</v>
       </c>
     </row>
     <row r="336">
@@ -8116,10 +8143,10 @@
         <v>726</v>
       </c>
       <c r="C336" s="0" t="s">
-        <v>21</v>
+        <v>97</v>
       </c>
       <c r="D336" s="0">
-        <v>285.6</v>
+        <v>26620</v>
       </c>
     </row>
     <row r="337">
@@ -8130,10 +8157,10 @@
         <v>728</v>
       </c>
       <c r="C337" s="0" t="s">
-        <v>21</v>
+        <v>97</v>
       </c>
       <c r="D337" s="0">
-        <v>338</v>
+        <v>266200</v>
       </c>
     </row>
     <row r="338">
@@ -8144,66 +8171,66 @@
         <v>730</v>
       </c>
       <c r="C338" s="0" t="s">
-        <v>731</v>
+        <v>52</v>
       </c>
       <c r="D338" s="0">
-        <v>770</v>
+        <v>160</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" s="0" t="s">
+        <v>731</v>
+      </c>
+      <c r="B339" s="0" t="s">
         <v>732</v>
       </c>
-      <c r="B339" s="0" t="s">
-        <v>733</v>
-      </c>
       <c r="C339" s="0" t="s">
-        <v>734</v>
+        <v>21</v>
       </c>
       <c r="D339" s="0">
-        <v>770</v>
+        <v>285.6</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" s="0" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="B340" s="0" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="C340" s="0" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D340" s="0">
-        <v>973.5</v>
+        <v>338</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" s="0" t="s">
+        <v>735</v>
+      </c>
+      <c r="B341" s="0" t="s">
+        <v>736</v>
+      </c>
+      <c r="C341" s="0" t="s">
         <v>737</v>
       </c>
-      <c r="B341" s="0" t="s">
-        <v>738</v>
-      </c>
-      <c r="C341" s="0" t="s">
-        <v>21</v>
-      </c>
       <c r="D341" s="0">
-        <v>507.08</v>
+        <v>770</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" s="0" t="s">
+        <v>738</v>
+      </c>
+      <c r="B342" s="0" t="s">
         <v>739</v>
       </c>
-      <c r="B342" s="0" t="s">
+      <c r="C342" s="0" t="s">
         <v>740</v>
       </c>
-      <c r="C342" s="0" t="s">
-        <v>15</v>
-      </c>
       <c r="D342" s="0">
-        <v>450</v>
+        <v>770</v>
       </c>
     </row>
     <row r="343">
@@ -8214,10 +8241,10 @@
         <v>742</v>
       </c>
       <c r="C343" s="0" t="s">
-        <v>156</v>
+        <v>15</v>
       </c>
       <c r="D343" s="0">
-        <v>760</v>
+        <v>973.5</v>
       </c>
     </row>
     <row r="344">
@@ -8228,10 +8255,10 @@
         <v>744</v>
       </c>
       <c r="C344" s="0" t="s">
-        <v>289</v>
+        <v>21</v>
       </c>
       <c r="D344" s="0">
-        <v>5900</v>
+        <v>490</v>
       </c>
     </row>
     <row r="345">
@@ -8242,10 +8269,10 @@
         <v>746</v>
       </c>
       <c r="C345" s="0" t="s">
-        <v>289</v>
+        <v>15</v>
       </c>
       <c r="D345" s="0">
-        <v>2900</v>
+        <v>450</v>
       </c>
     </row>
     <row r="346">
@@ -8256,10 +8283,10 @@
         <v>748</v>
       </c>
       <c r="C346" s="0" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="D346" s="0">
-        <v>935</v>
+        <v>760</v>
       </c>
     </row>
     <row r="347">
@@ -8270,10 +8297,10 @@
         <v>750</v>
       </c>
       <c r="C347" s="0" t="s">
-        <v>145</v>
+        <v>289</v>
       </c>
       <c r="D347" s="0">
-        <v>620</v>
+        <v>5900</v>
       </c>
     </row>
     <row r="348">
@@ -8284,10 +8311,10 @@
         <v>752</v>
       </c>
       <c r="C348" s="0" t="s">
-        <v>145</v>
+        <v>289</v>
       </c>
       <c r="D348" s="0">
-        <v>73</v>
+        <v>2900</v>
       </c>
     </row>
     <row r="349">
@@ -8298,10 +8325,10 @@
         <v>754</v>
       </c>
       <c r="C349" s="0" t="s">
-        <v>97</v>
+        <v>145</v>
       </c>
       <c r="D349" s="0">
-        <v>11313.5</v>
+        <v>935</v>
       </c>
     </row>
     <row r="350">
@@ -8312,10 +8339,10 @@
         <v>756</v>
       </c>
       <c r="C350" s="0" t="s">
-        <v>34</v>
+        <v>145</v>
       </c>
       <c r="D350" s="0">
-        <v>400</v>
+        <v>620</v>
       </c>
     </row>
     <row r="351">
@@ -8326,10 +8353,10 @@
         <v>758</v>
       </c>
       <c r="C351" s="0" t="s">
-        <v>367</v>
+        <v>145</v>
       </c>
       <c r="D351" s="0">
-        <v>400</v>
+        <v>73</v>
       </c>
     </row>
     <row r="352">
@@ -8340,10 +8367,10 @@
         <v>760</v>
       </c>
       <c r="C352" s="0" t="s">
-        <v>21</v>
+        <v>97</v>
       </c>
       <c r="D352" s="0">
-        <v>377</v>
+        <v>11313.5</v>
       </c>
     </row>
     <row r="353">
@@ -8354,10 +8381,10 @@
         <v>762</v>
       </c>
       <c r="C353" s="0" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="D353" s="0">
-        <v>5621.15</v>
+        <v>400</v>
       </c>
     </row>
     <row r="354">
@@ -8368,10 +8395,10 @@
         <v>764</v>
       </c>
       <c r="C354" s="0" t="s">
-        <v>75</v>
+        <v>369</v>
       </c>
       <c r="D354" s="0">
-        <v>898</v>
+        <v>400</v>
       </c>
     </row>
     <row r="355">
@@ -8385,7 +8412,7 @@
         <v>21</v>
       </c>
       <c r="D355" s="0">
-        <v>1120</v>
+        <v>377</v>
       </c>
     </row>
     <row r="356">
@@ -8396,10 +8423,10 @@
         <v>768</v>
       </c>
       <c r="C356" s="0" t="s">
-        <v>128</v>
+        <v>45</v>
       </c>
       <c r="D356" s="0">
-        <v>4767</v>
+        <v>5621.15</v>
       </c>
     </row>
     <row r="357">
@@ -8410,10 +8437,10 @@
         <v>770</v>
       </c>
       <c r="C357" s="0" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="D357" s="0">
-        <v>650</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="358">
@@ -8424,10 +8451,10 @@
         <v>772</v>
       </c>
       <c r="C358" s="0" t="s">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="D358" s="0">
-        <v>650</v>
+        <v>4767</v>
       </c>
     </row>
     <row r="359">
@@ -8438,10 +8465,10 @@
         <v>774</v>
       </c>
       <c r="C359" s="0" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="D359" s="0">
-        <v>2178</v>
+        <v>650</v>
       </c>
     </row>
     <row r="360">
@@ -8452,10 +8479,10 @@
         <v>776</v>
       </c>
       <c r="C360" s="0" t="s">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="D360" s="0">
-        <v>7986</v>
+        <v>650</v>
       </c>
     </row>
     <row r="361">
@@ -8466,38 +8493,38 @@
         <v>778</v>
       </c>
       <c r="C361" s="0" t="s">
-        <v>779</v>
+        <v>15</v>
       </c>
       <c r="D361" s="0">
-        <v>1910</v>
+        <v>2178</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" s="0" t="s">
+        <v>779</v>
+      </c>
+      <c r="B362" s="0" t="s">
         <v>780</v>
       </c>
-      <c r="B362" s="0" t="s">
-        <v>781</v>
-      </c>
       <c r="C362" s="0" t="s">
-        <v>156</v>
+        <v>97</v>
       </c>
       <c r="D362" s="0">
-        <v>900</v>
+        <v>7986</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" s="0" t="s">
+        <v>781</v>
+      </c>
+      <c r="B363" s="0" t="s">
         <v>782</v>
       </c>
-      <c r="B363" s="0" t="s">
+      <c r="C363" s="0" t="s">
         <v>783</v>
       </c>
-      <c r="C363" s="0" t="s">
-        <v>21</v>
-      </c>
       <c r="D363" s="0">
-        <v>1722</v>
+        <v>1910</v>
       </c>
     </row>
     <row r="364">
@@ -8508,10 +8535,10 @@
         <v>785</v>
       </c>
       <c r="C364" s="0" t="s">
-        <v>34</v>
+        <v>156</v>
       </c>
       <c r="D364" s="0">
-        <v>59000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="365">
@@ -8522,458 +8549,458 @@
         <v>787</v>
       </c>
       <c r="C365" s="0" t="s">
-        <v>156</v>
+        <v>788</v>
       </c>
       <c r="D365" s="0">
-        <v>750</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" s="0" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="B366" s="0" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="C366" s="0" t="s">
-        <v>156</v>
+        <v>21</v>
       </c>
       <c r="D366" s="0">
-        <v>1212</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" s="0" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="B367" s="0" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="C367" s="0" t="s">
-        <v>156</v>
+        <v>34</v>
       </c>
       <c r="D367" s="0">
-        <v>1300</v>
+        <v>59000</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" s="0" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="B368" s="0" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="C368" s="0" t="s">
         <v>156</v>
       </c>
       <c r="D368" s="0">
-        <v>1500</v>
+        <v>750</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" s="0" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="B369" s="0" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="C369" s="0" t="s">
         <v>156</v>
       </c>
       <c r="D369" s="0">
-        <v>1400</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" s="0" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="B370" s="0" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C370" s="0" t="s">
-        <v>269</v>
+        <v>156</v>
       </c>
       <c r="D370" s="0">
-        <v>11959</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" s="0" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="B371" s="0" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="C371" s="0" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="D371" s="0">
-        <v>365</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" s="0" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="B372" s="0" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="C372" s="0" t="s">
-        <v>289</v>
+        <v>156</v>
       </c>
       <c r="D372" s="0">
-        <v>1450</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" s="0" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="B373" s="0" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="C373" s="0" t="s">
-        <v>97</v>
+        <v>269</v>
       </c>
       <c r="D373" s="0">
-        <v>7320.5</v>
+        <v>11959</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" s="0" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="B374" s="0" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="C374" s="0" t="s">
-        <v>15</v>
+        <v>145</v>
       </c>
       <c r="D374" s="0">
-        <v>900</v>
+        <v>365</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" s="0" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="B375" s="0" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="C375" s="0" t="s">
         <v>289</v>
       </c>
       <c r="D375" s="0">
-        <v>566</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" s="0" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="B376" s="0" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C376" s="0" t="s">
-        <v>479</v>
+        <v>97</v>
       </c>
       <c r="D376" s="0">
-        <v>64925</v>
+        <v>7320.5</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" s="0" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="B377" s="0" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="C377" s="0" t="s">
         <v>15</v>
       </c>
       <c r="D377" s="0">
-        <v>1100</v>
+        <v>900</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" s="0" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B378" s="0" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="C378" s="0" t="s">
-        <v>21</v>
+        <v>289</v>
       </c>
       <c r="D378" s="0">
-        <v>1623</v>
+        <v>566</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" s="0" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="B379" s="0" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="C379" s="0" t="s">
-        <v>145</v>
+        <v>485</v>
       </c>
       <c r="D379" s="0">
-        <v>1269</v>
+        <v>64925</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" s="0" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="B380" s="0" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="C380" s="0" t="s">
-        <v>145</v>
+        <v>15</v>
       </c>
       <c r="D380" s="0">
-        <v>4712</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" s="0" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="B381" s="0" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="C381" s="0" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D381" s="0">
-        <v>1250</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" s="0" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="B382" s="0" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="C382" s="0" t="s">
-        <v>28</v>
+        <v>145</v>
       </c>
       <c r="D382" s="0">
-        <v>1986</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" s="0" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="B383" s="0" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="C383" s="0" t="s">
-        <v>15</v>
+        <v>145</v>
       </c>
       <c r="D383" s="0">
-        <v>450</v>
+        <v>4712</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" s="0" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="B384" s="0" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="C384" s="0" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="D384" s="0">
-        <v>825</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" s="0" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="B385" s="0" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="C385" s="0" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="D385" s="0">
-        <v>825</v>
+        <v>1986</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" s="0" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="B386" s="0" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="C386" s="0" t="s">
-        <v>387</v>
+        <v>15</v>
       </c>
       <c r="D386" s="0">
-        <v>134775.6</v>
+        <v>450</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" s="0" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="B387" s="0" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="C387" s="0" t="s">
-        <v>387</v>
+        <v>15</v>
       </c>
       <c r="D387" s="0">
-        <v>175991.55</v>
+        <v>825</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" s="0" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="B388" s="0" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="C388" s="0" t="s">
-        <v>75</v>
+        <v>15</v>
       </c>
       <c r="D388" s="0">
-        <v>3427</v>
+        <v>825</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" s="0" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="B389" s="0" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="C389" s="0" t="s">
-        <v>75</v>
+        <v>389</v>
       </c>
       <c r="D389" s="0">
-        <v>10618</v>
+        <v>134775.6</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" s="0" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="B390" s="0" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="C390" s="0" t="s">
-        <v>289</v>
+        <v>389</v>
       </c>
       <c r="D390" s="0">
-        <v>515</v>
+        <v>175991.55</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" s="0" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B391" s="0" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="C391" s="0" t="s">
-        <v>37</v>
+        <v>75</v>
       </c>
       <c r="D391" s="0">
-        <v>515</v>
+        <v>3427</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" s="0" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="B392" s="0" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="C392" s="0" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="D392" s="0">
-        <v>10000</v>
+        <v>10618</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" s="0" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B393" s="0" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="C393" s="0" t="s">
-        <v>479</v>
+        <v>289</v>
       </c>
       <c r="D393" s="0">
-        <v>213700</v>
+        <v>515</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" s="0" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="B394" s="0" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="C394" s="0" t="s">
-        <v>479</v>
+        <v>37</v>
       </c>
       <c r="D394" s="0">
-        <v>257000</v>
+        <v>515</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" s="0" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="B395" s="0" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="C395" s="0" t="s">
-        <v>75</v>
+        <v>52</v>
       </c>
       <c r="D395" s="0">
-        <v>10522</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" s="0" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="B396" s="0" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="C396" s="0" t="s">
-        <v>75</v>
+        <v>485</v>
       </c>
       <c r="D396" s="0">
-        <v>19481</v>
+        <v>213700</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" s="0" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="B397" s="0" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="C397" s="0" t="s">
-        <v>852</v>
+        <v>485</v>
       </c>
       <c r="D397" s="0">
-        <v>1080</v>
+        <v>257000</v>
       </c>
     </row>
     <row r="398">
@@ -8984,10 +9011,10 @@
         <v>854</v>
       </c>
       <c r="C398" s="0" t="s">
-        <v>18</v>
+        <v>75</v>
       </c>
       <c r="D398" s="0">
-        <v>586.49</v>
+        <v>10522</v>
       </c>
     </row>
     <row r="399">
@@ -8998,24 +9025,24 @@
         <v>856</v>
       </c>
       <c r="C399" s="0" t="s">
-        <v>857</v>
+        <v>75</v>
       </c>
       <c r="D399" s="0">
-        <v>520</v>
+        <v>19481</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" s="0" t="s">
+        <v>857</v>
+      </c>
+      <c r="B400" s="0" t="s">
         <v>858</v>
       </c>
-      <c r="B400" s="0" t="s">
+      <c r="C400" s="0" t="s">
         <v>859</v>
       </c>
-      <c r="C400" s="0" t="s">
-        <v>857</v>
-      </c>
       <c r="D400" s="0">
-        <v>300</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="401">
@@ -9026,10 +9053,10 @@
         <v>861</v>
       </c>
       <c r="C401" s="0" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="D401" s="0">
-        <v>630</v>
+        <v>586.49</v>
       </c>
     </row>
     <row r="402">
@@ -9040,94 +9067,94 @@
         <v>863</v>
       </c>
       <c r="C402" s="0" t="s">
-        <v>15</v>
+        <v>864</v>
       </c>
       <c r="D402" s="0">
-        <v>2200</v>
+        <v>520</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" s="0" t="s">
+        <v>865</v>
+      </c>
+      <c r="B403" s="0" t="s">
+        <v>866</v>
+      </c>
+      <c r="C403" s="0" t="s">
         <v>864</v>
       </c>
-      <c r="B403" s="0" t="s">
-        <v>865</v>
-      </c>
-      <c r="C403" s="0" t="s">
-        <v>15</v>
-      </c>
       <c r="D403" s="0">
-        <v>2800</v>
+        <v>340</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" s="0" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="B404" s="0" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="C404" s="0" t="s">
-        <v>97</v>
+        <v>34</v>
       </c>
       <c r="D404" s="0">
-        <v>5190.9</v>
+        <v>630</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" s="0" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="B405" s="0" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="C405" s="0" t="s">
-        <v>75</v>
+        <v>15</v>
       </c>
       <c r="D405" s="0">
-        <v>2969</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" s="0" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="B406" s="0" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="C406" s="0" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="D406" s="0">
-        <v>3800</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" s="0" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B407" s="0" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="C407" s="0" t="s">
-        <v>15</v>
+        <v>97</v>
       </c>
       <c r="D407" s="0">
-        <v>4000</v>
+        <v>5190.9</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" s="0" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="B408" s="0" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="C408" s="0" t="s">
-        <v>876</v>
+        <v>75</v>
       </c>
       <c r="D408" s="0">
-        <v>3800</v>
+        <v>2969</v>
       </c>
     </row>
     <row r="409">
@@ -9138,10 +9165,10 @@
         <v>878</v>
       </c>
       <c r="C409" s="0" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="D409" s="0">
-        <v>353</v>
+        <v>3800</v>
       </c>
     </row>
     <row r="410">
@@ -9152,10 +9179,10 @@
         <v>880</v>
       </c>
       <c r="C410" s="0" t="s">
-        <v>115</v>
+        <v>15</v>
       </c>
       <c r="D410" s="0">
-        <v>1800</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="411">
@@ -9166,290 +9193,290 @@
         <v>882</v>
       </c>
       <c r="C411" s="0" t="s">
-        <v>15</v>
+        <v>883</v>
       </c>
       <c r="D411" s="0">
-        <v>2948</v>
+        <v>3800</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" s="0" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="B412" s="0" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="C412" s="0" t="s">
-        <v>97</v>
+        <v>21</v>
       </c>
       <c r="D412" s="0">
-        <v>146.41</v>
+        <v>353</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" s="0" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="B413" s="0" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="C413" s="0" t="s">
-        <v>215</v>
+        <v>115</v>
       </c>
       <c r="D413" s="0">
-        <v>65537</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" s="0" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="B414" s="0" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="C414" s="0" t="s">
-        <v>145</v>
+        <v>15</v>
       </c>
       <c r="D414" s="0">
-        <v>4130.4</v>
+        <v>2948</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" s="0" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="B415" s="0" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="C415" s="0" t="s">
-        <v>145</v>
+        <v>97</v>
       </c>
       <c r="D415" s="0">
-        <v>4283</v>
+        <v>146.41</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" s="0" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="B416" s="0" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="C416" s="0" t="s">
-        <v>145</v>
+        <v>215</v>
       </c>
       <c r="D416" s="0">
-        <v>6524.8</v>
+        <v>65537</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" s="0" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="B417" s="0" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="C417" s="0" t="s">
-        <v>316</v>
+        <v>145</v>
       </c>
       <c r="D417" s="0">
-        <v>570</v>
+        <v>4130.4</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" s="0" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="B418" s="0" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="C418" s="0" t="s">
-        <v>75</v>
+        <v>145</v>
       </c>
       <c r="D418" s="0">
-        <v>550</v>
+        <v>4283</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" s="0" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="B419" s="0" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="C419" s="0" t="s">
-        <v>52</v>
+        <v>145</v>
       </c>
       <c r="D419" s="0">
-        <v>153</v>
+        <v>6524.8</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" s="0" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="B420" s="0" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="C420" s="0" t="s">
-        <v>28</v>
+        <v>316</v>
       </c>
       <c r="D420" s="0">
-        <v>740.7</v>
+        <v>570</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" s="0" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="B421" s="0" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="C421" s="0" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="D421" s="0">
-        <v>101000</v>
+        <v>550</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" s="0" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="B422" s="0" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="C422" s="0" t="s">
-        <v>128</v>
+        <v>52</v>
       </c>
       <c r="D422" s="0">
-        <v>6251</v>
+        <v>153</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" s="0" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="B423" s="0" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="C423" s="0" t="s">
-        <v>145</v>
+        <v>28</v>
       </c>
       <c r="D423" s="0">
-        <v>883</v>
+        <v>740.7</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" s="0" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="B424" s="0" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="C424" s="0" t="s">
-        <v>97</v>
+        <v>64</v>
       </c>
       <c r="D424" s="0">
-        <v>1164.66</v>
+        <v>101000</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" s="0" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="B425" s="0" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="C425" s="0" t="s">
-        <v>156</v>
+        <v>128</v>
       </c>
       <c r="D425" s="0">
-        <v>360</v>
+        <v>6251</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" s="0" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="B426" s="0" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="C426" s="0" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="D426" s="0">
-        <v>450</v>
+        <v>883</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" s="0" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="B427" s="0" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="C427" s="0" t="s">
-        <v>156</v>
+        <v>97</v>
       </c>
       <c r="D427" s="0">
-        <v>2150</v>
+        <v>1164.66</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" s="0" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="B428" s="0" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="C428" s="0" t="s">
-        <v>604</v>
+        <v>156</v>
       </c>
       <c r="D428" s="0">
-        <v>25192.82</v>
+        <v>360</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" s="0" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="B429" s="0" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="C429" s="0" t="s">
-        <v>75</v>
+        <v>156</v>
       </c>
       <c r="D429" s="0">
-        <v>3500</v>
+        <v>450</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" s="0" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="B430" s="0" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="C430" s="0" t="s">
-        <v>180</v>
+        <v>156</v>
       </c>
       <c r="D430" s="0">
-        <v>600</v>
+        <v>2150</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" s="0" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="B431" s="0" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="C431" s="0" t="s">
-        <v>923</v>
+        <v>610</v>
       </c>
       <c r="D431" s="0">
-        <v>1080</v>
+        <v>25192.82</v>
       </c>
     </row>
     <row r="432">
@@ -9460,10 +9487,10 @@
         <v>925</v>
       </c>
       <c r="C432" s="0" t="s">
-        <v>346</v>
+        <v>75</v>
       </c>
       <c r="D432" s="0">
-        <v>8628</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="433">
@@ -9474,10 +9501,10 @@
         <v>927</v>
       </c>
       <c r="C433" s="0" t="s">
-        <v>40</v>
+        <v>180</v>
       </c>
       <c r="D433" s="0">
-        <v>27991.54</v>
+        <v>600</v>
       </c>
     </row>
     <row r="434">
@@ -9488,178 +9515,178 @@
         <v>929</v>
       </c>
       <c r="C434" s="0" t="s">
-        <v>145</v>
+        <v>930</v>
       </c>
       <c r="D434" s="0">
-        <v>1020</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" s="0" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="B435" s="0" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="C435" s="0" t="s">
-        <v>145</v>
+        <v>348</v>
       </c>
       <c r="D435" s="0">
-        <v>4106</v>
+        <v>8628</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" s="0" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="B436" s="0" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="C436" s="0" t="s">
-        <v>289</v>
+        <v>40</v>
       </c>
       <c r="D436" s="0">
-        <v>450</v>
+        <v>27991.54</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" s="0" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="B437" s="0" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="C437" s="0" t="s">
-        <v>45</v>
+        <v>145</v>
       </c>
       <c r="D437" s="0">
-        <v>6398.6</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" s="0" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="B438" s="0" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="C438" s="0" t="s">
-        <v>45</v>
+        <v>145</v>
       </c>
       <c r="D438" s="0">
-        <v>2886.7</v>
+        <v>4106</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" s="0" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="B439" s="0" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="C439" s="0" t="s">
-        <v>45</v>
+        <v>289</v>
       </c>
       <c r="D439" s="0">
-        <v>2050.95</v>
+        <v>450</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" s="0" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="B440" s="0" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="C440" s="0" t="s">
         <v>45</v>
       </c>
       <c r="D440" s="0">
-        <v>30050.45</v>
+        <v>6398.6</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" s="0" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="B441" s="0" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="C441" s="0" t="s">
         <v>45</v>
       </c>
       <c r="D441" s="0">
-        <v>2326.8</v>
+        <v>2886.7</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" s="0" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="B442" s="0" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="C442" s="0" t="s">
         <v>45</v>
       </c>
       <c r="D442" s="0">
-        <v>6429.95</v>
+        <v>2050.95</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" s="0" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="B443" s="0" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="C443" s="0" t="s">
         <v>45</v>
       </c>
       <c r="D443" s="0">
-        <v>5180.26</v>
+        <v>30050.45</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" s="0" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="B444" s="0" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="C444" s="0" t="s">
-        <v>212</v>
+        <v>45</v>
       </c>
       <c r="D444" s="0">
-        <v>510</v>
+        <v>2326.8</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" s="0" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="B445" s="0" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="C445" s="0" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="D445" s="0">
-        <v>510</v>
+        <v>6429.95</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" s="0" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="B446" s="0" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="C446" s="0" t="s">
-        <v>954</v>
+        <v>45</v>
       </c>
       <c r="D446" s="0">
-        <v>626</v>
+        <v>5180.26</v>
       </c>
     </row>
     <row r="447">
@@ -9670,10 +9697,10 @@
         <v>956</v>
       </c>
       <c r="C447" s="0" t="s">
-        <v>954</v>
+        <v>212</v>
       </c>
       <c r="D447" s="0">
-        <v>626</v>
+        <v>510</v>
       </c>
     </row>
     <row r="448">
@@ -9684,10 +9711,10 @@
         <v>958</v>
       </c>
       <c r="C448" s="0" t="s">
-        <v>954</v>
+        <v>37</v>
       </c>
       <c r="D448" s="0">
-        <v>626</v>
+        <v>510</v>
       </c>
     </row>
     <row r="449">
@@ -9698,80 +9725,80 @@
         <v>960</v>
       </c>
       <c r="C449" s="0" t="s">
-        <v>954</v>
+        <v>961</v>
       </c>
       <c r="D449" s="0">
-        <v>342</v>
+        <v>626</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" s="0" t="s">
+        <v>962</v>
+      </c>
+      <c r="B450" s="0" t="s">
+        <v>963</v>
+      </c>
+      <c r="C450" s="0" t="s">
         <v>961</v>
       </c>
-      <c r="B450" s="0" t="s">
-        <v>962</v>
-      </c>
-      <c r="C450" s="0" t="s">
-        <v>954</v>
-      </c>
       <c r="D450" s="0">
-        <v>342</v>
+        <v>626</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" s="0" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="B451" s="0" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="C451" s="0" t="s">
-        <v>954</v>
+        <v>961</v>
       </c>
       <c r="D451" s="0">
-        <v>342</v>
+        <v>626</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" s="0" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="B452" s="0" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="C452" s="0" t="s">
-        <v>954</v>
+        <v>961</v>
       </c>
       <c r="D452" s="0">
-        <v>0</v>
+        <v>342</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" s="0" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="B453" s="0" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="C453" s="0" t="s">
-        <v>954</v>
+        <v>961</v>
       </c>
       <c r="D453" s="0">
-        <v>0</v>
+        <v>342</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" s="0" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="B454" s="0" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="C454" s="0" t="s">
-        <v>971</v>
+        <v>961</v>
       </c>
       <c r="D454" s="0">
-        <v>453</v>
+        <v>342</v>
       </c>
     </row>
     <row r="455">
@@ -9782,10 +9809,10 @@
         <v>973</v>
       </c>
       <c r="C455" s="0" t="s">
-        <v>954</v>
+        <v>961</v>
       </c>
       <c r="D455" s="0">
-        <v>453</v>
+        <v>0</v>
       </c>
     </row>
     <row r="456">
@@ -9796,10 +9823,10 @@
         <v>975</v>
       </c>
       <c r="C456" s="0" t="s">
-        <v>75</v>
+        <v>961</v>
       </c>
       <c r="D456" s="0">
-        <v>19322</v>
+        <v>0</v>
       </c>
     </row>
     <row r="457">
@@ -9810,122 +9837,122 @@
         <v>977</v>
       </c>
       <c r="C457" s="0" t="s">
-        <v>34</v>
+        <v>978</v>
       </c>
       <c r="D457" s="0">
-        <v>430</v>
+        <v>453</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" s="0" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="B458" s="0" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="C458" s="0" t="s">
-        <v>289</v>
+        <v>961</v>
       </c>
       <c r="D458" s="0">
-        <v>430</v>
+        <v>453</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" s="0" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="B459" s="0" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="C459" s="0" t="s">
-        <v>120</v>
+        <v>75</v>
       </c>
       <c r="D459" s="0">
-        <v>14000</v>
+        <v>19322</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" s="0" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="B460" s="0" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="C460" s="0" t="s">
-        <v>145</v>
+        <v>34</v>
       </c>
       <c r="D460" s="0">
-        <v>12049</v>
+        <v>430</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" s="0" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="B461" s="0" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="C461" s="0" t="s">
-        <v>145</v>
+        <v>289</v>
       </c>
       <c r="D461" s="0">
-        <v>2895</v>
+        <v>430</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" s="0" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="B462" s="0" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="C462" s="0" t="s">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="D462" s="0">
-        <v>266200</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" s="0" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="B463" s="0" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="C463" s="0" t="s">
-        <v>97</v>
+        <v>145</v>
       </c>
       <c r="D463" s="0">
-        <v>194991.5</v>
+        <v>12049</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" s="0" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="B464" s="0" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="C464" s="0" t="s">
-        <v>97</v>
+        <v>145</v>
       </c>
       <c r="D464" s="0">
-        <v>289492.5</v>
+        <v>2895</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" s="0" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="B465" s="0" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="C465" s="0" t="s">
-        <v>994</v>
+        <v>145</v>
       </c>
       <c r="D465" s="0">
-        <v>13722.52</v>
+        <v>2620</v>
       </c>
     </row>
     <row r="466">
@@ -9936,10 +9963,10 @@
         <v>996</v>
       </c>
       <c r="C466" s="0" t="s">
-        <v>994</v>
+        <v>97</v>
       </c>
       <c r="D466" s="0">
-        <v>15072</v>
+        <v>266200</v>
       </c>
     </row>
     <row r="467">
@@ -9950,10 +9977,10 @@
         <v>998</v>
       </c>
       <c r="C467" s="0" t="s">
-        <v>994</v>
+        <v>97</v>
       </c>
       <c r="D467" s="0">
-        <v>6555.64</v>
+        <v>194991.5</v>
       </c>
     </row>
     <row r="468">
@@ -9964,10 +9991,10 @@
         <v>1000</v>
       </c>
       <c r="C468" s="0" t="s">
-        <v>994</v>
+        <v>97</v>
       </c>
       <c r="D468" s="0">
-        <v>8964.61</v>
+        <v>289492.5</v>
       </c>
     </row>
     <row r="469">
@@ -9978,66 +10005,66 @@
         <v>1002</v>
       </c>
       <c r="C469" s="0" t="s">
-        <v>994</v>
+        <v>1003</v>
       </c>
       <c r="D469" s="0">
-        <v>11735</v>
+        <v>13722.52</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" s="0" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B470" s="0" t="s">
+        <v>1005</v>
+      </c>
+      <c r="C470" s="0" t="s">
         <v>1003</v>
       </c>
-      <c r="B470" s="0" t="s">
-        <v>1004</v>
-      </c>
-      <c r="C470" s="0" t="s">
-        <v>75</v>
-      </c>
       <c r="D470" s="0">
-        <v>4276</v>
+        <v>15072</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" s="0" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="B471" s="0" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="C471" s="0" t="s">
-        <v>145</v>
+        <v>1003</v>
       </c>
       <c r="D471" s="0">
-        <v>3930</v>
+        <v>6555.64</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" s="0" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="B472" s="0" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="C472" s="0" t="s">
-        <v>97</v>
+        <v>1003</v>
       </c>
       <c r="D472" s="0">
-        <v>4392.3</v>
+        <v>8964.61</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" s="0" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="B473" s="0" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="C473" s="0" t="s">
-        <v>1011</v>
+        <v>1003</v>
       </c>
       <c r="D473" s="0">
-        <v>5254.41</v>
+        <v>11735</v>
       </c>
     </row>
     <row r="474">
@@ -10048,10 +10075,10 @@
         <v>1013</v>
       </c>
       <c r="C474" s="0" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="D474" s="0">
-        <v>1297</v>
+        <v>4276</v>
       </c>
     </row>
     <row r="475">
@@ -10062,10 +10089,10 @@
         <v>1015</v>
       </c>
       <c r="C475" s="0" t="s">
-        <v>52</v>
+        <v>145</v>
       </c>
       <c r="D475" s="0">
-        <v>298</v>
+        <v>3930</v>
       </c>
     </row>
     <row r="476">
@@ -10076,10 +10103,10 @@
         <v>1017</v>
       </c>
       <c r="C476" s="0" t="s">
-        <v>52</v>
+        <v>97</v>
       </c>
       <c r="D476" s="0">
-        <v>596</v>
+        <v>4392.3</v>
       </c>
     </row>
     <row r="477">
@@ -10090,80 +10117,80 @@
         <v>1019</v>
       </c>
       <c r="C477" s="0" t="s">
-        <v>384</v>
+        <v>1020</v>
       </c>
       <c r="D477" s="0">
-        <v>65142.6</v>
+        <v>5254.41</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" s="0" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="B478" s="0" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="C478" s="0" t="s">
-        <v>384</v>
+        <v>52</v>
       </c>
       <c r="D478" s="0">
-        <v>23482.7</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" s="0" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="B479" s="0" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="C479" s="0" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="D479" s="0">
-        <v>6029.59</v>
+        <v>298</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" s="0" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="B480" s="0" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="C480" s="0" t="s">
         <v>52</v>
       </c>
       <c r="D480" s="0">
-        <v>12000</v>
+        <v>596</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" s="0" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="B481" s="0" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="C481" s="0" t="s">
-        <v>52</v>
+        <v>386</v>
       </c>
       <c r="D481" s="0">
-        <v>17425</v>
+        <v>65142.6</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" s="0" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="B482" s="0" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="C482" s="0" t="s">
-        <v>1030</v>
+        <v>386</v>
       </c>
       <c r="D482" s="0">
-        <v>1958</v>
+        <v>23482.7</v>
       </c>
     </row>
     <row r="483">
@@ -10174,80 +10201,80 @@
         <v>1032</v>
       </c>
       <c r="C483" s="0" t="s">
-        <v>1033</v>
+        <v>28</v>
       </c>
       <c r="D483" s="0">
-        <v>2282.3</v>
+        <v>6029.59</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" s="0" t="s">
+        <v>1033</v>
+      </c>
+      <c r="B484" s="0" t="s">
         <v>1034</v>
       </c>
-      <c r="B484" s="0" t="s">
-        <v>1035</v>
-      </c>
       <c r="C484" s="0" t="s">
-        <v>1036</v>
+        <v>52</v>
       </c>
       <c r="D484" s="0">
-        <v>386</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" s="0" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="B485" s="0" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="C485" s="0" t="s">
-        <v>1039</v>
+        <v>52</v>
       </c>
       <c r="D485" s="0">
-        <v>385.4</v>
+        <v>17425</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" s="0" t="s">
-        <v>1040</v>
+        <v>1037</v>
       </c>
       <c r="B486" s="0" t="s">
-        <v>1041</v>
+        <v>1038</v>
       </c>
       <c r="C486" s="0" t="s">
-        <v>97</v>
+        <v>1039</v>
       </c>
       <c r="D486" s="0">
-        <v>296147.5</v>
+        <v>1958</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" s="0" t="s">
+        <v>1040</v>
+      </c>
+      <c r="B487" s="0" t="s">
+        <v>1041</v>
+      </c>
+      <c r="C487" s="0" t="s">
         <v>1042</v>
       </c>
-      <c r="B487" s="0" t="s">
-        <v>1043</v>
-      </c>
-      <c r="C487" s="0" t="s">
-        <v>128</v>
-      </c>
       <c r="D487" s="0">
-        <v>1890</v>
+        <v>2282.3</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" s="0" t="s">
+        <v>1043</v>
+      </c>
+      <c r="B488" s="0" t="s">
         <v>1044</v>
       </c>
-      <c r="B488" s="0" t="s">
+      <c r="C488" s="0" t="s">
         <v>1045</v>
       </c>
-      <c r="C488" s="0" t="s">
-        <v>604</v>
-      </c>
       <c r="D488" s="0">
-        <v>83000</v>
+        <v>386</v>
       </c>
     </row>
     <row r="489">
@@ -10258,234 +10285,234 @@
         <v>1047</v>
       </c>
       <c r="C489" s="0" t="s">
-        <v>145</v>
+        <v>1048</v>
       </c>
       <c r="D489" s="0">
-        <v>99</v>
+        <v>385.4</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" s="0" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="B490" s="0" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="C490" s="0" t="s">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="D490" s="0">
-        <v>950</v>
+        <v>296147.5</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" s="0" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="B491" s="0" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="C491" s="0" t="s">
-        <v>479</v>
+        <v>128</v>
       </c>
       <c r="D491" s="0">
-        <v>398107</v>
+        <v>1890</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" s="0" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="B492" s="0" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="C492" s="0" t="s">
-        <v>165</v>
+        <v>610</v>
       </c>
       <c r="D492" s="0">
-        <v>2200</v>
+        <v>83000</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" s="0" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="B493" s="0" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="C493" s="0" t="s">
-        <v>212</v>
+        <v>145</v>
       </c>
       <c r="D493" s="0">
-        <v>41000</v>
+        <v>99</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" s="0" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="B494" s="0" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="C494" s="0" t="s">
         <v>75</v>
       </c>
       <c r="D494" s="0">
-        <v>5790</v>
+        <v>950</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" s="0" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="B495" s="0" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="C495" s="0" t="s">
-        <v>954</v>
+        <v>485</v>
       </c>
       <c r="D495" s="0">
-        <v>880</v>
+        <v>398107</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" s="0" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="B496" s="0" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="C496" s="0" t="s">
-        <v>954</v>
+        <v>165</v>
       </c>
       <c r="D496" s="0">
-        <v>880</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" s="0" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="B497" s="0" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="C497" s="0" t="s">
-        <v>954</v>
+        <v>212</v>
       </c>
       <c r="D497" s="0">
-        <v>880</v>
+        <v>41000</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" s="0" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="B498" s="0" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="C498" s="0" t="s">
-        <v>21</v>
+        <v>75</v>
       </c>
       <c r="D498" s="0">
-        <v>563.36</v>
+        <v>5790</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" s="0" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="B499" s="0" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="C499" s="0" t="s">
-        <v>15</v>
+        <v>961</v>
       </c>
       <c r="D499" s="0">
-        <v>3520</v>
+        <v>880</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" s="0" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="B500" s="0" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="C500" s="0" t="s">
-        <v>15</v>
+        <v>961</v>
       </c>
       <c r="D500" s="0">
-        <v>2600</v>
+        <v>880</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" s="0" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="B501" s="0" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="C501" s="0" t="s">
-        <v>289</v>
+        <v>961</v>
       </c>
       <c r="D501" s="0">
-        <v>3700</v>
+        <v>880</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" s="0" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="B502" s="0" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="C502" s="0" t="s">
-        <v>289</v>
+        <v>21</v>
       </c>
       <c r="D502" s="0">
-        <v>2600</v>
+        <v>563.36</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" s="0" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="B503" s="0" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="C503" s="0" t="s">
         <v>15</v>
       </c>
       <c r="D503" s="0">
-        <v>2235</v>
+        <v>3520</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" s="0" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="B504" s="0" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="C504" s="0" t="s">
         <v>15</v>
       </c>
       <c r="D504" s="0">
-        <v>3850</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" s="0" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="B505" s="0" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="C505" s="0" t="s">
-        <v>1080</v>
+        <v>289</v>
       </c>
       <c r="D505" s="0">
-        <v>1</v>
+        <v>3700</v>
       </c>
     </row>
     <row r="506">
@@ -10496,10 +10523,10 @@
         <v>1082</v>
       </c>
       <c r="C506" s="0" t="s">
-        <v>28</v>
+        <v>289</v>
       </c>
       <c r="D506" s="0">
-        <v>15189</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="507">
@@ -10510,10 +10537,10 @@
         <v>1084</v>
       </c>
       <c r="C507" s="0" t="s">
-        <v>384</v>
+        <v>15</v>
       </c>
       <c r="D507" s="0">
-        <v>3859.93</v>
+        <v>2235</v>
       </c>
     </row>
     <row r="508">
@@ -10524,10 +10551,10 @@
         <v>1086</v>
       </c>
       <c r="C508" s="0" t="s">
-        <v>384</v>
+        <v>15</v>
       </c>
       <c r="D508" s="0">
-        <v>11751.49</v>
+        <v>3850</v>
       </c>
     </row>
     <row r="509">
@@ -10538,52 +10565,52 @@
         <v>1088</v>
       </c>
       <c r="C509" s="0" t="s">
-        <v>346</v>
+        <v>1089</v>
       </c>
       <c r="D509" s="0">
-        <v>6000</v>
+        <v>1</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" s="0" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="B510" s="0" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="C510" s="0" t="s">
-        <v>346</v>
+        <v>28</v>
       </c>
       <c r="D510" s="0">
-        <v>3000</v>
+        <v>15189</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" s="0" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="B511" s="0" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="C511" s="0" t="s">
-        <v>37</v>
+        <v>386</v>
       </c>
       <c r="D511" s="0">
-        <v>618</v>
+        <v>3859.93</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" s="0" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="B512" s="0" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="C512" s="0" t="s">
-        <v>1095</v>
+        <v>386</v>
       </c>
       <c r="D512" s="0">
-        <v>24600</v>
+        <v>11751.49</v>
       </c>
     </row>
     <row r="513">
@@ -10594,10 +10621,10 @@
         <v>1097</v>
       </c>
       <c r="C513" s="0" t="s">
-        <v>110</v>
+        <v>348</v>
       </c>
       <c r="D513" s="0">
-        <v>0</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="514">
@@ -10608,10 +10635,10 @@
         <v>1099</v>
       </c>
       <c r="C514" s="0" t="s">
-        <v>97</v>
+        <v>348</v>
       </c>
       <c r="D514" s="0">
-        <v>43590.25</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="515">
@@ -10622,10 +10649,10 @@
         <v>1101</v>
       </c>
       <c r="C515" s="0" t="s">
-        <v>479</v>
+        <v>37</v>
       </c>
       <c r="D515" s="0">
-        <v>213700</v>
+        <v>618</v>
       </c>
     </row>
     <row r="516">
@@ -10636,149 +10663,205 @@
         <v>1103</v>
       </c>
       <c r="C516" s="0" t="s">
-        <v>384</v>
+        <v>1104</v>
       </c>
       <c r="D516" s="0">
-        <v>77429.29</v>
+        <v>24600</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" s="0" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="B517" s="0" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="C517" s="0" t="s">
-        <v>384</v>
+        <v>110</v>
       </c>
       <c r="D517" s="0">
-        <v>42913.42</v>
+        <v>0</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" s="0" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="B518" s="0" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="C518" s="0" t="s">
-        <v>384</v>
+        <v>97</v>
       </c>
       <c r="D518" s="0">
-        <v>88806.25</v>
+        <v>43590.25</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" s="0" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="B519" s="0" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C519" s="0" t="s">
-        <v>384</v>
+        <v>485</v>
       </c>
       <c r="D519" s="0">
-        <v>50781.52</v>
+        <v>213700</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" s="0" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="B520" s="0" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="C520" s="0" t="s">
-        <v>21</v>
+        <v>386</v>
       </c>
       <c r="D520" s="0">
-        <v>1600</v>
+        <v>77429.29</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" s="0" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="B521" s="0" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="C521" s="0" t="s">
-        <v>28</v>
+        <v>386</v>
       </c>
       <c r="D521" s="0">
-        <v>3521.4</v>
+        <v>42913.42</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" s="0" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="B522" s="0" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="C522" s="0" t="s">
-        <v>28</v>
+        <v>386</v>
       </c>
       <c r="D522" s="0">
-        <v>3987</v>
+        <v>88806.25</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" s="0" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="B523" s="0" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="C523" s="0" t="s">
-        <v>28</v>
+        <v>386</v>
       </c>
       <c r="D523" s="0">
-        <v>4086.37</v>
+        <v>50781.52</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" s="0" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="B524" s="0" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="C524" s="0" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D524" s="0">
-        <v>3382.65</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" s="0" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="B525" s="0" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="C525" s="0" t="s">
-        <v>165</v>
+        <v>28</v>
       </c>
       <c r="D525" s="0">
-        <v>430</v>
+        <v>3521.4</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" s="0" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="B526" s="0" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="C526" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="D526" s="0">
+        <v>3987</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" s="0" t="s">
+        <v>1125</v>
+      </c>
+      <c r="B527" s="0" t="s">
+        <v>1126</v>
+      </c>
+      <c r="C527" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="D527" s="0">
+        <v>4086.37</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" s="0" t="s">
+        <v>1127</v>
+      </c>
+      <c r="B528" s="0" t="s">
+        <v>1128</v>
+      </c>
+      <c r="C528" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="D528" s="0">
+        <v>3382.65</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" s="0" t="s">
+        <v>1129</v>
+      </c>
+      <c r="B529" s="0" t="s">
+        <v>1130</v>
+      </c>
+      <c r="C529" s="0" t="s">
+        <v>165</v>
+      </c>
+      <c r="D529" s="0">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" s="0" t="s">
+        <v>1131</v>
+      </c>
+      <c r="B530" s="0" t="s">
+        <v>1132</v>
+      </c>
+      <c r="C530" s="0" t="s">
         <v>145</v>
       </c>
-      <c r="D526" s="0">
+      <c r="D530" s="0">
         <v>495</v>
       </c>
     </row>

--- a/price_list.xlsx
+++ b/price_list.xlsx
@@ -5850,7 +5850,7 @@
         <v>386</v>
       </c>
       <c r="D172" s="0">
-        <v>55058.9</v>
+        <v>48270</v>
       </c>
     </row>
     <row r="173">
@@ -6060,7 +6060,7 @@
         <v>386</v>
       </c>
       <c r="D187" s="0">
-        <v>37527.35</v>
+        <v>38813.17</v>
       </c>
     </row>
     <row r="188">
@@ -10176,7 +10176,7 @@
         <v>386</v>
       </c>
       <c r="D481" s="0">
-        <v>65142.6</v>
+        <v>69890</v>
       </c>
     </row>
     <row r="482">
@@ -10190,7 +10190,7 @@
         <v>386</v>
       </c>
       <c r="D482" s="0">
-        <v>23482.7</v>
+        <v>25194.62</v>
       </c>
     </row>
     <row r="483">
@@ -10722,7 +10722,7 @@
         <v>386</v>
       </c>
       <c r="D520" s="0">
-        <v>77429.29</v>
+        <v>80241.15</v>
       </c>
     </row>
     <row r="521">
@@ -10736,7 +10736,7 @@
         <v>386</v>
       </c>
       <c r="D521" s="0">
-        <v>42913.42</v>
+        <v>44471.13</v>
       </c>
     </row>
     <row r="522">
@@ -10750,7 +10750,7 @@
         <v>386</v>
       </c>
       <c r="D522" s="0">
-        <v>88806.25</v>
+        <v>92031.39</v>
       </c>
     </row>
     <row r="523">
@@ -10764,7 +10764,7 @@
         <v>386</v>
       </c>
       <c r="D523" s="0">
-        <v>50781.52</v>
+        <v>52574</v>
       </c>
     </row>
     <row r="524">

--- a/price_list.xlsx
+++ b/price_list.xlsx
@@ -605,7 +605,7 @@
     <t>000023816</t>
   </si>
   <si>
-    <t>BOLSA COLECTORA ORINA K207 X 2LT C/2 GANCHOS - 000023816</t>
+    <t xml:space="preserve">BOLSA COLEC. ORINA  X 2 LT C/2 GANCH EUROMIX - 000023816</t>
   </si>
   <si>
     <t>000022350</t>
@@ -722,34 +722,40 @@
     <t>CATETER INTRAVENOSO 24G EUROMIX - 000023789</t>
   </si>
   <si>
+    <t>000024042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CEFALEXINA 500 MG COMP X 8  BUTEFINA - 000024042</t>
+  </si>
+  <si>
+    <t>000006382</t>
+  </si>
+  <si>
+    <t>CEFALEXINA 500 mg/5 ml Oral Susp. x 90 ml VELEXINA - 000006382</t>
+  </si>
+  <si>
+    <t>000000715</t>
+  </si>
+  <si>
+    <t>CEFALEXINA RICHET 1g Blst. Comp. x 8 - 000000715</t>
+  </si>
+  <si>
+    <t>000000720</t>
+  </si>
+  <si>
+    <t>CEFALEXINA RICHET 500mg Oral Polvo p/ Susp. x 12 Dosis x 60ml - 000000720</t>
+  </si>
+  <si>
+    <t>000000722</t>
+  </si>
+  <si>
+    <t>CEFALEXINA RICHET 500mg Oral Polvo p/ Susp. x 18 Dosis x 90ml - 000000722</t>
+  </si>
+  <si>
     <t>000000725</t>
   </si>
   <si>
-    <t>CEFADE 1000mg F.Amp. x 1 - 000000725</t>
-  </si>
-  <si>
-    <t>000024042</t>
-  </si>
-  <si>
-    <t>CEFALEXINA 500 X 8 - BUTEFINA - 000024042</t>
-  </si>
-  <si>
-    <t>000000715</t>
-  </si>
-  <si>
-    <t>CEFALEXINA RICHET 1g Blst. Comp. x 8 - 000000715</t>
-  </si>
-  <si>
-    <t>000000720</t>
-  </si>
-  <si>
-    <t>CEFALEXINA RICHET 500mg Oral Polvo p/ Susp. x 12 Dosis x 60ml - 000000720</t>
-  </si>
-  <si>
-    <t>000000722</t>
-  </si>
-  <si>
-    <t>CEFALEXINA RICHET 500mg Oral Polvo p/ Susp. x 18 Dosis x 90ml - 000000722</t>
+    <t>CEFALOTINA KLONAL 1000 mg F.Amp. x 1 - 000000725</t>
   </si>
   <si>
     <t>000024639</t>
@@ -785,16 +791,16 @@
     <t xml:space="preserve">CEFTRIAXONA DRAWER 1G INY. F.AMP. X   1 - 000023383</t>
   </si>
   <si>
+    <t>000020342</t>
+  </si>
+  <si>
+    <t>CEFTRIAXONA KLONAL 1000 MG F.AMP. X 1 - 000020342</t>
+  </si>
+  <si>
     <t>000024300</t>
   </si>
   <si>
-    <t xml:space="preserve">CEFTRIAXONA MORGAN 1G INY. F.AMP. X   1 - 000024300</t>
-  </si>
-  <si>
-    <t>000020342</t>
-  </si>
-  <si>
-    <t>CEFTRIAZ 1000MG F.AMP. X 1 - 000020342</t>
+    <t xml:space="preserve">CEFTRIAXONA LARJAN 1 GR  F.AMP. X   1 - 000024300</t>
   </si>
   <si>
     <t>123665412</t>
@@ -3267,12 +3273,6 @@
   </si>
   <si>
     <t>VELEXINA 250mg /5ml Oral Susp. x 90ml - 000006380</t>
-  </si>
-  <si>
-    <t>000006382</t>
-  </si>
-  <si>
-    <t>VELEXINA 500mg /5ml Oral Susp. x 90ml - 000006382</t>
   </si>
   <si>
     <t>990102972</t>
@@ -4881,10 +4881,10 @@
         <v>237</v>
       </c>
       <c r="C103" s="0" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D103" s="0">
-        <v>1760</v>
+        <v>1117.4</v>
       </c>
     </row>
     <row r="104">
@@ -4895,10 +4895,10 @@
         <v>239</v>
       </c>
       <c r="C104" s="0" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D104" s="0">
-        <v>1117.4</v>
+        <v>3850</v>
       </c>
     </row>
     <row r="105">
@@ -4951,10 +4951,10 @@
         <v>247</v>
       </c>
       <c r="C108" s="0" t="s">
-        <v>123</v>
+        <v>15</v>
       </c>
       <c r="D108" s="0">
-        <v>1810</v>
+        <v>1760</v>
       </c>
     </row>
     <row r="109">
@@ -4965,24 +4965,24 @@
         <v>249</v>
       </c>
       <c r="C109" s="0" t="s">
-        <v>250</v>
+        <v>123</v>
       </c>
       <c r="D109" s="0">
-        <v>1800</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="0" t="s">
+        <v>250</v>
+      </c>
+      <c r="B110" s="0" t="s">
         <v>251</v>
       </c>
-      <c r="B110" s="0" t="s">
+      <c r="C110" s="0" t="s">
         <v>252</v>
       </c>
-      <c r="C110" s="0" t="s">
-        <v>15</v>
-      </c>
       <c r="D110" s="0">
-        <v>1600</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="111">
@@ -4996,7 +4996,7 @@
         <v>15</v>
       </c>
       <c r="D111" s="0">
-        <v>1800</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="112">
@@ -5007,10 +5007,10 @@
         <v>256</v>
       </c>
       <c r="C112" s="0" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="D112" s="0">
-        <v>1600</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="113">
@@ -5021,10 +5021,10 @@
         <v>258</v>
       </c>
       <c r="C113" s="0" t="s">
-        <v>123</v>
+        <v>34</v>
       </c>
       <c r="D113" s="0">
-        <v>1900</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="114">
@@ -5049,10 +5049,10 @@
         <v>262</v>
       </c>
       <c r="C115" s="0" t="s">
-        <v>45</v>
+        <v>123</v>
       </c>
       <c r="D115" s="0">
-        <v>5556.47</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="116">
@@ -5063,10 +5063,10 @@
         <v>264</v>
       </c>
       <c r="C116" s="0" t="s">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="D116" s="0">
-        <v>975</v>
+        <v>5556.47</v>
       </c>
     </row>
     <row r="117">
@@ -5077,10 +5077,10 @@
         <v>266</v>
       </c>
       <c r="C117" s="0" t="s">
-        <v>145</v>
+        <v>18</v>
       </c>
       <c r="D117" s="0">
-        <v>970</v>
+        <v>975</v>
       </c>
     </row>
     <row r="118">
@@ -5091,24 +5091,24 @@
         <v>268</v>
       </c>
       <c r="C118" s="0" t="s">
-        <v>269</v>
+        <v>145</v>
       </c>
       <c r="D118" s="0">
-        <v>2800</v>
+        <v>970</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="0" t="s">
+        <v>269</v>
+      </c>
+      <c r="B119" s="0" t="s">
         <v>270</v>
       </c>
-      <c r="B119" s="0" t="s">
+      <c r="C119" s="0" t="s">
         <v>271</v>
       </c>
-      <c r="C119" s="0" t="s">
-        <v>269</v>
-      </c>
       <c r="D119" s="0">
-        <v>4525.4</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="120">
@@ -5119,10 +5119,10 @@
         <v>273</v>
       </c>
       <c r="C120" s="0" t="s">
-        <v>21</v>
+        <v>271</v>
       </c>
       <c r="D120" s="0">
-        <v>2954</v>
+        <v>4525.4</v>
       </c>
     </row>
     <row r="121">
@@ -5133,10 +5133,10 @@
         <v>275</v>
       </c>
       <c r="C121" s="0" t="s">
-        <v>97</v>
+        <v>21</v>
       </c>
       <c r="D121" s="0">
-        <v>11313.5</v>
+        <v>2954</v>
       </c>
     </row>
     <row r="122">
@@ -5147,10 +5147,10 @@
         <v>277</v>
       </c>
       <c r="C122" s="0" t="s">
-        <v>34</v>
+        <v>97</v>
       </c>
       <c r="D122" s="0">
-        <v>2200</v>
+        <v>11313.5</v>
       </c>
     </row>
     <row r="123">
@@ -5161,10 +5161,10 @@
         <v>279</v>
       </c>
       <c r="C123" s="0" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D123" s="0">
-        <v>2400</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="124">
@@ -5175,10 +5175,10 @@
         <v>281</v>
       </c>
       <c r="C124" s="0" t="s">
-        <v>97</v>
+        <v>37</v>
       </c>
       <c r="D124" s="0">
-        <v>212.96</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="125">
@@ -5189,21 +5189,21 @@
         <v>283</v>
       </c>
       <c r="C125" s="0" t="s">
-        <v>284</v>
+        <v>97</v>
       </c>
       <c r="D125" s="0">
-        <v>0</v>
+        <v>212.96</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="0" t="s">
+        <v>284</v>
+      </c>
+      <c r="B126" s="0" t="s">
         <v>285</v>
       </c>
-      <c r="B126" s="0" t="s">
+      <c r="C126" s="0" t="s">
         <v>286</v>
-      </c>
-      <c r="C126" s="0" t="s">
-        <v>284</v>
       </c>
       <c r="D126" s="0">
         <v>0</v>
@@ -5217,21 +5217,21 @@
         <v>288</v>
       </c>
       <c r="C127" s="0" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="D127" s="0">
-        <v>520</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="0" t="s">
+        <v>289</v>
+      </c>
+      <c r="B128" s="0" t="s">
         <v>290</v>
       </c>
-      <c r="B128" s="0" t="s">
+      <c r="C128" s="0" t="s">
         <v>291</v>
-      </c>
-      <c r="C128" s="0" t="s">
-        <v>34</v>
       </c>
       <c r="D128" s="0">
         <v>520</v>
@@ -5245,10 +5245,10 @@
         <v>293</v>
       </c>
       <c r="C129" s="0" t="s">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="D129" s="0">
-        <v>22</v>
+        <v>520</v>
       </c>
     </row>
     <row r="130">
@@ -5259,10 +5259,10 @@
         <v>295</v>
       </c>
       <c r="C130" s="0" t="s">
-        <v>15</v>
+        <v>52</v>
       </c>
       <c r="D130" s="0">
-        <v>3200</v>
+        <v>22</v>
       </c>
     </row>
     <row r="131">
@@ -5273,10 +5273,10 @@
         <v>297</v>
       </c>
       <c r="C131" s="0" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="D131" s="0">
-        <v>7377.5</v>
+        <v>3200</v>
       </c>
     </row>
     <row r="132">
@@ -5287,24 +5287,24 @@
         <v>299</v>
       </c>
       <c r="C132" s="0" t="s">
-        <v>300</v>
+        <v>28</v>
       </c>
       <c r="D132" s="0">
-        <v>16095</v>
+        <v>7377.5</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="0" t="s">
+        <v>300</v>
+      </c>
+      <c r="B133" s="0" t="s">
         <v>301</v>
       </c>
-      <c r="B133" s="0" t="s">
+      <c r="C133" s="0" t="s">
         <v>302</v>
       </c>
-      <c r="C133" s="0" t="s">
-        <v>145</v>
-      </c>
       <c r="D133" s="0">
-        <v>3100</v>
+        <v>16095</v>
       </c>
     </row>
     <row r="134">
@@ -5318,7 +5318,7 @@
         <v>145</v>
       </c>
       <c r="D134" s="0">
-        <v>6700</v>
+        <v>3100</v>
       </c>
     </row>
     <row r="135">
@@ -5329,10 +5329,10 @@
         <v>306</v>
       </c>
       <c r="C135" s="0" t="s">
-        <v>15</v>
+        <v>145</v>
       </c>
       <c r="D135" s="0">
-        <v>4200</v>
+        <v>6700</v>
       </c>
     </row>
     <row r="136">
@@ -5346,7 +5346,7 @@
         <v>15</v>
       </c>
       <c r="D136" s="0">
-        <v>1050</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="137">
@@ -5357,21 +5357,21 @@
         <v>310</v>
       </c>
       <c r="C137" s="0" t="s">
-        <v>311</v>
+        <v>15</v>
       </c>
       <c r="D137" s="0">
-        <v>3350</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="0" t="s">
+        <v>311</v>
+      </c>
+      <c r="B138" s="0" t="s">
         <v>312</v>
       </c>
-      <c r="B138" s="0" t="s">
+      <c r="C138" s="0" t="s">
         <v>313</v>
-      </c>
-      <c r="C138" s="0" t="s">
-        <v>128</v>
       </c>
       <c r="D138" s="0">
         <v>3350</v>
@@ -5385,24 +5385,24 @@
         <v>315</v>
       </c>
       <c r="C139" s="0" t="s">
-        <v>316</v>
+        <v>128</v>
       </c>
       <c r="D139" s="0">
-        <v>0</v>
+        <v>3350</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="0" t="s">
+        <v>316</v>
+      </c>
+      <c r="B140" s="0" t="s">
         <v>317</v>
       </c>
-      <c r="B140" s="0" t="s">
+      <c r="C140" s="0" t="s">
         <v>318</v>
       </c>
-      <c r="C140" s="0" t="s">
-        <v>18</v>
-      </c>
       <c r="D140" s="0">
-        <v>589.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="141">
@@ -5413,10 +5413,10 @@
         <v>320</v>
       </c>
       <c r="C141" s="0" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D141" s="0">
-        <v>1600</v>
+        <v>589.9</v>
       </c>
     </row>
     <row r="142">
@@ -5430,7 +5430,7 @@
         <v>15</v>
       </c>
       <c r="D142" s="0">
-        <v>2000</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="143">
@@ -5441,24 +5441,24 @@
         <v>324</v>
       </c>
       <c r="C143" s="0" t="s">
-        <v>325</v>
+        <v>15</v>
       </c>
       <c r="D143" s="0">
-        <v>2728</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="0" t="s">
+        <v>325</v>
+      </c>
+      <c r="B144" s="0" t="s">
         <v>326</v>
       </c>
-      <c r="B144" s="0" t="s">
+      <c r="C144" s="0" t="s">
         <v>327</v>
       </c>
-      <c r="C144" s="0" t="s">
-        <v>75</v>
-      </c>
       <c r="D144" s="0">
-        <v>89185.6</v>
+        <v>2728</v>
       </c>
     </row>
     <row r="145">
@@ -5486,7 +5486,7 @@
         <v>75</v>
       </c>
       <c r="D146" s="0">
-        <v>126551.04</v>
+        <v>89185.6</v>
       </c>
     </row>
     <row r="147">
@@ -5497,10 +5497,10 @@
         <v>333</v>
       </c>
       <c r="C147" s="0" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="D147" s="0">
-        <v>1785</v>
+        <v>126551.04</v>
       </c>
     </row>
     <row r="148">
@@ -5514,7 +5514,7 @@
         <v>52</v>
       </c>
       <c r="D148" s="0">
-        <v>2058</v>
+        <v>1785</v>
       </c>
     </row>
     <row r="149">
@@ -5525,10 +5525,10 @@
         <v>337</v>
       </c>
       <c r="C149" s="0" t="s">
-        <v>15</v>
+        <v>52</v>
       </c>
       <c r="D149" s="0">
-        <v>1270</v>
+        <v>2058</v>
       </c>
     </row>
     <row r="150">
@@ -5539,10 +5539,10 @@
         <v>339</v>
       </c>
       <c r="C150" s="0" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="D150" s="0">
-        <v>550</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="151">
@@ -5553,7 +5553,7 @@
         <v>341</v>
       </c>
       <c r="C151" s="0" t="s">
-        <v>75</v>
+        <v>31</v>
       </c>
       <c r="D151" s="0">
         <v>550</v>
@@ -5567,7 +5567,7 @@
         <v>343</v>
       </c>
       <c r="C152" s="0" t="s">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="D152" s="0">
         <v>550</v>
@@ -5581,10 +5581,10 @@
         <v>345</v>
       </c>
       <c r="C153" s="0" t="s">
-        <v>97</v>
+        <v>34</v>
       </c>
       <c r="D153" s="0">
-        <v>1663.75</v>
+        <v>550</v>
       </c>
     </row>
     <row r="154">
@@ -5595,24 +5595,24 @@
         <v>347</v>
       </c>
       <c r="C154" s="0" t="s">
-        <v>348</v>
+        <v>97</v>
       </c>
       <c r="D154" s="0">
-        <v>4500</v>
+        <v>1663.75</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="0" t="s">
+        <v>348</v>
+      </c>
+      <c r="B155" s="0" t="s">
         <v>349</v>
       </c>
-      <c r="B155" s="0" t="s">
+      <c r="C155" s="0" t="s">
         <v>350</v>
       </c>
-      <c r="C155" s="0" t="s">
-        <v>34</v>
-      </c>
       <c r="D155" s="0">
-        <v>390</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="156">
@@ -5623,10 +5623,10 @@
         <v>352</v>
       </c>
       <c r="C156" s="0" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="D156" s="0">
-        <v>500</v>
+        <v>390</v>
       </c>
     </row>
     <row r="157">
@@ -5637,10 +5637,10 @@
         <v>354</v>
       </c>
       <c r="C157" s="0" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="D157" s="0">
-        <v>380</v>
+        <v>500</v>
       </c>
     </row>
     <row r="158">
@@ -5651,7 +5651,7 @@
         <v>356</v>
       </c>
       <c r="C158" s="0" t="s">
-        <v>75</v>
+        <v>34</v>
       </c>
       <c r="D158" s="0">
         <v>380</v>
@@ -5668,7 +5668,7 @@
         <v>75</v>
       </c>
       <c r="D159" s="0">
-        <v>580</v>
+        <v>380</v>
       </c>
     </row>
     <row r="160">
@@ -5679,10 +5679,10 @@
         <v>360</v>
       </c>
       <c r="C160" s="0" t="s">
-        <v>15</v>
+        <v>75</v>
       </c>
       <c r="D160" s="0">
-        <v>572</v>
+        <v>580</v>
       </c>
     </row>
     <row r="161">
@@ -5693,10 +5693,10 @@
         <v>362</v>
       </c>
       <c r="C161" s="0" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="D161" s="0">
-        <v>106950.8</v>
+        <v>572</v>
       </c>
     </row>
     <row r="162">
@@ -5710,7 +5710,7 @@
         <v>28</v>
       </c>
       <c r="D162" s="0">
-        <v>118372.7</v>
+        <v>106950.8</v>
       </c>
     </row>
     <row r="163">
@@ -5724,7 +5724,7 @@
         <v>28</v>
       </c>
       <c r="D163" s="0">
-        <v>140178.2</v>
+        <v>118372.7</v>
       </c>
     </row>
     <row r="164">
@@ -5735,24 +5735,24 @@
         <v>368</v>
       </c>
       <c r="C164" s="0" t="s">
-        <v>369</v>
+        <v>28</v>
       </c>
       <c r="D164" s="0">
-        <v>650</v>
+        <v>140178.2</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="0" t="s">
+        <v>369</v>
+      </c>
+      <c r="B165" s="0" t="s">
         <v>370</v>
       </c>
-      <c r="B165" s="0" t="s">
+      <c r="C165" s="0" t="s">
         <v>371</v>
       </c>
-      <c r="C165" s="0" t="s">
-        <v>115</v>
-      </c>
       <c r="D165" s="0">
-        <v>1590</v>
+        <v>650</v>
       </c>
     </row>
     <row r="166">
@@ -5763,10 +5763,10 @@
         <v>373</v>
       </c>
       <c r="C166" s="0" t="s">
-        <v>34</v>
+        <v>115</v>
       </c>
       <c r="D166" s="0">
-        <v>550</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="167">
@@ -5777,7 +5777,7 @@
         <v>375</v>
       </c>
       <c r="C167" s="0" t="s">
-        <v>156</v>
+        <v>34</v>
       </c>
       <c r="D167" s="0">
         <v>550</v>
@@ -5791,7 +5791,7 @@
         <v>377</v>
       </c>
       <c r="C168" s="0" t="s">
-        <v>15</v>
+        <v>156</v>
       </c>
       <c r="D168" s="0">
         <v>550</v>
@@ -5808,7 +5808,7 @@
         <v>15</v>
       </c>
       <c r="D169" s="0">
-        <v>1700</v>
+        <v>550</v>
       </c>
     </row>
     <row r="170">
@@ -5822,7 +5822,7 @@
         <v>15</v>
       </c>
       <c r="D170" s="0">
-        <v>0</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="171">
@@ -5833,10 +5833,10 @@
         <v>383</v>
       </c>
       <c r="C171" s="0" t="s">
-        <v>120</v>
+        <v>15</v>
       </c>
       <c r="D171" s="0">
-        <v>1290</v>
+        <v>0</v>
       </c>
     </row>
     <row r="172">
@@ -5847,38 +5847,38 @@
         <v>385</v>
       </c>
       <c r="C172" s="0" t="s">
-        <v>386</v>
+        <v>120</v>
       </c>
       <c r="D172" s="0">
-        <v>48270</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="0" t="s">
+        <v>386</v>
+      </c>
+      <c r="B173" s="0" t="s">
         <v>387</v>
       </c>
-      <c r="B173" s="0" t="s">
+      <c r="C173" s="0" t="s">
         <v>388</v>
       </c>
-      <c r="C173" s="0" t="s">
-        <v>389</v>
-      </c>
       <c r="D173" s="0">
-        <v>104695.98</v>
+        <v>48270</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="0" t="s">
+        <v>389</v>
+      </c>
+      <c r="B174" s="0" t="s">
         <v>390</v>
       </c>
-      <c r="B174" s="0" t="s">
+      <c r="C174" s="0" t="s">
         <v>391</v>
       </c>
-      <c r="C174" s="0" t="s">
-        <v>389</v>
-      </c>
       <c r="D174" s="0">
-        <v>80478.92</v>
+        <v>104695.98</v>
       </c>
     </row>
     <row r="175">
@@ -5889,10 +5889,10 @@
         <v>393</v>
       </c>
       <c r="C175" s="0" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="D175" s="0">
-        <v>92546.68</v>
+        <v>80478.92</v>
       </c>
     </row>
     <row r="176">
@@ -5903,10 +5903,10 @@
         <v>395</v>
       </c>
       <c r="C176" s="0" t="s">
-        <v>28</v>
+        <v>391</v>
       </c>
       <c r="D176" s="0">
-        <v>972.9</v>
+        <v>92546.68</v>
       </c>
     </row>
     <row r="177">
@@ -5920,7 +5920,7 @@
         <v>28</v>
       </c>
       <c r="D177" s="0">
-        <v>265.3</v>
+        <v>972.9</v>
       </c>
     </row>
     <row r="178">
@@ -5934,7 +5934,7 @@
         <v>28</v>
       </c>
       <c r="D178" s="0">
-        <v>2908.78</v>
+        <v>265.3</v>
       </c>
     </row>
     <row r="179">
@@ -5945,24 +5945,24 @@
         <v>401</v>
       </c>
       <c r="C179" s="0" t="s">
-        <v>402</v>
+        <v>28</v>
       </c>
       <c r="D179" s="0">
-        <v>61</v>
+        <v>2908.78</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="0" t="s">
+        <v>402</v>
+      </c>
+      <c r="B180" s="0" t="s">
         <v>403</v>
       </c>
-      <c r="B180" s="0" t="s">
+      <c r="C180" s="0" t="s">
         <v>404</v>
       </c>
-      <c r="C180" s="0" t="s">
-        <v>18</v>
-      </c>
       <c r="D180" s="0">
-        <v>270</v>
+        <v>61</v>
       </c>
     </row>
     <row r="181">
@@ -5973,10 +5973,10 @@
         <v>406</v>
       </c>
       <c r="C181" s="0" t="s">
-        <v>156</v>
+        <v>18</v>
       </c>
       <c r="D181" s="0">
-        <v>257</v>
+        <v>270</v>
       </c>
     </row>
     <row r="182">
@@ -5987,10 +5987,10 @@
         <v>408</v>
       </c>
       <c r="C182" s="0" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="D182" s="0">
-        <v>2859</v>
+        <v>257</v>
       </c>
     </row>
     <row r="183">
@@ -6004,7 +6004,7 @@
         <v>145</v>
       </c>
       <c r="D183" s="0">
-        <v>3573.45</v>
+        <v>2859</v>
       </c>
     </row>
     <row r="184">
@@ -6015,10 +6015,10 @@
         <v>412</v>
       </c>
       <c r="C184" s="0" t="s">
-        <v>15</v>
+        <v>145</v>
       </c>
       <c r="D184" s="0">
-        <v>1550</v>
+        <v>3573.45</v>
       </c>
     </row>
     <row r="185">
@@ -6032,7 +6032,7 @@
         <v>15</v>
       </c>
       <c r="D185" s="0">
-        <v>750</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="186">
@@ -6043,10 +6043,10 @@
         <v>416</v>
       </c>
       <c r="C186" s="0" t="s">
-        <v>128</v>
+        <v>15</v>
       </c>
       <c r="D186" s="0">
-        <v>5218</v>
+        <v>750</v>
       </c>
     </row>
     <row r="187">
@@ -6057,10 +6057,10 @@
         <v>418</v>
       </c>
       <c r="C187" s="0" t="s">
-        <v>386</v>
+        <v>128</v>
       </c>
       <c r="D187" s="0">
-        <v>38813.17</v>
+        <v>5218</v>
       </c>
     </row>
     <row r="188">
@@ -6071,10 +6071,10 @@
         <v>420</v>
       </c>
       <c r="C188" s="0" t="s">
-        <v>18</v>
+        <v>388</v>
       </c>
       <c r="D188" s="0">
-        <v>825.18</v>
+        <v>38813.17</v>
       </c>
     </row>
     <row r="189">
@@ -6088,7 +6088,7 @@
         <v>18</v>
       </c>
       <c r="D189" s="0">
-        <v>2687.98</v>
+        <v>825.18</v>
       </c>
     </row>
     <row r="190">
@@ -6102,7 +6102,7 @@
         <v>18</v>
       </c>
       <c r="D190" s="0">
-        <v>6764.67</v>
+        <v>2687.98</v>
       </c>
     </row>
     <row r="191">
@@ -6116,7 +6116,7 @@
         <v>18</v>
       </c>
       <c r="D191" s="0">
-        <v>353.46</v>
+        <v>6764.67</v>
       </c>
     </row>
     <row r="192">
@@ -6130,7 +6130,7 @@
         <v>18</v>
       </c>
       <c r="D192" s="0">
-        <v>10799.76</v>
+        <v>353.46</v>
       </c>
     </row>
     <row r="193">
@@ -6144,7 +6144,7 @@
         <v>18</v>
       </c>
       <c r="D193" s="0">
-        <v>3939.57</v>
+        <v>10799.76</v>
       </c>
     </row>
     <row r="194">
@@ -6158,7 +6158,7 @@
         <v>18</v>
       </c>
       <c r="D194" s="0">
-        <v>412.8</v>
+        <v>3939.57</v>
       </c>
     </row>
     <row r="195">
@@ -6172,7 +6172,7 @@
         <v>18</v>
       </c>
       <c r="D195" s="0">
-        <v>320</v>
+        <v>412.8</v>
       </c>
     </row>
     <row r="196">
@@ -6186,7 +6186,7 @@
         <v>18</v>
       </c>
       <c r="D196" s="0">
-        <v>2184.81</v>
+        <v>320</v>
       </c>
     </row>
     <row r="197">
@@ -6197,10 +6197,10 @@
         <v>438</v>
       </c>
       <c r="C197" s="0" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D197" s="0">
-        <v>9748.5</v>
+        <v>2184.81</v>
       </c>
     </row>
     <row r="198">
@@ -6211,10 +6211,10 @@
         <v>440</v>
       </c>
       <c r="C198" s="0" t="s">
-        <v>75</v>
+        <v>28</v>
       </c>
       <c r="D198" s="0">
-        <v>430</v>
+        <v>9748.5</v>
       </c>
     </row>
     <row r="199">
@@ -6228,7 +6228,7 @@
         <v>75</v>
       </c>
       <c r="D199" s="0">
-        <v>800</v>
+        <v>430</v>
       </c>
     </row>
     <row r="200">
@@ -6239,10 +6239,10 @@
         <v>444</v>
       </c>
       <c r="C200" s="0" t="s">
-        <v>250</v>
+        <v>75</v>
       </c>
       <c r="D200" s="0">
-        <v>2040</v>
+        <v>800</v>
       </c>
     </row>
     <row r="201">
@@ -6253,10 +6253,10 @@
         <v>446</v>
       </c>
       <c r="C201" s="0" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D201" s="0">
-        <v>1380</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="202">
@@ -6267,10 +6267,10 @@
         <v>448</v>
       </c>
       <c r="C202" s="0" t="s">
-        <v>386</v>
+        <v>252</v>
       </c>
       <c r="D202" s="0">
-        <v>236458.17</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="203">
@@ -6281,10 +6281,10 @@
         <v>450</v>
       </c>
       <c r="C203" s="0" t="s">
-        <v>28</v>
+        <v>388</v>
       </c>
       <c r="D203" s="0">
-        <v>317.2</v>
+        <v>236458.17</v>
       </c>
     </row>
     <row r="204">
@@ -6295,10 +6295,10 @@
         <v>452</v>
       </c>
       <c r="C204" s="0" t="s">
-        <v>386</v>
+        <v>28</v>
       </c>
       <c r="D204" s="0">
-        <v>25100</v>
+        <v>317.2</v>
       </c>
     </row>
     <row r="205">
@@ -6309,24 +6309,24 @@
         <v>454</v>
       </c>
       <c r="C205" s="0" t="s">
-        <v>455</v>
+        <v>388</v>
       </c>
       <c r="D205" s="0">
-        <v>20900</v>
+        <v>25100</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="0" t="s">
+        <v>455</v>
+      </c>
+      <c r="B206" s="0" t="s">
         <v>456</v>
       </c>
-      <c r="B206" s="0" t="s">
+      <c r="C206" s="0" t="s">
         <v>457</v>
       </c>
-      <c r="C206" s="0" t="s">
-        <v>45</v>
-      </c>
       <c r="D206" s="0">
-        <v>6014.63</v>
+        <v>20900</v>
       </c>
     </row>
     <row r="207">
@@ -6337,10 +6337,10 @@
         <v>459</v>
       </c>
       <c r="C207" s="0" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="D207" s="0">
-        <v>1104.46</v>
+        <v>6014.63</v>
       </c>
     </row>
     <row r="208">
@@ -6351,10 +6351,10 @@
         <v>461</v>
       </c>
       <c r="C208" s="0" t="s">
-        <v>97</v>
+        <v>21</v>
       </c>
       <c r="D208" s="0">
-        <v>11646.25</v>
+        <v>1104.46</v>
       </c>
     </row>
     <row r="209">
@@ -6365,10 +6365,10 @@
         <v>463</v>
       </c>
       <c r="C209" s="0" t="s">
-        <v>128</v>
+        <v>97</v>
       </c>
       <c r="D209" s="0">
-        <v>6072</v>
+        <v>11646.25</v>
       </c>
     </row>
     <row r="210">
@@ -6379,10 +6379,10 @@
         <v>465</v>
       </c>
       <c r="C210" s="0" t="s">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="D210" s="0">
-        <v>400</v>
+        <v>6072</v>
       </c>
     </row>
     <row r="211">
@@ -6393,10 +6393,10 @@
         <v>467</v>
       </c>
       <c r="C211" s="0" t="s">
-        <v>21</v>
+        <v>75</v>
       </c>
       <c r="D211" s="0">
-        <v>409</v>
+        <v>400</v>
       </c>
     </row>
     <row r="212">
@@ -6407,10 +6407,10 @@
         <v>469</v>
       </c>
       <c r="C212" s="0" t="s">
-        <v>69</v>
+        <v>21</v>
       </c>
       <c r="D212" s="0">
-        <v>10748</v>
+        <v>409</v>
       </c>
     </row>
     <row r="213">
@@ -6424,7 +6424,7 @@
         <v>69</v>
       </c>
       <c r="D213" s="0">
-        <v>12898</v>
+        <v>10748</v>
       </c>
     </row>
     <row r="214">
@@ -6435,10 +6435,10 @@
         <v>473</v>
       </c>
       <c r="C214" s="0" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="D214" s="0">
-        <v>2000</v>
+        <v>12898</v>
       </c>
     </row>
     <row r="215">
@@ -6449,24 +6449,24 @@
         <v>475</v>
       </c>
       <c r="C215" s="0" t="s">
-        <v>476</v>
+        <v>52</v>
       </c>
       <c r="D215" s="0">
-        <v>0</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="0" t="s">
+        <v>476</v>
+      </c>
+      <c r="B216" s="0" t="s">
         <v>477</v>
       </c>
-      <c r="B216" s="0" t="s">
+      <c r="C216" s="0" t="s">
         <v>478</v>
       </c>
-      <c r="C216" s="0" t="s">
-        <v>15</v>
-      </c>
       <c r="D216" s="0">
-        <v>490</v>
+        <v>0</v>
       </c>
     </row>
     <row r="217">
@@ -6477,10 +6477,10 @@
         <v>480</v>
       </c>
       <c r="C217" s="0" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="D217" s="0">
-        <v>0</v>
+        <v>490</v>
       </c>
     </row>
     <row r="218">
@@ -6491,10 +6491,10 @@
         <v>482</v>
       </c>
       <c r="C218" s="0" t="s">
-        <v>165</v>
+        <v>34</v>
       </c>
       <c r="D218" s="0">
-        <v>25676.62</v>
+        <v>0</v>
       </c>
     </row>
     <row r="219">
@@ -6505,24 +6505,24 @@
         <v>484</v>
       </c>
       <c r="C219" s="0" t="s">
-        <v>485</v>
+        <v>165</v>
       </c>
       <c r="D219" s="0">
-        <v>70443</v>
+        <v>25676.62</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="0" t="s">
+        <v>485</v>
+      </c>
+      <c r="B220" s="0" t="s">
         <v>486</v>
       </c>
-      <c r="B220" s="0" t="s">
+      <c r="C220" s="0" t="s">
         <v>487</v>
       </c>
-      <c r="C220" s="0" t="s">
-        <v>156</v>
-      </c>
       <c r="D220" s="0">
-        <v>1800</v>
+        <v>70443</v>
       </c>
     </row>
     <row r="221">
@@ -6533,10 +6533,10 @@
         <v>489</v>
       </c>
       <c r="C221" s="0" t="s">
-        <v>34</v>
+        <v>156</v>
       </c>
       <c r="D221" s="0">
-        <v>0</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="222">
@@ -6547,10 +6547,10 @@
         <v>491</v>
       </c>
       <c r="C222" s="0" t="s">
-        <v>145</v>
+        <v>34</v>
       </c>
       <c r="D222" s="0">
-        <v>492.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="223">
@@ -6561,10 +6561,10 @@
         <v>493</v>
       </c>
       <c r="C223" s="0" t="s">
-        <v>212</v>
+        <v>145</v>
       </c>
       <c r="D223" s="0">
-        <v>495</v>
+        <v>492.2</v>
       </c>
     </row>
     <row r="224">
@@ -6575,10 +6575,10 @@
         <v>495</v>
       </c>
       <c r="C224" s="0" t="s">
-        <v>18</v>
+        <v>212</v>
       </c>
       <c r="D224" s="0">
-        <v>1819.72</v>
+        <v>495</v>
       </c>
     </row>
     <row r="225">
@@ -6592,7 +6592,7 @@
         <v>18</v>
       </c>
       <c r="D225" s="0">
-        <v>4391.81</v>
+        <v>1819.72</v>
       </c>
     </row>
     <row r="226">
@@ -6603,21 +6603,21 @@
         <v>499</v>
       </c>
       <c r="C226" s="0" t="s">
-        <v>500</v>
+        <v>18</v>
       </c>
       <c r="D226" s="0">
-        <v>4100</v>
+        <v>4391.81</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="0" t="s">
+        <v>500</v>
+      </c>
+      <c r="B227" s="0" t="s">
         <v>501</v>
       </c>
-      <c r="B227" s="0" t="s">
+      <c r="C227" s="0" t="s">
         <v>502</v>
-      </c>
-      <c r="C227" s="0" t="s">
-        <v>500</v>
       </c>
       <c r="D227" s="0">
         <v>4100</v>
@@ -6631,7 +6631,7 @@
         <v>504</v>
       </c>
       <c r="C228" s="0" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="D228" s="0">
         <v>4100</v>
@@ -6645,10 +6645,10 @@
         <v>506</v>
       </c>
       <c r="C229" s="0" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="D229" s="0">
-        <v>4200</v>
+        <v>4100</v>
       </c>
     </row>
     <row r="230">
@@ -6659,10 +6659,10 @@
         <v>508</v>
       </c>
       <c r="C230" s="0" t="s">
-        <v>52</v>
+        <v>502</v>
       </c>
       <c r="D230" s="0">
-        <v>4700</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="231">
@@ -6673,10 +6673,10 @@
         <v>510</v>
       </c>
       <c r="C231" s="0" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="D231" s="0">
-        <v>235</v>
+        <v>4700</v>
       </c>
     </row>
     <row r="232">
@@ -6715,10 +6715,10 @@
         <v>516</v>
       </c>
       <c r="C234" s="0" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="D234" s="0">
-        <v>4670</v>
+        <v>235</v>
       </c>
     </row>
     <row r="235">
@@ -6757,21 +6757,21 @@
         <v>522</v>
       </c>
       <c r="C237" s="0" t="s">
-        <v>523</v>
+        <v>52</v>
       </c>
       <c r="D237" s="0">
-        <v>265</v>
+        <v>4670</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="0" t="s">
+        <v>523</v>
+      </c>
+      <c r="B238" s="0" t="s">
         <v>524</v>
       </c>
-      <c r="B238" s="0" t="s">
+      <c r="C238" s="0" t="s">
         <v>525</v>
-      </c>
-      <c r="C238" s="0" t="s">
-        <v>523</v>
       </c>
       <c r="D238" s="0">
         <v>265</v>
@@ -6785,7 +6785,7 @@
         <v>527</v>
       </c>
       <c r="C239" s="0" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="D239" s="0">
         <v>265</v>
@@ -6799,7 +6799,7 @@
         <v>529</v>
       </c>
       <c r="C240" s="0" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="D240" s="0">
         <v>265</v>
@@ -6813,7 +6813,7 @@
         <v>531</v>
       </c>
       <c r="C241" s="0" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="D241" s="0">
         <v>265</v>
@@ -6827,7 +6827,7 @@
         <v>533</v>
       </c>
       <c r="C242" s="0" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="D242" s="0">
         <v>265</v>
@@ -6841,21 +6841,21 @@
         <v>535</v>
       </c>
       <c r="C243" s="0" t="s">
-        <v>536</v>
+        <v>525</v>
       </c>
       <c r="D243" s="0">
-        <v>4700</v>
+        <v>265</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="0" t="s">
+        <v>536</v>
+      </c>
+      <c r="B244" s="0" t="s">
         <v>537</v>
       </c>
-      <c r="B244" s="0" t="s">
+      <c r="C244" s="0" t="s">
         <v>538</v>
-      </c>
-      <c r="C244" s="0" t="s">
-        <v>539</v>
       </c>
       <c r="D244" s="0">
         <v>4700</v>
@@ -6863,13 +6863,13 @@
     </row>
     <row r="245">
       <c r="A245" s="0" t="s">
+        <v>539</v>
+      </c>
+      <c r="B245" s="0" t="s">
         <v>540</v>
       </c>
-      <c r="B245" s="0" t="s">
+      <c r="C245" s="0" t="s">
         <v>541</v>
-      </c>
-      <c r="C245" s="0" t="s">
-        <v>52</v>
       </c>
       <c r="D245" s="0">
         <v>4700</v>
@@ -6886,7 +6886,7 @@
         <v>52</v>
       </c>
       <c r="D246" s="0">
-        <v>597</v>
+        <v>4700</v>
       </c>
     </row>
     <row r="247">
@@ -6900,7 +6900,7 @@
         <v>52</v>
       </c>
       <c r="D247" s="0">
-        <v>223</v>
+        <v>597</v>
       </c>
     </row>
     <row r="248">
@@ -6914,7 +6914,7 @@
         <v>52</v>
       </c>
       <c r="D248" s="0">
-        <v>247</v>
+        <v>223</v>
       </c>
     </row>
     <row r="249">
@@ -6925,10 +6925,10 @@
         <v>549</v>
       </c>
       <c r="C249" s="0" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="D249" s="0">
-        <v>5600</v>
+        <v>247</v>
       </c>
     </row>
     <row r="250">
@@ -6939,10 +6939,10 @@
         <v>551</v>
       </c>
       <c r="C250" s="0" t="s">
-        <v>156</v>
+        <v>37</v>
       </c>
       <c r="D250" s="0">
-        <v>6000</v>
+        <v>5600</v>
       </c>
     </row>
     <row r="251">
@@ -6953,10 +6953,10 @@
         <v>553</v>
       </c>
       <c r="C251" s="0" t="s">
-        <v>75</v>
+        <v>156</v>
       </c>
       <c r="D251" s="0">
-        <v>80000</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="252">
@@ -6970,7 +6970,7 @@
         <v>75</v>
       </c>
       <c r="D252" s="0">
-        <v>110000</v>
+        <v>80000</v>
       </c>
     </row>
     <row r="253">
@@ -6984,7 +6984,7 @@
         <v>75</v>
       </c>
       <c r="D253" s="0">
-        <v>130000</v>
+        <v>110000</v>
       </c>
     </row>
     <row r="254">
@@ -6995,10 +6995,10 @@
         <v>559</v>
       </c>
       <c r="C254" s="0" t="s">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="D254" s="0">
-        <v>900</v>
+        <v>130000</v>
       </c>
     </row>
     <row r="255">
@@ -7009,10 +7009,10 @@
         <v>561</v>
       </c>
       <c r="C255" s="0" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="D255" s="0">
-        <v>1100</v>
+        <v>900</v>
       </c>
     </row>
     <row r="256">
@@ -7026,7 +7026,7 @@
         <v>15</v>
       </c>
       <c r="D256" s="0">
-        <v>2500</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="257">
@@ -7037,10 +7037,10 @@
         <v>565</v>
       </c>
       <c r="C257" s="0" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="D257" s="0">
-        <v>14608.16</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="258">
@@ -7051,10 +7051,10 @@
         <v>567</v>
       </c>
       <c r="C258" s="0" t="s">
-        <v>156</v>
+        <v>28</v>
       </c>
       <c r="D258" s="0">
-        <v>700</v>
+        <v>14608.16</v>
       </c>
     </row>
     <row r="259">
@@ -7065,7 +7065,7 @@
         <v>569</v>
       </c>
       <c r="C259" s="0" t="s">
-        <v>37</v>
+        <v>156</v>
       </c>
       <c r="D259" s="0">
         <v>700</v>
@@ -7079,10 +7079,10 @@
         <v>571</v>
       </c>
       <c r="C260" s="0" t="s">
-        <v>289</v>
+        <v>37</v>
       </c>
       <c r="D260" s="0">
-        <v>450</v>
+        <v>700</v>
       </c>
     </row>
     <row r="261">
@@ -7093,10 +7093,10 @@
         <v>573</v>
       </c>
       <c r="C261" s="0" t="s">
-        <v>15</v>
+        <v>291</v>
       </c>
       <c r="D261" s="0">
-        <v>555</v>
+        <v>450</v>
       </c>
     </row>
     <row r="262">
@@ -7110,7 +7110,7 @@
         <v>15</v>
       </c>
       <c r="D262" s="0">
-        <v>825</v>
+        <v>555</v>
       </c>
     </row>
     <row r="263">
@@ -7124,7 +7124,7 @@
         <v>15</v>
       </c>
       <c r="D263" s="0">
-        <v>36.3</v>
+        <v>825</v>
       </c>
     </row>
     <row r="264">
@@ -7138,7 +7138,7 @@
         <v>15</v>
       </c>
       <c r="D264" s="0">
-        <v>544.5</v>
+        <v>36.3</v>
       </c>
     </row>
     <row r="265">
@@ -7152,7 +7152,7 @@
         <v>15</v>
       </c>
       <c r="D265" s="0">
-        <v>750</v>
+        <v>544.5</v>
       </c>
     </row>
     <row r="266">
@@ -7163,10 +7163,10 @@
         <v>583</v>
       </c>
       <c r="C266" s="0" t="s">
-        <v>156</v>
+        <v>15</v>
       </c>
       <c r="D266" s="0">
-        <v>1130</v>
+        <v>750</v>
       </c>
     </row>
     <row r="267">
@@ -7177,10 +7177,10 @@
         <v>585</v>
       </c>
       <c r="C267" s="0" t="s">
-        <v>52</v>
+        <v>156</v>
       </c>
       <c r="D267" s="0">
-        <v>4510</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="268">
@@ -7233,10 +7233,10 @@
         <v>593</v>
       </c>
       <c r="C271" s="0" t="s">
-        <v>15</v>
+        <v>52</v>
       </c>
       <c r="D271" s="0">
-        <v>902</v>
+        <v>4510</v>
       </c>
     </row>
     <row r="272">
@@ -7250,7 +7250,7 @@
         <v>15</v>
       </c>
       <c r="D272" s="0">
-        <v>880</v>
+        <v>902</v>
       </c>
     </row>
     <row r="273">
@@ -7261,10 +7261,10 @@
         <v>597</v>
       </c>
       <c r="C273" s="0" t="s">
-        <v>145</v>
+        <v>15</v>
       </c>
       <c r="D273" s="0">
-        <v>446</v>
+        <v>880</v>
       </c>
     </row>
     <row r="274">
@@ -7278,7 +7278,7 @@
         <v>145</v>
       </c>
       <c r="D274" s="0">
-        <v>370</v>
+        <v>446</v>
       </c>
     </row>
     <row r="275">
@@ -7289,10 +7289,10 @@
         <v>601</v>
       </c>
       <c r="C275" s="0" t="s">
-        <v>18</v>
+        <v>145</v>
       </c>
       <c r="D275" s="0">
-        <v>300</v>
+        <v>370</v>
       </c>
     </row>
     <row r="276">
@@ -7306,7 +7306,7 @@
         <v>18</v>
       </c>
       <c r="D276" s="0">
-        <v>420</v>
+        <v>300</v>
       </c>
     </row>
     <row r="277">
@@ -7320,7 +7320,7 @@
         <v>18</v>
       </c>
       <c r="D277" s="0">
-        <v>760</v>
+        <v>420</v>
       </c>
     </row>
     <row r="278">
@@ -7334,7 +7334,7 @@
         <v>18</v>
       </c>
       <c r="D278" s="0">
-        <v>820</v>
+        <v>760</v>
       </c>
     </row>
     <row r="279">
@@ -7345,24 +7345,24 @@
         <v>609</v>
       </c>
       <c r="C279" s="0" t="s">
-        <v>610</v>
+        <v>18</v>
       </c>
       <c r="D279" s="0">
-        <v>189016.25</v>
+        <v>820</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="0" t="s">
+        <v>610</v>
+      </c>
+      <c r="B280" s="0" t="s">
         <v>611</v>
       </c>
-      <c r="B280" s="0" t="s">
+      <c r="C280" s="0" t="s">
         <v>612</v>
       </c>
-      <c r="C280" s="0" t="s">
-        <v>75</v>
-      </c>
       <c r="D280" s="0">
-        <v>36000</v>
+        <v>189016.25</v>
       </c>
     </row>
     <row r="281">
@@ -7376,7 +7376,7 @@
         <v>75</v>
       </c>
       <c r="D281" s="0">
-        <v>42480</v>
+        <v>36000</v>
       </c>
     </row>
     <row r="282">
@@ -7387,10 +7387,10 @@
         <v>616</v>
       </c>
       <c r="C282" s="0" t="s">
-        <v>485</v>
+        <v>75</v>
       </c>
       <c r="D282" s="0">
-        <v>243315</v>
+        <v>42480</v>
       </c>
     </row>
     <row r="283">
@@ -7401,10 +7401,10 @@
         <v>618</v>
       </c>
       <c r="C283" s="0" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="D283" s="0">
-        <v>196835</v>
+        <v>243315</v>
       </c>
     </row>
     <row r="284">
@@ -7415,10 +7415,10 @@
         <v>620</v>
       </c>
       <c r="C284" s="0" t="s">
-        <v>15</v>
+        <v>487</v>
       </c>
       <c r="D284" s="0">
-        <v>1760</v>
+        <v>196835</v>
       </c>
     </row>
     <row r="285">
@@ -7429,24 +7429,24 @@
         <v>622</v>
       </c>
       <c r="C285" s="0" t="s">
-        <v>623</v>
+        <v>15</v>
       </c>
       <c r="D285" s="0">
-        <v>26350</v>
+        <v>1760</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="0" t="s">
+        <v>623</v>
+      </c>
+      <c r="B286" s="0" t="s">
         <v>624</v>
       </c>
-      <c r="B286" s="0" t="s">
+      <c r="C286" s="0" t="s">
         <v>625</v>
       </c>
-      <c r="C286" s="0" t="s">
-        <v>212</v>
-      </c>
       <c r="D286" s="0">
-        <v>31250</v>
+        <v>26350</v>
       </c>
     </row>
     <row r="287">
@@ -7457,10 +7457,10 @@
         <v>627</v>
       </c>
       <c r="C287" s="0" t="s">
-        <v>59</v>
+        <v>212</v>
       </c>
       <c r="D287" s="0">
-        <v>69</v>
+        <v>31250</v>
       </c>
     </row>
     <row r="288">
@@ -7471,10 +7471,10 @@
         <v>629</v>
       </c>
       <c r="C288" s="0" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="D288" s="0">
-        <v>34.98</v>
+        <v>69</v>
       </c>
     </row>
     <row r="289">
@@ -7485,7 +7485,7 @@
         <v>631</v>
       </c>
       <c r="C289" s="0" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="D289" s="0">
         <v>34.98</v>
@@ -7499,21 +7499,21 @@
         <v>633</v>
       </c>
       <c r="C290" s="0" t="s">
-        <v>634</v>
+        <v>59</v>
       </c>
       <c r="D290" s="0">
-        <v>65</v>
+        <v>34.98</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="0" t="s">
+        <v>634</v>
+      </c>
+      <c r="B291" s="0" t="s">
         <v>635</v>
       </c>
-      <c r="B291" s="0" t="s">
+      <c r="C291" s="0" t="s">
         <v>636</v>
-      </c>
-      <c r="C291" s="0" t="s">
-        <v>52</v>
       </c>
       <c r="D291" s="0">
         <v>65</v>
@@ -7521,30 +7521,30 @@
     </row>
     <row r="292">
       <c r="A292" s="0" t="s">
-        <v>626</v>
+        <v>637</v>
       </c>
       <c r="B292" s="0" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C292" s="0" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="D292" s="0">
-        <v>0</v>
+        <v>65</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="0" t="s">
-        <v>638</v>
+        <v>628</v>
       </c>
       <c r="B293" s="0" t="s">
         <v>639</v>
       </c>
       <c r="C293" s="0" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="D293" s="0">
-        <v>92</v>
+        <v>0</v>
       </c>
     </row>
     <row r="294">
@@ -7558,7 +7558,7 @@
         <v>52</v>
       </c>
       <c r="D294" s="0">
-        <v>33</v>
+        <v>92</v>
       </c>
     </row>
     <row r="295">
@@ -7572,7 +7572,7 @@
         <v>52</v>
       </c>
       <c r="D295" s="0">
-        <v>54.8</v>
+        <v>33</v>
       </c>
     </row>
     <row r="296">
@@ -7583,10 +7583,10 @@
         <v>645</v>
       </c>
       <c r="C296" s="0" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="D296" s="0">
-        <v>44</v>
+        <v>54.8</v>
       </c>
     </row>
     <row r="297">
@@ -7597,10 +7597,10 @@
         <v>647</v>
       </c>
       <c r="C297" s="0" t="s">
-        <v>348</v>
+        <v>59</v>
       </c>
       <c r="D297" s="0">
-        <v>300</v>
+        <v>44</v>
       </c>
     </row>
     <row r="298">
@@ -7611,10 +7611,10 @@
         <v>649</v>
       </c>
       <c r="C298" s="0" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="D298" s="0">
-        <v>370</v>
+        <v>300</v>
       </c>
     </row>
     <row r="299">
@@ -7625,10 +7625,10 @@
         <v>651</v>
       </c>
       <c r="C299" s="0" t="s">
-        <v>369</v>
+        <v>350</v>
       </c>
       <c r="D299" s="0">
-        <v>450</v>
+        <v>370</v>
       </c>
     </row>
     <row r="300">
@@ -7639,7 +7639,7 @@
         <v>653</v>
       </c>
       <c r="C300" s="0" t="s">
-        <v>37</v>
+        <v>371</v>
       </c>
       <c r="D300" s="0">
         <v>450</v>
@@ -7653,7 +7653,7 @@
         <v>655</v>
       </c>
       <c r="C301" s="0" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="D301" s="0">
         <v>450</v>
@@ -7670,7 +7670,7 @@
         <v>15</v>
       </c>
       <c r="D302" s="0">
-        <v>1650</v>
+        <v>450</v>
       </c>
     </row>
     <row r="303">
@@ -7684,7 +7684,7 @@
         <v>15</v>
       </c>
       <c r="D303" s="0">
-        <v>2100</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="304">
@@ -7698,7 +7698,7 @@
         <v>15</v>
       </c>
       <c r="D304" s="0">
-        <v>1980</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="305">
@@ -7712,7 +7712,7 @@
         <v>15</v>
       </c>
       <c r="D305" s="0">
-        <v>2160</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="306">
@@ -7726,7 +7726,7 @@
         <v>15</v>
       </c>
       <c r="D306" s="0">
-        <v>1300</v>
+        <v>2160</v>
       </c>
     </row>
     <row r="307">
@@ -7740,7 +7740,7 @@
         <v>15</v>
       </c>
       <c r="D307" s="0">
-        <v>2600</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="308">
@@ -7754,7 +7754,7 @@
         <v>15</v>
       </c>
       <c r="D308" s="0">
-        <v>2000</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="309">
@@ -7768,7 +7768,7 @@
         <v>15</v>
       </c>
       <c r="D309" s="0">
-        <v>6700</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="310">
@@ -7782,7 +7782,7 @@
         <v>15</v>
       </c>
       <c r="D310" s="0">
-        <v>1650</v>
+        <v>6700</v>
       </c>
     </row>
     <row r="311">
@@ -7796,7 +7796,7 @@
         <v>15</v>
       </c>
       <c r="D311" s="0">
-        <v>1035</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="312">
@@ -7810,7 +7810,7 @@
         <v>15</v>
       </c>
       <c r="D312" s="0">
-        <v>2600</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="313">
@@ -7824,7 +7824,7 @@
         <v>15</v>
       </c>
       <c r="D313" s="0">
-        <v>2400</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="314">
@@ -7835,10 +7835,10 @@
         <v>681</v>
       </c>
       <c r="C314" s="0" t="s">
-        <v>145</v>
+        <v>15</v>
       </c>
       <c r="D314" s="0">
-        <v>4730</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="315">
@@ -7852,7 +7852,7 @@
         <v>145</v>
       </c>
       <c r="D315" s="0">
-        <v>2517</v>
+        <v>4730</v>
       </c>
     </row>
     <row r="316">
@@ -7866,7 +7866,7 @@
         <v>145</v>
       </c>
       <c r="D316" s="0">
-        <v>1190</v>
+        <v>2517</v>
       </c>
     </row>
     <row r="317">
@@ -7877,10 +7877,10 @@
         <v>687</v>
       </c>
       <c r="C317" s="0" t="s">
-        <v>28</v>
+        <v>145</v>
       </c>
       <c r="D317" s="0">
-        <v>7655.2</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="318">
@@ -7891,10 +7891,10 @@
         <v>689</v>
       </c>
       <c r="C318" s="0" t="s">
-        <v>128</v>
+        <v>28</v>
       </c>
       <c r="D318" s="0">
-        <v>1790</v>
+        <v>7655.2</v>
       </c>
     </row>
     <row r="319">
@@ -7908,7 +7908,7 @@
         <v>128</v>
       </c>
       <c r="D319" s="0">
-        <v>3016.53</v>
+        <v>1790</v>
       </c>
     </row>
     <row r="320">
@@ -7922,7 +7922,7 @@
         <v>128</v>
       </c>
       <c r="D320" s="0">
-        <v>4800</v>
+        <v>3016.53</v>
       </c>
     </row>
     <row r="321">
@@ -7936,7 +7936,7 @@
         <v>128</v>
       </c>
       <c r="D321" s="0">
-        <v>4450</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="322">
@@ -7947,24 +7947,24 @@
         <v>697</v>
       </c>
       <c r="C322" s="0" t="s">
-        <v>698</v>
+        <v>128</v>
       </c>
       <c r="D322" s="0">
-        <v>0</v>
+        <v>4450</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="0" t="s">
+        <v>698</v>
+      </c>
+      <c r="B323" s="0" t="s">
         <v>699</v>
       </c>
-      <c r="B323" s="0" t="s">
+      <c r="C323" s="0" t="s">
         <v>700</v>
       </c>
-      <c r="C323" s="0" t="s">
-        <v>28</v>
-      </c>
       <c r="D323" s="0">
-        <v>494</v>
+        <v>0</v>
       </c>
     </row>
     <row r="324">
@@ -7978,7 +7978,7 @@
         <v>28</v>
       </c>
       <c r="D324" s="0">
-        <v>665.3</v>
+        <v>494</v>
       </c>
     </row>
     <row r="325">
@@ -7989,10 +7989,10 @@
         <v>704</v>
       </c>
       <c r="C325" s="0" t="s">
-        <v>97</v>
+        <v>28</v>
       </c>
       <c r="D325" s="0">
-        <v>33940.5</v>
+        <v>665.3</v>
       </c>
     </row>
     <row r="326">
@@ -8006,7 +8006,7 @@
         <v>97</v>
       </c>
       <c r="D326" s="0">
-        <v>4525.4</v>
+        <v>33940.5</v>
       </c>
     </row>
     <row r="327">
@@ -8017,10 +8017,10 @@
         <v>708</v>
       </c>
       <c r="C327" s="0" t="s">
-        <v>156</v>
+        <v>97</v>
       </c>
       <c r="D327" s="0">
-        <v>896</v>
+        <v>4525.4</v>
       </c>
     </row>
     <row r="328">
@@ -8031,10 +8031,10 @@
         <v>710</v>
       </c>
       <c r="C328" s="0" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="D328" s="0">
-        <v>1125</v>
+        <v>896</v>
       </c>
     </row>
     <row r="329">
@@ -8045,10 +8045,10 @@
         <v>712</v>
       </c>
       <c r="C329" s="0" t="s">
-        <v>97</v>
+        <v>145</v>
       </c>
       <c r="D329" s="0">
-        <v>342732.5</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="330">
@@ -8059,10 +8059,10 @@
         <v>714</v>
       </c>
       <c r="C330" s="0" t="s">
-        <v>207</v>
+        <v>97</v>
       </c>
       <c r="D330" s="0">
-        <v>17440</v>
+        <v>342732.5</v>
       </c>
     </row>
     <row r="331">
@@ -8076,7 +8076,7 @@
         <v>207</v>
       </c>
       <c r="D331" s="0">
-        <v>4390</v>
+        <v>17440</v>
       </c>
     </row>
     <row r="332">
@@ -8101,10 +8101,10 @@
         <v>720</v>
       </c>
       <c r="C333" s="0" t="s">
-        <v>289</v>
+        <v>207</v>
       </c>
       <c r="D333" s="0">
-        <v>2250</v>
+        <v>4390</v>
       </c>
     </row>
     <row r="334">
@@ -8115,10 +8115,10 @@
         <v>722</v>
       </c>
       <c r="C334" s="0" t="s">
-        <v>207</v>
+        <v>291</v>
       </c>
       <c r="D334" s="0">
-        <v>3355</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="335">
@@ -8129,10 +8129,10 @@
         <v>724</v>
       </c>
       <c r="C335" s="0" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="D335" s="0">
-        <v>7500</v>
+        <v>3355</v>
       </c>
     </row>
     <row r="336">
@@ -8143,10 +8143,10 @@
         <v>726</v>
       </c>
       <c r="C336" s="0" t="s">
-        <v>97</v>
+        <v>215</v>
       </c>
       <c r="D336" s="0">
-        <v>26620</v>
+        <v>7500</v>
       </c>
     </row>
     <row r="337">
@@ -8160,7 +8160,7 @@
         <v>97</v>
       </c>
       <c r="D337" s="0">
-        <v>266200</v>
+        <v>26620</v>
       </c>
     </row>
     <row r="338">
@@ -8171,10 +8171,10 @@
         <v>730</v>
       </c>
       <c r="C338" s="0" t="s">
-        <v>52</v>
+        <v>97</v>
       </c>
       <c r="D338" s="0">
-        <v>160</v>
+        <v>266200</v>
       </c>
     </row>
     <row r="339">
@@ -8185,10 +8185,10 @@
         <v>732</v>
       </c>
       <c r="C339" s="0" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="D339" s="0">
-        <v>285.6</v>
+        <v>160</v>
       </c>
     </row>
     <row r="340">
@@ -8202,7 +8202,7 @@
         <v>21</v>
       </c>
       <c r="D340" s="0">
-        <v>338</v>
+        <v>285.6</v>
       </c>
     </row>
     <row r="341">
@@ -8213,21 +8213,21 @@
         <v>736</v>
       </c>
       <c r="C341" s="0" t="s">
-        <v>737</v>
+        <v>21</v>
       </c>
       <c r="D341" s="0">
-        <v>770</v>
+        <v>338</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" s="0" t="s">
+        <v>737</v>
+      </c>
+      <c r="B342" s="0" t="s">
         <v>738</v>
       </c>
-      <c r="B342" s="0" t="s">
+      <c r="C342" s="0" t="s">
         <v>739</v>
-      </c>
-      <c r="C342" s="0" t="s">
-        <v>740</v>
       </c>
       <c r="D342" s="0">
         <v>770</v>
@@ -8235,16 +8235,16 @@
     </row>
     <row r="343">
       <c r="A343" s="0" t="s">
+        <v>740</v>
+      </c>
+      <c r="B343" s="0" t="s">
         <v>741</v>
       </c>
-      <c r="B343" s="0" t="s">
+      <c r="C343" s="0" t="s">
         <v>742</v>
       </c>
-      <c r="C343" s="0" t="s">
-        <v>15</v>
-      </c>
       <c r="D343" s="0">
-        <v>973.5</v>
+        <v>770</v>
       </c>
     </row>
     <row r="344">
@@ -8255,10 +8255,10 @@
         <v>744</v>
       </c>
       <c r="C344" s="0" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="D344" s="0">
-        <v>490</v>
+        <v>973.5</v>
       </c>
     </row>
     <row r="345">
@@ -8269,10 +8269,10 @@
         <v>746</v>
       </c>
       <c r="C345" s="0" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D345" s="0">
-        <v>450</v>
+        <v>490</v>
       </c>
     </row>
     <row r="346">
@@ -8283,10 +8283,10 @@
         <v>748</v>
       </c>
       <c r="C346" s="0" t="s">
-        <v>156</v>
+        <v>15</v>
       </c>
       <c r="D346" s="0">
-        <v>760</v>
+        <v>450</v>
       </c>
     </row>
     <row r="347">
@@ -8297,10 +8297,10 @@
         <v>750</v>
       </c>
       <c r="C347" s="0" t="s">
-        <v>289</v>
+        <v>156</v>
       </c>
       <c r="D347" s="0">
-        <v>5900</v>
+        <v>760</v>
       </c>
     </row>
     <row r="348">
@@ -8311,10 +8311,10 @@
         <v>752</v>
       </c>
       <c r="C348" s="0" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="D348" s="0">
-        <v>2900</v>
+        <v>5900</v>
       </c>
     </row>
     <row r="349">
@@ -8325,10 +8325,10 @@
         <v>754</v>
       </c>
       <c r="C349" s="0" t="s">
-        <v>145</v>
+        <v>291</v>
       </c>
       <c r="D349" s="0">
-        <v>935</v>
+        <v>2900</v>
       </c>
     </row>
     <row r="350">
@@ -8342,7 +8342,7 @@
         <v>145</v>
       </c>
       <c r="D350" s="0">
-        <v>620</v>
+        <v>935</v>
       </c>
     </row>
     <row r="351">
@@ -8356,7 +8356,7 @@
         <v>145</v>
       </c>
       <c r="D351" s="0">
-        <v>73</v>
+        <v>620</v>
       </c>
     </row>
     <row r="352">
@@ -8367,10 +8367,10 @@
         <v>760</v>
       </c>
       <c r="C352" s="0" t="s">
-        <v>97</v>
+        <v>145</v>
       </c>
       <c r="D352" s="0">
-        <v>11313.5</v>
+        <v>73</v>
       </c>
     </row>
     <row r="353">
@@ -8381,10 +8381,10 @@
         <v>762</v>
       </c>
       <c r="C353" s="0" t="s">
-        <v>34</v>
+        <v>97</v>
       </c>
       <c r="D353" s="0">
-        <v>400</v>
+        <v>11313.5</v>
       </c>
     </row>
     <row r="354">
@@ -8395,7 +8395,7 @@
         <v>764</v>
       </c>
       <c r="C354" s="0" t="s">
-        <v>369</v>
+        <v>34</v>
       </c>
       <c r="D354" s="0">
         <v>400</v>
@@ -8409,10 +8409,10 @@
         <v>766</v>
       </c>
       <c r="C355" s="0" t="s">
-        <v>21</v>
+        <v>371</v>
       </c>
       <c r="D355" s="0">
-        <v>377</v>
+        <v>400</v>
       </c>
     </row>
     <row r="356">
@@ -8423,10 +8423,10 @@
         <v>768</v>
       </c>
       <c r="C356" s="0" t="s">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="D356" s="0">
-        <v>5621.15</v>
+        <v>377</v>
       </c>
     </row>
     <row r="357">
@@ -8437,10 +8437,10 @@
         <v>770</v>
       </c>
       <c r="C357" s="0" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="D357" s="0">
-        <v>1120</v>
+        <v>5621.15</v>
       </c>
     </row>
     <row r="358">
@@ -8451,10 +8451,10 @@
         <v>772</v>
       </c>
       <c r="C358" s="0" t="s">
-        <v>128</v>
+        <v>21</v>
       </c>
       <c r="D358" s="0">
-        <v>4767</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="359">
@@ -8465,10 +8465,10 @@
         <v>774</v>
       </c>
       <c r="C359" s="0" t="s">
-        <v>34</v>
+        <v>128</v>
       </c>
       <c r="D359" s="0">
-        <v>650</v>
+        <v>4767</v>
       </c>
     </row>
     <row r="360">
@@ -8479,7 +8479,7 @@
         <v>776</v>
       </c>
       <c r="C360" s="0" t="s">
-        <v>75</v>
+        <v>34</v>
       </c>
       <c r="D360" s="0">
         <v>650</v>
@@ -8493,10 +8493,10 @@
         <v>778</v>
       </c>
       <c r="C361" s="0" t="s">
-        <v>15</v>
+        <v>75</v>
       </c>
       <c r="D361" s="0">
-        <v>2178</v>
+        <v>650</v>
       </c>
     </row>
     <row r="362">
@@ -8507,10 +8507,10 @@
         <v>780</v>
       </c>
       <c r="C362" s="0" t="s">
-        <v>97</v>
+        <v>15</v>
       </c>
       <c r="D362" s="0">
-        <v>7986</v>
+        <v>2178</v>
       </c>
     </row>
     <row r="363">
@@ -8521,24 +8521,24 @@
         <v>782</v>
       </c>
       <c r="C363" s="0" t="s">
-        <v>783</v>
+        <v>97</v>
       </c>
       <c r="D363" s="0">
-        <v>1910</v>
+        <v>7986</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" s="0" t="s">
+        <v>783</v>
+      </c>
+      <c r="B364" s="0" t="s">
         <v>784</v>
       </c>
-      <c r="B364" s="0" t="s">
+      <c r="C364" s="0" t="s">
         <v>785</v>
       </c>
-      <c r="C364" s="0" t="s">
-        <v>156</v>
-      </c>
       <c r="D364" s="0">
-        <v>1000</v>
+        <v>1910</v>
       </c>
     </row>
     <row r="365">
@@ -8549,24 +8549,24 @@
         <v>787</v>
       </c>
       <c r="C365" s="0" t="s">
-        <v>788</v>
+        <v>156</v>
       </c>
       <c r="D365" s="0">
-        <v>1650</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" s="0" t="s">
+        <v>788</v>
+      </c>
+      <c r="B366" s="0" t="s">
         <v>789</v>
       </c>
-      <c r="B366" s="0" t="s">
+      <c r="C366" s="0" t="s">
         <v>790</v>
       </c>
-      <c r="C366" s="0" t="s">
-        <v>21</v>
-      </c>
       <c r="D366" s="0">
-        <v>2001</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="367">
@@ -8577,10 +8577,10 @@
         <v>792</v>
       </c>
       <c r="C367" s="0" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="D367" s="0">
-        <v>59000</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="368">
@@ -8591,10 +8591,10 @@
         <v>794</v>
       </c>
       <c r="C368" s="0" t="s">
-        <v>156</v>
+        <v>34</v>
       </c>
       <c r="D368" s="0">
-        <v>750</v>
+        <v>59000</v>
       </c>
     </row>
     <row r="369">
@@ -8608,7 +8608,7 @@
         <v>156</v>
       </c>
       <c r="D369" s="0">
-        <v>1212</v>
+        <v>750</v>
       </c>
     </row>
     <row r="370">
@@ -8622,7 +8622,7 @@
         <v>156</v>
       </c>
       <c r="D370" s="0">
-        <v>1300</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="371">
@@ -8636,7 +8636,7 @@
         <v>156</v>
       </c>
       <c r="D371" s="0">
-        <v>1500</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="372">
@@ -8650,7 +8650,7 @@
         <v>156</v>
       </c>
       <c r="D372" s="0">
-        <v>1400</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="373">
@@ -8661,10 +8661,10 @@
         <v>804</v>
       </c>
       <c r="C373" s="0" t="s">
-        <v>269</v>
+        <v>156</v>
       </c>
       <c r="D373" s="0">
-        <v>11959</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="374">
@@ -8675,10 +8675,10 @@
         <v>806</v>
       </c>
       <c r="C374" s="0" t="s">
-        <v>145</v>
+        <v>271</v>
       </c>
       <c r="D374" s="0">
-        <v>365</v>
+        <v>11959</v>
       </c>
     </row>
     <row r="375">
@@ -8689,10 +8689,10 @@
         <v>808</v>
       </c>
       <c r="C375" s="0" t="s">
-        <v>289</v>
+        <v>145</v>
       </c>
       <c r="D375" s="0">
-        <v>1450</v>
+        <v>365</v>
       </c>
     </row>
     <row r="376">
@@ -8703,10 +8703,10 @@
         <v>810</v>
       </c>
       <c r="C376" s="0" t="s">
-        <v>97</v>
+        <v>291</v>
       </c>
       <c r="D376" s="0">
-        <v>7320.5</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="377">
@@ -8717,10 +8717,10 @@
         <v>812</v>
       </c>
       <c r="C377" s="0" t="s">
-        <v>15</v>
+        <v>97</v>
       </c>
       <c r="D377" s="0">
-        <v>900</v>
+        <v>7320.5</v>
       </c>
     </row>
     <row r="378">
@@ -8731,10 +8731,10 @@
         <v>814</v>
       </c>
       <c r="C378" s="0" t="s">
-        <v>289</v>
+        <v>15</v>
       </c>
       <c r="D378" s="0">
-        <v>566</v>
+        <v>900</v>
       </c>
     </row>
     <row r="379">
@@ -8745,10 +8745,10 @@
         <v>816</v>
       </c>
       <c r="C379" s="0" t="s">
-        <v>485</v>
+        <v>291</v>
       </c>
       <c r="D379" s="0">
-        <v>64925</v>
+        <v>566</v>
       </c>
     </row>
     <row r="380">
@@ -8759,10 +8759,10 @@
         <v>818</v>
       </c>
       <c r="C380" s="0" t="s">
-        <v>15</v>
+        <v>487</v>
       </c>
       <c r="D380" s="0">
-        <v>1100</v>
+        <v>64925</v>
       </c>
     </row>
     <row r="381">
@@ -8773,10 +8773,10 @@
         <v>820</v>
       </c>
       <c r="C381" s="0" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="D381" s="0">
-        <v>1623</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="382">
@@ -8787,10 +8787,10 @@
         <v>822</v>
       </c>
       <c r="C382" s="0" t="s">
-        <v>145</v>
+        <v>21</v>
       </c>
       <c r="D382" s="0">
-        <v>1269</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="383">
@@ -8804,7 +8804,7 @@
         <v>145</v>
       </c>
       <c r="D383" s="0">
-        <v>4712</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="384">
@@ -8815,10 +8815,10 @@
         <v>826</v>
       </c>
       <c r="C384" s="0" t="s">
-        <v>28</v>
+        <v>145</v>
       </c>
       <c r="D384" s="0">
-        <v>1250</v>
+        <v>4712</v>
       </c>
     </row>
     <row r="385">
@@ -8832,7 +8832,7 @@
         <v>28</v>
       </c>
       <c r="D385" s="0">
-        <v>1986</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="386">
@@ -8843,10 +8843,10 @@
         <v>830</v>
       </c>
       <c r="C386" s="0" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="D386" s="0">
-        <v>450</v>
+        <v>1986</v>
       </c>
     </row>
     <row r="387">
@@ -8860,7 +8860,7 @@
         <v>15</v>
       </c>
       <c r="D387" s="0">
-        <v>825</v>
+        <v>450</v>
       </c>
     </row>
     <row r="388">
@@ -8885,10 +8885,10 @@
         <v>836</v>
       </c>
       <c r="C389" s="0" t="s">
-        <v>389</v>
+        <v>15</v>
       </c>
       <c r="D389" s="0">
-        <v>134775.6</v>
+        <v>825</v>
       </c>
     </row>
     <row r="390">
@@ -8899,10 +8899,10 @@
         <v>838</v>
       </c>
       <c r="C390" s="0" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="D390" s="0">
-        <v>175991.55</v>
+        <v>134775.6</v>
       </c>
     </row>
     <row r="391">
@@ -8913,10 +8913,10 @@
         <v>840</v>
       </c>
       <c r="C391" s="0" t="s">
-        <v>75</v>
+        <v>391</v>
       </c>
       <c r="D391" s="0">
-        <v>3427</v>
+        <v>175991.55</v>
       </c>
     </row>
     <row r="392">
@@ -8930,7 +8930,7 @@
         <v>75</v>
       </c>
       <c r="D392" s="0">
-        <v>10618</v>
+        <v>3427</v>
       </c>
     </row>
     <row r="393">
@@ -8941,10 +8941,10 @@
         <v>844</v>
       </c>
       <c r="C393" s="0" t="s">
-        <v>289</v>
+        <v>75</v>
       </c>
       <c r="D393" s="0">
-        <v>515</v>
+        <v>10618</v>
       </c>
     </row>
     <row r="394">
@@ -8955,7 +8955,7 @@
         <v>846</v>
       </c>
       <c r="C394" s="0" t="s">
-        <v>37</v>
+        <v>291</v>
       </c>
       <c r="D394" s="0">
         <v>515</v>
@@ -8969,10 +8969,10 @@
         <v>848</v>
       </c>
       <c r="C395" s="0" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="D395" s="0">
-        <v>10000</v>
+        <v>515</v>
       </c>
     </row>
     <row r="396">
@@ -8983,10 +8983,10 @@
         <v>850</v>
       </c>
       <c r="C396" s="0" t="s">
-        <v>485</v>
+        <v>52</v>
       </c>
       <c r="D396" s="0">
-        <v>213700</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="397">
@@ -8997,10 +8997,10 @@
         <v>852</v>
       </c>
       <c r="C397" s="0" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="D397" s="0">
-        <v>257000</v>
+        <v>213700</v>
       </c>
     </row>
     <row r="398">
@@ -9011,10 +9011,10 @@
         <v>854</v>
       </c>
       <c r="C398" s="0" t="s">
-        <v>75</v>
+        <v>487</v>
       </c>
       <c r="D398" s="0">
-        <v>10522</v>
+        <v>257000</v>
       </c>
     </row>
     <row r="399">
@@ -9028,7 +9028,7 @@
         <v>75</v>
       </c>
       <c r="D399" s="0">
-        <v>19481</v>
+        <v>10522</v>
       </c>
     </row>
     <row r="400">
@@ -9039,24 +9039,24 @@
         <v>858</v>
       </c>
       <c r="C400" s="0" t="s">
-        <v>859</v>
+        <v>75</v>
       </c>
       <c r="D400" s="0">
-        <v>1080</v>
+        <v>19481</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" s="0" t="s">
+        <v>859</v>
+      </c>
+      <c r="B401" s="0" t="s">
         <v>860</v>
       </c>
-      <c r="B401" s="0" t="s">
+      <c r="C401" s="0" t="s">
         <v>861</v>
       </c>
-      <c r="C401" s="0" t="s">
-        <v>18</v>
-      </c>
       <c r="D401" s="0">
-        <v>586.49</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="402">
@@ -9067,24 +9067,24 @@
         <v>863</v>
       </c>
       <c r="C402" s="0" t="s">
-        <v>864</v>
+        <v>18</v>
       </c>
       <c r="D402" s="0">
-        <v>520</v>
+        <v>586.49</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" s="0" t="s">
+        <v>864</v>
+      </c>
+      <c r="B403" s="0" t="s">
         <v>865</v>
       </c>
-      <c r="B403" s="0" t="s">
+      <c r="C403" s="0" t="s">
         <v>866</v>
       </c>
-      <c r="C403" s="0" t="s">
-        <v>864</v>
-      </c>
       <c r="D403" s="0">
-        <v>340</v>
+        <v>520</v>
       </c>
     </row>
     <row r="404">
@@ -9095,10 +9095,10 @@
         <v>868</v>
       </c>
       <c r="C404" s="0" t="s">
-        <v>34</v>
+        <v>866</v>
       </c>
       <c r="D404" s="0">
-        <v>630</v>
+        <v>340</v>
       </c>
     </row>
     <row r="405">
@@ -9109,10 +9109,10 @@
         <v>870</v>
       </c>
       <c r="C405" s="0" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="D405" s="0">
-        <v>2200</v>
+        <v>630</v>
       </c>
     </row>
     <row r="406">
@@ -9126,7 +9126,7 @@
         <v>15</v>
       </c>
       <c r="D406" s="0">
-        <v>2800</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="407">
@@ -9137,10 +9137,10 @@
         <v>874</v>
       </c>
       <c r="C407" s="0" t="s">
-        <v>97</v>
+        <v>15</v>
       </c>
       <c r="D407" s="0">
-        <v>5190.9</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="408">
@@ -9151,10 +9151,10 @@
         <v>876</v>
       </c>
       <c r="C408" s="0" t="s">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="D408" s="0">
-        <v>2969</v>
+        <v>5190.9</v>
       </c>
     </row>
     <row r="409">
@@ -9165,10 +9165,10 @@
         <v>878</v>
       </c>
       <c r="C409" s="0" t="s">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="D409" s="0">
-        <v>3800</v>
+        <v>2969</v>
       </c>
     </row>
     <row r="410">
@@ -9179,10 +9179,10 @@
         <v>880</v>
       </c>
       <c r="C410" s="0" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="D410" s="0">
-        <v>4000</v>
+        <v>3800</v>
       </c>
     </row>
     <row r="411">
@@ -9193,24 +9193,24 @@
         <v>882</v>
       </c>
       <c r="C411" s="0" t="s">
-        <v>883</v>
+        <v>15</v>
       </c>
       <c r="D411" s="0">
-        <v>3800</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" s="0" t="s">
+        <v>883</v>
+      </c>
+      <c r="B412" s="0" t="s">
         <v>884</v>
       </c>
-      <c r="B412" s="0" t="s">
+      <c r="C412" s="0" t="s">
         <v>885</v>
       </c>
-      <c r="C412" s="0" t="s">
-        <v>21</v>
-      </c>
       <c r="D412" s="0">
-        <v>353</v>
+        <v>3800</v>
       </c>
     </row>
     <row r="413">
@@ -9221,10 +9221,10 @@
         <v>887</v>
       </c>
       <c r="C413" s="0" t="s">
-        <v>115</v>
+        <v>21</v>
       </c>
       <c r="D413" s="0">
-        <v>1800</v>
+        <v>353</v>
       </c>
     </row>
     <row r="414">
@@ -9235,10 +9235,10 @@
         <v>889</v>
       </c>
       <c r="C414" s="0" t="s">
-        <v>15</v>
+        <v>115</v>
       </c>
       <c r="D414" s="0">
-        <v>2948</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="415">
@@ -9249,10 +9249,10 @@
         <v>891</v>
       </c>
       <c r="C415" s="0" t="s">
-        <v>97</v>
+        <v>15</v>
       </c>
       <c r="D415" s="0">
-        <v>146.41</v>
+        <v>2948</v>
       </c>
     </row>
     <row r="416">
@@ -9263,10 +9263,10 @@
         <v>893</v>
       </c>
       <c r="C416" s="0" t="s">
-        <v>215</v>
+        <v>97</v>
       </c>
       <c r="D416" s="0">
-        <v>65537</v>
+        <v>146.41</v>
       </c>
     </row>
     <row r="417">
@@ -9277,10 +9277,10 @@
         <v>895</v>
       </c>
       <c r="C417" s="0" t="s">
-        <v>145</v>
+        <v>215</v>
       </c>
       <c r="D417" s="0">
-        <v>4130.4</v>
+        <v>65537</v>
       </c>
     </row>
     <row r="418">
@@ -9294,7 +9294,7 @@
         <v>145</v>
       </c>
       <c r="D418" s="0">
-        <v>4283</v>
+        <v>4130.4</v>
       </c>
     </row>
     <row r="419">
@@ -9308,7 +9308,7 @@
         <v>145</v>
       </c>
       <c r="D419" s="0">
-        <v>6524.8</v>
+        <v>4283</v>
       </c>
     </row>
     <row r="420">
@@ -9319,10 +9319,10 @@
         <v>901</v>
       </c>
       <c r="C420" s="0" t="s">
-        <v>316</v>
+        <v>145</v>
       </c>
       <c r="D420" s="0">
-        <v>570</v>
+        <v>6524.8</v>
       </c>
     </row>
     <row r="421">
@@ -9333,10 +9333,10 @@
         <v>903</v>
       </c>
       <c r="C421" s="0" t="s">
-        <v>75</v>
+        <v>318</v>
       </c>
       <c r="D421" s="0">
-        <v>550</v>
+        <v>570</v>
       </c>
     </row>
     <row r="422">
@@ -9347,10 +9347,10 @@
         <v>905</v>
       </c>
       <c r="C422" s="0" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="D422" s="0">
-        <v>153</v>
+        <v>550</v>
       </c>
     </row>
     <row r="423">
@@ -9361,10 +9361,10 @@
         <v>907</v>
       </c>
       <c r="C423" s="0" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="D423" s="0">
-        <v>740.7</v>
+        <v>153</v>
       </c>
     </row>
     <row r="424">
@@ -9375,10 +9375,10 @@
         <v>909</v>
       </c>
       <c r="C424" s="0" t="s">
-        <v>64</v>
+        <v>28</v>
       </c>
       <c r="D424" s="0">
-        <v>101000</v>
+        <v>740.7</v>
       </c>
     </row>
     <row r="425">
@@ -9389,10 +9389,10 @@
         <v>911</v>
       </c>
       <c r="C425" s="0" t="s">
-        <v>128</v>
+        <v>64</v>
       </c>
       <c r="D425" s="0">
-        <v>6251</v>
+        <v>101000</v>
       </c>
     </row>
     <row r="426">
@@ -9403,10 +9403,10 @@
         <v>913</v>
       </c>
       <c r="C426" s="0" t="s">
-        <v>145</v>
+        <v>128</v>
       </c>
       <c r="D426" s="0">
-        <v>883</v>
+        <v>6251</v>
       </c>
     </row>
     <row r="427">
@@ -9417,10 +9417,10 @@
         <v>915</v>
       </c>
       <c r="C427" s="0" t="s">
-        <v>97</v>
+        <v>145</v>
       </c>
       <c r="D427" s="0">
-        <v>1164.66</v>
+        <v>883</v>
       </c>
     </row>
     <row r="428">
@@ -9431,10 +9431,10 @@
         <v>917</v>
       </c>
       <c r="C428" s="0" t="s">
-        <v>156</v>
+        <v>97</v>
       </c>
       <c r="D428" s="0">
-        <v>360</v>
+        <v>1164.66</v>
       </c>
     </row>
     <row r="429">
@@ -9448,7 +9448,7 @@
         <v>156</v>
       </c>
       <c r="D429" s="0">
-        <v>450</v>
+        <v>360</v>
       </c>
     </row>
     <row r="430">
@@ -9462,7 +9462,7 @@
         <v>156</v>
       </c>
       <c r="D430" s="0">
-        <v>2150</v>
+        <v>450</v>
       </c>
     </row>
     <row r="431">
@@ -9473,10 +9473,10 @@
         <v>923</v>
       </c>
       <c r="C431" s="0" t="s">
-        <v>610</v>
+        <v>156</v>
       </c>
       <c r="D431" s="0">
-        <v>25192.82</v>
+        <v>2150</v>
       </c>
     </row>
     <row r="432">
@@ -9487,10 +9487,10 @@
         <v>925</v>
       </c>
       <c r="C432" s="0" t="s">
-        <v>75</v>
+        <v>612</v>
       </c>
       <c r="D432" s="0">
-        <v>3500</v>
+        <v>25192.82</v>
       </c>
     </row>
     <row r="433">
@@ -9501,10 +9501,10 @@
         <v>927</v>
       </c>
       <c r="C433" s="0" t="s">
-        <v>180</v>
+        <v>75</v>
       </c>
       <c r="D433" s="0">
-        <v>600</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="434">
@@ -9515,24 +9515,24 @@
         <v>929</v>
       </c>
       <c r="C434" s="0" t="s">
-        <v>930</v>
+        <v>180</v>
       </c>
       <c r="D434" s="0">
-        <v>1080</v>
+        <v>600</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" s="0" t="s">
+        <v>930</v>
+      </c>
+      <c r="B435" s="0" t="s">
         <v>931</v>
       </c>
-      <c r="B435" s="0" t="s">
+      <c r="C435" s="0" t="s">
         <v>932</v>
       </c>
-      <c r="C435" s="0" t="s">
-        <v>348</v>
-      </c>
       <c r="D435" s="0">
-        <v>8628</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="436">
@@ -9543,10 +9543,10 @@
         <v>934</v>
       </c>
       <c r="C436" s="0" t="s">
-        <v>40</v>
+        <v>350</v>
       </c>
       <c r="D436" s="0">
-        <v>27991.54</v>
+        <v>8628</v>
       </c>
     </row>
     <row r="437">
@@ -9557,10 +9557,10 @@
         <v>936</v>
       </c>
       <c r="C437" s="0" t="s">
-        <v>145</v>
+        <v>40</v>
       </c>
       <c r="D437" s="0">
-        <v>1020</v>
+        <v>27991.54</v>
       </c>
     </row>
     <row r="438">
@@ -9574,7 +9574,7 @@
         <v>145</v>
       </c>
       <c r="D438" s="0">
-        <v>4106</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="439">
@@ -9585,10 +9585,10 @@
         <v>940</v>
       </c>
       <c r="C439" s="0" t="s">
-        <v>289</v>
+        <v>145</v>
       </c>
       <c r="D439" s="0">
-        <v>450</v>
+        <v>4106</v>
       </c>
     </row>
     <row r="440">
@@ -9599,10 +9599,10 @@
         <v>942</v>
       </c>
       <c r="C440" s="0" t="s">
-        <v>45</v>
+        <v>291</v>
       </c>
       <c r="D440" s="0">
-        <v>6398.6</v>
+        <v>450</v>
       </c>
     </row>
     <row r="441">
@@ -9616,7 +9616,7 @@
         <v>45</v>
       </c>
       <c r="D441" s="0">
-        <v>2886.7</v>
+        <v>6398.6</v>
       </c>
     </row>
     <row r="442">
@@ -9630,7 +9630,7 @@
         <v>45</v>
       </c>
       <c r="D442" s="0">
-        <v>2050.95</v>
+        <v>2886.7</v>
       </c>
     </row>
     <row r="443">
@@ -9644,7 +9644,7 @@
         <v>45</v>
       </c>
       <c r="D443" s="0">
-        <v>30050.45</v>
+        <v>2050.95</v>
       </c>
     </row>
     <row r="444">
@@ -9658,7 +9658,7 @@
         <v>45</v>
       </c>
       <c r="D444" s="0">
-        <v>2326.8</v>
+        <v>30050.45</v>
       </c>
     </row>
     <row r="445">
@@ -9672,7 +9672,7 @@
         <v>45</v>
       </c>
       <c r="D445" s="0">
-        <v>6429.95</v>
+        <v>2326.8</v>
       </c>
     </row>
     <row r="446">
@@ -9686,7 +9686,7 @@
         <v>45</v>
       </c>
       <c r="D446" s="0">
-        <v>5180.26</v>
+        <v>6429.95</v>
       </c>
     </row>
     <row r="447">
@@ -9697,10 +9697,10 @@
         <v>956</v>
       </c>
       <c r="C447" s="0" t="s">
-        <v>212</v>
+        <v>45</v>
       </c>
       <c r="D447" s="0">
-        <v>510</v>
+        <v>5180.26</v>
       </c>
     </row>
     <row r="448">
@@ -9711,7 +9711,7 @@
         <v>958</v>
       </c>
       <c r="C448" s="0" t="s">
-        <v>37</v>
+        <v>212</v>
       </c>
       <c r="D448" s="0">
         <v>510</v>
@@ -9725,21 +9725,21 @@
         <v>960</v>
       </c>
       <c r="C449" s="0" t="s">
-        <v>961</v>
+        <v>37</v>
       </c>
       <c r="D449" s="0">
-        <v>626</v>
+        <v>510</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" s="0" t="s">
+        <v>961</v>
+      </c>
+      <c r="B450" s="0" t="s">
         <v>962</v>
       </c>
-      <c r="B450" s="0" t="s">
+      <c r="C450" s="0" t="s">
         <v>963</v>
-      </c>
-      <c r="C450" s="0" t="s">
-        <v>961</v>
       </c>
       <c r="D450" s="0">
         <v>626</v>
@@ -9753,7 +9753,7 @@
         <v>965</v>
       </c>
       <c r="C451" s="0" t="s">
-        <v>961</v>
+        <v>963</v>
       </c>
       <c r="D451" s="0">
         <v>626</v>
@@ -9767,10 +9767,10 @@
         <v>967</v>
       </c>
       <c r="C452" s="0" t="s">
-        <v>961</v>
+        <v>963</v>
       </c>
       <c r="D452" s="0">
-        <v>342</v>
+        <v>626</v>
       </c>
     </row>
     <row r="453">
@@ -9781,7 +9781,7 @@
         <v>969</v>
       </c>
       <c r="C453" s="0" t="s">
-        <v>961</v>
+        <v>963</v>
       </c>
       <c r="D453" s="0">
         <v>342</v>
@@ -9795,7 +9795,7 @@
         <v>971</v>
       </c>
       <c r="C454" s="0" t="s">
-        <v>961</v>
+        <v>963</v>
       </c>
       <c r="D454" s="0">
         <v>342</v>
@@ -9809,10 +9809,10 @@
         <v>973</v>
       </c>
       <c r="C455" s="0" t="s">
-        <v>961</v>
+        <v>963</v>
       </c>
       <c r="D455" s="0">
-        <v>0</v>
+        <v>342</v>
       </c>
     </row>
     <row r="456">
@@ -9823,7 +9823,7 @@
         <v>975</v>
       </c>
       <c r="C456" s="0" t="s">
-        <v>961</v>
+        <v>963</v>
       </c>
       <c r="D456" s="0">
         <v>0</v>
@@ -9837,21 +9837,21 @@
         <v>977</v>
       </c>
       <c r="C457" s="0" t="s">
-        <v>978</v>
+        <v>963</v>
       </c>
       <c r="D457" s="0">
-        <v>453</v>
+        <v>0</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" s="0" t="s">
+        <v>978</v>
+      </c>
+      <c r="B458" s="0" t="s">
         <v>979</v>
       </c>
-      <c r="B458" s="0" t="s">
+      <c r="C458" s="0" t="s">
         <v>980</v>
-      </c>
-      <c r="C458" s="0" t="s">
-        <v>961</v>
       </c>
       <c r="D458" s="0">
         <v>453</v>
@@ -9865,10 +9865,10 @@
         <v>982</v>
       </c>
       <c r="C459" s="0" t="s">
-        <v>75</v>
+        <v>963</v>
       </c>
       <c r="D459" s="0">
-        <v>19322</v>
+        <v>453</v>
       </c>
     </row>
     <row r="460">
@@ -9879,10 +9879,10 @@
         <v>984</v>
       </c>
       <c r="C460" s="0" t="s">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="D460" s="0">
-        <v>430</v>
+        <v>19322</v>
       </c>
     </row>
     <row r="461">
@@ -9893,7 +9893,7 @@
         <v>986</v>
       </c>
       <c r="C461" s="0" t="s">
-        <v>289</v>
+        <v>34</v>
       </c>
       <c r="D461" s="0">
         <v>430</v>
@@ -9907,10 +9907,10 @@
         <v>988</v>
       </c>
       <c r="C462" s="0" t="s">
-        <v>120</v>
+        <v>291</v>
       </c>
       <c r="D462" s="0">
-        <v>14000</v>
+        <v>430</v>
       </c>
     </row>
     <row r="463">
@@ -9921,10 +9921,10 @@
         <v>990</v>
       </c>
       <c r="C463" s="0" t="s">
-        <v>145</v>
+        <v>120</v>
       </c>
       <c r="D463" s="0">
-        <v>12049</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="464">
@@ -9938,7 +9938,7 @@
         <v>145</v>
       </c>
       <c r="D464" s="0">
-        <v>2895</v>
+        <v>12049</v>
       </c>
     </row>
     <row r="465">
@@ -9952,7 +9952,7 @@
         <v>145</v>
       </c>
       <c r="D465" s="0">
-        <v>2620</v>
+        <v>2895</v>
       </c>
     </row>
     <row r="466">
@@ -9963,10 +9963,10 @@
         <v>996</v>
       </c>
       <c r="C466" s="0" t="s">
-        <v>97</v>
+        <v>145</v>
       </c>
       <c r="D466" s="0">
-        <v>266200</v>
+        <v>2620</v>
       </c>
     </row>
     <row r="467">
@@ -9980,7 +9980,7 @@
         <v>97</v>
       </c>
       <c r="D467" s="0">
-        <v>194991.5</v>
+        <v>266200</v>
       </c>
     </row>
     <row r="468">
@@ -9994,7 +9994,7 @@
         <v>97</v>
       </c>
       <c r="D468" s="0">
-        <v>289492.5</v>
+        <v>194991.5</v>
       </c>
     </row>
     <row r="469">
@@ -10005,24 +10005,24 @@
         <v>1002</v>
       </c>
       <c r="C469" s="0" t="s">
-        <v>1003</v>
+        <v>97</v>
       </c>
       <c r="D469" s="0">
-        <v>13722.52</v>
+        <v>289492.5</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" s="0" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B470" s="0" t="s">
         <v>1004</v>
       </c>
-      <c r="B470" s="0" t="s">
+      <c r="C470" s="0" t="s">
         <v>1005</v>
       </c>
-      <c r="C470" s="0" t="s">
-        <v>1003</v>
-      </c>
       <c r="D470" s="0">
-        <v>15072</v>
+        <v>13722.52</v>
       </c>
     </row>
     <row r="471">
@@ -10033,10 +10033,10 @@
         <v>1007</v>
       </c>
       <c r="C471" s="0" t="s">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="D471" s="0">
-        <v>6555.64</v>
+        <v>15072</v>
       </c>
     </row>
     <row r="472">
@@ -10047,10 +10047,10 @@
         <v>1009</v>
       </c>
       <c r="C472" s="0" t="s">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="D472" s="0">
-        <v>8964.61</v>
+        <v>6555.64</v>
       </c>
     </row>
     <row r="473">
@@ -10061,10 +10061,10 @@
         <v>1011</v>
       </c>
       <c r="C473" s="0" t="s">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="D473" s="0">
-        <v>11735</v>
+        <v>8964.61</v>
       </c>
     </row>
     <row r="474">
@@ -10075,10 +10075,10 @@
         <v>1013</v>
       </c>
       <c r="C474" s="0" t="s">
-        <v>75</v>
+        <v>1005</v>
       </c>
       <c r="D474" s="0">
-        <v>4276</v>
+        <v>11735</v>
       </c>
     </row>
     <row r="475">
@@ -10089,10 +10089,10 @@
         <v>1015</v>
       </c>
       <c r="C475" s="0" t="s">
-        <v>145</v>
+        <v>75</v>
       </c>
       <c r="D475" s="0">
-        <v>3930</v>
+        <v>4276</v>
       </c>
     </row>
     <row r="476">
@@ -10103,10 +10103,10 @@
         <v>1017</v>
       </c>
       <c r="C476" s="0" t="s">
-        <v>97</v>
+        <v>145</v>
       </c>
       <c r="D476" s="0">
-        <v>4392.3</v>
+        <v>3930</v>
       </c>
     </row>
     <row r="477">
@@ -10117,24 +10117,24 @@
         <v>1019</v>
       </c>
       <c r="C477" s="0" t="s">
-        <v>1020</v>
+        <v>97</v>
       </c>
       <c r="D477" s="0">
-        <v>5254.41</v>
+        <v>4392.3</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" s="0" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B478" s="0" t="s">
         <v>1021</v>
       </c>
-      <c r="B478" s="0" t="s">
+      <c r="C478" s="0" t="s">
         <v>1022</v>
       </c>
-      <c r="C478" s="0" t="s">
-        <v>52</v>
-      </c>
       <c r="D478" s="0">
-        <v>1297</v>
+        <v>5254.41</v>
       </c>
     </row>
     <row r="479">
@@ -10148,7 +10148,7 @@
         <v>52</v>
       </c>
       <c r="D479" s="0">
-        <v>298</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="480">
@@ -10162,7 +10162,7 @@
         <v>52</v>
       </c>
       <c r="D480" s="0">
-        <v>596</v>
+        <v>298</v>
       </c>
     </row>
     <row r="481">
@@ -10173,10 +10173,10 @@
         <v>1028</v>
       </c>
       <c r="C481" s="0" t="s">
-        <v>386</v>
+        <v>52</v>
       </c>
       <c r="D481" s="0">
-        <v>69890</v>
+        <v>596</v>
       </c>
     </row>
     <row r="482">
@@ -10187,10 +10187,10 @@
         <v>1030</v>
       </c>
       <c r="C482" s="0" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="D482" s="0">
-        <v>25194.62</v>
+        <v>69890</v>
       </c>
     </row>
     <row r="483">
@@ -10201,10 +10201,10 @@
         <v>1032</v>
       </c>
       <c r="C483" s="0" t="s">
-        <v>28</v>
+        <v>388</v>
       </c>
       <c r="D483" s="0">
-        <v>6029.59</v>
+        <v>25194.62</v>
       </c>
     </row>
     <row r="484">
@@ -10215,10 +10215,10 @@
         <v>1034</v>
       </c>
       <c r="C484" s="0" t="s">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="D484" s="0">
-        <v>12000</v>
+        <v>6029.59</v>
       </c>
     </row>
     <row r="485">
@@ -10232,7 +10232,7 @@
         <v>52</v>
       </c>
       <c r="D485" s="0">
-        <v>17425</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="486">
@@ -10243,66 +10243,66 @@
         <v>1038</v>
       </c>
       <c r="C486" s="0" t="s">
-        <v>1039</v>
+        <v>52</v>
       </c>
       <c r="D486" s="0">
-        <v>1958</v>
+        <v>17425</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" s="0" t="s">
+        <v>1039</v>
+      </c>
+      <c r="B487" s="0" t="s">
         <v>1040</v>
       </c>
-      <c r="B487" s="0" t="s">
+      <c r="C487" s="0" t="s">
         <v>1041</v>
       </c>
-      <c r="C487" s="0" t="s">
-        <v>1042</v>
-      </c>
       <c r="D487" s="0">
-        <v>2282.3</v>
+        <v>1958</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" s="0" t="s">
+        <v>1042</v>
+      </c>
+      <c r="B488" s="0" t="s">
         <v>1043</v>
       </c>
-      <c r="B488" s="0" t="s">
+      <c r="C488" s="0" t="s">
         <v>1044</v>
       </c>
-      <c r="C488" s="0" t="s">
-        <v>1045</v>
-      </c>
       <c r="D488" s="0">
-        <v>386</v>
+        <v>2282.3</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" s="0" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B489" s="0" t="s">
         <v>1046</v>
       </c>
-      <c r="B489" s="0" t="s">
+      <c r="C489" s="0" t="s">
         <v>1047</v>
       </c>
-      <c r="C489" s="0" t="s">
-        <v>1048</v>
-      </c>
       <c r="D489" s="0">
-        <v>385.4</v>
+        <v>386</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" s="0" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B490" s="0" t="s">
         <v>1049</v>
       </c>
-      <c r="B490" s="0" t="s">
+      <c r="C490" s="0" t="s">
         <v>1050</v>
       </c>
-      <c r="C490" s="0" t="s">
-        <v>97</v>
-      </c>
       <c r="D490" s="0">
-        <v>296147.5</v>
+        <v>385.4</v>
       </c>
     </row>
     <row r="491">
@@ -10313,10 +10313,10 @@
         <v>1052</v>
       </c>
       <c r="C491" s="0" t="s">
-        <v>128</v>
+        <v>97</v>
       </c>
       <c r="D491" s="0">
-        <v>1890</v>
+        <v>296147.5</v>
       </c>
     </row>
     <row r="492">
@@ -10327,10 +10327,10 @@
         <v>1054</v>
       </c>
       <c r="C492" s="0" t="s">
-        <v>610</v>
+        <v>128</v>
       </c>
       <c r="D492" s="0">
-        <v>83000</v>
+        <v>1890</v>
       </c>
     </row>
     <row r="493">
@@ -10341,10 +10341,10 @@
         <v>1056</v>
       </c>
       <c r="C493" s="0" t="s">
-        <v>145</v>
+        <v>612</v>
       </c>
       <c r="D493" s="0">
-        <v>99</v>
+        <v>83000</v>
       </c>
     </row>
     <row r="494">
@@ -10355,10 +10355,10 @@
         <v>1058</v>
       </c>
       <c r="C494" s="0" t="s">
-        <v>75</v>
+        <v>145</v>
       </c>
       <c r="D494" s="0">
-        <v>950</v>
+        <v>99</v>
       </c>
     </row>
     <row r="495">
@@ -10369,10 +10369,10 @@
         <v>1060</v>
       </c>
       <c r="C495" s="0" t="s">
-        <v>485</v>
+        <v>75</v>
       </c>
       <c r="D495" s="0">
-        <v>398107</v>
+        <v>950</v>
       </c>
     </row>
     <row r="496">
@@ -10383,10 +10383,10 @@
         <v>1062</v>
       </c>
       <c r="C496" s="0" t="s">
-        <v>165</v>
+        <v>487</v>
       </c>
       <c r="D496" s="0">
-        <v>2200</v>
+        <v>398107</v>
       </c>
     </row>
     <row r="497">
@@ -10397,10 +10397,10 @@
         <v>1064</v>
       </c>
       <c r="C497" s="0" t="s">
-        <v>212</v>
+        <v>165</v>
       </c>
       <c r="D497" s="0">
-        <v>41000</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="498">
@@ -10411,10 +10411,10 @@
         <v>1066</v>
       </c>
       <c r="C498" s="0" t="s">
-        <v>75</v>
+        <v>212</v>
       </c>
       <c r="D498" s="0">
-        <v>5790</v>
+        <v>41000</v>
       </c>
     </row>
     <row r="499">
@@ -10425,10 +10425,10 @@
         <v>1068</v>
       </c>
       <c r="C499" s="0" t="s">
-        <v>961</v>
+        <v>75</v>
       </c>
       <c r="D499" s="0">
-        <v>880</v>
+        <v>5790</v>
       </c>
     </row>
     <row r="500">
@@ -10439,7 +10439,7 @@
         <v>1070</v>
       </c>
       <c r="C500" s="0" t="s">
-        <v>961</v>
+        <v>963</v>
       </c>
       <c r="D500" s="0">
         <v>880</v>
@@ -10453,7 +10453,7 @@
         <v>1072</v>
       </c>
       <c r="C501" s="0" t="s">
-        <v>961</v>
+        <v>963</v>
       </c>
       <c r="D501" s="0">
         <v>880</v>
@@ -10467,10 +10467,10 @@
         <v>1074</v>
       </c>
       <c r="C502" s="0" t="s">
-        <v>21</v>
+        <v>963</v>
       </c>
       <c r="D502" s="0">
-        <v>563.36</v>
+        <v>880</v>
       </c>
     </row>
     <row r="503">
@@ -10481,10 +10481,10 @@
         <v>1076</v>
       </c>
       <c r="C503" s="0" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D503" s="0">
-        <v>3520</v>
+        <v>563.36</v>
       </c>
     </row>
     <row r="504">
@@ -10498,7 +10498,7 @@
         <v>15</v>
       </c>
       <c r="D504" s="0">
-        <v>2600</v>
+        <v>3520</v>
       </c>
     </row>
     <row r="505">
@@ -10509,10 +10509,10 @@
         <v>1080</v>
       </c>
       <c r="C505" s="0" t="s">
-        <v>289</v>
+        <v>15</v>
       </c>
       <c r="D505" s="0">
-        <v>3700</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="506">
@@ -10523,10 +10523,10 @@
         <v>1082</v>
       </c>
       <c r="C506" s="0" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="D506" s="0">
-        <v>2600</v>
+        <v>3700</v>
       </c>
     </row>
     <row r="507">
@@ -10537,10 +10537,10 @@
         <v>1084</v>
       </c>
       <c r="C507" s="0" t="s">
-        <v>15</v>
+        <v>291</v>
       </c>
       <c r="D507" s="0">
-        <v>2235</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="508">
@@ -10554,7 +10554,7 @@
         <v>15</v>
       </c>
       <c r="D508" s="0">
-        <v>3850</v>
+        <v>2235</v>
       </c>
     </row>
     <row r="509">
@@ -10593,7 +10593,7 @@
         <v>1093</v>
       </c>
       <c r="C511" s="0" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="D511" s="0">
         <v>3859.93</v>
@@ -10607,7 +10607,7 @@
         <v>1095</v>
       </c>
       <c r="C512" s="0" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="D512" s="0">
         <v>11751.49</v>
@@ -10621,7 +10621,7 @@
         <v>1097</v>
       </c>
       <c r="C513" s="0" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="D513" s="0">
         <v>6000</v>
@@ -10635,7 +10635,7 @@
         <v>1099</v>
       </c>
       <c r="C514" s="0" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="D514" s="0">
         <v>3000</v>
@@ -10705,7 +10705,7 @@
         <v>1110</v>
       </c>
       <c r="C519" s="0" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="D519" s="0">
         <v>213700</v>
@@ -10719,7 +10719,7 @@
         <v>1112</v>
       </c>
       <c r="C520" s="0" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="D520" s="0">
         <v>80241.15</v>
@@ -10733,7 +10733,7 @@
         <v>1114</v>
       </c>
       <c r="C521" s="0" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="D521" s="0">
         <v>44471.13</v>
@@ -10747,7 +10747,7 @@
         <v>1116</v>
       </c>
       <c r="C522" s="0" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="D522" s="0">
         <v>92031.39</v>
@@ -10761,7 +10761,7 @@
         <v>1118</v>
       </c>
       <c r="C523" s="0" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="D523" s="0">
         <v>52574</v>
